--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324DB59E-5F54-42E9-8DA5-CB6EDE1DA7B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94066445-166C-4FAA-B08C-5FEBEA2C6D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="1" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="2" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1680" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1706" uniqueCount="46">
   <si>
     <t>Booking</t>
   </si>
@@ -141,34 +141,10 @@
     <t>A6</t>
   </si>
   <si>
-    <t xml:space="preserve">Sunday </t>
-  </si>
-  <si>
     <t>Negotiate</t>
   </si>
   <si>
-    <t>Sohail SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jabran </t>
-  </si>
-  <si>
-    <t>Shahid SB</t>
-  </si>
-  <si>
-    <t>Jabran</t>
-  </si>
-  <si>
-    <t>Jabran Iqbal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jabran Iqbal </t>
-  </si>
-  <si>
     <t>Furqan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hasan </t>
   </si>
   <si>
     <t xml:space="preserve">Jabbar </t>
@@ -214,6 +190,9 @@
   </si>
   <si>
     <t>Aqib</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aqib </t>
   </si>
 </sst>
 </file>
@@ -577,7 +556,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -754,6 +733,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1135,7 +1117,10 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="M1" s="1"/>
+      <c r="L1" s="80">
+        <v>46032</v>
+      </c>
+      <c r="M1" s="81"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -1158,7 +1143,8 @@
       <c r="H2" s="77"/>
       <c r="I2" s="77"/>
       <c r="J2" s="77"/>
-      <c r="M2" s="1"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
       <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
@@ -1589,7 +1575,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -1620,7 +1606,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11">
@@ -1664,7 +1650,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11">
@@ -1695,7 +1681,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11">
@@ -1773,18 +1759,30 @@
         <v>16</v>
       </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="P13" s="11">
+        <v>465</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>395</v>
+      </c>
+      <c r="R13" s="11">
+        <v>460</v>
+      </c>
+      <c r="S13" s="11">
+        <v>295</v>
+      </c>
+      <c r="T13" s="11">
+        <v>195</v>
+      </c>
+      <c r="U13" s="11">
+        <v>220</v>
+      </c>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>50.75</v>
       </c>
       <c r="W13" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
@@ -1793,7 +1791,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -1809,7 +1807,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -1830,7 +1828,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -1846,7 +1844,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -1867,7 +1865,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -1884,7 +1882,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -1982,31 +1980,31 @@
       </c>
       <c r="P18" s="24">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>493</v>
       </c>
       <c r="Q18" s="24">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>420</v>
       </c>
       <c r="R18" s="24">
         <f t="shared" si="6"/>
-        <v>106</v>
+        <v>566</v>
       </c>
       <c r="S18" s="24">
         <f t="shared" si="6"/>
-        <v>248</v>
+        <v>543</v>
       </c>
       <c r="T18" s="24">
         <f t="shared" si="6"/>
-        <v>216</v>
+        <v>411</v>
       </c>
       <c r="U18" s="24">
         <f t="shared" si="6"/>
-        <v>386</v>
+        <v>606</v>
       </c>
       <c r="V18" s="19">
         <f>SUM(O18:U18)</f>
-        <v>1009</v>
+        <v>3039</v>
       </c>
       <c r="W18" s="27"/>
       <c r="Y18" s="31">
@@ -2070,31 +2068,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0.7</v>
+        <v>12.324999999999999</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0.625</v>
+        <v>10.5</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>2.65</v>
+        <v>14.15</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>6.2</v>
+        <v>13.574999999999999</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>5.4</v>
+        <v>10.275</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>9.65</v>
+        <v>15.15</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>25.225000000000001</v>
+        <v>75.974999999999994</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -2111,7 +2109,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="Y3:AA4"/>
     <mergeCell ref="B2:J5"/>
     <mergeCell ref="N2:V5"/>
@@ -2119,6 +2117,7 @@
     <mergeCell ref="G6:I6"/>
     <mergeCell ref="P6:R6"/>
     <mergeCell ref="S6:U6"/>
+    <mergeCell ref="L1:M2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2218,11 +2217,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -2245,9 +2244,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -2574,7 +2573,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11">
         <v>119</v>
@@ -2607,7 +2606,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -2639,7 +2638,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11">
         <v>60</v>
@@ -2672,7 +2671,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -2704,7 +2703,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="11">
         <v>200</v>
@@ -2737,7 +2736,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -2760,7 +2759,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -2778,7 +2777,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -2799,7 +2798,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -2817,7 +2816,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -2838,7 +2837,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -2856,7 +2855,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -2876,7 +2875,9 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
-      <c r="B17" s="17"/>
+      <c r="B17" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
@@ -2884,11 +2885,13 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
-      <c r="J17" s="15"/>
+      <c r="J17" s="15">
+        <v>6</v>
+      </c>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -2901,7 +2904,7 @@
       <c r="W17" s="18"/>
       <c r="Y17" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z17" s="37">
         <f t="shared" si="3"/>
@@ -2909,7 +2912,7 @@
       </c>
       <c r="AA17" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
@@ -2985,7 +2988,7 @@
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>53.424999999999997</v>
+        <v>59.424999999999997</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
@@ -2993,7 +2996,7 @@
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>53.174999999999997</v>
+        <v>59.174999999999997</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3073,7 +3076,7 @@
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>1.3356249999999998</v>
+        <v>1.485625</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
@@ -3081,7 +3084,7 @@
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>1.329375</v>
+        <v>1.4793749999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3193,11 +3196,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -3220,9 +3223,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -3495,15 +3498,15 @@
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="83" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="84"/>
-      <c r="E10" s="84"/>
-      <c r="F10" s="84"/>
-      <c r="G10" s="84"/>
-      <c r="H10" s="84"/>
-      <c r="I10" s="85"/>
+      <c r="C10" s="84" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="85"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="85"/>
+      <c r="H10" s="85"/>
+      <c r="I10" s="86"/>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3542,7 +3545,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11">
         <v>120</v>
@@ -3575,7 +3578,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -3607,7 +3610,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11">
         <v>124</v>
@@ -3640,7 +3643,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -3672,7 +3675,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -3690,7 +3693,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -3713,7 +3716,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -3731,7 +3734,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -3752,7 +3755,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -3770,7 +3773,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -3791,7 +3794,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -3809,7 +3812,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -3829,7 +3832,9 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
-      <c r="B17" s="17"/>
+      <c r="B17" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
@@ -3837,11 +3842,13 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
-      <c r="J17" s="15"/>
+      <c r="J17" s="15">
+        <v>6</v>
+      </c>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -3857,7 +3864,7 @@
       <c r="W17" s="12"/>
       <c r="Y17" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z17" s="37">
         <f t="shared" si="3"/>
@@ -3865,7 +3872,7 @@
       </c>
       <c r="AA17" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
@@ -3941,7 +3948,7 @@
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>30.95</v>
+        <v>36.950000000000003</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
@@ -3949,7 +3956,7 @@
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>30.95</v>
+        <v>36.950000000000003</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4029,7 +4036,7 @@
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0.77374999999999994</v>
+        <v>0.92375000000000007</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
@@ -4037,7 +4044,7 @@
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.77374999999999994</v>
+        <v>0.92375000000000007</v>
       </c>
     </row>
   </sheetData>
@@ -4149,11 +4156,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -4176,9 +4183,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -4518,7 +4525,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11">
         <v>106</v>
@@ -4551,7 +4558,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -4583,7 +4590,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11">
         <v>24</v>
@@ -4616,7 +4623,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -4648,7 +4655,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="11">
         <v>200</v>
@@ -4681,7 +4688,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -4704,7 +4711,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -4721,7 +4728,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -4742,7 +4749,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -4759,7 +4766,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -4780,7 +4787,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -4797,7 +4804,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -4818,7 +4825,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -4834,7 +4841,7 @@
       <c r="K17" s="12"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -5086,7 +5093,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="L1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
@@ -5145,11 +5152,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -5172,9 +5179,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -5458,7 +5465,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="43"/>
       <c r="D11" s="43"/>
@@ -5475,7 +5482,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="43"/>
       <c r="P11" s="43"/>
@@ -5505,7 +5512,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="43"/>
       <c r="D12" s="43"/>
@@ -5522,7 +5529,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="43"/>
       <c r="P12" s="43"/>
@@ -5552,7 +5559,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="43"/>
       <c r="D13" s="43"/>
@@ -5569,7 +5576,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="43"/>
       <c r="P13" s="43"/>
@@ -5590,7 +5597,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="43"/>
       <c r="D14" s="43"/>
@@ -5607,7 +5614,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="43"/>
       <c r="P14" s="43"/>
@@ -5628,7 +5635,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="43"/>
       <c r="D15" s="43"/>
@@ -5645,7 +5652,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="43"/>
       <c r="P15" s="43"/>
@@ -5666,7 +5673,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="43"/>
       <c r="D16" s="43"/>
@@ -5683,7 +5690,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -5704,7 +5711,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C17" s="43"/>
       <c r="D17" s="43"/>
@@ -5720,7 +5727,7 @@
       <c r="K17" s="12"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -5974,7 +5981,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="M1" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -6032,11 +6039,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -6059,9 +6066,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -6281,7 +6288,7 @@
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
+        <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
         <v>0</v>
       </c>
       <c r="K9" s="12"/>
@@ -6381,7 +6388,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11">
         <v>32</v>
@@ -6414,7 +6421,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -6446,7 +6453,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11">
         <v>166</v>
@@ -6479,7 +6486,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -6511,7 +6518,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11">
@@ -6542,7 +6549,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -6563,7 +6570,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -6580,7 +6587,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -6601,7 +6608,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -6618,7 +6625,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -6639,7 +6646,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -6656,7 +6663,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -6676,7 +6683,9 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
-      <c r="B17" s="17"/>
+      <c r="B17" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
@@ -6684,10 +6693,15 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
-      <c r="J17" s="15"/>
+      <c r="J17" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+      <c r="N17" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
@@ -6991,11 +7005,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -7018,9 +7032,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -7254,7 +7268,7 @@
         <v>61</v>
       </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
+        <f t="shared" ref="J9:J13" si="0">SUM(C9:I9)/40</f>
         <v>10.025</v>
       </c>
       <c r="K9" s="12">
@@ -7361,7 +7375,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11">
         <v>136</v>
@@ -7394,7 +7408,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -7426,7 +7440,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11">
         <v>142</v>
@@ -7459,7 +7473,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -7491,7 +7505,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -7508,7 +7522,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -7531,7 +7545,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -7549,7 +7563,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -7570,7 +7584,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -7588,7 +7602,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -7609,7 +7623,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -7627,7 +7641,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -7648,7 +7662,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -7658,13 +7672,12 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
       <c r="J17" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -7677,7 +7690,7 @@
       <c r="W17" s="18"/>
       <c r="Y17" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z17" s="37">
         <f t="shared" si="3"/>
@@ -7685,7 +7698,7 @@
       </c>
       <c r="AA17" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
@@ -7761,7 +7774,7 @@
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>60.25</v>
+        <v>68.25</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
@@ -7769,7 +7782,7 @@
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>58.174999999999997</v>
+        <v>66.174999999999997</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7849,7 +7862,7 @@
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>1.5062500000000001</v>
+        <v>1.70625</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
@@ -7857,7 +7870,7 @@
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>1.454375</v>
+        <v>1.6543749999999999</v>
       </c>
     </row>
   </sheetData>
@@ -7969,11 +7982,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -7996,9 +8009,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -8297,7 +8310,7 @@
         <v>13</v>
       </c>
       <c r="J10" s="15">
-        <f t="shared" ref="J10:J16" si="4">SUM(C10:I10)/40</f>
+        <f t="shared" ref="J10:J17" si="4">SUM(C10:I10)/40</f>
         <v>7.7750000000000004</v>
       </c>
       <c r="K10" s="12">
@@ -8338,7 +8351,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11">
         <v>44</v>
@@ -8371,7 +8384,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -8403,7 +8416,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11">
         <v>150</v>
@@ -8436,7 +8449,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -8468,7 +8481,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -8486,7 +8499,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -8509,7 +8522,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -8527,7 +8540,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -8548,7 +8561,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -8565,7 +8578,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -8586,7 +8599,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -8603,7 +8616,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -8623,7 +8636,9 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
-      <c r="B17" s="17"/>
+      <c r="B17" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
@@ -8631,10 +8646,15 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
-      <c r="J17" s="15"/>
+      <c r="J17" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+      <c r="N17" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
@@ -8937,11 +8957,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -8964,9 +8984,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -9300,7 +9320,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11">
         <v>284</v>
@@ -9333,7 +9353,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -9365,7 +9385,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11">
         <v>205</v>
@@ -9398,7 +9418,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -9430,7 +9450,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -9447,7 +9467,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -9470,7 +9490,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -9487,7 +9507,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -9508,7 +9528,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -9525,7 +9545,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -9546,7 +9566,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -9563,7 +9583,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -9584,7 +9604,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -9600,7 +9620,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -9910,11 +9930,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -9937,9 +9957,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -10167,7 +10187,7 @@
         <v>32</v>
       </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
+        <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
         <v>5.7</v>
       </c>
       <c r="K9" s="12">
@@ -10271,7 +10291,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -10302,7 +10322,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -10332,7 +10352,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11">
@@ -10363,7 +10383,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -10395,7 +10415,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -10412,7 +10432,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -10435,7 +10455,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -10452,7 +10472,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -10473,7 +10493,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -10490,7 +10510,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -10511,7 +10531,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -10528,7 +10548,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -10548,7 +10568,9 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
-      <c r="B17" s="17"/>
+      <c r="B17" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
@@ -10556,10 +10578,15 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
-      <c r="J17" s="15"/>
+      <c r="J17" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+      <c r="N17" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
@@ -10863,11 +10890,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -10890,9 +10917,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -11120,7 +11147,7 @@
         <v>99</v>
       </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
+        <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
         <v>6.6</v>
       </c>
       <c r="K9" s="12">
@@ -11224,7 +11251,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -11255,7 +11282,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -11287,7 +11314,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -11304,7 +11331,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -11334,7 +11361,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -11351,7 +11378,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -11374,7 +11401,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -11391,7 +11418,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -11412,7 +11439,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -11429,7 +11456,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -11450,7 +11477,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -11467,7 +11494,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -11487,7 +11514,9 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
-      <c r="B17" s="17"/>
+      <c r="B17" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
@@ -11495,10 +11524,15 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
-      <c r="J17" s="15"/>
+      <c r="J17" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+      <c r="N17" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
@@ -11753,10 +11787,10 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="L1" s="80" t="s">
-        <v>28</v>
-      </c>
-      <c r="M1" s="80"/>
+      <c r="L1" s="80">
+        <v>46063</v>
+      </c>
+      <c r="M1" s="81"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -11779,7 +11813,8 @@
       <c r="H2" s="77"/>
       <c r="I2" s="77"/>
       <c r="J2" s="77"/>
-      <c r="M2" s="1"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
       <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
@@ -11813,11 +11848,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -11840,9 +11875,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -12019,28 +12054,42 @@
         <v>13</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>30</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>30</v>
+      </c>
+      <c r="R8" s="11">
+        <v>60</v>
+      </c>
+      <c r="S8" s="11">
+        <v>80</v>
+      </c>
+      <c r="T8" s="11">
+        <v>80</v>
+      </c>
+      <c r="U8" s="11">
+        <v>80</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>9</v>
+      </c>
+      <c r="W8" s="12">
+        <v>5</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>9.375</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>9.375</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -12080,28 +12129,42 @@
         <v>14</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>53</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>90</v>
+      </c>
+      <c r="R9" s="11">
+        <v>95</v>
+      </c>
+      <c r="S9" s="11">
+        <v>55</v>
+      </c>
+      <c r="T9" s="11">
+        <v>48</v>
+      </c>
+      <c r="U9" s="11">
+        <v>55</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>9.9</v>
+      </c>
+      <c r="W9" s="12">
+        <v>4</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
         <v>11</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>11</v>
+        <v>1.0999999999999996</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -12141,34 +12204,48 @@
         <v>15</v>
       </c>
       <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="P10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <v>140</v>
+      </c>
+      <c r="T10" s="11">
+        <v>80</v>
+      </c>
+      <c r="U10" s="11">
+        <v>40</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>6.5</v>
+      </c>
+      <c r="W10" s="12">
+        <v>5</v>
+      </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
         <v>6.5</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>6.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -12199,37 +12276,51 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>55</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>10</v>
+      </c>
+      <c r="R11" s="11">
+        <v>55</v>
+      </c>
+      <c r="S11" s="11">
+        <v>50</v>
+      </c>
+      <c r="T11" s="11">
+        <v>20</v>
+      </c>
+      <c r="U11" s="11">
+        <v>62</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>6.3</v>
+      </c>
+      <c r="W11" s="12">
+        <v>4</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>6.3</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>6.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11">
@@ -12260,31 +12351,45 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>32</v>
+      </c>
+      <c r="R12" s="11">
+        <v>35</v>
+      </c>
+      <c r="S12" s="11">
+        <v>47</v>
+      </c>
+      <c r="T12" s="11">
+        <v>35</v>
+      </c>
+      <c r="U12" s="11">
+        <v>70</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>5.4749999999999996</v>
+      </c>
+      <c r="W12" s="12">
+        <v>5</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
         <v>5.7750000000000004</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5.4749999999999996</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>5.7750000000000004</v>
+        <v>0.30000000000000071</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -12342,7 +12447,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -12359,7 +12464,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -12380,7 +12485,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -12397,7 +12502,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -12418,7 +12523,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -12435,7 +12540,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -12533,31 +12638,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>372</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>307</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>1487</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -12566,11 +12671,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>37.174999999999997</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>38.949999999999996</v>
+        <v>1.7750000000000004</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -12579,7 +12684,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="21">
-        <f t="shared" ref="C19:J19" si="7">C18/40</f>
+        <f t="shared" ref="C19:I19" si="7">C18/40</f>
         <v>0</v>
       </c>
       <c r="D19" s="21">
@@ -12621,31 +12726,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6.125</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6.5750000000000002</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7.6749999999999998</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>37.174999999999997</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -12654,16 +12759,15 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>0.92937499999999995</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.97374999999999989</v>
+        <v>4.4375000000000012E-2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="L1:M1"/>
     <mergeCell ref="Y3:AA4"/>
     <mergeCell ref="B2:J5"/>
     <mergeCell ref="N2:V5"/>
@@ -12671,6 +12775,7 @@
     <mergeCell ref="G6:I6"/>
     <mergeCell ref="P6:R6"/>
     <mergeCell ref="S6:U6"/>
+    <mergeCell ref="L1:M2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12771,11 +12876,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -12798,9 +12903,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -13084,7 +13189,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="43"/>
       <c r="D11" s="43"/>
@@ -13101,7 +13206,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="43"/>
       <c r="P11" s="43"/>
@@ -13131,7 +13236,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="43"/>
       <c r="D12" s="43"/>
@@ -13148,7 +13253,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="43"/>
       <c r="P12" s="43"/>
@@ -13178,7 +13283,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="43"/>
       <c r="D13" s="43"/>
@@ -13195,7 +13300,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="43"/>
       <c r="P13" s="43"/>
@@ -13216,7 +13321,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="43"/>
       <c r="D14" s="43"/>
@@ -13233,7 +13338,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="43"/>
       <c r="P14" s="43"/>
@@ -13254,7 +13359,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="43"/>
       <c r="D15" s="43"/>
@@ -13271,7 +13376,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="43"/>
       <c r="P15" s="43"/>
@@ -13292,7 +13397,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="43"/>
       <c r="D16" s="43"/>
@@ -13309,7 +13414,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="43"/>
       <c r="P16" s="43"/>
@@ -13330,7 +13435,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C17" s="43"/>
       <c r="D17" s="43"/>
@@ -13346,7 +13451,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O17" s="43"/>
       <c r="P17" s="43"/>
@@ -13757,11 +13862,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -13784,9 +13889,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -14012,7 +14117,7 @@
         <v>60</v>
       </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
+        <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
         <v>6</v>
       </c>
       <c r="K9" s="12">
@@ -14116,7 +14221,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -14147,7 +14252,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -14179,23 +14284,23 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="86" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" s="87"/>
-      <c r="F12" s="87"/>
-      <c r="G12" s="87"/>
-      <c r="H12" s="87"/>
-      <c r="I12" s="87"/>
-      <c r="J12" s="88"/>
+      <c r="D12" s="87" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="88"/>
+      <c r="F12" s="88"/>
+      <c r="G12" s="88"/>
+      <c r="H12" s="88"/>
+      <c r="I12" s="88"/>
+      <c r="J12" s="89"/>
       <c r="K12" s="12"/>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -14225,7 +14330,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -14242,7 +14347,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -14263,7 +14368,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -14280,7 +14385,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -14301,7 +14406,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -14318,7 +14423,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -14339,7 +14444,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -14356,7 +14461,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -14377,7 +14482,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -14386,11 +14491,14 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
-      <c r="J17" s="15"/>
+      <c r="J17" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -14694,11 +14802,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -14721,9 +14829,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -14951,7 +15059,7 @@
         <v>120</v>
       </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
+        <f t="shared" ref="J9:J11" si="0">SUM(C9:I9)/40</f>
         <v>9.1</v>
       </c>
       <c r="K9" s="12">
@@ -15055,7 +15163,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -15086,7 +15194,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -15118,23 +15226,23 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="86" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="87"/>
-      <c r="E12" s="87"/>
-      <c r="F12" s="87"/>
-      <c r="G12" s="87"/>
-      <c r="H12" s="87"/>
-      <c r="I12" s="87"/>
-      <c r="J12" s="88"/>
+        <v>29</v>
+      </c>
+      <c r="C12" s="87" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="88"/>
+      <c r="E12" s="88"/>
+      <c r="F12" s="88"/>
+      <c r="G12" s="88"/>
+      <c r="H12" s="88"/>
+      <c r="I12" s="88"/>
+      <c r="J12" s="89"/>
       <c r="K12" s="12"/>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -15164,7 +15272,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -15182,7 +15290,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -15205,7 +15313,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -15223,7 +15331,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -15245,7 +15353,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -15263,7 +15371,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -15285,7 +15393,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -15303,7 +15411,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -15325,7 +15433,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -15335,13 +15443,12 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
       <c r="J17" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -15354,7 +15461,7 @@
       <c r="W17" s="18"/>
       <c r="Y17" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z17" s="37">
         <f t="shared" si="3"/>
@@ -15362,7 +15469,7 @@
       </c>
       <c r="AA17" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
@@ -15438,7 +15545,7 @@
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>49.5</v>
+        <v>56.5</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
@@ -15526,7 +15633,7 @@
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>1.2375</v>
+        <v>1.4125000000000001</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
@@ -15647,11 +15754,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -15674,9 +15781,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -15884,16 +15991,16 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="86" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="87"/>
-      <c r="E9" s="87"/>
-      <c r="F9" s="87"/>
-      <c r="G9" s="87"/>
-      <c r="H9" s="87"/>
-      <c r="I9" s="87"/>
-      <c r="J9" s="88"/>
+      <c r="C9" s="87" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="88"/>
+      <c r="E9" s="88"/>
+      <c r="F9" s="88"/>
+      <c r="G9" s="88"/>
+      <c r="H9" s="88"/>
+      <c r="I9" s="88"/>
+      <c r="J9" s="89"/>
       <c r="K9" s="12"/>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
@@ -15950,7 +16057,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="15">
-        <f t="shared" ref="J10:J16" si="3">SUM(C10:I10)/40</f>
+        <f t="shared" ref="J10:J17" si="3">SUM(C10:I10)/40</f>
         <v>2.4500000000000002</v>
       </c>
       <c r="K10" s="12">
@@ -15991,7 +16098,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -16022,7 +16129,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -16054,7 +16161,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11">
@@ -16085,7 +16192,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -16117,7 +16224,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11">
@@ -16148,7 +16255,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -16171,7 +16278,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -16188,7 +16295,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -16209,7 +16316,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -16226,7 +16333,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -16247,7 +16354,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -16264,7 +16371,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -16284,7 +16391,9 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
-      <c r="B17" s="17"/>
+      <c r="B17" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
@@ -16292,10 +16401,15 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
-      <c r="J17" s="15"/>
+      <c r="J17" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+      <c r="N17" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
@@ -16599,11 +16713,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -16626,9 +16740,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -16771,7 +16885,7 @@
     <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="14"/>
       <c r="B8" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C8" s="11">
         <v>17</v>
@@ -16804,7 +16918,7 @@
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="O8" s="11">
         <v>17</v>
@@ -16838,7 +16952,7 @@
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11">
@@ -16869,7 +16983,7 @@
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="O9" s="11"/>
       <c r="P9" s="11"/>
@@ -16901,7 +17015,7 @@
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="7" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11">
@@ -16932,7 +17046,7 @@
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
@@ -16964,7 +17078,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -16995,7 +17109,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -17027,7 +17141,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11">
@@ -17058,7 +17172,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -17090,7 +17204,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -17115,7 +17229,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -17138,7 +17252,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -17155,7 +17269,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -17176,7 +17290,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -17193,7 +17307,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -17214,7 +17328,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -17232,7 +17346,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -17253,7 +17367,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -17262,11 +17376,13 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
-      <c r="J17" s="15"/>
+      <c r="J17" s="15">
+        <v>8</v>
+      </c>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -17284,7 +17400,7 @@
       </c>
       <c r="Y17" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z17" s="37">
         <f t="shared" si="3"/>
@@ -17292,7 +17408,7 @@
       </c>
       <c r="AA17" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
@@ -17368,7 +17484,7 @@
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>38.824999999999996</v>
+        <v>46.824999999999996</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
@@ -17376,7 +17492,7 @@
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>38.4</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -17456,7 +17572,7 @@
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0.97062499999999985</v>
+        <v>1.1706249999999998</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
@@ -17464,7 +17580,7 @@
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.96</v>
+        <v>1.1599999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -17576,11 +17692,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -17603,9 +17719,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -17811,7 +17927,7 @@
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="43"/>
@@ -17821,14 +17937,14 @@
       <c r="H9" s="43"/>
       <c r="I9" s="43"/>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
+        <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
         <v>0</v>
       </c>
       <c r="K9" s="12"/>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="O9" s="11"/>
       <c r="P9" s="43"/>
@@ -17858,7 +17974,7 @@
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="7" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
@@ -17887,7 +18003,7 @@
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
@@ -17919,7 +18035,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -17950,7 +18066,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -17982,7 +18098,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11">
@@ -18013,7 +18129,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -18045,7 +18161,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -18062,7 +18178,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -18085,7 +18201,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -18102,7 +18218,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -18123,7 +18239,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -18140,7 +18256,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -18161,7 +18277,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -18178,7 +18294,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -18199,7 +18315,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -18208,11 +18324,14 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
-      <c r="J17" s="15"/>
+      <c r="J17" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -18520,11 +18639,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -18547,9 +18666,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -18765,7 +18884,7 @@
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
+        <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
         <v>0</v>
       </c>
       <c r="K9" s="12"/>
@@ -18865,7 +18984,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -18896,7 +19015,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -18928,7 +19047,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11">
@@ -18959,7 +19078,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -18991,7 +19110,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -19008,7 +19127,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -19031,7 +19150,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -19048,7 +19167,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -19069,7 +19188,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -19086,7 +19205,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -19107,7 +19226,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -19124,7 +19243,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -19144,7 +19263,9 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
-      <c r="B17" s="17"/>
+      <c r="B17" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
@@ -19152,10 +19273,15 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
-      <c r="J17" s="15"/>
+      <c r="J17" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+      <c r="N17" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
@@ -19457,11 +19583,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -19484,9 +19610,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -19629,7 +19755,7 @@
     <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="14"/>
       <c r="B8" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
@@ -19646,7 +19772,7 @@
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="O8" s="11"/>
       <c r="P8" s="11"/>
@@ -19676,7 +19802,7 @@
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
@@ -19686,14 +19812,14 @@
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
+        <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
         <v>0</v>
       </c>
       <c r="K9" s="12"/>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="O9" s="11"/>
       <c r="P9" s="11"/>
@@ -19723,7 +19849,7 @@
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="7" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
@@ -19740,7 +19866,7 @@
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
@@ -19770,7 +19896,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -19787,7 +19913,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -19817,7 +19943,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -19834,7 +19960,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -19864,7 +19990,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -19881,7 +20007,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -19902,7 +20028,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -19919,7 +20045,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -19940,7 +20066,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -19957,7 +20083,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -19978,7 +20104,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -19995,7 +20121,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -20015,7 +20141,9 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
-      <c r="B17" s="17"/>
+      <c r="B17" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
@@ -20023,12 +20151,15 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
-      <c r="J17" s="15"/>
+      <c r="J17" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="K17" s="12"/>
       <c r="L17" s="13"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -20116,7 +20247,7 @@
       <c r="K20" s="18"/>
       <c r="M20" s="16"/>
       <c r="N20" s="17" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="O20" s="11"/>
       <c r="P20" s="11"/>
@@ -20421,11 +20552,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -20448,9 +20579,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -20593,7 +20724,7 @@
     <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="14"/>
       <c r="B8" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
@@ -20616,7 +20747,7 @@
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="O8" s="11"/>
       <c r="P8" s="11"/>
@@ -20648,7 +20779,7 @@
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11">
@@ -20677,7 +20808,7 @@
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="O9" s="11"/>
       <c r="P9" s="11"/>
@@ -20709,7 +20840,7 @@
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="7" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11">
@@ -20738,7 +20869,7 @@
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
@@ -20770,7 +20901,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -20799,7 +20930,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -20829,7 +20960,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11">
@@ -20858,7 +20989,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -20890,7 +21021,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11">
@@ -20919,7 +21050,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -20942,7 +21073,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -20959,7 +21090,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -20980,7 +21111,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -20997,7 +21128,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -21018,7 +21149,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -21032,7 +21163,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -21053,7 +21184,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -21066,7 +21197,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -21093,7 +21224,7 @@
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A18" s="16"/>
       <c r="B18" s="17" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
@@ -21122,7 +21253,7 @@
     <row r="19" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A19" s="16"/>
       <c r="B19" s="17" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
@@ -21151,7 +21282,7 @@
     <row r="20" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A20" s="16"/>
       <c r="B20" s="17" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
@@ -21457,11 +21588,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -21484,9 +21615,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -21629,7 +21760,7 @@
     <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="14"/>
       <c r="B8" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11">
@@ -21660,7 +21791,7 @@
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="O8" s="11"/>
       <c r="P8" s="11"/>
@@ -21692,7 +21823,7 @@
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11">
@@ -21723,7 +21854,7 @@
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="O9" s="11"/>
       <c r="P9" s="11"/>
@@ -21755,7 +21886,7 @@
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="7" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11">
@@ -21786,7 +21917,7 @@
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
@@ -21818,7 +21949,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -21849,7 +21980,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -21881,7 +22012,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11">
@@ -21912,7 +22043,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -21944,7 +22075,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11">
@@ -21975,7 +22106,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -21998,7 +22129,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -22015,7 +22146,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -22036,7 +22167,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -22053,7 +22184,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -22074,7 +22205,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -22091,7 +22222,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -22112,7 +22243,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -22129,7 +22260,7 @@
       <c r="L17" s="13"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -22150,7 +22281,7 @@
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A18" s="16"/>
       <c r="B18" s="17" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
@@ -22164,7 +22295,7 @@
       <c r="L18" s="13"/>
       <c r="M18" s="16"/>
       <c r="N18" s="17" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="O18" s="11"/>
       <c r="P18" s="11"/>
@@ -22185,7 +22316,7 @@
     <row r="19" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A19" s="16"/>
       <c r="B19" s="17" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
@@ -22199,7 +22330,7 @@
       <c r="L19" s="13"/>
       <c r="M19" s="16"/>
       <c r="N19" s="17" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="O19" s="11"/>
       <c r="P19" s="11"/>
@@ -22220,7 +22351,7 @@
     <row r="20" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A20" s="16"/>
       <c r="B20" s="17" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
@@ -22233,7 +22364,7 @@
       <c r="K20" s="18"/>
       <c r="M20" s="16"/>
       <c r="N20" s="17" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="O20" s="11"/>
       <c r="P20" s="11"/>
@@ -22383,7 +22514,7 @@
       </c>
       <c r="K22" s="23"/>
       <c r="M22" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="N22" s="20" t="s">
         <v>18</v>
@@ -22545,11 +22676,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -22572,9 +22703,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -22720,26 +22851,37 @@
         <v>13</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="D8" s="11">
+        <v>44</v>
+      </c>
+      <c r="E8" s="11">
+        <v>114</v>
+      </c>
+      <c r="F8" s="11">
+        <v>154</v>
+      </c>
+      <c r="G8" s="11">
+        <v>79</v>
+      </c>
+      <c r="H8" s="11">
+        <v>54</v>
+      </c>
+      <c r="I8" s="11">
+        <v>99</v>
+      </c>
       <c r="J8" s="15">
-        <v>42</v>
+        <f>SUM(C8:I8)/40</f>
+        <v>13.6</v>
       </c>
       <c r="K8" s="12">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11">
-        <v>590</v>
-      </c>
+      <c r="O8" s="11"/>
       <c r="P8" s="11"/>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
@@ -22748,22 +22890,20 @@
       <c r="U8" s="11"/>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>14.75</v>
-      </c>
-      <c r="W8" s="12">
-        <v>24</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>42</v>
+        <v>13.6</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>14.75</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>27.25</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -22772,18 +22912,30 @@
         <v>14</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="D9" s="11">
+        <v>0</v>
+      </c>
+      <c r="E9" s="11">
+        <v>0</v>
+      </c>
+      <c r="F9" s="11">
+        <v>10</v>
+      </c>
+      <c r="G9" s="11">
+        <v>65</v>
+      </c>
+      <c r="H9" s="11">
+        <v>60</v>
+      </c>
+      <c r="I9" s="11">
+        <v>65</v>
+      </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
+        <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
+        <v>5</v>
       </c>
       <c r="K9" s="12">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
@@ -22801,12 +22953,10 @@
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
         <v>0</v>
       </c>
-      <c r="W9" s="12">
-        <v>13</v>
-      </c>
+      <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
@@ -22814,7 +22964,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -22823,17 +22973,30 @@
         <v>15</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="D10" s="11">
+        <v>70</v>
+      </c>
+      <c r="E10" s="11">
+        <v>64</v>
+      </c>
+      <c r="F10" s="11">
+        <v>66</v>
+      </c>
+      <c r="G10" s="11">
+        <v>80</v>
+      </c>
+      <c r="H10" s="11">
+        <v>70</v>
+      </c>
+      <c r="I10" s="11">
+        <v>131</v>
+      </c>
       <c r="J10" s="15">
-        <v>12</v>
+        <f t="shared" si="0"/>
+        <v>12.025</v>
       </c>
       <c r="K10" s="12">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
@@ -22851,12 +23014,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W10" s="12">
-        <v>10</v>
-      </c>
+      <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>12.025</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -22864,32 +23025,44 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>12.025</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="D11" s="11">
+        <v>17</v>
+      </c>
+      <c r="E11" s="11">
+        <v>17</v>
+      </c>
+      <c r="F11" s="11">
+        <v>14</v>
+      </c>
+      <c r="G11" s="11">
+        <v>4</v>
+      </c>
+      <c r="H11" s="11">
+        <v>4</v>
+      </c>
+      <c r="I11" s="11">
+        <v>0</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="K11" s="12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -22902,12 +23075,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W11" s="12">
-        <v>5</v>
-      </c>
+      <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -22915,32 +23086,44 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="D12" s="11">
+        <v>20</v>
+      </c>
+      <c r="E12" s="11">
+        <v>30</v>
+      </c>
+      <c r="F12" s="11">
+        <v>42</v>
+      </c>
+      <c r="G12" s="11">
+        <v>65</v>
+      </c>
+      <c r="H12" s="11">
+        <v>25</v>
+      </c>
+      <c r="I12" s="11">
+        <v>70</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="K12" s="12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -22953,12 +23136,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W12" s="12">
-        <v>2</v>
-      </c>
+      <c r="W12" s="12"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
@@ -22966,13 +23147,13 @@
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -22989,7 +23170,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -23002,9 +23183,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W13" s="12">
-        <v>3</v>
-      </c>
+      <c r="W13" s="12"/>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -23012,24 +23191,38 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
+      <c r="D14" s="11">
+        <v>240</v>
+      </c>
+      <c r="E14" s="11">
+        <v>160</v>
+      </c>
+      <c r="F14" s="11">
+        <v>280</v>
+      </c>
+      <c r="G14" s="11">
+        <v>320</v>
+      </c>
+      <c r="H14" s="11">
+        <v>280</v>
+      </c>
+      <c r="I14" s="11">
+        <v>520</v>
+      </c>
       <c r="J14" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="12"/>
+        <v>45</v>
+      </c>
+      <c r="K14" s="12">
+        <v>3</v>
+      </c>
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -23050,7 +23243,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -23060,14 +23253,15 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="12"/>
+        <v>10</v>
+      </c>
+      <c r="K15" s="12">
+        <v>9</v>
+      </c>
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -23088,7 +23282,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -23098,14 +23292,15 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="12"/>
+        <v>8</v>
+      </c>
+      <c r="K16" s="12">
+        <v>9</v>
+      </c>
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -23125,7 +23320,9 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
-      <c r="B17" s="17"/>
+      <c r="B17" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
@@ -23133,10 +23330,15 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
-      <c r="J17" s="15"/>
+      <c r="J17" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+      <c r="N17" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
@@ -23168,38 +23370,38 @@
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>391</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>566</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>613</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>493</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>885</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>0</v>
+        <v>3333</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>590</v>
+        <v>0</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
@@ -23227,20 +23429,20 @@
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>590</v>
+        <v>0</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>54</v>
+        <v>38.324999999999996</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>14.75</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>39.25</v>
+        <v>38.324999999999996</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -23254,31 +23456,31 @@
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9.7750000000000004</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9.625</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>14.15</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>15.324999999999999</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>12.324999999999999</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>22.125</v>
       </c>
       <c r="J19" s="22">
         <f>SUM(J8:J16)</f>
-        <v>54</v>
+        <v>101.32499999999999</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -23287,7 +23489,7 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>14.75</v>
+        <v>0</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
@@ -23315,20 +23517,20 @@
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>14.75</v>
+        <v>0</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>1.35</v>
+        <v>0.95812499999999989</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0.36875000000000002</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.98124999999999996</v>
+        <v>0.95812499999999989</v>
       </c>
     </row>
   </sheetData>
@@ -23439,11 +23641,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -23466,9 +23668,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -23611,7 +23813,7 @@
     <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="14"/>
       <c r="B8" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
@@ -23628,7 +23830,7 @@
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="O8" s="11"/>
       <c r="P8" s="11"/>
@@ -23660,7 +23862,7 @@
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
@@ -23677,7 +23879,7 @@
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="O9" s="11"/>
       <c r="P9" s="11"/>
@@ -23709,7 +23911,7 @@
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="7" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
@@ -23726,7 +23928,7 @@
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
@@ -23758,7 +23960,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -23775,7 +23977,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -23807,7 +24009,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -23824,7 +24026,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -23896,7 +24098,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -23913,7 +24115,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -23934,7 +24136,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -23951,7 +24153,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -23972,7 +24174,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -23989,7 +24191,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -24051,7 +24253,7 @@
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A18" s="16"/>
       <c r="B18" s="17" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
@@ -24065,7 +24267,7 @@
       <c r="L18" s="13"/>
       <c r="M18" s="16"/>
       <c r="N18" s="17" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="O18" s="11"/>
       <c r="P18" s="11">
@@ -24100,7 +24302,7 @@
     <row r="19" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A19" s="16"/>
       <c r="B19" s="17" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
@@ -24114,7 +24316,7 @@
       <c r="L19" s="13"/>
       <c r="M19" s="16"/>
       <c r="N19" s="17" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="O19" s="11"/>
       <c r="P19" s="11"/>
@@ -24132,7 +24334,7 @@
     <row r="20" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A20" s="16"/>
       <c r="B20" s="17" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
@@ -24146,7 +24348,7 @@
       <c r="L20" s="13"/>
       <c r="M20" s="16"/>
       <c r="N20" s="17" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="O20" s="11"/>
       <c r="P20" s="11"/>
@@ -24459,11 +24661,11 @@
       <c r="T2" s="77"/>
       <c r="U2" s="77"/>
       <c r="V2" s="77"/>
-      <c r="Y2" s="81" t="s">
+      <c r="Y2" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z2" s="81"/>
-      <c r="AA2" s="81"/>
+      <c r="Z2" s="82"/>
+      <c r="AA2" s="82"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1"/>
@@ -24486,9 +24688,9 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81"/>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Y3" s="82"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -24631,7 +24833,7 @@
     <row r="7" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A7" s="14"/>
       <c r="B7" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C7" s="11"/>
       <c r="D7" s="11">
@@ -24662,7 +24864,7 @@
       <c r="L7" s="13"/>
       <c r="M7" s="14"/>
       <c r="N7" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="O7" s="11"/>
       <c r="P7" s="11">
@@ -24706,7 +24908,7 @@
     <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="14"/>
       <c r="B8" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11">
@@ -24737,7 +24939,7 @@
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="O8" s="11"/>
       <c r="P8" s="11">
@@ -24781,7 +24983,7 @@
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="7" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11">
@@ -24812,7 +25014,7 @@
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="O9" s="11"/>
       <c r="P9" s="11">
@@ -24931,7 +25133,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -24962,7 +25164,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11">
@@ -25049,7 +25251,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -25066,7 +25268,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -25087,7 +25289,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -25104,7 +25306,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -25125,7 +25327,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -25142,7 +25344,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -25163,7 +25365,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -25179,7 +25381,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -25197,7 +25399,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -25213,7 +25415,7 @@
       <c r="L17" s="13"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -25231,7 +25433,7 @@
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A18" s="16"/>
       <c r="B18" s="17" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
@@ -25247,7 +25449,7 @@
       <c r="L18" s="13"/>
       <c r="M18" s="16"/>
       <c r="N18" s="17" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="O18" s="11"/>
       <c r="P18" s="11"/>
@@ -25587,11 +25789,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -25614,9 +25816,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -25869,7 +26071,7 @@
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
       <c r="J10" s="15">
-        <f t="shared" ref="J10:J16" si="4">SUM(C10:I10)/40</f>
+        <f t="shared" ref="J10:J17" si="4">SUM(C10:I10)/40</f>
         <v>0</v>
       </c>
       <c r="K10" s="12"/>
@@ -25908,7 +26110,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -25925,7 +26127,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -25957,7 +26159,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -25974,7 +26176,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -26006,7 +26208,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -26023,7 +26225,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -26046,7 +26248,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -26063,7 +26265,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -26084,7 +26286,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -26101,7 +26303,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -26122,7 +26324,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -26139,7 +26341,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -26159,7 +26361,9 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
-      <c r="B17" s="17"/>
+      <c r="B17" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
@@ -26167,10 +26371,15 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
-      <c r="J17" s="15"/>
+      <c r="J17" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+      <c r="N17" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
@@ -26482,11 +26691,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="44"/>
@@ -26511,9 +26720,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="44"/>
@@ -26554,16 +26763,16 @@
       <c r="C6" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="82" t="s">
+      <c r="D6" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="82"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="82" t="s">
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="82"/>
-      <c r="I6" s="82"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
       <c r="J6" s="47"/>
       <c r="K6" s="48"/>
       <c r="L6" s="44"/>
@@ -26720,7 +26929,7 @@
       <c r="H9" s="54"/>
       <c r="I9" s="54"/>
       <c r="J9" s="58">
-        <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
+        <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
         <v>0</v>
       </c>
       <c r="K9" s="55"/>
@@ -26808,7 +27017,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="59"/>
       <c r="B11" s="60" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="54"/>
       <c r="D11" s="54"/>
@@ -26825,7 +27034,7 @@
       <c r="L11" s="56"/>
       <c r="M11" s="16"/>
       <c r="N11" s="60" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -26857,7 +27066,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="59"/>
       <c r="B12" s="60" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="54"/>
       <c r="D12" s="54"/>
@@ -26874,7 +27083,7 @@
       <c r="L12" s="56"/>
       <c r="M12" s="16"/>
       <c r="N12" s="60" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -26906,7 +27115,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="59"/>
       <c r="B13" s="60" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="54"/>
       <c r="D13" s="54"/>
@@ -26923,7 +27132,7 @@
       <c r="L13" s="56"/>
       <c r="M13" s="16"/>
       <c r="N13" s="60" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -26944,7 +27153,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="59"/>
       <c r="B14" s="60" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="54"/>
       <c r="D14" s="54"/>
@@ -26961,7 +27170,7 @@
       <c r="L14" s="56"/>
       <c r="M14" s="16"/>
       <c r="N14" s="60" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -26982,7 +27191,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="59"/>
       <c r="B15" s="60" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="54"/>
       <c r="D15" s="54"/>
@@ -26999,7 +27208,7 @@
       <c r="L15" s="56"/>
       <c r="M15" s="16"/>
       <c r="N15" s="60" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -27020,7 +27229,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="59"/>
       <c r="B16" s="60" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="54"/>
       <c r="D16" s="54"/>
@@ -27037,7 +27246,7 @@
       <c r="L16" s="56"/>
       <c r="M16" s="16"/>
       <c r="N16" s="60" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -27057,7 +27266,9 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="59"/>
-      <c r="B17" s="60"/>
+      <c r="B17" s="60" t="s">
+        <v>39</v>
+      </c>
       <c r="C17" s="54"/>
       <c r="D17" s="54"/>
       <c r="E17" s="54"/>
@@ -27065,11 +27276,16 @@
       <c r="G17" s="54"/>
       <c r="H17" s="54"/>
       <c r="I17" s="54"/>
-      <c r="J17" s="58"/>
+      <c r="J17" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="K17" s="61"/>
       <c r="L17" s="44"/>
       <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+      <c r="N17" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
@@ -27391,11 +27607,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -27418,9 +27634,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -27620,7 +27836,7 @@
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
+        <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
         <v>0</v>
       </c>
       <c r="K9" s="12"/>
@@ -27704,7 +27920,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -27721,7 +27937,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -27751,7 +27967,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -27767,10 +27983,10 @@
       <c r="K12" s="12"/>
       <c r="L12" s="13"/>
       <c r="M12" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="N12" s="17" t="s">
         <v>29</v>
-      </c>
-      <c r="N12" s="17" t="s">
-        <v>36</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -27800,7 +28016,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -27817,7 +28033,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -27838,7 +28054,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -27855,7 +28071,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -27876,7 +28092,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -27893,7 +28109,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -27914,7 +28130,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -27931,7 +28147,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -27951,7 +28167,9 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
-      <c r="B17" s="17"/>
+      <c r="B17" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
@@ -27959,11 +28177,14 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
-      <c r="J17" s="15"/>
+      <c r="J17" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -28273,11 +28494,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -28300,9 +28521,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -28585,7 +28806,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -28602,7 +28823,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -28632,7 +28853,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -28648,7 +28869,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -28678,7 +28899,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -28695,7 +28916,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -28716,7 +28937,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -28732,7 +28953,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -28753,7 +28974,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -28769,7 +28990,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -28790,7 +29011,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -28806,7 +29027,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -28826,7 +29047,9 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
-      <c r="B17" s="17"/>
+      <c r="B17" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
@@ -28834,11 +29057,13 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
-      <c r="J17" s="15"/>
+      <c r="J17" s="15">
+        <v>5</v>
+      </c>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -28854,7 +29079,7 @@
       <c r="W17" s="18"/>
       <c r="Y17" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z17" s="37">
         <f t="shared" si="3"/>
@@ -28862,7 +29087,7 @@
       </c>
       <c r="AA17" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
@@ -28938,7 +29163,7 @@
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
@@ -28946,7 +29171,7 @@
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -29026,7 +29251,7 @@
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0.27500000000000002</v>
+        <v>0.4</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
@@ -29034,7 +29259,7 @@
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.27500000000000002</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -29145,11 +29370,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -29172,9 +29397,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -29466,7 +29691,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -29483,7 +29708,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -29515,7 +29740,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -29532,7 +29757,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -29564,7 +29789,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -29581,7 +29806,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -29604,7 +29829,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -29620,7 +29845,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -29641,7 +29866,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -29657,7 +29882,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -29678,7 +29903,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -29694,7 +29919,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -29714,7 +29939,9 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
-      <c r="B17" s="17"/>
+      <c r="B17" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
@@ -29722,10 +29949,14 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
-      <c r="J17" s="15"/>
+      <c r="J17" s="15">
+        <v>11</v>
+      </c>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+      <c r="N17" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
@@ -29737,7 +29968,7 @@
       <c r="W17" s="18"/>
       <c r="Y17" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z17" s="37">
         <f t="shared" si="3"/>
@@ -29745,7 +29976,7 @@
       </c>
       <c r="AA17" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
@@ -29821,7 +30052,7 @@
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
@@ -29829,7 +30060,7 @@
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>-3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -29909,7 +30140,7 @@
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
@@ -29917,7 +30148,7 @@
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>-7.4999999999999997E-2</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -30029,11 +30260,11 @@
       <c r="T3" s="77"/>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -30056,9 +30287,9 @@
       <c r="T4" s="77"/>
       <c r="U4" s="77"/>
       <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -30350,7 +30581,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -30367,7 +30598,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -30399,7 +30630,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -30416,7 +30647,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -30448,7 +30679,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -30464,7 +30695,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -30487,7 +30718,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -30503,7 +30734,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -30524,7 +30755,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -30540,7 +30771,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -30561,7 +30792,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -30577,7 +30808,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -30597,7 +30828,9 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
-      <c r="B17" s="17"/>
+      <c r="B17" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
@@ -30605,10 +30838,14 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
-      <c r="J17" s="15"/>
+      <c r="J17" s="15">
+        <v>6</v>
+      </c>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+      <c r="N17" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
@@ -30620,7 +30857,7 @@
       <c r="W17" s="18"/>
       <c r="Y17" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z17" s="37">
         <f t="shared" si="3"/>
@@ -30628,7 +30865,7 @@
       </c>
       <c r="AA17" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
@@ -30704,7 +30941,7 @@
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
@@ -30712,7 +30949,7 @@
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>-1.25</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -30792,7 +31029,7 @@
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
@@ -30800,12 +31037,12 @@
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>-3.125E-2</v>
+        <v>0.11874999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.35">
       <c r="J22" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94066445-166C-4FAA-B08C-5FEBEA2C6D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E8B19D6-CAC9-4B0D-8634-E674E9F462EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="2" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
@@ -12429,17 +12429,31 @@
         <v>16</v>
       </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="P13" s="11">
+        <v>317</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>175</v>
+      </c>
+      <c r="R13" s="11">
+        <v>611</v>
+      </c>
+      <c r="S13" s="11">
+        <v>360</v>
+      </c>
+      <c r="T13" s="11">
+        <v>442</v>
+      </c>
+      <c r="U13" s="11">
+        <v>720</v>
+      </c>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12"/>
+        <v>65.625</v>
+      </c>
+      <c r="W13" s="12">
+        <v>11</v>
+      </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -12638,31 +12652,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>138</v>
+        <v>455</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>162</v>
+        <v>337</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>245</v>
+        <v>856</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>372</v>
+        <v>732</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>263</v>
+        <v>705</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>307</v>
+        <v>1027</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>1487</v>
+        <v>4112</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -12726,31 +12740,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>3.45</v>
+        <v>11.375</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>4.05</v>
+        <v>8.4250000000000007</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>6.125</v>
+        <v>21.4</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>9.3000000000000007</v>
+        <v>18.3</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>6.5750000000000002</v>
+        <v>17.625</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>7.6749999999999998</v>
+        <v>25.675000000000001</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>37.174999999999997</v>
+        <v>102.8</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -22882,28 +22896,42 @@
         <v>13</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>44</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>62</v>
+      </c>
+      <c r="R8" s="11">
+        <v>114</v>
+      </c>
+      <c r="S8" s="11">
+        <v>79</v>
+      </c>
+      <c r="T8" s="11">
+        <v>42</v>
+      </c>
+      <c r="U8" s="11">
+        <v>99</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>11</v>
+      </c>
+      <c r="W8" s="12">
+        <v>15</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>13.6</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>13.6</v>
+        <v>2.5999999999999996</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -22943,28 +22971,42 @@
         <v>14</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>0</v>
+      </c>
+      <c r="R9" s="11">
+        <v>10</v>
+      </c>
+      <c r="S9" s="11">
+        <v>65</v>
+      </c>
+      <c r="T9" s="11">
+        <v>20</v>
+      </c>
+      <c r="U9" s="11">
+        <v>25</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>3</v>
+      </c>
+      <c r="W9" s="12">
+        <v>6</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
         <v>5</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -23004,28 +23046,42 @@
         <v>15</v>
       </c>
       <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="P10" s="11">
+        <v>70</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>44</v>
+      </c>
+      <c r="R10" s="11">
+        <v>26</v>
+      </c>
+      <c r="S10" s="11">
+        <v>74</v>
+      </c>
+      <c r="T10" s="11">
+        <v>64</v>
+      </c>
+      <c r="U10" s="11">
+        <v>119</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>9.9250000000000007</v>
+      </c>
+      <c r="W10" s="12">
+        <v>6</v>
+      </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
         <v>12.025</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.9250000000000007</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>12.025</v>
+        <v>2.0999999999999996</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -23065,28 +23121,42 @@
         <v>30</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>17</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>17</v>
+      </c>
+      <c r="R11" s="11">
+        <v>14</v>
+      </c>
+      <c r="S11" s="11">
+        <v>4</v>
+      </c>
+      <c r="T11" s="11">
+        <v>4</v>
+      </c>
+      <c r="U11" s="11">
+        <v>0</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>1.4</v>
+      </c>
+      <c r="W11" s="12">
+        <v>2</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>1.4</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>1.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -23126,28 +23196,42 @@
         <v>29</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>0</v>
+      </c>
+      <c r="R12" s="11">
+        <v>12</v>
+      </c>
+      <c r="S12" s="11">
+        <v>65</v>
+      </c>
+      <c r="T12" s="11">
+        <v>25</v>
+      </c>
+      <c r="U12" s="11">
+        <v>70</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>4.3</v>
+      </c>
+      <c r="W12" s="12">
+        <v>3</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
         <v>6.3</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>6.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -23405,31 +23489,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>287</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>313</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>1185</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -23438,11 +23522,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>29.625</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>38.324999999999996</v>
+        <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -23493,31 +23577,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.2749999999999999</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.0750000000000002</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7.1749999999999998</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.875</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7.8250000000000002</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>29.625</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -23526,11 +23610,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>0.74062499999999998</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.95812499999999989</v>
+        <v>0.21749999999999997</v>
       </c>
     </row>
   </sheetData>

--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E8B19D6-CAC9-4B0D-8634-E674E9F462EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191EA1A0-EE1D-4DC2-8AC8-2CC6BB7E6438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="2" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="4" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1706" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="45">
   <si>
     <t>Booking</t>
   </si>
@@ -139,9 +139,6 @@
   </si>
   <si>
     <t>A6</t>
-  </si>
-  <si>
-    <t>Negotiate</t>
   </si>
   <si>
     <t>Furqan</t>
@@ -1575,7 +1572,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -1606,7 +1603,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11">
@@ -1650,7 +1647,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11">
@@ -1681,7 +1678,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11">
@@ -1791,7 +1788,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -1807,7 +1804,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -1828,7 +1825,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -1844,7 +1841,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -1865,7 +1862,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -1882,7 +1879,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -2573,7 +2570,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11">
         <v>119</v>
@@ -2606,7 +2603,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -2638,7 +2635,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="11">
         <v>60</v>
@@ -2671,7 +2668,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -2703,7 +2700,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="11">
         <v>200</v>
@@ -2736,7 +2733,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -2798,7 +2795,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -2816,7 +2813,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -2837,7 +2834,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -2855,7 +2852,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -2876,7 +2873,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -2891,7 +2888,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -3499,7 +3496,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="84" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D10" s="85"/>
       <c r="E10" s="85"/>
@@ -3545,7 +3542,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11">
         <v>120</v>
@@ -3578,7 +3575,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -3610,7 +3607,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="11">
         <v>124</v>
@@ -3643,7 +3640,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -3675,7 +3672,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -3693,7 +3690,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -3755,7 +3752,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -3773,7 +3770,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -3794,7 +3791,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -3812,7 +3809,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -3833,7 +3830,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -3848,7 +3845,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -4525,7 +4522,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11">
         <v>106</v>
@@ -4558,7 +4555,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -4590,7 +4587,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="11">
         <v>24</v>
@@ -4623,7 +4620,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -4655,7 +4652,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="11">
         <v>200</v>
@@ -4688,7 +4685,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -4749,7 +4746,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -4766,7 +4763,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -4787,7 +4784,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -4804,7 +4801,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -4825,7 +4822,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -4841,7 +4838,7 @@
       <c r="K17" s="12"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -5093,7 +5090,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="L1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
@@ -5465,7 +5462,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="43"/>
       <c r="D11" s="43"/>
@@ -5482,7 +5479,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="43"/>
       <c r="P11" s="43"/>
@@ -5512,7 +5509,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="43"/>
       <c r="D12" s="43"/>
@@ -5529,7 +5526,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="43"/>
       <c r="P12" s="43"/>
@@ -5559,7 +5556,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="43"/>
       <c r="D13" s="43"/>
@@ -5576,7 +5573,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="43"/>
       <c r="P13" s="43"/>
@@ -5635,7 +5632,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="43"/>
       <c r="D15" s="43"/>
@@ -5652,7 +5649,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O15" s="43"/>
       <c r="P15" s="43"/>
@@ -5673,7 +5670,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="43"/>
       <c r="D16" s="43"/>
@@ -5690,7 +5687,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -5711,7 +5708,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="43"/>
       <c r="D17" s="43"/>
@@ -5727,7 +5724,7 @@
       <c r="K17" s="12"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -5981,7 +5978,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="M1" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -6388,7 +6385,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11">
         <v>32</v>
@@ -6421,7 +6418,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -6453,7 +6450,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="11">
         <v>166</v>
@@ -6486,7 +6483,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -6518,7 +6515,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11">
@@ -6549,7 +6546,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -6608,7 +6605,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -6625,7 +6622,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -6646,7 +6643,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -6663,7 +6660,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -6684,7 +6681,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -6700,7 +6697,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -7375,7 +7372,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11">
         <v>136</v>
@@ -7408,7 +7405,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -7440,7 +7437,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="11">
         <v>142</v>
@@ -7473,7 +7470,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -7505,7 +7502,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -7522,7 +7519,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -7584,7 +7581,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -7602,7 +7599,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -7623,7 +7620,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -7641,7 +7638,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -7662,7 +7659,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -7677,7 +7674,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -8351,7 +8348,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11">
         <v>44</v>
@@ -8384,7 +8381,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -8416,7 +8413,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="11">
         <v>150</v>
@@ -8449,7 +8446,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -8481,7 +8478,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -8499,7 +8496,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -8561,7 +8558,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -8578,7 +8575,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -8599,7 +8596,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -8616,7 +8613,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -8637,7 +8634,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -8653,7 +8650,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -9320,7 +9317,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11">
         <v>284</v>
@@ -9353,7 +9350,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -9385,7 +9382,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="11">
         <v>205</v>
@@ -9418,7 +9415,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -9450,7 +9447,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -9467,7 +9464,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -9528,7 +9525,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -9545,7 +9542,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -9566,7 +9563,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -9583,7 +9580,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -9604,7 +9601,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -9620,7 +9617,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -10291,7 +10288,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -10322,7 +10319,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -10352,7 +10349,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11">
@@ -10383,7 +10380,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -10415,7 +10412,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -10432,7 +10429,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -10493,7 +10490,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -10510,7 +10507,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -10531,7 +10528,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -10548,7 +10545,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -10569,7 +10566,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -10585,7 +10582,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -11251,7 +11248,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -11282,7 +11279,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -11314,7 +11311,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -11331,7 +11328,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -11361,7 +11358,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -11378,7 +11375,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -11439,7 +11436,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -11456,7 +11453,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -11477,7 +11474,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -11494,7 +11491,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -11515,7 +11512,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -11531,7 +11528,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -12245,7 +12242,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -12276,7 +12273,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11">
@@ -12320,7 +12317,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11">
@@ -12351,7 +12348,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11">
@@ -12461,7 +12458,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -12478,7 +12475,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -12499,7 +12496,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -12516,7 +12513,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -12537,7 +12534,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -12554,7 +12551,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -13203,7 +13200,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="43"/>
       <c r="D11" s="43"/>
@@ -13220,7 +13217,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="43"/>
       <c r="P11" s="43"/>
@@ -13250,7 +13247,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="43"/>
       <c r="D12" s="43"/>
@@ -13267,7 +13264,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="43"/>
       <c r="P12" s="43"/>
@@ -13297,7 +13294,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="43"/>
       <c r="D13" s="43"/>
@@ -13314,7 +13311,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="43"/>
       <c r="P13" s="43"/>
@@ -13373,7 +13370,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="43"/>
       <c r="D15" s="43"/>
@@ -13390,7 +13387,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O15" s="43"/>
       <c r="P15" s="43"/>
@@ -13411,7 +13408,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="43"/>
       <c r="D16" s="43"/>
@@ -13428,7 +13425,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="43"/>
       <c r="P16" s="43"/>
@@ -13449,7 +13446,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="43"/>
       <c r="D17" s="43"/>
@@ -13465,7 +13462,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="43"/>
       <c r="P17" s="43"/>
@@ -14235,7 +14232,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -14266,7 +14263,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -14298,11 +14295,11 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="87" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E12" s="88"/>
       <c r="F12" s="88"/>
@@ -14314,7 +14311,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -14344,7 +14341,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -14361,7 +14358,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -14420,7 +14417,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -14437,7 +14434,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -14458,7 +14455,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -14475,7 +14472,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -14496,7 +14493,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -14512,7 +14509,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -15177,7 +15174,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -15208,7 +15205,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -15240,10 +15237,10 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="87" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" s="88"/>
       <c r="E12" s="88"/>
@@ -15256,7 +15253,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -15286,7 +15283,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -15304,7 +15301,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -15367,7 +15364,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -15385,7 +15382,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -15407,7 +15404,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -15425,7 +15422,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -15447,7 +15444,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -15462,7 +15459,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -16006,7 +16003,7 @@
         <v>14</v>
       </c>
       <c r="C9" s="87" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D9" s="88"/>
       <c r="E9" s="88"/>
@@ -16112,7 +16109,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -16143,7 +16140,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -16175,7 +16172,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11">
@@ -16206,7 +16203,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -16238,7 +16235,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11">
@@ -16269,7 +16266,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -16330,7 +16327,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -16347,7 +16344,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -16368,7 +16365,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -16385,7 +16382,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -16406,7 +16403,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -16422,7 +16419,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -16899,7 +16896,7 @@
     <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="14"/>
       <c r="B8" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="11">
         <v>17</v>
@@ -16932,7 +16929,7 @@
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O8" s="11">
         <v>17</v>
@@ -16966,7 +16963,7 @@
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11">
@@ -16997,7 +16994,7 @@
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O9" s="11"/>
       <c r="P9" s="11"/>
@@ -17029,7 +17026,7 @@
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11">
@@ -17060,7 +17057,7 @@
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
@@ -17092,7 +17089,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -17123,7 +17120,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -17155,7 +17152,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11">
@@ -17186,7 +17183,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -17218,7 +17215,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -17243,7 +17240,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -17304,7 +17301,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -17321,7 +17318,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -17342,7 +17339,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -17360,7 +17357,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -17381,7 +17378,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -17396,7 +17393,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -17941,7 +17938,7 @@
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="43"/>
@@ -17958,7 +17955,7 @@
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O9" s="11"/>
       <c r="P9" s="43"/>
@@ -17988,7 +17985,7 @@
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
@@ -18017,7 +18014,7 @@
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
@@ -18049,7 +18046,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -18080,7 +18077,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -18112,7 +18109,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11">
@@ -18143,7 +18140,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -18175,7 +18172,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -18192,7 +18189,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -18253,7 +18250,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -18270,7 +18267,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -18291,7 +18288,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -18308,7 +18305,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -18329,7 +18326,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -18345,7 +18342,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -18998,7 +18995,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -19029,7 +19026,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -19061,7 +19058,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11">
@@ -19092,7 +19089,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -19124,7 +19121,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -19141,7 +19138,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -19202,7 +19199,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -19219,7 +19216,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -19240,7 +19237,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -19257,7 +19254,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -19278,7 +19275,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -19294,7 +19291,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -19769,7 +19766,7 @@
     <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="14"/>
       <c r="B8" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
@@ -19786,7 +19783,7 @@
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O8" s="11"/>
       <c r="P8" s="11"/>
@@ -19816,7 +19813,7 @@
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
@@ -19833,7 +19830,7 @@
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O9" s="11"/>
       <c r="P9" s="11"/>
@@ -19863,7 +19860,7 @@
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
@@ -19880,7 +19877,7 @@
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
@@ -19910,7 +19907,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -19927,7 +19924,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -19957,7 +19954,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -19974,7 +19971,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -20004,7 +20001,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -20021,7 +20018,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -20080,7 +20077,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -20097,7 +20094,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -20118,7 +20115,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -20135,7 +20132,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -20156,7 +20153,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -20173,7 +20170,7 @@
       <c r="L17" s="13"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -20261,7 +20258,7 @@
       <c r="K20" s="18"/>
       <c r="M20" s="16"/>
       <c r="N20" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O20" s="11"/>
       <c r="P20" s="11"/>
@@ -20738,7 +20735,7 @@
     <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="14"/>
       <c r="B8" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
@@ -20761,7 +20758,7 @@
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O8" s="11"/>
       <c r="P8" s="11"/>
@@ -20793,7 +20790,7 @@
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11">
@@ -20822,7 +20819,7 @@
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O9" s="11"/>
       <c r="P9" s="11"/>
@@ -20854,7 +20851,7 @@
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11">
@@ -20883,7 +20880,7 @@
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
@@ -20915,7 +20912,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -20944,7 +20941,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -20974,7 +20971,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11">
@@ -21003,7 +21000,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -21035,7 +21032,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11">
@@ -21064,7 +21061,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -21125,7 +21122,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -21142,7 +21139,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -21163,7 +21160,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -21177,7 +21174,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -21198,7 +21195,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -21211,7 +21208,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -21238,7 +21235,7 @@
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A18" s="16"/>
       <c r="B18" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
@@ -21267,7 +21264,7 @@
     <row r="19" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A19" s="16"/>
       <c r="B19" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
@@ -21296,7 +21293,7 @@
     <row r="20" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A20" s="16"/>
       <c r="B20" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
@@ -21774,7 +21771,7 @@
     <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="14"/>
       <c r="B8" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11">
@@ -21805,7 +21802,7 @@
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O8" s="11"/>
       <c r="P8" s="11"/>
@@ -21837,7 +21834,7 @@
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11">
@@ -21868,7 +21865,7 @@
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O9" s="11"/>
       <c r="P9" s="11"/>
@@ -21900,7 +21897,7 @@
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11">
@@ -21931,7 +21928,7 @@
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
@@ -21963,7 +21960,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -21994,7 +21991,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -22026,7 +22023,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11">
@@ -22057,7 +22054,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -22089,7 +22086,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11">
@@ -22120,7 +22117,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -22181,7 +22178,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -22198,7 +22195,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -22219,7 +22216,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -22236,7 +22233,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -22257,7 +22254,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -22274,7 +22271,7 @@
       <c r="L17" s="13"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -22295,7 +22292,7 @@
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A18" s="16"/>
       <c r="B18" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
@@ -22309,7 +22306,7 @@
       <c r="L18" s="13"/>
       <c r="M18" s="16"/>
       <c r="N18" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O18" s="11"/>
       <c r="P18" s="11"/>
@@ -22330,7 +22327,7 @@
     <row r="19" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A19" s="16"/>
       <c r="B19" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
@@ -22344,7 +22341,7 @@
       <c r="L19" s="13"/>
       <c r="M19" s="16"/>
       <c r="N19" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O19" s="11"/>
       <c r="P19" s="11"/>
@@ -22365,7 +22362,7 @@
     <row r="20" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A20" s="16"/>
       <c r="B20" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
@@ -22378,7 +22375,7 @@
       <c r="K20" s="18"/>
       <c r="M20" s="16"/>
       <c r="N20" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O20" s="11"/>
       <c r="P20" s="11"/>
@@ -22528,7 +22525,7 @@
       </c>
       <c r="K22" s="23"/>
       <c r="M22" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N22" s="20" t="s">
         <v>18</v>
@@ -23087,7 +23084,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -23118,7 +23115,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11">
@@ -23162,7 +23159,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11">
@@ -23193,7 +23190,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11">
@@ -23237,7 +23234,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -23254,7 +23251,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -23309,17 +23306,31 @@
         <v>17</v>
       </c>
       <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
+      <c r="P14" s="11">
+        <v>190</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>140</v>
+      </c>
+      <c r="R14" s="11">
+        <v>180</v>
+      </c>
+      <c r="S14" s="11">
+        <v>120</v>
+      </c>
+      <c r="T14" s="11">
+        <v>140</v>
+      </c>
+      <c r="U14" s="11">
+        <v>180</v>
+      </c>
       <c r="V14" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="12"/>
+        <v>23.75</v>
+      </c>
+      <c r="W14" s="12">
+        <v>3</v>
+      </c>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
       <c r="AA14" s="38"/>
@@ -23327,7 +23338,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -23345,7 +23356,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -23366,7 +23377,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -23384,7 +23395,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -23405,7 +23416,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -23421,7 +23432,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -23489,31 +23500,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>131</v>
+        <v>321</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>123</v>
+        <v>263</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>176</v>
+        <v>356</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>287</v>
+        <v>407</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>155</v>
+        <v>295</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>313</v>
+        <v>493</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>1185</v>
+        <v>2135</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -23577,31 +23588,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>3.2749999999999999</v>
+        <v>8.0250000000000004</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>3.0750000000000002</v>
+        <v>6.5750000000000002</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>4.4000000000000004</v>
+        <v>8.9</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>7.1749999999999998</v>
+        <v>10.175000000000001</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>3.875</v>
+        <v>7.375</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>7.8250000000000002</v>
+        <v>12.324999999999999</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>29.625</v>
+        <v>53.375</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -23897,7 +23908,7 @@
     <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="14"/>
       <c r="B8" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
@@ -23914,7 +23925,7 @@
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O8" s="11"/>
       <c r="P8" s="11"/>
@@ -23946,7 +23957,7 @@
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
@@ -23963,7 +23974,7 @@
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O9" s="11"/>
       <c r="P9" s="11"/>
@@ -23995,7 +24006,7 @@
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
@@ -24012,7 +24023,7 @@
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
@@ -24044,7 +24055,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -24061,7 +24072,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -24093,7 +24104,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -24110,7 +24121,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -24182,7 +24193,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -24199,7 +24210,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -24220,7 +24231,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -24237,7 +24248,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -24258,7 +24269,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -24275,7 +24286,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -24337,7 +24348,7 @@
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A18" s="16"/>
       <c r="B18" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
@@ -24351,7 +24362,7 @@
       <c r="L18" s="13"/>
       <c r="M18" s="16"/>
       <c r="N18" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O18" s="11"/>
       <c r="P18" s="11">
@@ -24386,7 +24397,7 @@
     <row r="19" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A19" s="16"/>
       <c r="B19" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
@@ -24400,7 +24411,7 @@
       <c r="L19" s="13"/>
       <c r="M19" s="16"/>
       <c r="N19" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O19" s="11"/>
       <c r="P19" s="11"/>
@@ -24418,7 +24429,7 @@
     <row r="20" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A20" s="16"/>
       <c r="B20" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
@@ -24432,7 +24443,7 @@
       <c r="L20" s="13"/>
       <c r="M20" s="16"/>
       <c r="N20" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O20" s="11"/>
       <c r="P20" s="11"/>
@@ -24917,7 +24928,7 @@
     <row r="7" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A7" s="14"/>
       <c r="B7" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" s="11"/>
       <c r="D7" s="11">
@@ -24948,7 +24959,7 @@
       <c r="L7" s="13"/>
       <c r="M7" s="14"/>
       <c r="N7" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O7" s="11"/>
       <c r="P7" s="11">
@@ -24992,7 +25003,7 @@
     <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="14"/>
       <c r="B8" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11">
@@ -25023,7 +25034,7 @@
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O8" s="11"/>
       <c r="P8" s="11">
@@ -25067,7 +25078,7 @@
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11">
@@ -25098,7 +25109,7 @@
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O9" s="11"/>
       <c r="P9" s="11">
@@ -25217,7 +25228,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
@@ -25248,7 +25259,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11">
@@ -25335,7 +25346,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -25352,7 +25363,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -25373,7 +25384,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -25390,7 +25401,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -25411,7 +25422,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -25428,7 +25439,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -25449,7 +25460,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -25465,7 +25476,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -25483,7 +25494,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -25499,7 +25510,7 @@
       <c r="L17" s="13"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -25517,7 +25528,7 @@
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A18" s="16"/>
       <c r="B18" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
@@ -25533,7 +25544,7 @@
       <c r="L18" s="13"/>
       <c r="M18" s="16"/>
       <c r="N18" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O18" s="11"/>
       <c r="P18" s="11"/>
@@ -26047,14 +26058,14 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="15">
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="74">
         <f>SUM(C8:I8)/40</f>
         <v>0</v>
       </c>
@@ -26064,18 +26075,16 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11">
-        <v>84</v>
-      </c>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
-      <c r="V8" s="15">
+      <c r="O8" s="43"/>
+      <c r="P8" s="43"/>
+      <c r="Q8" s="43"/>
+      <c r="R8" s="43"/>
+      <c r="S8" s="43"/>
+      <c r="T8" s="43"/>
+      <c r="U8" s="43"/>
+      <c r="V8" s="74">
         <f>SUM(O8:U8)/40</f>
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="W8" s="12">
         <v>12</v>
@@ -26086,11 +26095,11 @@
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>-2.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -26098,14 +26107,14 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="15">
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="74">
         <f>SUM(C9:I9)/40</f>
         <v>0</v>
       </c>
@@ -26115,14 +26124,14 @@
       <c r="N9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
-      <c r="V9" s="15">
+      <c r="O9" s="43"/>
+      <c r="P9" s="43"/>
+      <c r="Q9" s="43"/>
+      <c r="R9" s="43"/>
+      <c r="S9" s="43"/>
+      <c r="T9" s="43"/>
+      <c r="U9" s="43"/>
+      <c r="V9" s="74">
         <f t="shared" ref="V9:V16" si="0">SUM(O9:U9)/40</f>
         <v>0</v>
       </c>
@@ -26147,14 +26156,14 @@
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="15">
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="74">
         <f t="shared" ref="J10:J17" si="4">SUM(C10:I10)/40</f>
         <v>0</v>
       </c>
@@ -26164,14 +26173,14 @@
       <c r="N10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
-      <c r="V10" s="15">
+      <c r="O10" s="43"/>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="43"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="43"/>
+      <c r="T10" s="43"/>
+      <c r="U10" s="43"/>
+      <c r="V10" s="74">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -26194,16 +26203,16 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="15">
+        <v>29</v>
+      </c>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="74">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -26211,16 +26220,16 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
-      <c r="V11" s="15">
+        <v>29</v>
+      </c>
+      <c r="O11" s="43"/>
+      <c r="P11" s="43"/>
+      <c r="Q11" s="43"/>
+      <c r="R11" s="43"/>
+      <c r="S11" s="43"/>
+      <c r="T11" s="43"/>
+      <c r="U11" s="43"/>
+      <c r="V11" s="74">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -26243,16 +26252,16 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="15">
+        <v>28</v>
+      </c>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="74">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -26260,16 +26269,16 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="15">
+        <v>28</v>
+      </c>
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="43"/>
+      <c r="V12" s="74">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -26292,16 +26301,16 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="15">
+        <v>44</v>
+      </c>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="74">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -26309,16 +26318,16 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="15">
+        <v>44</v>
+      </c>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="43"/>
+      <c r="T13" s="43"/>
+      <c r="U13" s="43"/>
+      <c r="V13" s="74">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -26334,14 +26343,14 @@
       <c r="B14" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="15">
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="74">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -26351,14 +26360,14 @@
       <c r="N14" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="15">
+      <c r="O14" s="43"/>
+      <c r="P14" s="43"/>
+      <c r="Q14" s="43"/>
+      <c r="R14" s="43"/>
+      <c r="S14" s="43"/>
+      <c r="T14" s="43"/>
+      <c r="U14" s="43"/>
+      <c r="V14" s="74">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -26370,16 +26379,16 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="15">
+        <v>35</v>
+      </c>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="74">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -26387,16 +26396,16 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="11"/>
-      <c r="S15" s="11"/>
-      <c r="T15" s="11"/>
-      <c r="U15" s="11"/>
-      <c r="V15" s="15">
+        <v>35</v>
+      </c>
+      <c r="O15" s="43"/>
+      <c r="P15" s="43"/>
+      <c r="Q15" s="43"/>
+      <c r="R15" s="43"/>
+      <c r="S15" s="43"/>
+      <c r="T15" s="43"/>
+      <c r="U15" s="43"/>
+      <c r="V15" s="74">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -26408,16 +26417,16 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="15">
+        <v>36</v>
+      </c>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="74">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -26425,16 +26434,16 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="15">
+        <v>36</v>
+      </c>
+      <c r="O16" s="43"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="43"/>
+      <c r="R16" s="43"/>
+      <c r="S16" s="43"/>
+      <c r="T16" s="43"/>
+      <c r="U16" s="43"/>
+      <c r="V16" s="74">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -26446,32 +26455,32 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="15">
+        <v>38</v>
+      </c>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="74">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
-      <c r="S17" s="11"/>
-      <c r="T17" s="11"/>
-      <c r="U17" s="11"/>
-      <c r="V17" s="15"/>
+        <v>38</v>
+      </c>
+      <c r="O17" s="43"/>
+      <c r="P17" s="43"/>
+      <c r="Q17" s="43"/>
+      <c r="R17" s="43"/>
+      <c r="S17" s="43"/>
+      <c r="T17" s="43"/>
+      <c r="U17" s="43"/>
+      <c r="V17" s="74"/>
       <c r="W17" s="18"/>
       <c r="Y17" s="36">
         <f t="shared" si="1"/>
@@ -26526,7 +26535,7 @@
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
@@ -26554,7 +26563,7 @@
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -26563,11 +26572,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>-2.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -26614,7 +26623,7 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
@@ -26642,7 +26651,7 @@
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -26651,11 +26660,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>5.2500000000000005E-2</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>-5.2500000000000005E-2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -26678,7 +26687,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.36328125" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="4.08984375" bestFit="1" customWidth="1"/>
@@ -26955,49 +26964,73 @@
         <v>13</v>
       </c>
       <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="54"/>
+      <c r="D8" s="54">
+        <v>80</v>
+      </c>
+      <c r="E8" s="54">
+        <v>40</v>
+      </c>
+      <c r="F8" s="54">
+        <v>120</v>
+      </c>
+      <c r="G8" s="54">
+        <v>159</v>
+      </c>
+      <c r="H8" s="54">
+        <v>83</v>
+      </c>
+      <c r="I8" s="54">
+        <v>193</v>
+      </c>
       <c r="J8" s="58">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="55"/>
+        <v>16.875</v>
+      </c>
+      <c r="K8" s="55">
+        <v>14</v>
+      </c>
       <c r="L8" s="56"/>
       <c r="M8" s="14"/>
       <c r="N8" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11">
+      <c r="O8" s="11"/>
+      <c r="P8" s="11">
         <v>40</v>
       </c>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="Q8" s="11">
+        <v>40</v>
+      </c>
+      <c r="R8" s="11">
+        <v>40</v>
+      </c>
+      <c r="S8" s="11">
+        <v>119</v>
+      </c>
+      <c r="T8" s="11">
+        <v>83</v>
+      </c>
+      <c r="U8" s="11">
+        <v>113</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>1</v>
+        <v>10.875</v>
       </c>
       <c r="W8" s="12">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>16.875</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>1</v>
+        <v>10.875</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -27006,47 +27039,73 @@
         <v>14</v>
       </c>
       <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="54"/>
+      <c r="D9" s="54">
+        <v>0</v>
+      </c>
+      <c r="E9" s="54">
+        <v>20</v>
+      </c>
+      <c r="F9" s="54">
+        <v>20</v>
+      </c>
+      <c r="G9" s="54">
+        <v>150</v>
+      </c>
+      <c r="H9" s="54">
+        <v>60</v>
+      </c>
+      <c r="I9" s="54">
+        <v>95</v>
+      </c>
       <c r="J9" s="58">
-        <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="55"/>
+        <f t="shared" ref="J9:J15" si="0">SUM(C9:I9)/40</f>
+        <v>8.625</v>
+      </c>
+      <c r="K9" s="55">
+        <v>6</v>
+      </c>
       <c r="L9" s="56"/>
       <c r="M9" s="14"/>
       <c r="N9" s="50" t="s">
         <v>14</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>0</v>
+      </c>
+      <c r="R9" s="11">
+        <v>0</v>
+      </c>
+      <c r="S9" s="11">
+        <v>134</v>
+      </c>
+      <c r="T9" s="11">
+        <v>45</v>
+      </c>
+      <c r="U9" s="11">
+        <v>85</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="W9" s="12">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>0</v>
+        <v>8.625</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>2.0250000000000004</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -27055,151 +27114,229 @@
         <v>15</v>
       </c>
       <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
+      <c r="D10" s="54">
+        <v>0</v>
+      </c>
+      <c r="E10" s="54">
+        <v>0</v>
+      </c>
+      <c r="F10" s="54">
+        <v>0</v>
+      </c>
+      <c r="G10" s="54">
+        <v>20</v>
+      </c>
+      <c r="H10" s="54">
+        <v>60</v>
+      </c>
+      <c r="I10" s="54">
+        <v>120</v>
+      </c>
       <c r="J10" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="55"/>
+        <v>5</v>
+      </c>
+      <c r="K10" s="55">
+        <v>4</v>
+      </c>
       <c r="L10" s="56"/>
       <c r="M10" s="14"/>
       <c r="N10" s="50" t="s">
         <v>15</v>
       </c>
       <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="P10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <v>0</v>
+      </c>
+      <c r="T10" s="11">
+        <v>60</v>
+      </c>
+      <c r="U10" s="11">
+        <v>110</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="W10" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="59"/>
       <c r="B11" s="60" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
+      <c r="D11" s="54">
+        <v>46</v>
+      </c>
+      <c r="E11" s="54">
+        <v>6</v>
+      </c>
+      <c r="F11" s="54">
+        <v>6</v>
+      </c>
+      <c r="G11" s="54">
+        <v>86</v>
+      </c>
+      <c r="H11" s="54">
+        <v>6</v>
+      </c>
+      <c r="I11" s="54">
+        <v>86</v>
+      </c>
       <c r="J11" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="55"/>
+        <v>5.9</v>
+      </c>
+      <c r="K11" s="55">
+        <v>4</v>
+      </c>
       <c r="L11" s="56"/>
       <c r="M11" s="16"/>
       <c r="N11" s="60" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>40</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>0</v>
+      </c>
+      <c r="R11" s="11">
+        <v>0</v>
+      </c>
+      <c r="S11" s="11">
+        <v>40</v>
+      </c>
+      <c r="T11" s="11">
+        <v>0</v>
+      </c>
+      <c r="U11" s="11">
+        <v>40</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W11" s="12">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.9000000000000004</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="59"/>
       <c r="B12" s="60" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
+      <c r="D12" s="54">
+        <v>40</v>
+      </c>
+      <c r="E12" s="54">
+        <v>56</v>
+      </c>
+      <c r="F12" s="54">
+        <v>100</v>
+      </c>
+      <c r="G12" s="54">
+        <v>16</v>
+      </c>
+      <c r="H12" s="54">
+        <v>10</v>
+      </c>
+      <c r="I12" s="54">
+        <v>6</v>
+      </c>
       <c r="J12" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="55"/>
+        <v>5.7</v>
+      </c>
+      <c r="K12" s="55">
+        <v>7</v>
+      </c>
       <c r="L12" s="56"/>
       <c r="M12" s="16"/>
       <c r="N12" s="60" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>40</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>50</v>
+      </c>
+      <c r="R12" s="11">
+        <v>82</v>
+      </c>
+      <c r="S12" s="11">
+        <v>10</v>
+      </c>
+      <c r="T12" s="11">
+        <v>10</v>
+      </c>
+      <c r="U12" s="11">
+        <v>6</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="W12" s="12">
         <v>6</v>
       </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="59"/>
       <c r="B13" s="60" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="54"/>
       <c r="D13" s="54"/>
@@ -27216,7 +27353,7 @@
       <c r="L13" s="56"/>
       <c r="M13" s="16"/>
       <c r="N13" s="60" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -27275,7 +27412,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="59"/>
       <c r="B15" s="60" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="54"/>
       <c r="D15" s="54"/>
@@ -27292,7 +27429,7 @@
       <c r="L15" s="56"/>
       <c r="M15" s="16"/>
       <c r="N15" s="60" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -27313,7 +27450,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="59"/>
       <c r="B16" s="60" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="54"/>
       <c r="D16" s="54"/>
@@ -27323,14 +27460,15 @@
       <c r="H16" s="54"/>
       <c r="I16" s="54"/>
       <c r="J16" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="55"/>
+        <v>28</v>
+      </c>
+      <c r="K16" s="55">
+        <v>22</v>
+      </c>
       <c r="L16" s="56"/>
       <c r="M16" s="16"/>
       <c r="N16" s="60" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -27351,7 +27489,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="59"/>
       <c r="B17" s="60" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="54"/>
       <c r="D17" s="54"/>
@@ -27361,14 +27499,15 @@
       <c r="H17" s="54"/>
       <c r="I17" s="54"/>
       <c r="J17" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="61"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="61">
+        <v>0</v>
+      </c>
       <c r="L17" s="44"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -27401,31 +27540,31 @@
       </c>
       <c r="D18" s="62">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="E18" s="62">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="F18" s="62">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="G18" s="62">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>431</v>
       </c>
       <c r="H18" s="62">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="I18" s="62">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J18" s="63">
         <f>SUM(C18:I18)</f>
-        <v>0</v>
+        <v>1684</v>
       </c>
       <c r="K18" s="64"/>
       <c r="L18" s="44"/>
@@ -27433,48 +27572,48 @@
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>354</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>40</v>
+        <v>1187</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>0</v>
+        <v>42.1</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>1</v>
+        <v>29.675000000000001</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>-1</v>
+        <v>12.425000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -27488,31 +27627,31 @@
       </c>
       <c r="D19" s="66">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="E19" s="66">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="F19" s="66">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="G19" s="66">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10.775</v>
       </c>
       <c r="H19" s="66">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5.4749999999999996</v>
       </c>
       <c r="I19" s="66">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="J19" s="67">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>42.1</v>
       </c>
       <c r="K19" s="68"/>
       <c r="L19" s="44"/>
@@ -27522,48 +27661,48 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7.5750000000000002</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>29.675000000000001</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0</v>
+        <v>1.0525</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>2.5000000000000001E-2</v>
+        <v>0.74187500000000006</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>-2.5000000000000001E-2</v>
+        <v>0.31062500000000004</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.35">
@@ -28004,7 +28143,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -28021,7 +28160,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -28051,7 +28190,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -28066,11 +28205,9 @@
       </c>
       <c r="K12" s="12"/>
       <c r="L12" s="13"/>
-      <c r="M12" s="16" t="s">
+      <c r="M12" s="16"/>
+      <c r="N12" s="17" t="s">
         <v>28</v>
-      </c>
-      <c r="N12" s="17" t="s">
-        <v>29</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -28100,7 +28237,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -28117,7 +28254,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -28176,7 +28313,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -28193,7 +28330,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -28214,7 +28351,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -28231,7 +28368,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -28252,7 +28389,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -28268,7 +28405,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -28890,7 +29027,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -28907,7 +29044,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -28937,7 +29074,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -28953,7 +29090,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -28983,7 +29120,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -29000,7 +29137,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -29058,7 +29195,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -29074,7 +29211,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -29095,7 +29232,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -29111,7 +29248,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -29132,7 +29269,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -29147,7 +29284,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -29775,7 +29912,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -29792,7 +29929,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -29824,7 +29961,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -29841,7 +29978,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -29873,7 +30010,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -29890,7 +30027,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -29950,7 +30087,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -29966,7 +30103,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -29987,7 +30124,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -30003,7 +30140,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -30024,7 +30161,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -30039,7 +30176,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -30665,7 +30802,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -30682,7 +30819,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -30714,7 +30851,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -30731,7 +30868,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -30763,7 +30900,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -30779,7 +30916,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -30839,7 +30976,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -30855,7 +30992,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -30876,7 +31013,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -30892,7 +31029,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -30913,7 +31050,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -30928,7 +31065,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -31126,7 +31263,7 @@
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.35">
       <c r="J22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191EA1A0-EE1D-4DC2-8AC8-2CC6BB7E6438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460104B6-2C26-45A9-9247-92C7FD84C063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="4" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="5" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -28005,41 +28005,69 @@
         <v>13</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="D8" s="11">
+        <v>100</v>
+      </c>
+      <c r="E8" s="11">
+        <v>50</v>
+      </c>
+      <c r="F8" s="11">
+        <v>130</v>
+      </c>
+      <c r="G8" s="11">
+        <v>125</v>
+      </c>
+      <c r="H8" s="11">
+        <v>90</v>
+      </c>
+      <c r="I8" s="11">
+        <v>220</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>17.875</v>
+      </c>
+      <c r="K8" s="12">
+        <v>9</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>100</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>50</v>
+      </c>
+      <c r="R8" s="11">
+        <v>130</v>
+      </c>
+      <c r="S8" s="11">
+        <v>125</v>
+      </c>
+      <c r="T8" s="11">
+        <v>90</v>
+      </c>
+      <c r="U8" s="11">
+        <v>220</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>17.875</v>
+      </c>
+      <c r="W8" s="12">
+        <v>9</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>17.875</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>17.875</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
@@ -28052,41 +28080,69 @@
         <v>14</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="D9" s="11">
+        <v>8</v>
+      </c>
+      <c r="E9" s="11">
+        <v>28</v>
+      </c>
+      <c r="F9" s="11">
+        <v>28</v>
+      </c>
+      <c r="G9" s="11">
+        <v>25</v>
+      </c>
+      <c r="H9" s="11">
+        <v>55</v>
+      </c>
+      <c r="I9" s="11">
+        <v>60</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="K9" s="12">
+        <v>5</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
         <v>14</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>8</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>28</v>
+      </c>
+      <c r="R9" s="11">
+        <v>28</v>
+      </c>
+      <c r="S9" s="11">
+        <v>25</v>
+      </c>
+      <c r="T9" s="11">
+        <v>55</v>
+      </c>
+      <c r="U9" s="11">
+        <v>60</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V17" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="W9" s="12">
+        <v>5</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>0</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
@@ -28099,45 +28155,73 @@
         <v>15</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="D10" s="11">
+        <v>19</v>
+      </c>
+      <c r="E10" s="11">
+        <v>33</v>
+      </c>
+      <c r="F10" s="11">
+        <v>36</v>
+      </c>
+      <c r="G10" s="11">
+        <v>65</v>
+      </c>
+      <c r="H10" s="11">
+        <v>55</v>
+      </c>
+      <c r="I10" s="11">
+        <v>90</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>7.45</v>
+      </c>
+      <c r="K10" s="12">
+        <v>8</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
         <v>15</v>
       </c>
       <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="P10" s="11">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>15</v>
+      </c>
+      <c r="R10" s="11">
+        <v>15</v>
+      </c>
+      <c r="S10" s="11">
+        <v>25</v>
+      </c>
+      <c r="T10" s="11">
+        <v>25</v>
+      </c>
+      <c r="U10" s="11">
+        <v>70</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>4</v>
+      </c>
+      <c r="W10" s="12">
+        <v>4</v>
+      </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.45</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -28146,45 +28230,73 @@
         <v>29</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="D11" s="11">
+        <v>45</v>
+      </c>
+      <c r="E11" s="11">
+        <v>55</v>
+      </c>
+      <c r="F11" s="11">
+        <v>40</v>
+      </c>
+      <c r="G11" s="11">
+        <v>105</v>
+      </c>
+      <c r="H11" s="11">
+        <v>95</v>
+      </c>
+      <c r="I11" s="11">
+        <v>102</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>11.05</v>
+      </c>
+      <c r="K11" s="12">
+        <v>7</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
         <v>29</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>15</v>
+      </c>
+      <c r="R11" s="11">
+        <v>0</v>
+      </c>
+      <c r="S11" s="11">
+        <v>65</v>
+      </c>
+      <c r="T11" s="11">
+        <v>65</v>
+      </c>
+      <c r="U11" s="11">
+        <v>52</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>5.05</v>
+      </c>
+      <c r="W11" s="12">
+        <v>6</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11.05</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.0000000000000009</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -28193,45 +28305,73 @@
         <v>28</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="D12" s="11">
+        <v>29</v>
+      </c>
+      <c r="E12" s="11">
+        <v>24</v>
+      </c>
+      <c r="F12" s="11">
+        <v>63</v>
+      </c>
+      <c r="G12" s="11">
+        <v>45</v>
+      </c>
+      <c r="H12" s="11">
+        <v>40</v>
+      </c>
+      <c r="I12" s="11">
+        <v>59</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>6.5</v>
+      </c>
+      <c r="K12" s="12">
+        <v>9</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
         <v>28</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>29</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>24</v>
+      </c>
+      <c r="R12" s="11">
+        <v>54</v>
+      </c>
+      <c r="S12" s="11">
+        <v>34</v>
+      </c>
+      <c r="T12" s="11">
+        <v>30</v>
+      </c>
+      <c r="U12" s="11">
+        <v>35</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>5.15</v>
+      </c>
+      <c r="W12" s="12">
+        <v>7</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.3499999999999996</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -28443,31 +28583,31 @@
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>297</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>365</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>335</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>0</v>
+        <v>1919</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
@@ -28478,44 +28618,44 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>274</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>437</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>1487</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>0</v>
+        <v>47.975000000000001</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>37.174999999999997</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>0</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -28529,31 +28669,31 @@
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5.0250000000000004</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>7.4249999999999998</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9.125</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>8.375</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>13.275</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>47.975000000000001</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -28566,44 +28706,44 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5.6749999999999998</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6.625</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>10.925000000000001</v>
       </c>
       <c r="V19" s="69">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>37.174999999999997</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0</v>
+        <v>1.1993750000000001</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>0.92937499999999995</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0</v>
+        <v>0.27</v>
       </c>
     </row>
   </sheetData>
@@ -28937,17 +29077,31 @@
         <v>14</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="D9" s="11">
+        <v>63</v>
+      </c>
+      <c r="E9" s="11">
+        <v>62</v>
+      </c>
+      <c r="F9" s="11">
+        <v>75</v>
+      </c>
+      <c r="G9" s="11">
+        <v>50</v>
+      </c>
+      <c r="H9" s="11">
+        <v>50</v>
+      </c>
+      <c r="I9" s="11">
+        <v>60</v>
+      </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J13" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)</f>
+        <v>360</v>
+      </c>
+      <c r="K9" s="12">
+        <v>4</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -28967,7 +29121,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
@@ -28975,7 +29129,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -28991,7 +29145,8 @@
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
       <c r="J10" s="15">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="K10" s="12"/>
       <c r="L10" s="13"/>
@@ -29013,7 +29168,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -29021,7 +29176,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -29030,17 +29185,31 @@
         <v>29</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="D11" s="11">
+        <v>13</v>
+      </c>
+      <c r="E11" s="11">
+        <v>13</v>
+      </c>
+      <c r="F11" s="11">
+        <v>14</v>
+      </c>
+      <c r="G11" s="11">
+        <v>78</v>
+      </c>
+      <c r="H11" s="11">
+        <v>78</v>
+      </c>
+      <c r="I11" s="11">
+        <v>84</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>280</v>
+      </c>
+      <c r="K11" s="12">
+        <v>6</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -29060,7 +29229,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -29068,7 +29237,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -29077,16 +29246,31 @@
         <v>28</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="D12" s="11">
+        <v>33</v>
+      </c>
+      <c r="E12" s="11">
+        <v>40</v>
+      </c>
+      <c r="F12" s="11">
+        <v>50</v>
+      </c>
+      <c r="G12" s="11">
+        <v>25</v>
+      </c>
+      <c r="H12" s="11">
+        <v>20</v>
+      </c>
+      <c r="I12" s="11">
+        <v>22</v>
+      </c>
       <c r="J12" s="15">
-        <v>5</v>
-      </c>
-      <c r="K12" s="12"/>
+        <f t="shared" si="0"/>
+        <v>190</v>
+      </c>
+      <c r="K12" s="12">
+        <v>7</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
@@ -29106,7 +29290,7 @@
       <c r="W12" s="12"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>190</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
@@ -29114,7 +29298,7 @@
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -29168,7 +29352,8 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
       <c r="J14" s="15">
-        <v>12</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="K14" s="12"/>
       <c r="L14" s="13"/>
@@ -29205,7 +29390,8 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="15">
-        <v>20</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="K15" s="12"/>
       <c r="L15" s="13"/>
@@ -29242,7 +29428,8 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="15">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="K16" s="12"/>
       <c r="L16" s="13"/>
@@ -29279,7 +29466,8 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
       <c r="J17" s="15">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
@@ -29300,7 +29488,7 @@
       <c r="W17" s="18"/>
       <c r="Y17" s="36">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="37">
         <f t="shared" si="3"/>
@@ -29308,7 +29496,7 @@
       </c>
       <c r="AA17" s="38">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
@@ -29320,31 +29508,31 @@
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>0</v>
+        <v>830</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
@@ -29384,7 +29572,7 @@
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>16</v>
+        <v>830</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
@@ -29392,7 +29580,7 @@
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>16</v>
+        <v>830</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -29406,31 +29594,31 @@
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.7250000000000001</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.875</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3.4750000000000001</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3.8250000000000002</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="J19" s="22">
         <f>SUM(J8:J16)</f>
-        <v>48</v>
+        <v>830</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -29472,7 +29660,7 @@
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0.4</v>
+        <v>20.75</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
@@ -29480,7 +29668,7 @@
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.4</v>
+        <v>20.75</v>
       </c>
     </row>
   </sheetData>

--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460104B6-2C26-45A9-9247-92C7FD84C063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{018414C3-7580-47FC-A3B1-B40962F0E182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="5" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="2" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="47">
   <si>
     <t>Booking</t>
   </si>
@@ -190,6 +190,12 @@
   </si>
   <si>
     <t xml:space="preserve">Aqib </t>
+  </si>
+  <si>
+    <t>KasoorSD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalal Sons </t>
   </si>
 </sst>
 </file>
@@ -23432,15 +23438,27 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
-      <c r="S17" s="11"/>
-      <c r="T17" s="11"/>
-      <c r="U17" s="11"/>
+      <c r="P17" s="11">
+        <v>199</v>
+      </c>
+      <c r="Q17" s="11">
+        <v>120</v>
+      </c>
+      <c r="R17" s="11">
+        <v>280</v>
+      </c>
+      <c r="S17" s="11">
+        <v>280</v>
+      </c>
+      <c r="T17" s="11">
+        <v>240</v>
+      </c>
+      <c r="U17" s="11">
+        <v>480</v>
+      </c>
       <c r="V17" s="15"/>
       <c r="W17" s="18"/>
       <c r="Y17" s="36">
@@ -23500,31 +23518,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>321</v>
+        <v>520</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>263</v>
+        <v>383</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>356</v>
+        <v>636</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>407</v>
+        <v>687</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>295</v>
+        <v>535</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>493</v>
+        <v>973</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>2135</v>
+        <v>3734</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -23588,31 +23606,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>8.0250000000000004</v>
+        <v>13</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>6.5750000000000002</v>
+        <v>9.5749999999999993</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>8.9</v>
+        <v>15.9</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>10.175000000000001</v>
+        <v>17.175000000000001</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>7.375</v>
+        <v>13.375</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>12.324999999999999</v>
+        <v>24.324999999999999</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>53.375</v>
+        <v>93.35</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -27751,7 +27769,7 @@
     <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="3.26953125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="3.6328125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="3.54296875" bestFit="1" customWidth="1"/>
@@ -28394,20 +28412,30 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="R13" s="11">
+        <v>600</v>
+      </c>
+      <c r="S13" s="11">
+        <v>800</v>
+      </c>
+      <c r="T13" s="11">
+        <v>1200</v>
+      </c>
+      <c r="U13" s="11">
+        <v>1000</v>
+      </c>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12"/>
+        <v>90</v>
+      </c>
+      <c r="W13" s="12">
+        <v>1</v>
+      </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -28435,17 +28463,31 @@
         <v>17</v>
       </c>
       <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
+      <c r="P14" s="11">
+        <v>120</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>160</v>
+      </c>
+      <c r="R14" s="11">
+        <v>480</v>
+      </c>
+      <c r="S14" s="11">
+        <v>320</v>
+      </c>
+      <c r="T14" s="11">
+        <v>440</v>
+      </c>
+      <c r="U14" s="11">
+        <v>560</v>
+      </c>
       <c r="V14" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="12"/>
+        <v>52</v>
+      </c>
+      <c r="W14" s="12">
+        <v>4</v>
+      </c>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
       <c r="AA14" s="38"/>
@@ -28545,21 +28587,33 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
-      <c r="S17" s="11"/>
-      <c r="T17" s="11"/>
-      <c r="U17" s="11"/>
+      <c r="P17" s="11">
+        <v>199</v>
+      </c>
+      <c r="Q17" s="11">
+        <v>120</v>
+      </c>
+      <c r="R17" s="11">
+        <v>280</v>
+      </c>
+      <c r="S17" s="11">
+        <v>280</v>
+      </c>
+      <c r="T17" s="11">
+        <v>240</v>
+      </c>
+      <c r="U17" s="11">
+        <v>480</v>
+      </c>
       <c r="V17" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>39.975000000000001</v>
       </c>
       <c r="W17" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y17" s="36">
         <f t="shared" si="2"/>
@@ -28567,11 +28621,11 @@
       </c>
       <c r="Z17" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>39.975000000000001</v>
       </c>
       <c r="AA17" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-39.975000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
@@ -28618,31 +28672,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>152</v>
+        <v>471</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>132</v>
+        <v>412</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>227</v>
+        <v>1587</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>274</v>
+        <v>1674</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>265</v>
+        <v>2145</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>437</v>
+        <v>2477</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>1487</v>
+        <v>8766</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -28651,11 +28705,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>37.174999999999997</v>
+        <v>77.150000000000006</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>10.8</v>
+        <v>-29.175000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -28706,31 +28760,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>3.8</v>
+        <v>11.775</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>3.3</v>
+        <v>10.3</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>5.6749999999999998</v>
+        <v>39.674999999999997</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>6.85</v>
+        <v>41.85</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>6.625</v>
+        <v>53.625</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>10.925000000000001</v>
+        <v>61.924999999999997</v>
       </c>
       <c r="V19" s="69">
         <f t="shared" si="8"/>
-        <v>37.174999999999997</v>
+        <v>219.15</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -28739,11 +28793,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0.92937499999999995</v>
+        <v>1.9287500000000002</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.27</v>
+        <v>-0.729375</v>
       </c>
     </row>
   </sheetData>
@@ -29030,17 +29084,31 @@
         <v>13</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="D8" s="11">
+        <v>30</v>
+      </c>
+      <c r="E8" s="11">
+        <v>20</v>
+      </c>
+      <c r="F8" s="11">
+        <v>70</v>
+      </c>
+      <c r="G8" s="11">
+        <v>50</v>
+      </c>
+      <c r="H8" s="11">
+        <v>40</v>
+      </c>
+      <c r="I8" s="11">
+        <v>70</v>
+      </c>
       <c r="J8" s="15">
-        <f>SUM(C8:I8)</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <f>SUM(C8:I8)/40</f>
+        <v>7</v>
+      </c>
+      <c r="K8" s="12">
+        <v>11</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -29060,7 +29128,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -29068,7 +29136,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -29096,8 +29164,8 @@
         <v>60</v>
       </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)</f>
-        <v>360</v>
+        <f t="shared" ref="J9:J14" si="0">SUM(C9:I9)/40</f>
+        <v>9</v>
       </c>
       <c r="K9" s="12">
         <v>4</v>
@@ -29121,7 +29189,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>360</v>
+        <v>9</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
@@ -29129,7 +29197,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>360</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -29138,12 +29206,12 @@
         <v>15</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -29205,7 +29273,7 @@
       </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>280</v>
+        <v>7</v>
       </c>
       <c r="K11" s="12">
         <v>6</v>
@@ -29229,7 +29297,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>280</v>
+        <v>7</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -29237,7 +29305,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>280</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -29266,7 +29334,7 @@
       </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>190</v>
+        <v>4.75</v>
       </c>
       <c r="K12" s="12">
         <v>7</v>
@@ -29290,7 +29358,7 @@
       <c r="W12" s="12"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>190</v>
+        <v>4.75</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
@@ -29298,7 +29366,7 @@
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>190</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -29345,17 +29413,31 @@
         <v>17</v>
       </c>
       <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
+      <c r="D14" s="11">
+        <v>360</v>
+      </c>
+      <c r="E14" s="11">
+        <v>440</v>
+      </c>
+      <c r="F14" s="11">
+        <v>640</v>
+      </c>
+      <c r="G14" s="11">
+        <v>840</v>
+      </c>
+      <c r="H14" s="11">
+        <v>880</v>
+      </c>
+      <c r="I14" s="11">
+        <v>1120</v>
+      </c>
       <c r="J14" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="12"/>
+        <v>107</v>
+      </c>
+      <c r="K14" s="12">
+        <v>5</v>
+      </c>
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
@@ -29390,10 +29472,11 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="12"/>
+        <v>8</v>
+      </c>
+      <c r="K15" s="12">
+        <v>10</v>
+      </c>
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
@@ -29428,10 +29511,11 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="K16" s="12">
+        <v>8</v>
+      </c>
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
@@ -29466,10 +29550,11 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
       <c r="J17" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="18"/>
+        <v>5</v>
+      </c>
+      <c r="K17" s="18">
+        <v>7</v>
+      </c>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
         <v>38</v>
@@ -29488,7 +29573,7 @@
       <c r="W17" s="18"/>
       <c r="Y17" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z17" s="37">
         <f t="shared" si="3"/>
@@ -29496,7 +29581,7 @@
       </c>
       <c r="AA17" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
@@ -29508,31 +29593,31 @@
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>109</v>
+        <v>499</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>115</v>
+        <v>575</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>139</v>
+        <v>849</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>153</v>
+        <v>1043</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>148</v>
+        <v>1068</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>166</v>
+        <v>1356</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>830</v>
+        <v>5390</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
@@ -29572,7 +29657,7 @@
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>830</v>
+        <v>32.75</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
@@ -29580,7 +29665,7 @@
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>830</v>
+        <v>32.75</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -29594,31 +29679,31 @@
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>2.7250000000000001</v>
+        <v>12.475</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>2.875</v>
+        <v>14.375</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>3.4750000000000001</v>
+        <v>21.225000000000001</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>3.8250000000000002</v>
+        <v>26.074999999999999</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>3.7</v>
+        <v>26.7</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>4.1500000000000004</v>
+        <v>33.9</v>
       </c>
       <c r="J19" s="22">
         <f>SUM(J8:J16)</f>
-        <v>830</v>
+        <v>149.75</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -29660,7 +29745,7 @@
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>20.75</v>
+        <v>0.81874999999999998</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
@@ -29668,7 +29753,7 @@
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>20.75</v>
+        <v>0.81874999999999998</v>
       </c>
     </row>
   </sheetData>

--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{018414C3-7580-47FC-A3B1-B40962F0E182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B20C42-2C3C-4031-AD4F-B0B0B3A2BB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="2" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="6" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1707" uniqueCount="49">
   <si>
     <t>Booking</t>
   </si>
@@ -196,6 +196,12 @@
   </si>
   <si>
     <t xml:space="preserve">Jalal Sons </t>
+  </si>
+  <si>
+    <t>C102609154</t>
+  </si>
+  <si>
+    <t>C102609155</t>
   </si>
 </sst>
 </file>
@@ -28861,6 +28867,9 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
+      <c r="X1" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
@@ -28887,6 +28896,9 @@
       <c r="T2" s="77"/>
       <c r="U2" s="77"/>
       <c r="V2" s="77"/>
+      <c r="X2" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
@@ -29115,28 +29127,42 @@
         <v>13</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>30</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>20</v>
+      </c>
+      <c r="R8" s="11">
+        <v>70</v>
+      </c>
+      <c r="S8" s="11">
+        <v>50</v>
+      </c>
+      <c r="T8" s="11">
+        <v>40</v>
+      </c>
+      <c r="U8" s="11">
+        <v>70</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="W8" s="12">
+        <v>11</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>7</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -29176,28 +29202,42 @@
         <v>14</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>18</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>17</v>
+      </c>
+      <c r="R9" s="11">
+        <v>25</v>
+      </c>
+      <c r="S9" s="11">
+        <v>10</v>
+      </c>
+      <c r="T9" s="11">
+        <v>10</v>
+      </c>
+      <c r="U9" s="11">
+        <v>20</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V17" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>2.5</v>
+      </c>
+      <c r="W9" s="12">
+        <v>3</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
         <v>9</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -29284,28 +29324,42 @@
         <v>29</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>13</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>13</v>
+      </c>
+      <c r="R11" s="11">
+        <v>14</v>
+      </c>
+      <c r="S11" s="11">
+        <v>52</v>
+      </c>
+      <c r="T11" s="11">
+        <v>52</v>
+      </c>
+      <c r="U11" s="11">
+        <v>56</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>5</v>
+      </c>
+      <c r="W11" s="12">
+        <v>4</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -29345,28 +29399,42 @@
         <v>28</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>14</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>26</v>
+      </c>
+      <c r="R12" s="11">
+        <v>31</v>
+      </c>
+      <c r="S12" s="11">
+        <v>25</v>
+      </c>
+      <c r="T12" s="11">
+        <v>20</v>
+      </c>
+      <c r="U12" s="11">
+        <v>22</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>3.45</v>
+      </c>
+      <c r="W12" s="12">
+        <v>6</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
         <v>4.75</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>4.75</v>
+        <v>1.2999999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -29444,17 +29512,31 @@
         <v>17</v>
       </c>
       <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
+      <c r="P14" s="11">
+        <v>200</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>240</v>
+      </c>
+      <c r="R14" s="11">
+        <v>560</v>
+      </c>
+      <c r="S14" s="11">
+        <v>520</v>
+      </c>
+      <c r="T14" s="11">
+        <v>640</v>
+      </c>
+      <c r="U14" s="11">
+        <v>720</v>
+      </c>
       <c r="V14" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="12"/>
+        <v>72</v>
+      </c>
+      <c r="W14" s="12">
+        <v>4</v>
+      </c>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
       <c r="AA14" s="38"/>
@@ -29490,10 +29572,11 @@
       <c r="T15" s="11"/>
       <c r="U15" s="11"/>
       <c r="V15" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W15" s="12"/>
+        <v>8</v>
+      </c>
+      <c r="W15" s="12">
+        <v>10</v>
+      </c>
       <c r="Y15" s="36"/>
       <c r="Z15" s="37"/>
       <c r="AA15" s="38"/>
@@ -29529,10 +29612,11 @@
       <c r="T16" s="11"/>
       <c r="U16" s="11"/>
       <c r="V16" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W16" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="W16" s="12">
+        <v>8</v>
+      </c>
       <c r="Y16" s="36"/>
       <c r="Z16" s="37"/>
       <c r="AA16" s="38"/>
@@ -29567,21 +29651,22 @@
       <c r="T17" s="11"/>
       <c r="U17" s="11"/>
       <c r="V17" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W17" s="18"/>
+        <v>5</v>
+      </c>
+      <c r="W17" s="18">
+        <v>7</v>
+      </c>
       <c r="Y17" s="36">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Z17" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA17" s="38">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
@@ -29628,31 +29713,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" ref="P18:U18" si="6">SUM(P8:P16)</f>
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>316</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>657</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>762</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>3598</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -29661,11 +29746,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>22.95</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>32.75</v>
+        <v>9.8000000000000007</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -29716,31 +29801,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6.875</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>16.425000000000001</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>19.05</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>89.95</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -29749,11 +29834,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>0.57374999999999998</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.81874999999999998</v>
+        <v>0.24500000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -30039,25 +30124,37 @@
         <v>13</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="D8" s="11">
+        <v>30</v>
+      </c>
+      <c r="E8" s="11">
+        <v>30</v>
+      </c>
+      <c r="F8" s="11">
+        <v>60</v>
+      </c>
+      <c r="G8" s="11">
+        <v>55</v>
+      </c>
+      <c r="H8" s="11">
+        <v>40</v>
+      </c>
+      <c r="I8" s="11">
+        <v>65</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="K8" s="12">
+        <v>11</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11">
-        <v>120</v>
-      </c>
+      <c r="O8" s="11"/>
       <c r="P8" s="11"/>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
@@ -30066,22 +30163,20 @@
       <c r="U8" s="11"/>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>3</v>
-      </c>
-      <c r="W8" s="12">
-        <v>11</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>-3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -30090,17 +30185,31 @@
         <v>14</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="D9" s="11">
+        <v>20</v>
+      </c>
+      <c r="E9" s="11">
+        <v>20</v>
+      </c>
+      <c r="F9" s="11">
+        <v>20</v>
+      </c>
+      <c r="G9" s="11">
+        <v>100</v>
+      </c>
+      <c r="H9" s="11">
+        <v>20</v>
+      </c>
+      <c r="I9" s="11">
+        <v>40</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J13" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>5.5</v>
+      </c>
+      <c r="K9" s="12">
+        <v>4</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -30117,12 +30226,10 @@
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
         <v>0</v>
       </c>
-      <c r="W9" s="12">
-        <v>14</v>
-      </c>
+      <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
@@ -30130,7 +30237,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -30139,12 +30246,12 @@
         <v>15</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -30166,9 +30273,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W10" s="12">
-        <v>11</v>
-      </c>
+      <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -30188,17 +30293,31 @@
         <v>29</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="D11" s="11">
+        <v>31</v>
+      </c>
+      <c r="E11" s="11">
+        <v>31</v>
+      </c>
+      <c r="F11" s="11">
+        <v>37</v>
+      </c>
+      <c r="G11" s="11">
+        <v>158</v>
+      </c>
+      <c r="H11" s="11">
+        <v>92</v>
+      </c>
+      <c r="I11" s="11">
+        <v>189</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>13.45</v>
+      </c>
+      <c r="K11" s="12">
+        <v>9</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -30215,12 +30334,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W11" s="12">
-        <v>5</v>
-      </c>
+      <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>13.45</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -30228,7 +30345,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>13.45</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -30237,17 +30354,31 @@
         <v>28</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="D12" s="11">
+        <v>74</v>
+      </c>
+      <c r="E12" s="11">
+        <v>49</v>
+      </c>
+      <c r="F12" s="11">
+        <v>50</v>
+      </c>
+      <c r="G12" s="11">
+        <v>68</v>
+      </c>
+      <c r="H12" s="11">
+        <v>49</v>
+      </c>
+      <c r="I12" s="11">
+        <v>50</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>8.5</v>
+      </c>
+      <c r="K12" s="12">
+        <v>6</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
@@ -30264,12 +30395,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W12" s="12">
-        <v>11</v>
-      </c>
+      <c r="W12" s="12"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
@@ -30277,7 +30406,7 @@
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -30313,9 +30442,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W13" s="12">
-        <v>5</v>
-      </c>
+      <c r="W13" s="12"/>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -30333,9 +30460,11 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
       <c r="J14" s="15">
-        <v>13</v>
-      </c>
-      <c r="K14" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="K14" s="12">
+        <v>69.5</v>
+      </c>
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
@@ -30370,9 +30499,11 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="15">
-        <v>6</v>
-      </c>
-      <c r="K15" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="K15" s="12">
+        <v>10</v>
+      </c>
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
@@ -30407,9 +30538,11 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="15">
-        <v>11</v>
-      </c>
-      <c r="K16" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="K16" s="12">
+        <v>9</v>
+      </c>
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
@@ -30444,9 +30577,11 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
       <c r="J17" s="15">
-        <v>11</v>
-      </c>
-      <c r="K17" s="18"/>
+        <v>15</v>
+      </c>
+      <c r="K17" s="18">
+        <v>8</v>
+      </c>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
         <v>38</v>
@@ -30462,7 +30597,7 @@
       <c r="W17" s="18"/>
       <c r="Y17" s="36">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Z17" s="37">
         <f t="shared" si="3"/>
@@ -30470,7 +30605,7 @@
       </c>
       <c r="AA17" s="38">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
@@ -30482,38 +30617,38 @@
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>0</v>
+        <v>1378</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
@@ -30541,20 +30676,20 @@
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>11</v>
+        <v>49.45</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>8</v>
+        <v>49.45</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -30568,31 +30703,31 @@
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3.875</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4.1749999999999998</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9.5250000000000004</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5.0250000000000004</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="J19" s="22">
         <f>SUM(J8:J16)</f>
-        <v>30</v>
+        <v>59.45</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -30601,7 +30736,7 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
@@ -30629,20 +30764,20 @@
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0.27500000000000002</v>
+        <v>1.2362500000000001</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>7.4999999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.2</v>
+        <v>1.2362500000000001</v>
       </c>
     </row>
   </sheetData>

--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B20C42-2C3C-4031-AD4F-B0B0B3A2BB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F69CEBF-BB0E-4EB8-94B1-F81AFBE1A47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="6" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="9" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -2400,41 +2400,38 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11">
-        <v>10</v>
-      </c>
+      <c r="C8" s="11"/>
       <c r="D8" s="11">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="E8" s="11">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F8" s="11">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="G8" s="11">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H8" s="11">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I8" s="11">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J8" s="15">
-        <v>13</v>
+        <f>SUM(D8:I8)/40</f>
+        <v>9</v>
       </c>
       <c r="K8" s="12">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11">
-        <v>10</v>
-      </c>
+      <c r="O8" s="11"/>
       <c r="P8" s="11"/>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
@@ -2443,22 +2440,20 @@
       <c r="U8" s="11"/>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0.25</v>
-      </c>
-      <c r="W8" s="12">
-        <v>14</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>12.75</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -2466,33 +2461,31 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11">
-        <v>80</v>
-      </c>
+      <c r="C9" s="11"/>
       <c r="D9" s="11">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E9" s="11">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F9" s="11">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="G9" s="11">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="H9" s="11">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="I9" s="11">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J13" si="0">SUM(C9:I9)/40</f>
-        <v>12</v>
+        <f t="shared" ref="J9:J17" si="0">SUM(D9:I9)/40</f>
+        <v>6</v>
       </c>
       <c r="K9" s="12">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
@@ -2510,12 +2503,10 @@
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
         <v>0</v>
       </c>
-      <c r="W9" s="12">
-        <v>21</v>
-      </c>
+      <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
@@ -2523,7 +2514,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -2531,9 +2522,7 @@
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="11">
-        <v>530</v>
-      </c>
+      <c r="C10" s="11"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
@@ -2542,11 +2531,9 @@
       <c r="I10" s="11"/>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>13.25</v>
-      </c>
-      <c r="K10" s="12">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K10" s="12"/>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -2563,12 +2550,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W10" s="12">
-        <v>4</v>
-      </c>
+      <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>13.25</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -2576,7 +2561,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>13.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -2584,33 +2569,31 @@
       <c r="B11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="11">
-        <v>119</v>
-      </c>
+      <c r="C11" s="11"/>
       <c r="D11" s="11">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E11" s="11">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F11" s="11">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G11" s="11">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="H11" s="11">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I11" s="11">
-        <v>71</v>
+        <v>152</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>9.0250000000000004</v>
+        <v>8.1</v>
       </c>
       <c r="K11" s="12">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
@@ -2628,12 +2611,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W11" s="12">
-        <v>10</v>
-      </c>
+      <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>9.0250000000000004</v>
+        <v>8.1</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -2641,7 +2622,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>9.0250000000000004</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -2649,34 +2630,18 @@
       <c r="B12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="11">
-        <v>60</v>
-      </c>
-      <c r="D12" s="11">
-        <v>30</v>
-      </c>
-      <c r="E12" s="11">
-        <v>44</v>
-      </c>
-      <c r="F12" s="11">
-        <v>44</v>
-      </c>
-      <c r="G12" s="11">
-        <v>22</v>
-      </c>
-      <c r="H12" s="11">
-        <v>23</v>
-      </c>
-      <c r="I12" s="11">
-        <v>23</v>
-      </c>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>6.15</v>
-      </c>
-      <c r="K12" s="12">
-        <v>10</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K12" s="12"/>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
@@ -2693,12 +2658,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W12" s="12">
-        <v>9</v>
-      </c>
+      <c r="W12" s="12"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
@@ -2706,7 +2669,7 @@
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>6.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -2714,34 +2677,18 @@
       <c r="B13" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="11">
-        <v>200</v>
-      </c>
-      <c r="D13" s="11">
-        <v>340</v>
-      </c>
-      <c r="E13" s="11">
-        <v>320</v>
-      </c>
-      <c r="F13" s="11">
-        <v>440</v>
-      </c>
-      <c r="G13" s="11">
-        <v>380</v>
-      </c>
-      <c r="H13" s="11">
-        <v>360</v>
-      </c>
-      <c r="I13" s="11">
-        <v>600</v>
-      </c>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
       <c r="J13" s="15">
         <f t="shared" si="0"/>
-        <v>66</v>
-      </c>
-      <c r="K13" s="12">
-        <v>5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K13" s="12"/>
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
@@ -2758,9 +2705,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W13" s="12">
-        <v>4</v>
-      </c>
+      <c r="W13" s="12"/>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -2778,11 +2723,10 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
       <c r="J14" s="15">
-        <v>16</v>
-      </c>
-      <c r="K14" s="12">
-        <v>14</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="12"/>
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
@@ -2817,11 +2761,10 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="15">
-        <v>9</v>
-      </c>
-      <c r="K15" s="12">
-        <v>10</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="12"/>
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
@@ -2856,11 +2799,10 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="15">
-        <v>6</v>
-      </c>
-      <c r="K16" s="12">
-        <v>5</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="12"/>
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
@@ -2895,7 +2837,8 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
       <c r="J17" s="15">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
@@ -2913,7 +2856,7 @@
       <c r="W17" s="18"/>
       <c r="Y17" s="36">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="37">
         <f t="shared" si="3"/>
@@ -2921,7 +2864,7 @@
       </c>
       <c r="AA17" s="38">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
@@ -2929,42 +2872,42 @@
       <c r="B18" s="7"/>
       <c r="C18" s="25">
         <f t="shared" ref="C18:I18" si="5">SUM(C8:C17)</f>
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>518</v>
+        <v>85</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>492</v>
+        <v>110</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>598</v>
+        <v>115</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>645</v>
+        <v>218</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>576</v>
+        <v>69</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>849</v>
+        <v>327</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>4677</v>
+        <v>924</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
@@ -2992,20 +2935,20 @@
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>59.424999999999997</v>
+        <v>23.1</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>59.174999999999997</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3015,35 +2958,35 @@
       </c>
       <c r="C19" s="21">
         <f t="shared" ref="C19:J19" si="7">C18/40</f>
-        <v>24.975000000000001</v>
+        <v>0</v>
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>12.95</v>
+        <v>2.125</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>12.3</v>
+        <v>2.75</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>14.95</v>
+        <v>2.875</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>16.125</v>
+        <v>5.45</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>14.4</v>
+        <v>1.7250000000000001</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>21.225000000000001</v>
+        <v>8.1750000000000007</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>116.925</v>
+        <v>23.1</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -3052,7 +2995,7 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
@@ -3080,20 +3023,20 @@
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>1.485625</v>
+        <v>0.57750000000000001</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>6.2500000000000003E-3</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>1.4793749999999999</v>
+        <v>0.57750000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -29221,7 +29164,7 @@
         <v>20</v>
       </c>
       <c r="V9" s="15">
-        <f t="shared" ref="V9:V17" si="1">SUM(O9:U9)/40</f>
+        <f t="shared" ref="V9:V14" si="1">SUM(O9:U9)/40</f>
         <v>2.5</v>
       </c>
       <c r="W9" s="12">
@@ -30155,28 +30098,42 @@
         <v>13</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>15</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>20</v>
+      </c>
+      <c r="R8" s="11">
+        <v>45</v>
+      </c>
+      <c r="S8" s="11">
+        <v>40</v>
+      </c>
+      <c r="T8" s="11">
+        <v>30</v>
+      </c>
+      <c r="U8" s="11">
+        <v>50</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>5</v>
+      </c>
+      <c r="W8" s="12">
+        <v>10</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>7</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -30204,7 +30161,7 @@
         <v>40</v>
       </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J13" si="0">SUM(C9:I9)/40</f>
+        <f t="shared" ref="J9:J14" si="0">SUM(C9:I9)/40</f>
         <v>5.5</v>
       </c>
       <c r="K9" s="12">
@@ -30216,28 +30173,42 @@
         <v>14</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>20</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>20</v>
+      </c>
+      <c r="R9" s="11">
+        <v>20</v>
+      </c>
+      <c r="S9" s="11">
+        <v>90</v>
+      </c>
+      <c r="T9" s="11">
+        <v>10</v>
+      </c>
+      <c r="U9" s="11">
+        <v>20</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>4.5</v>
+      </c>
+      <c r="W9" s="12">
+        <v>3</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
         <v>5.5</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>5.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -30324,28 +30295,42 @@
         <v>29</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>31</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>31</v>
+      </c>
+      <c r="R11" s="11">
+        <v>37</v>
+      </c>
+      <c r="S11" s="11">
+        <v>158</v>
+      </c>
+      <c r="T11" s="11">
+        <v>92</v>
+      </c>
+      <c r="U11" s="11">
+        <v>189</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>13.45</v>
+      </c>
+      <c r="W11" s="12">
+        <v>9</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>13.45</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>13.45</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>13.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -30385,28 +30370,42 @@
         <v>28</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>52</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>48</v>
+      </c>
+      <c r="R12" s="11">
+        <v>50</v>
+      </c>
+      <c r="S12" s="11">
+        <v>68</v>
+      </c>
+      <c r="T12" s="11">
+        <v>49</v>
+      </c>
+      <c r="U12" s="11">
+        <v>50</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>7.9249999999999998</v>
+      </c>
+      <c r="W12" s="12">
+        <v>6</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
         <v>8.5</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.9249999999999998</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>8.5</v>
+        <v>0.57500000000000018</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -30453,17 +30452,30 @@
         <v>17</v>
       </c>
       <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
+      <c r="D14" s="11">
+        <v>360</v>
+      </c>
+      <c r="E14" s="11">
+        <v>480</v>
+      </c>
+      <c r="F14" s="11">
+        <v>480</v>
+      </c>
+      <c r="G14" s="11">
+        <v>480</v>
+      </c>
+      <c r="H14" s="11">
+        <v>460</v>
+      </c>
+      <c r="I14" s="11">
+        <v>520</v>
+      </c>
       <c r="J14" s="15">
+        <f t="shared" si="0"/>
+        <v>69.5</v>
+      </c>
+      <c r="K14" s="12">
         <v>6</v>
-      </c>
-      <c r="K14" s="12">
-        <v>69.5</v>
       </c>
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
@@ -30471,17 +30483,31 @@
         <v>17</v>
       </c>
       <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
+      <c r="P14" s="11">
+        <v>360</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>480</v>
+      </c>
+      <c r="R14" s="11">
+        <v>480</v>
+      </c>
+      <c r="S14" s="11">
+        <v>480</v>
+      </c>
+      <c r="T14" s="11">
+        <v>460</v>
+      </c>
+      <c r="U14" s="11">
+        <v>520</v>
+      </c>
       <c r="V14" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="12"/>
+        <v>69.5</v>
+      </c>
+      <c r="W14" s="12">
+        <v>6</v>
+      </c>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
       <c r="AA14" s="38"/>
@@ -30617,31 +30643,31 @@
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>155</v>
+        <v>515</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>130</v>
+        <v>610</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>167</v>
+        <v>647</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>381</v>
+        <v>861</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>201</v>
+        <v>661</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>344</v>
+        <v>864</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>1378</v>
+        <v>4158</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
@@ -30652,31 +30678,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>478</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>599</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>836</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>641</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>829</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>4015</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -30685,11 +30711,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>30.875</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>49.45</v>
+        <v>18.574999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -30703,31 +30729,31 @@
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>3.875</v>
+        <v>12.875</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>3.25</v>
+        <v>15.25</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>4.1749999999999998</v>
+        <v>16.175000000000001</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>9.5250000000000004</v>
+        <v>21.524999999999999</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>5.0250000000000004</v>
+        <v>16.524999999999999</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>8.6</v>
+        <v>21.6</v>
       </c>
       <c r="J19" s="22">
         <f>SUM(J8:J16)</f>
-        <v>59.45</v>
+        <v>122.95</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -30740,31 +30766,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>11.95</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>14.975</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>16.024999999999999</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>20.725000000000001</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>100.375</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -30773,11 +30799,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>0.77187499999999998</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>1.2362500000000001</v>
+        <v>0.46437499999999998</v>
       </c>
     </row>
   </sheetData>
@@ -31064,49 +31090,73 @@
         <v>13</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="D8" s="11">
+        <v>10</v>
+      </c>
+      <c r="E8" s="11">
+        <v>10</v>
+      </c>
+      <c r="F8" s="11">
+        <v>20</v>
+      </c>
+      <c r="G8" s="11">
+        <v>100</v>
+      </c>
+      <c r="H8" s="11">
+        <v>50</v>
+      </c>
+      <c r="I8" s="11">
+        <v>260</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>11.25</v>
+      </c>
+      <c r="K8" s="12">
+        <v>11</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11">
+      <c r="O8" s="11"/>
+      <c r="P8" s="11">
+        <v>10</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>10</v>
+      </c>
+      <c r="R8" s="11">
+        <v>20</v>
+      </c>
+      <c r="S8" s="11">
+        <v>100</v>
+      </c>
+      <c r="T8" s="11">
         <v>50</v>
       </c>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="U8" s="11">
+        <v>260</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>1.25</v>
+        <v>11.25</v>
       </c>
       <c r="W8" s="12">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>11.25</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>1.25</v>
+        <v>11.25</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>-1.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -31115,43 +31165,69 @@
         <v>14</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="D9" s="11">
+        <v>0</v>
+      </c>
+      <c r="E9" s="11">
+        <v>0</v>
+      </c>
+      <c r="F9" s="11">
+        <v>0</v>
+      </c>
+      <c r="G9" s="11">
+        <v>121</v>
+      </c>
+      <c r="H9" s="11">
+        <v>111</v>
+      </c>
+      <c r="I9" s="11">
+        <v>168</v>
+      </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
+        <v>10</v>
+      </c>
+      <c r="K9" s="12">
+        <v>4</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
         <v>14</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>0</v>
+      </c>
+      <c r="R9" s="11">
+        <v>0</v>
+      </c>
+      <c r="S9" s="11">
+        <v>121</v>
+      </c>
+      <c r="T9" s="11">
+        <v>111</v>
+      </c>
+      <c r="U9" s="11">
+        <v>168</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W9" s="12">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
@@ -31191,9 +31267,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W10" s="12">
-        <v>11</v>
-      </c>
+      <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -31240,9 +31314,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W11" s="12">
-        <v>4</v>
-      </c>
+      <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -31262,47 +31334,73 @@
         <v>28</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="D12" s="11">
+        <v>27</v>
+      </c>
+      <c r="E12" s="11">
+        <v>13</v>
+      </c>
+      <c r="F12" s="11">
+        <v>30</v>
+      </c>
+      <c r="G12" s="11">
+        <v>36</v>
+      </c>
+      <c r="H12" s="11">
+        <v>20</v>
+      </c>
+      <c r="I12" s="11">
+        <v>30</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>3.9</v>
+      </c>
+      <c r="K12" s="12">
+        <v>4</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
         <v>28</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>27</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>10</v>
+      </c>
+      <c r="R12" s="11">
+        <v>27</v>
+      </c>
+      <c r="S12" s="11">
+        <v>30</v>
+      </c>
+      <c r="T12" s="11">
+        <v>20</v>
+      </c>
+      <c r="U12" s="11">
+        <v>30</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="W12" s="12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.29999999999999982</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -31318,7 +31416,8 @@
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
       <c r="J13" s="15">
-        <v>192</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="K13" s="12"/>
       <c r="L13" s="13"/>
@@ -31337,9 +31436,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W13" s="12">
-        <v>2</v>
-      </c>
+      <c r="W13" s="12"/>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -31357,9 +31454,11 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
       <c r="J14" s="15">
-        <v>12</v>
-      </c>
-      <c r="K14" s="12"/>
+        <v>52</v>
+      </c>
+      <c r="K14" s="12">
+        <v>2</v>
+      </c>
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
@@ -31394,7 +31493,8 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="15">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="K15" s="12"/>
       <c r="L15" s="13"/>
@@ -31431,7 +31531,8 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="15">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="K16" s="12"/>
       <c r="L16" s="13"/>
@@ -31468,7 +31569,8 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
       <c r="J17" s="15">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
@@ -31486,7 +31588,7 @@
       <c r="W17" s="18"/>
       <c r="Y17" s="36">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="37">
         <f t="shared" si="3"/>
@@ -31494,7 +31596,7 @@
       </c>
       <c r="AA17" s="38">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
@@ -31506,79 +31608,79 @@
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>458</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>0</v>
+        <v>1006</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>458</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>50</v>
+        <v>994</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>6</v>
+        <v>25.15</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>1.25</v>
+        <v>24.85</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>4.75</v>
+        <v>0.29999999999999982</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -31592,31 +31694,31 @@
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6.4249999999999998</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4.5250000000000004</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>11.45</v>
       </c>
       <c r="J19" s="22">
         <f>SUM(J8:J16)</f>
-        <v>220</v>
+        <v>77.150000000000006</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -31625,48 +31727,48 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1.175</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6.2750000000000004</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.5250000000000004</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>11.45</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>1.25</v>
+        <v>24.85</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0.15</v>
+        <v>0.62874999999999992</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>3.125E-2</v>
+        <v>0.62125000000000008</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.11874999999999999</v>
+        <v>7.4999999999999954E-3</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.35">

--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F69CEBF-BB0E-4EB8-94B1-F81AFBE1A47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3932A8D-3A98-435F-B04D-5C676601A36E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="9" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="8" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1707" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1707" uniqueCount="50">
   <si>
     <t>Booking</t>
   </si>
@@ -202,6 +202,9 @@
   </si>
   <si>
     <t>C102609155</t>
+  </si>
+  <si>
+    <t>Nabeel SD</t>
   </si>
 </sst>
 </file>
@@ -2631,17 +2634,31 @@
         <v>28</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="D12" s="11">
+        <v>48</v>
+      </c>
+      <c r="E12" s="11">
+        <v>43</v>
+      </c>
+      <c r="F12" s="11">
+        <v>106</v>
+      </c>
+      <c r="G12" s="11">
+        <v>13</v>
+      </c>
+      <c r="H12" s="11">
+        <v>3</v>
+      </c>
+      <c r="I12" s="11">
+        <v>15</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>5.7</v>
+      </c>
+      <c r="K12" s="12">
+        <v>6</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
@@ -2661,7 +2678,7 @@
       <c r="W12" s="12"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
@@ -2669,7 +2686,7 @@
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -2716,17 +2733,31 @@
         <v>17</v>
       </c>
       <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
+      <c r="D14" s="11">
+        <v>400</v>
+      </c>
+      <c r="E14" s="11">
+        <v>480</v>
+      </c>
+      <c r="F14" s="11">
+        <v>440</v>
+      </c>
+      <c r="G14" s="11">
+        <v>440</v>
+      </c>
+      <c r="H14" s="11">
+        <v>480</v>
+      </c>
+      <c r="I14" s="11">
+        <v>400</v>
+      </c>
       <c r="J14" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="12"/>
+        <v>66</v>
+      </c>
+      <c r="K14" s="12">
+        <v>3</v>
+      </c>
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
@@ -2876,31 +2907,31 @@
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>85</v>
+        <v>533</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>110</v>
+        <v>633</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>115</v>
+        <v>661</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>218</v>
+        <v>671</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>69</v>
+        <v>552</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>327</v>
+        <v>742</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>924</v>
+        <v>3792</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
@@ -2940,7 +2971,7 @@
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>23.1</v>
+        <v>28.8</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
@@ -2948,7 +2979,7 @@
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>23.1</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2962,31 +2993,31 @@
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>2.125</v>
+        <v>13.324999999999999</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>2.75</v>
+        <v>15.824999999999999</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>2.875</v>
+        <v>16.524999999999999</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>5.45</v>
+        <v>16.774999999999999</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>1.7250000000000001</v>
+        <v>13.8</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>8.1750000000000007</v>
+        <v>18.55</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>23.1</v>
+        <v>94.8</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -3028,7 +3059,7 @@
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0.57750000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
@@ -3036,7 +3067,7 @@
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.57750000000000001</v>
+        <v>0.72</v>
       </c>
     </row>
   </sheetData>
@@ -31423,20 +31454,28 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
       <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="S13" s="11">
+        <v>3000</v>
+      </c>
+      <c r="T13" s="11">
+        <v>2000</v>
+      </c>
+      <c r="U13" s="11">
+        <v>3000</v>
+      </c>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12"/>
+        <v>200</v>
+      </c>
+      <c r="W13" s="12">
+        <v>1</v>
+      </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -31465,17 +31504,31 @@
         <v>17</v>
       </c>
       <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
+      <c r="P14" s="11">
+        <v>280</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>160</v>
+      </c>
+      <c r="R14" s="11">
+        <v>80</v>
+      </c>
+      <c r="S14" s="11">
+        <v>340</v>
+      </c>
+      <c r="T14" s="11">
+        <v>300</v>
+      </c>
+      <c r="U14" s="11">
+        <v>700</v>
+      </c>
       <c r="V14" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="12"/>
+        <v>46.5</v>
+      </c>
+      <c r="W14" s="12">
+        <v>2</v>
+      </c>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
       <c r="AA14" s="38"/>
@@ -31643,31 +31696,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>37</v>
+        <v>317</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>251</v>
+        <v>3591</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>181</v>
+        <v>2481</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>458</v>
+        <v>4158</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>994</v>
+        <v>10854</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -31731,31 +31784,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0.92500000000000004</v>
+        <v>7.9249999999999998</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>1.175</v>
+        <v>3.1749999999999998</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>6.2750000000000004</v>
+        <v>89.775000000000006</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>4.5250000000000004</v>
+        <v>62.024999999999999</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>11.45</v>
+        <v>103.95</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>24.85</v>
+        <v>271.35000000000002</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">

--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3932A8D-3A98-435F-B04D-5C676601A36E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6F3148E-0072-4133-A9E5-92F8F17C90B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="8" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="9" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1707" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1706" uniqueCount="50">
   <si>
     <t>Booking</t>
   </si>
@@ -2435,28 +2435,42 @@
         <v>13</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>40</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>70</v>
+      </c>
+      <c r="R8" s="11">
+        <v>90</v>
+      </c>
+      <c r="S8" s="11">
+        <v>80</v>
+      </c>
+      <c r="T8" s="11">
+        <v>0</v>
+      </c>
+      <c r="U8" s="11">
+        <v>80</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>9</v>
+      </c>
+      <c r="W8" s="12">
+        <v>8</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>9</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -2496,28 +2510,42 @@
         <v>14</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>20</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>20</v>
+      </c>
+      <c r="R9" s="11">
+        <v>0</v>
+      </c>
+      <c r="S9" s="11">
+        <v>35</v>
+      </c>
+      <c r="T9" s="11">
+        <v>10</v>
+      </c>
+      <c r="U9" s="11">
+        <v>75</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>4</v>
+      </c>
+      <c r="W9" s="12">
+        <v>3</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
         <v>6</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -2604,28 +2632,42 @@
         <v>29</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>10</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>10</v>
+      </c>
+      <c r="R11" s="11">
+        <v>10</v>
+      </c>
+      <c r="S11" s="11">
+        <v>89</v>
+      </c>
+      <c r="T11" s="11">
+        <v>49</v>
+      </c>
+      <c r="U11" s="11">
+        <v>64</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>5.8</v>
+      </c>
+      <c r="W11" s="12">
+        <v>7</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>8.1</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>8.1</v>
+        <v>2.2999999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -2665,28 +2707,42 @@
         <v>28</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>48</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>33</v>
+      </c>
+      <c r="R12" s="11">
+        <v>76</v>
+      </c>
+      <c r="S12" s="11">
+        <v>13</v>
+      </c>
+      <c r="T12" s="11">
+        <v>3</v>
+      </c>
+      <c r="U12" s="11">
+        <v>15</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>4.7</v>
+      </c>
+      <c r="W12" s="12">
+        <v>5</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
         <v>5.7</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>5.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -2942,31 +2998,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>940</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -2975,11 +3031,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>28.8</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3030,31 +3086,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.3250000000000002</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5.4249999999999998</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -3063,11 +3119,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>0.58750000000000002</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.72</v>
+        <v>0.13250000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3353,34 +3409,18 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11">
-        <v>80</v>
-      </c>
-      <c r="D8" s="11">
-        <v>30</v>
-      </c>
-      <c r="E8" s="11">
-        <v>30</v>
-      </c>
-      <c r="F8" s="11">
-        <v>20</v>
-      </c>
-      <c r="G8" s="11">
-        <v>15</v>
-      </c>
-      <c r="H8" s="11">
-        <v>10</v>
-      </c>
-      <c r="I8" s="11">
-        <v>15</v>
-      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>5</v>
-      </c>
-      <c r="K8" s="12">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K8" s="12"/>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -3397,12 +3437,10 @@
         <f>SUM(O8:U8)/40</f>
         <v>0</v>
       </c>
-      <c r="W8" s="12">
-        <v>7</v>
-      </c>
+      <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -3410,7 +3448,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -3419,31 +3457,17 @@
         <v>14</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="11">
-        <v>0</v>
-      </c>
-      <c r="E9" s="11">
-        <v>0</v>
-      </c>
-      <c r="F9" s="11">
-        <v>0</v>
-      </c>
-      <c r="G9" s="11">
-        <v>94</v>
-      </c>
-      <c r="H9" s="11">
-        <v>40</v>
-      </c>
-      <c r="I9" s="11">
-        <v>186</v>
-      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
-        <v>8</v>
-      </c>
-      <c r="K9" s="12">
-        <v>15</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K9" s="12"/>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -3460,12 +3484,10 @@
         <f t="shared" ref="V9:V17" si="1">SUM(O9:U9)/40</f>
         <v>0</v>
       </c>
-      <c r="W9" s="12">
-        <v>15</v>
-      </c>
+      <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
@@ -3473,7 +3495,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
@@ -3481,9 +3503,7 @@
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="84" t="s">
-        <v>40</v>
-      </c>
+      <c r="C10" s="84"/>
       <c r="D10" s="85"/>
       <c r="E10" s="85"/>
       <c r="F10" s="85"/>
@@ -3530,34 +3550,18 @@
       <c r="B11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="11">
-        <v>120</v>
-      </c>
-      <c r="D11" s="11">
-        <v>15</v>
-      </c>
-      <c r="E11" s="11">
-        <v>10</v>
-      </c>
-      <c r="F11" s="11">
-        <v>15</v>
-      </c>
-      <c r="G11" s="11">
-        <v>97</v>
-      </c>
-      <c r="H11" s="11">
-        <v>92</v>
-      </c>
-      <c r="I11" s="11">
-        <v>99</v>
-      </c>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>11.2</v>
-      </c>
-      <c r="K11" s="12">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K11" s="12"/>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -3574,12 +3578,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W11" s="12">
-        <v>5</v>
-      </c>
+      <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>11.2</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -3587,7 +3589,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>11.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -3595,34 +3597,18 @@
       <c r="B12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="11">
-        <v>124</v>
-      </c>
-      <c r="D12" s="11">
-        <v>29</v>
-      </c>
-      <c r="E12" s="11">
-        <v>24</v>
-      </c>
-      <c r="F12" s="11">
-        <v>29</v>
-      </c>
-      <c r="G12" s="11">
-        <v>23</v>
-      </c>
-      <c r="H12" s="11">
-        <v>18</v>
-      </c>
-      <c r="I12" s="11">
-        <v>23</v>
-      </c>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>6.75</v>
-      </c>
-      <c r="K12" s="12">
-        <v>7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K12" s="12"/>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
@@ -3639,12 +3625,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W12" s="12">
-        <v>6</v>
-      </c>
+      <c r="W12" s="12"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
@@ -3652,7 +3636,7 @@
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>6.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -3670,9 +3654,7 @@
       <c r="J13" s="15">
         <v>90</v>
       </c>
-      <c r="K13" s="12">
-        <v>4</v>
-      </c>
+      <c r="K13" s="12"/>
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
@@ -3689,9 +3671,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W13" s="12">
-        <v>4</v>
-      </c>
+      <c r="W13" s="12"/>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -3711,9 +3691,7 @@
       <c r="J14" s="15">
         <v>16</v>
       </c>
-      <c r="K14" s="12">
-        <v>14</v>
-      </c>
+      <c r="K14" s="12"/>
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
@@ -3750,9 +3728,7 @@
       <c r="J15" s="15">
         <v>9</v>
       </c>
-      <c r="K15" s="12">
-        <v>10</v>
-      </c>
+      <c r="K15" s="12"/>
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
@@ -3789,9 +3765,7 @@
       <c r="J16" s="15">
         <v>6</v>
       </c>
-      <c r="K16" s="12">
-        <v>5</v>
-      </c>
+      <c r="K16" s="12"/>
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
@@ -3863,35 +3837,35 @@
       <c r="B18" s="7"/>
       <c r="C18" s="25">
         <f t="shared" ref="C18:I18" si="5">SUM(C8:C17)</f>
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>323</v>
+        <v>0</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>1238</v>
+        <v>0</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
@@ -3931,7 +3905,7 @@
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>36.950000000000003</v>
+        <v>6</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
@@ -3939,7 +3913,7 @@
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>36.950000000000003</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3949,35 +3923,35 @@
       </c>
       <c r="C19" s="21">
         <f t="shared" ref="C19:I19" si="7">C18/40</f>
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>5.7249999999999996</v>
+        <v>0</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>8.0749999999999993</v>
+        <v>0</v>
       </c>
       <c r="J19" s="22">
         <f>SUM(J8:J16)</f>
-        <v>151.94999999999999</v>
+        <v>121</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -4019,7 +3993,7 @@
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0.92375000000000007</v>
+        <v>0.15</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
@@ -4027,7 +4001,7 @@
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.92375000000000007</v>
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>

--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6F3148E-0072-4133-A9E5-92F8F17C90B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D63B38-5381-43B7-A846-17271EBA1E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="9" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="11" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -2820,17 +2820,31 @@
         <v>17</v>
       </c>
       <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
+      <c r="P14" s="11">
+        <v>400</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>478</v>
+      </c>
+      <c r="R14" s="11">
+        <v>440</v>
+      </c>
+      <c r="S14" s="11">
+        <v>440</v>
+      </c>
+      <c r="T14" s="11">
+        <v>480</v>
+      </c>
+      <c r="U14" s="11">
+        <v>400</v>
+      </c>
       <c r="V14" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="12"/>
+        <v>65.95</v>
+      </c>
+      <c r="W14" s="12">
+        <v>3</v>
+      </c>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
       <c r="AA14" s="38"/>
@@ -2998,31 +3012,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>118</v>
+        <v>518</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>133</v>
+        <v>611</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>176</v>
+        <v>616</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>217</v>
+        <v>657</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>62</v>
+        <v>542</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>234</v>
+        <v>634</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>940</v>
+        <v>3578</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -3086,31 +3100,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>2.95</v>
+        <v>12.95</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>3.3250000000000002</v>
+        <v>15.275</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>4.4000000000000004</v>
+        <v>15.4</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>5.4249999999999998</v>
+        <v>16.425000000000001</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>1.55</v>
+        <v>13.55</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>5.85</v>
+        <v>15.85</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>23.5</v>
+        <v>89.45</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -4287,42 +4301,38 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11">
-        <v>80</v>
-      </c>
+      <c r="C8" s="11"/>
       <c r="D8" s="11">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E8" s="11">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F8" s="11">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="G8" s="11">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H8" s="11">
         <v>80</v>
       </c>
       <c r="I8" s="11">
-        <v>240</v>
+        <v>85</v>
       </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K8" s="12">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11">
-        <v>80</v>
-      </c>
+      <c r="O8" s="11"/>
       <c r="P8" s="11"/>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
@@ -4331,22 +4341,20 @@
       <c r="U8" s="11"/>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>2</v>
-      </c>
-      <c r="W8" s="12">
-        <v>13</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -4354,30 +4362,28 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11">
-        <v>70</v>
-      </c>
+      <c r="C9" s="11"/>
       <c r="D9" s="11">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="E9" s="11">
-        <v>31</v>
+        <v>122</v>
       </c>
       <c r="F9" s="11">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="G9" s="11">
-        <v>170</v>
+        <v>125</v>
       </c>
       <c r="H9" s="11">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="I9" s="11">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
-        <v>18.824999999999999</v>
+        <v>21.9</v>
       </c>
       <c r="K9" s="12">
         <v>9</v>
@@ -4398,12 +4404,10 @@
         <f t="shared" ref="V9:V17" si="1">SUM(O9:U9)/40</f>
         <v>0</v>
       </c>
-      <c r="W9" s="12">
-        <v>9</v>
-      </c>
+      <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>18.824999999999999</v>
+        <v>21.9</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
@@ -4411,7 +4415,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>18.824999999999999</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -4419,34 +4423,18 @@
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="11">
-        <v>118</v>
-      </c>
-      <c r="D10" s="11">
-        <v>0</v>
-      </c>
-      <c r="E10" s="11">
-        <v>0</v>
-      </c>
-      <c r="F10" s="11">
-        <v>0</v>
-      </c>
-      <c r="G10" s="11">
-        <v>45</v>
-      </c>
-      <c r="H10" s="11">
-        <v>34</v>
-      </c>
-      <c r="I10" s="11">
-        <v>28</v>
-      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>5.625</v>
-      </c>
-      <c r="K10" s="12">
-        <v>10</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K10" s="12"/>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -4463,12 +4451,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W10" s="12">
-        <v>9</v>
-      </c>
+      <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>5.625</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -4476,7 +4462,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>5.625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -4484,33 +4470,31 @@
       <c r="B11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="11"/>
+      <c r="D11" s="11">
+        <v>12</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11">
+        <v>6</v>
+      </c>
+      <c r="G11" s="11">
+        <v>53</v>
+      </c>
+      <c r="H11" s="11">
+        <v>53</v>
+      </c>
+      <c r="I11" s="11">
         <v>106</v>
-      </c>
-      <c r="D11" s="11">
-        <v>6</v>
-      </c>
-      <c r="E11" s="11">
-        <v>0</v>
-      </c>
-      <c r="F11" s="11">
-        <v>0</v>
-      </c>
-      <c r="G11" s="11">
-        <v>86</v>
-      </c>
-      <c r="H11" s="11">
-        <v>52</v>
-      </c>
-      <c r="I11" s="11">
-        <v>133</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>9.5749999999999993</v>
+        <v>5.75</v>
       </c>
       <c r="K11" s="12">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
@@ -4528,12 +4512,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W11" s="12">
-        <v>11</v>
-      </c>
+      <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>9.5749999999999993</v>
+        <v>5.75</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -4541,7 +4523,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>9.5749999999999993</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -4549,33 +4531,31 @@
       <c r="B12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="11">
-        <v>24</v>
-      </c>
+      <c r="C12" s="11"/>
       <c r="D12" s="11">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="E12" s="11">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="F12" s="11">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="G12" s="11">
-        <v>25</v>
+        <v>146</v>
       </c>
       <c r="H12" s="11">
-        <v>20</v>
+        <v>122</v>
       </c>
       <c r="I12" s="11">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>2.6</v>
+        <v>16.7</v>
       </c>
       <c r="K12" s="12">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
@@ -4593,12 +4573,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W12" s="12">
-        <v>2</v>
-      </c>
+      <c r="W12" s="12"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>2.6</v>
+        <v>16.7</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
@@ -4606,7 +4584,7 @@
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>2.6</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -4614,34 +4592,18 @@
       <c r="B13" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="11">
-        <v>200</v>
-      </c>
-      <c r="D13" s="11">
-        <v>600</v>
-      </c>
-      <c r="E13" s="11">
-        <v>480</v>
-      </c>
-      <c r="F13" s="11">
-        <v>600</v>
-      </c>
-      <c r="G13" s="11">
-        <v>1080</v>
-      </c>
-      <c r="H13" s="11">
-        <v>800</v>
-      </c>
-      <c r="I13" s="11">
-        <v>720</v>
-      </c>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
       <c r="J13" s="15">
         <f t="shared" si="0"/>
-        <v>112</v>
-      </c>
-      <c r="K13" s="12">
-        <v>5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K13" s="12"/>
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
@@ -4658,9 +4620,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W13" s="12">
-        <v>4</v>
-      </c>
+      <c r="W13" s="12"/>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -4830,42 +4790,42 @@
       <c r="B18" s="7"/>
       <c r="C18" s="25">
         <f t="shared" ref="C18:I18" si="5">SUM(C8:C17)</f>
-        <v>598</v>
+        <v>0</v>
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>797</v>
+        <v>317</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>571</v>
+        <v>325</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>621</v>
+        <v>458</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>1486</v>
+        <v>399</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>1126</v>
+        <v>360</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>1346</v>
+        <v>395</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>6545</v>
+        <v>2254</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
@@ -4893,20 +4853,20 @@
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>51.625000000000007</v>
+        <v>56.349999999999994</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>49.625000000000007</v>
+        <v>56.349999999999994</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4916,35 +4876,35 @@
       </c>
       <c r="C19" s="21">
         <f t="shared" ref="C19:J19" si="7">C18/40</f>
-        <v>14.95</v>
+        <v>0</v>
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>19.925000000000001</v>
+        <v>7.9249999999999998</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>14.275</v>
+        <v>8.125</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>15.525</v>
+        <v>11.45</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>37.15</v>
+        <v>9.9749999999999996</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>28.15</v>
+        <v>9</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>33.65</v>
+        <v>9.875</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>163.625</v>
+        <v>56.35</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -4953,7 +4913,7 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
@@ -4981,20 +4941,20 @@
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>1.2906250000000001</v>
+        <v>1.4087499999999999</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>1.2406250000000001</v>
+        <v>1.4087499999999999</v>
       </c>
     </row>
   </sheetData>

--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D63B38-5381-43B7-A846-17271EBA1E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{352FA7C7-CA52-484F-BBB2-8B4D94A19E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="11" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="12" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1706" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="49">
   <si>
     <t>Booking</t>
   </si>
@@ -178,9 +178,6 @@
   </si>
   <si>
     <t>Leave</t>
-  </si>
-  <si>
-    <t>Sunday</t>
   </si>
   <si>
     <t xml:space="preserve">Monday </t>
@@ -568,7 +565,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -777,6 +774,25 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2748,7 +2764,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -2765,7 +2781,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -3656,7 +3672,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -3672,7 +3688,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -4590,7 +4606,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -4607,7 +4623,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -5009,9 +5025,6 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="L1" t="s">
-        <v>41</v>
-      </c>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -5243,38 +5256,52 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="15">
+      <c r="C8" s="90"/>
+      <c r="D8" s="90">
+        <v>145</v>
+      </c>
+      <c r="E8" s="90">
+        <v>60</v>
+      </c>
+      <c r="F8" s="90">
+        <v>105</v>
+      </c>
+      <c r="G8" s="90">
+        <v>150</v>
+      </c>
+      <c r="H8" s="90">
+        <v>134</v>
+      </c>
+      <c r="I8" s="90">
+        <v>120</v>
+      </c>
+      <c r="J8" s="91">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="7" t="s">
+        <v>17.850000000000001</v>
+      </c>
+      <c r="K8" s="92">
         <v>13</v>
       </c>
-      <c r="O8" s="43"/>
-      <c r="P8" s="43"/>
-      <c r="Q8" s="43"/>
-      <c r="R8" s="43"/>
-      <c r="S8" s="43"/>
-      <c r="T8" s="43"/>
-      <c r="U8" s="43"/>
-      <c r="V8" s="15">
+      <c r="L8" s="93"/>
+      <c r="M8" s="94"/>
+      <c r="N8" s="95" t="s">
+        <v>13</v>
+      </c>
+      <c r="O8" s="90"/>
+      <c r="P8" s="90"/>
+      <c r="Q8" s="90"/>
+      <c r="R8" s="90"/>
+      <c r="S8" s="90"/>
+      <c r="T8" s="90"/>
+      <c r="U8" s="90"/>
+      <c r="V8" s="91">
         <f>SUM(O8:U8)/40</f>
         <v>0</v>
       </c>
-      <c r="W8" s="12"/>
+      <c r="W8" s="92"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>17.850000000000001</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -5282,7 +5309,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>17.850000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -5290,38 +5317,52 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="15">
+      <c r="C9" s="90"/>
+      <c r="D9" s="90">
+        <v>100</v>
+      </c>
+      <c r="E9" s="90">
+        <v>30</v>
+      </c>
+      <c r="F9" s="90">
+        <v>92</v>
+      </c>
+      <c r="G9" s="90">
+        <v>92</v>
+      </c>
+      <c r="H9" s="90">
+        <v>46</v>
+      </c>
+      <c r="I9" s="90">
+        <v>61</v>
+      </c>
+      <c r="J9" s="91">
         <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="7" t="s">
+        <v>10.525</v>
+      </c>
+      <c r="K9" s="92">
+        <v>7</v>
+      </c>
+      <c r="L9" s="93"/>
+      <c r="M9" s="94"/>
+      <c r="N9" s="95" t="s">
         <v>14</v>
       </c>
-      <c r="O9" s="43"/>
-      <c r="P9" s="43"/>
-      <c r="Q9" s="43"/>
-      <c r="R9" s="43"/>
-      <c r="S9" s="43"/>
-      <c r="T9" s="43"/>
-      <c r="U9" s="43"/>
-      <c r="V9" s="15">
+      <c r="O9" s="90"/>
+      <c r="P9" s="90"/>
+      <c r="Q9" s="90"/>
+      <c r="R9" s="90"/>
+      <c r="S9" s="90"/>
+      <c r="T9" s="90"/>
+      <c r="U9" s="90"/>
+      <c r="V9" s="91">
         <f t="shared" ref="V9:V17" si="1">SUM(O9:U9)/40</f>
         <v>0</v>
       </c>
-      <c r="W9" s="12"/>
+      <c r="W9" s="92"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>0</v>
+        <v>10.525</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
@@ -5329,7 +5370,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>10.525</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -5337,35 +5378,35 @@
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="43"/>
-      <c r="J10" s="15">
+      <c r="C10" s="90"/>
+      <c r="D10" s="90"/>
+      <c r="E10" s="90"/>
+      <c r="F10" s="90"/>
+      <c r="G10" s="90"/>
+      <c r="H10" s="90"/>
+      <c r="I10" s="90"/>
+      <c r="J10" s="91">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K10" s="12"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="7" t="s">
+      <c r="K10" s="92"/>
+      <c r="L10" s="93"/>
+      <c r="M10" s="94"/>
+      <c r="N10" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="O10" s="43"/>
-      <c r="P10" s="43"/>
-      <c r="Q10" s="43"/>
-      <c r="R10" s="43"/>
-      <c r="S10" s="43"/>
-      <c r="T10" s="43"/>
-      <c r="U10" s="43"/>
-      <c r="V10" s="15">
+      <c r="O10" s="90"/>
+      <c r="P10" s="90"/>
+      <c r="Q10" s="90"/>
+      <c r="R10" s="90"/>
+      <c r="S10" s="90"/>
+      <c r="T10" s="90"/>
+      <c r="U10" s="90"/>
+      <c r="V10" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W10" s="12"/>
+      <c r="W10" s="92"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5384,38 +5425,52 @@
       <c r="B11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="43"/>
-      <c r="J11" s="15">
+      <c r="C11" s="90"/>
+      <c r="D11" s="90">
+        <v>23</v>
+      </c>
+      <c r="E11" s="90">
+        <v>17</v>
+      </c>
+      <c r="F11" s="90">
+        <v>33</v>
+      </c>
+      <c r="G11" s="90">
+        <v>154</v>
+      </c>
+      <c r="H11" s="90">
+        <v>86</v>
+      </c>
+      <c r="I11" s="90">
+        <v>113</v>
+      </c>
+      <c r="J11" s="91">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17" t="s">
+        <v>10.65</v>
+      </c>
+      <c r="K11" s="92">
+        <v>10</v>
+      </c>
+      <c r="L11" s="93"/>
+      <c r="M11" s="96"/>
+      <c r="N11" s="97" t="s">
         <v>29</v>
       </c>
-      <c r="O11" s="43"/>
-      <c r="P11" s="43"/>
-      <c r="Q11" s="43"/>
-      <c r="R11" s="43"/>
-      <c r="S11" s="43"/>
-      <c r="T11" s="43"/>
-      <c r="U11" s="43"/>
-      <c r="V11" s="15">
+      <c r="O11" s="90"/>
+      <c r="P11" s="90"/>
+      <c r="Q11" s="90"/>
+      <c r="R11" s="90"/>
+      <c r="S11" s="90"/>
+      <c r="T11" s="90"/>
+      <c r="U11" s="90"/>
+      <c r="V11" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W11" s="12"/>
+      <c r="W11" s="92"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10.65</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -5423,7 +5478,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10.65</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -5431,38 +5486,52 @@
       <c r="B12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="15">
+      <c r="C12" s="90"/>
+      <c r="D12" s="90">
+        <v>40</v>
+      </c>
+      <c r="E12" s="90">
+        <v>39</v>
+      </c>
+      <c r="F12" s="90">
+        <v>101</v>
+      </c>
+      <c r="G12" s="90">
+        <v>101</v>
+      </c>
+      <c r="H12" s="90">
+        <v>67</v>
+      </c>
+      <c r="I12" s="90">
+        <v>97</v>
+      </c>
+      <c r="J12" s="91">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17" t="s">
+        <v>11.125</v>
+      </c>
+      <c r="K12" s="92">
+        <v>11</v>
+      </c>
+      <c r="L12" s="93"/>
+      <c r="M12" s="96"/>
+      <c r="N12" s="97" t="s">
         <v>28</v>
       </c>
-      <c r="O12" s="43"/>
-      <c r="P12" s="43"/>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="43"/>
-      <c r="S12" s="43"/>
-      <c r="T12" s="43"/>
-      <c r="U12" s="43"/>
-      <c r="V12" s="15">
+      <c r="O12" s="90"/>
+      <c r="P12" s="90"/>
+      <c r="Q12" s="90"/>
+      <c r="R12" s="90"/>
+      <c r="S12" s="90"/>
+      <c r="T12" s="90"/>
+      <c r="U12" s="90"/>
+      <c r="V12" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W12" s="12"/>
+      <c r="W12" s="92"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11.125</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
@@ -5470,43 +5539,43 @@
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11.125</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="15">
+        <v>43</v>
+      </c>
+      <c r="C13" s="90"/>
+      <c r="D13" s="90"/>
+      <c r="E13" s="90"/>
+      <c r="F13" s="90"/>
+      <c r="G13" s="90"/>
+      <c r="H13" s="90"/>
+      <c r="I13" s="90"/>
+      <c r="J13" s="91">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K13" s="12"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="43"/>
-      <c r="T13" s="43"/>
-      <c r="U13" s="43"/>
-      <c r="V13" s="15">
+      <c r="K13" s="92"/>
+      <c r="L13" s="93"/>
+      <c r="M13" s="96"/>
+      <c r="N13" s="97" t="s">
+        <v>43</v>
+      </c>
+      <c r="O13" s="90"/>
+      <c r="P13" s="90"/>
+      <c r="Q13" s="90"/>
+      <c r="R13" s="90"/>
+      <c r="S13" s="90"/>
+      <c r="T13" s="90"/>
+      <c r="U13" s="90"/>
+      <c r="V13" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W13" s="12"/>
+      <c r="W13" s="92"/>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -5516,35 +5585,35 @@
       <c r="B14" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="15">
+      <c r="C14" s="90"/>
+      <c r="D14" s="90"/>
+      <c r="E14" s="90"/>
+      <c r="F14" s="90"/>
+      <c r="G14" s="90"/>
+      <c r="H14" s="90"/>
+      <c r="I14" s="90"/>
+      <c r="J14" s="91">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K14" s="12"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17" t="s">
+      <c r="K14" s="92"/>
+      <c r="L14" s="93"/>
+      <c r="M14" s="96"/>
+      <c r="N14" s="97" t="s">
         <v>17</v>
       </c>
-      <c r="O14" s="43"/>
-      <c r="P14" s="43"/>
-      <c r="Q14" s="43"/>
-      <c r="R14" s="43"/>
-      <c r="S14" s="43"/>
-      <c r="T14" s="43"/>
-      <c r="U14" s="43"/>
-      <c r="V14" s="15">
+      <c r="O14" s="90"/>
+      <c r="P14" s="90"/>
+      <c r="Q14" s="90"/>
+      <c r="R14" s="90"/>
+      <c r="S14" s="90"/>
+      <c r="T14" s="90"/>
+      <c r="U14" s="90"/>
+      <c r="V14" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W14" s="12"/>
+      <c r="W14" s="92"/>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
       <c r="AA14" s="38"/>
@@ -5554,35 +5623,35 @@
       <c r="B15" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="15">
+      <c r="C15" s="90"/>
+      <c r="D15" s="90"/>
+      <c r="E15" s="90"/>
+      <c r="F15" s="90"/>
+      <c r="G15" s="90"/>
+      <c r="H15" s="90"/>
+      <c r="I15" s="90"/>
+      <c r="J15" s="91">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K15" s="12"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17" t="s">
+      <c r="K15" s="92"/>
+      <c r="L15" s="93"/>
+      <c r="M15" s="96"/>
+      <c r="N15" s="97" t="s">
         <v>35</v>
       </c>
-      <c r="O15" s="43"/>
-      <c r="P15" s="43"/>
-      <c r="Q15" s="43"/>
-      <c r="R15" s="43"/>
-      <c r="S15" s="43"/>
-      <c r="T15" s="43"/>
-      <c r="U15" s="43"/>
-      <c r="V15" s="15">
+      <c r="O15" s="90"/>
+      <c r="P15" s="90"/>
+      <c r="Q15" s="90"/>
+      <c r="R15" s="90"/>
+      <c r="S15" s="90"/>
+      <c r="T15" s="90"/>
+      <c r="U15" s="90"/>
+      <c r="V15" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W15" s="12"/>
+      <c r="W15" s="92"/>
       <c r="Y15" s="36"/>
       <c r="Z15" s="37"/>
       <c r="AA15" s="38"/>
@@ -5592,35 +5661,35 @@
       <c r="B16" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="15">
+      <c r="C16" s="90"/>
+      <c r="D16" s="90"/>
+      <c r="E16" s="90"/>
+      <c r="F16" s="90"/>
+      <c r="G16" s="90"/>
+      <c r="H16" s="90"/>
+      <c r="I16" s="90"/>
+      <c r="J16" s="91">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K16" s="12"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17" t="s">
+      <c r="K16" s="92"/>
+      <c r="L16" s="93"/>
+      <c r="M16" s="96"/>
+      <c r="N16" s="97" t="s">
         <v>36</v>
       </c>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="15">
+      <c r="O16" s="90"/>
+      <c r="P16" s="90"/>
+      <c r="Q16" s="90"/>
+      <c r="R16" s="90"/>
+      <c r="S16" s="90"/>
+      <c r="T16" s="90"/>
+      <c r="U16" s="90"/>
+      <c r="V16" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W16" s="12"/>
+      <c r="W16" s="92"/>
       <c r="Y16" s="36"/>
       <c r="Z16" s="37"/>
       <c r="AA16" s="38"/>
@@ -5630,36 +5699,35 @@
       <c r="B17" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="15">
+      <c r="C17" s="90"/>
+      <c r="D17" s="90"/>
+      <c r="E17" s="90"/>
+      <c r="F17" s="90"/>
+      <c r="G17" s="90"/>
+      <c r="H17" s="90"/>
+      <c r="I17" s="90"/>
+      <c r="J17" s="91">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K17" s="12"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17" t="s">
+      <c r="K17" s="92"/>
+      <c r="L17" s="98"/>
+      <c r="M17" s="96"/>
+      <c r="N17" s="97" t="s">
         <v>38</v>
       </c>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
-      <c r="S17" s="11"/>
-      <c r="T17" s="11"/>
-      <c r="U17" s="11"/>
-      <c r="V17" s="15">
+      <c r="O17" s="90"/>
+      <c r="P17" s="90"/>
+      <c r="Q17" s="90"/>
+      <c r="R17" s="90"/>
+      <c r="S17" s="90"/>
+      <c r="T17" s="90"/>
+      <c r="U17" s="90"/>
+      <c r="V17" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W17" s="12">
-        <v>2</v>
-      </c>
+      <c r="W17" s="92"/>
       <c r="Y17" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5682,31 +5750,31 @@
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>308</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>331</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>391</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>0</v>
+        <v>2006</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
@@ -5746,7 +5814,7 @@
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>0</v>
+        <v>50.15</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
@@ -5754,7 +5822,7 @@
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>0</v>
+        <v>50.15</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5768,31 +5836,31 @@
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>8.2750000000000004</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>12.425000000000001</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>8.3249999999999993</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9.7750000000000004</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>50.15</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -5834,7 +5902,7 @@
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0</v>
+        <v>1.2537499999999999</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
@@ -5842,7 +5910,7 @@
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0</v>
+        <v>1.2537499999999999</v>
       </c>
     </row>
   </sheetData>
@@ -5898,7 +5966,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="M1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -6435,7 +6503,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11">
@@ -6466,7 +6534,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -7422,7 +7490,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -7439,7 +7507,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -8398,7 +8466,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -8416,7 +8484,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -9367,7 +9435,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -9384,7 +9452,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -10332,7 +10400,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -10349,7 +10417,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -11278,7 +11346,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -11295,7 +11363,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -13214,7 +13282,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="43"/>
       <c r="D13" s="43"/>
@@ -13231,7 +13299,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="43"/>
       <c r="P13" s="43"/>
@@ -14261,7 +14329,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -14278,7 +14346,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -15203,7 +15271,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -15221,7 +15289,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -16155,7 +16223,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11">
@@ -16186,7 +16254,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -17135,7 +17203,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -17160,7 +17228,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -18092,7 +18160,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -18109,7 +18177,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -19041,7 +19109,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -19058,7 +19126,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -19921,7 +19989,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -19938,7 +20006,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -20952,7 +21020,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11">
@@ -20981,7 +21049,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -22006,7 +22074,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11">
@@ -22037,7 +22105,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -23154,7 +23222,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -23171,7 +23239,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -23352,7 +23420,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11">
@@ -24294,7 +24362,7 @@
       <c r="L18" s="13"/>
       <c r="M18" s="16"/>
       <c r="N18" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O18" s="11"/>
       <c r="P18" s="11">
@@ -26233,7 +26301,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="43"/>
       <c r="D13" s="43"/>
@@ -26250,7 +26318,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="43"/>
       <c r="P13" s="43"/>
@@ -27268,7 +27336,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="59"/>
       <c r="B13" s="60" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="54"/>
       <c r="D13" s="54"/>
@@ -27285,7 +27353,7 @@
       <c r="L13" s="56"/>
       <c r="M13" s="16"/>
       <c r="N13" s="60" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -28309,7 +28377,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -28326,7 +28394,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -28501,7 +28569,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11">
@@ -28776,7 +28844,7 @@
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="X1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
@@ -28805,7 +28873,7 @@
       <c r="U2" s="77"/>
       <c r="V2" s="77"/>
       <c r="X2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -29348,7 +29416,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -29365,7 +29433,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -30376,7 +30444,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -30393,7 +30461,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -31371,7 +31439,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -31388,7 +31456,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>

--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{352FA7C7-CA52-484F-BBB2-8B4D94A19E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A643C5A2-AC90-4A78-9407-DBE588C60ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="12" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1707" uniqueCount="52">
   <si>
     <t>Booking</t>
   </si>
@@ -203,12 +203,24 @@
   <si>
     <t>Nabeel SD</t>
   </si>
+  <si>
+    <t>Nishat</t>
+  </si>
+  <si>
+    <t>Bedian road</t>
+  </si>
+  <si>
+    <t>Nabeel Traders</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -338,6 +350,23 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -562,10 +591,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -774,27 +806,11 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="4">
+    <cellStyle name="Comma 2 10" xfId="1" xr:uid="{AE1F4535-4203-4FAC-A25F-A3FC5C82F4CA}"/>
+    <cellStyle name="Comma 2170" xfId="2" xr:uid="{A3A2CD98-A5C9-4E32-9D03-99DC1324ECE2}"/>
+    <cellStyle name="Comma 4" xfId="3" xr:uid="{B2B0F83C-1332-4925-B670-C7673016AE04}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4063,7 +4079,7 @@
     <col min="7" max="9" width="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="4.36328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="3.54296875" bestFit="1" customWidth="1"/>
@@ -4095,6 +4111,12 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
+      <c r="W1" t="s">
+        <v>49</v>
+      </c>
+      <c r="X1" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
@@ -4349,28 +4371,42 @@
         <v>13</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>60</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>60</v>
+      </c>
+      <c r="R8" s="11">
+        <v>60</v>
+      </c>
+      <c r="S8" s="11">
+        <v>60</v>
+      </c>
+      <c r="T8" s="11">
+        <v>60</v>
+      </c>
+      <c r="U8" s="11">
+        <v>60</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>9</v>
+      </c>
+      <c r="W8" s="12">
+        <v>8</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>12</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -4410,28 +4446,42 @@
         <v>14</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>122</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>72</v>
+      </c>
+      <c r="R9" s="11">
+        <v>202</v>
+      </c>
+      <c r="S9" s="11">
+        <v>110</v>
+      </c>
+      <c r="T9" s="11">
+        <v>60</v>
+      </c>
+      <c r="U9" s="11">
+        <v>70</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V17" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>15.9</v>
+      </c>
+      <c r="W9" s="12">
+        <v>8</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
         <v>21.9</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>15.9</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>21.9</v>
+        <v>5.9999999999999982</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -4518,28 +4568,42 @@
         <v>29</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>12</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>0</v>
+      </c>
+      <c r="R11" s="11">
+        <v>6</v>
+      </c>
+      <c r="S11" s="11">
+        <v>53</v>
+      </c>
+      <c r="T11" s="11">
+        <v>53</v>
+      </c>
+      <c r="U11" s="11">
+        <v>106</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>5.75</v>
+      </c>
+      <c r="W11" s="12">
+        <v>9</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>5.75</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>5.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -4579,28 +4643,42 @@
         <v>28</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>36</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>121</v>
+      </c>
+      <c r="R12" s="11">
+        <v>127</v>
+      </c>
+      <c r="S12" s="11">
+        <v>126</v>
+      </c>
+      <c r="T12" s="11">
+        <v>110</v>
+      </c>
+      <c r="U12" s="11">
+        <v>56</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>14.4</v>
+      </c>
+      <c r="W12" s="12">
+        <v>7</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
         <v>16.7</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>14.4</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>16.7</v>
+        <v>2.2999999999999989</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -4623,10 +4701,12 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
+      <c r="P13" s="11">
+        <v>600</v>
+      </c>
       <c r="Q13" s="11"/>
       <c r="R13" s="11"/>
       <c r="S13" s="11"/>
@@ -4634,7 +4714,7 @@
       <c r="U13" s="11"/>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W13" s="12"/>
       <c r="Y13" s="36"/>
@@ -4664,15 +4744,27 @@
         <v>17</v>
       </c>
       <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
+      <c r="P14" s="11">
+        <v>440</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>440</v>
+      </c>
+      <c r="R14" s="11">
+        <v>480</v>
+      </c>
+      <c r="S14" s="11">
+        <v>680</v>
+      </c>
+      <c r="T14" s="11">
+        <v>720</v>
+      </c>
+      <c r="U14" s="11">
+        <v>920</v>
+      </c>
       <c r="V14" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="W14" s="12"/>
       <c r="Y14" s="36"/>
@@ -4845,31 +4937,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1270</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>693</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>875</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1029</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1003</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1212</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>6082</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -4878,11 +4970,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>45.05</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>56.349999999999994</v>
+        <v>11.299999999999997</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4933,31 +5025,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>31.75</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>17.324999999999999</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>21.875</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>25.725000000000001</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>25.074999999999999</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>30.3</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>152.05000000000001</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -4966,11 +5058,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>1.12625</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>1.4087499999999999</v>
+        <v>0.28249999999999992</v>
       </c>
     </row>
   </sheetData>
@@ -5008,7 +5100,7 @@
     <col min="18" max="18" width="3.08984375" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="3.6328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="5.453125" customWidth="1"/>
     <col min="25" max="25" width="7.453125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9.36328125" bestFit="1" customWidth="1"/>
@@ -5256,60 +5348,74 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="90"/>
-      <c r="D8" s="90">
+      <c r="C8" s="11"/>
+      <c r="D8" s="11">
         <v>145</v>
       </c>
-      <c r="E8" s="90">
+      <c r="E8" s="11">
         <v>60</v>
       </c>
-      <c r="F8" s="90">
+      <c r="F8" s="11">
         <v>105</v>
       </c>
-      <c r="G8" s="90">
+      <c r="G8" s="11">
         <v>150</v>
       </c>
-      <c r="H8" s="90">
+      <c r="H8" s="11">
         <v>134</v>
       </c>
-      <c r="I8" s="90">
+      <c r="I8" s="11">
         <v>120</v>
       </c>
-      <c r="J8" s="91">
+      <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
         <v>17.850000000000001</v>
       </c>
-      <c r="K8" s="92">
+      <c r="K8" s="12">
         <v>13</v>
       </c>
-      <c r="L8" s="93"/>
-      <c r="M8" s="94"/>
-      <c r="N8" s="95" t="s">
+      <c r="L8" s="13"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="90"/>
-      <c r="P8" s="90"/>
-      <c r="Q8" s="90"/>
-      <c r="R8" s="90"/>
-      <c r="S8" s="90"/>
-      <c r="T8" s="90"/>
-      <c r="U8" s="90"/>
-      <c r="V8" s="91">
+      <c r="O8" s="11"/>
+      <c r="P8" s="11">
+        <v>55</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>50</v>
+      </c>
+      <c r="R8" s="11">
+        <v>95</v>
+      </c>
+      <c r="S8" s="11">
+        <v>190</v>
+      </c>
+      <c r="T8" s="11">
+        <v>134</v>
+      </c>
+      <c r="U8" s="11">
+        <v>120</v>
+      </c>
+      <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="92"/>
+        <v>16.100000000000001</v>
+      </c>
+      <c r="W8" s="12">
+        <v>12</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>17.850000000000001</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>17.850000000000001</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -5317,60 +5423,74 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="90"/>
-      <c r="D9" s="90">
+      <c r="C9" s="11"/>
+      <c r="D9" s="11">
         <v>100</v>
       </c>
-      <c r="E9" s="90">
+      <c r="E9" s="11">
         <v>30</v>
       </c>
-      <c r="F9" s="90">
+      <c r="F9" s="11">
         <v>92</v>
       </c>
-      <c r="G9" s="90">
+      <c r="G9" s="11">
         <v>92</v>
       </c>
-      <c r="H9" s="90">
+      <c r="H9" s="11">
         <v>46</v>
       </c>
-      <c r="I9" s="90">
+      <c r="I9" s="11">
         <v>61</v>
       </c>
-      <c r="J9" s="91">
+      <c r="J9" s="15">
         <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
         <v>10.525</v>
       </c>
-      <c r="K9" s="92">
+      <c r="K9" s="12">
         <v>7</v>
       </c>
-      <c r="L9" s="93"/>
-      <c r="M9" s="94"/>
-      <c r="N9" s="95" t="s">
+      <c r="L9" s="13"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="O9" s="90"/>
-      <c r="P9" s="90"/>
-      <c r="Q9" s="90"/>
-      <c r="R9" s="90"/>
-      <c r="S9" s="90"/>
-      <c r="T9" s="90"/>
-      <c r="U9" s="90"/>
-      <c r="V9" s="91">
+      <c r="O9" s="11"/>
+      <c r="P9" s="11">
+        <v>65</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>20</v>
+      </c>
+      <c r="R9" s="11">
+        <v>77</v>
+      </c>
+      <c r="S9" s="11">
+        <v>92</v>
+      </c>
+      <c r="T9" s="11">
+        <v>46</v>
+      </c>
+      <c r="U9" s="11">
+        <v>61</v>
+      </c>
+      <c r="V9" s="15">
         <f t="shared" ref="V9:V17" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="92"/>
+        <v>9.0250000000000004</v>
+      </c>
+      <c r="W9" s="12">
+        <v>5</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
         <v>10.525</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>9.0250000000000004</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>10.525</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -5378,35 +5498,35 @@
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="90"/>
-      <c r="D10" s="90"/>
-      <c r="E10" s="90"/>
-      <c r="F10" s="90"/>
-      <c r="G10" s="90"/>
-      <c r="H10" s="90"/>
-      <c r="I10" s="90"/>
-      <c r="J10" s="91">
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K10" s="92"/>
-      <c r="L10" s="93"/>
-      <c r="M10" s="94"/>
-      <c r="N10" s="95" t="s">
+      <c r="K10" s="12"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O10" s="90"/>
-      <c r="P10" s="90"/>
-      <c r="Q10" s="90"/>
-      <c r="R10" s="90"/>
-      <c r="S10" s="90"/>
-      <c r="T10" s="90"/>
-      <c r="U10" s="90"/>
-      <c r="V10" s="91">
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="11"/>
+      <c r="T10" s="11"/>
+      <c r="U10" s="11"/>
+      <c r="V10" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W10" s="92"/>
+      <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5425,60 +5545,74 @@
       <c r="B11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="90"/>
-      <c r="D11" s="90">
+      <c r="C11" s="11"/>
+      <c r="D11" s="11">
         <v>23</v>
       </c>
-      <c r="E11" s="90">
+      <c r="E11" s="11">
         <v>17</v>
       </c>
-      <c r="F11" s="90">
+      <c r="F11" s="11">
         <v>33</v>
       </c>
-      <c r="G11" s="90">
+      <c r="G11" s="11">
         <v>154</v>
       </c>
-      <c r="H11" s="90">
+      <c r="H11" s="11">
         <v>86</v>
       </c>
-      <c r="I11" s="90">
+      <c r="I11" s="11">
         <v>113</v>
       </c>
-      <c r="J11" s="91">
+      <c r="J11" s="15">
         <f t="shared" si="0"/>
         <v>10.65</v>
       </c>
-      <c r="K11" s="92">
+      <c r="K11" s="12">
         <v>10</v>
       </c>
-      <c r="L11" s="93"/>
-      <c r="M11" s="96"/>
-      <c r="N11" s="97" t="s">
+      <c r="L11" s="13"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="O11" s="90"/>
-      <c r="P11" s="90"/>
-      <c r="Q11" s="90"/>
-      <c r="R11" s="90"/>
-      <c r="S11" s="90"/>
-      <c r="T11" s="90"/>
-      <c r="U11" s="90"/>
-      <c r="V11" s="91">
+      <c r="O11" s="11"/>
+      <c r="P11" s="11">
+        <v>23</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>17</v>
+      </c>
+      <c r="R11" s="11">
+        <v>33</v>
+      </c>
+      <c r="S11" s="11">
+        <v>123</v>
+      </c>
+      <c r="T11" s="11">
+        <v>75</v>
+      </c>
+      <c r="U11" s="11">
+        <v>108</v>
+      </c>
+      <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="92"/>
+        <v>9.4749999999999996</v>
+      </c>
+      <c r="W11" s="12">
+        <v>8</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>10.65</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.4749999999999996</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>10.65</v>
+        <v>1.1750000000000007</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -5486,60 +5620,74 @@
       <c r="B12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="90"/>
-      <c r="D12" s="90">
+      <c r="C12" s="11"/>
+      <c r="D12" s="11">
         <v>40</v>
       </c>
-      <c r="E12" s="90">
+      <c r="E12" s="11">
         <v>39</v>
       </c>
-      <c r="F12" s="90">
+      <c r="F12" s="11">
         <v>101</v>
       </c>
-      <c r="G12" s="90">
+      <c r="G12" s="11">
         <v>101</v>
       </c>
-      <c r="H12" s="90">
+      <c r="H12" s="11">
         <v>67</v>
       </c>
-      <c r="I12" s="90">
+      <c r="I12" s="11">
         <v>97</v>
       </c>
-      <c r="J12" s="91">
+      <c r="J12" s="15">
         <f t="shared" si="0"/>
         <v>11.125</v>
       </c>
-      <c r="K12" s="92">
+      <c r="K12" s="12">
         <v>11</v>
       </c>
-      <c r="L12" s="93"/>
-      <c r="M12" s="96"/>
-      <c r="N12" s="97" t="s">
+      <c r="L12" s="13"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="O12" s="90"/>
-      <c r="P12" s="90"/>
-      <c r="Q12" s="90"/>
-      <c r="R12" s="90"/>
-      <c r="S12" s="90"/>
-      <c r="T12" s="90"/>
-      <c r="U12" s="90"/>
-      <c r="V12" s="91">
+      <c r="O12" s="11"/>
+      <c r="P12" s="11">
+        <v>32</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>31</v>
+      </c>
+      <c r="R12" s="11">
+        <v>93</v>
+      </c>
+      <c r="S12" s="11">
+        <v>60</v>
+      </c>
+      <c r="T12" s="11">
+        <v>36</v>
+      </c>
+      <c r="U12" s="11">
+        <v>51</v>
+      </c>
+      <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="92"/>
+        <v>7.5750000000000002</v>
+      </c>
+      <c r="W12" s="12">
+        <v>8</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
         <v>11.125</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.5750000000000002</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>11.125</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -5547,35 +5695,35 @@
       <c r="B13" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="90"/>
-      <c r="D13" s="90"/>
-      <c r="E13" s="90"/>
-      <c r="F13" s="90"/>
-      <c r="G13" s="90"/>
-      <c r="H13" s="90"/>
-      <c r="I13" s="90"/>
-      <c r="J13" s="91">
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K13" s="92"/>
-      <c r="L13" s="93"/>
-      <c r="M13" s="96"/>
-      <c r="N13" s="97" t="s">
+      <c r="K13" s="12"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="O13" s="90"/>
-      <c r="P13" s="90"/>
-      <c r="Q13" s="90"/>
-      <c r="R13" s="90"/>
-      <c r="S13" s="90"/>
-      <c r="T13" s="90"/>
-      <c r="U13" s="90"/>
-      <c r="V13" s="91">
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
+      <c r="T13" s="11"/>
+      <c r="U13" s="11"/>
+      <c r="V13" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W13" s="92"/>
+      <c r="W13" s="12"/>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -5585,35 +5733,35 @@
       <c r="B14" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="90"/>
-      <c r="D14" s="90"/>
-      <c r="E14" s="90"/>
-      <c r="F14" s="90"/>
-      <c r="G14" s="90"/>
-      <c r="H14" s="90"/>
-      <c r="I14" s="90"/>
-      <c r="J14" s="91">
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K14" s="92"/>
-      <c r="L14" s="93"/>
-      <c r="M14" s="96"/>
-      <c r="N14" s="97" t="s">
+      <c r="K14" s="12"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="O14" s="90"/>
-      <c r="P14" s="90"/>
-      <c r="Q14" s="90"/>
-      <c r="R14" s="90"/>
-      <c r="S14" s="90"/>
-      <c r="T14" s="90"/>
-      <c r="U14" s="90"/>
-      <c r="V14" s="91">
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="11"/>
+      <c r="V14" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W14" s="92"/>
+      <c r="W14" s="12"/>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
       <c r="AA14" s="38"/>
@@ -5623,35 +5771,35 @@
       <c r="B15" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="90"/>
-      <c r="D15" s="90"/>
-      <c r="E15" s="90"/>
-      <c r="F15" s="90"/>
-      <c r="G15" s="90"/>
-      <c r="H15" s="90"/>
-      <c r="I15" s="90"/>
-      <c r="J15" s="91">
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K15" s="92"/>
-      <c r="L15" s="93"/>
-      <c r="M15" s="96"/>
-      <c r="N15" s="97" t="s">
+      <c r="K15" s="12"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="O15" s="90"/>
-      <c r="P15" s="90"/>
-      <c r="Q15" s="90"/>
-      <c r="R15" s="90"/>
-      <c r="S15" s="90"/>
-      <c r="T15" s="90"/>
-      <c r="U15" s="90"/>
-      <c r="V15" s="91">
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="11"/>
+      <c r="V15" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W15" s="92"/>
+      <c r="W15" s="12"/>
       <c r="Y15" s="36"/>
       <c r="Z15" s="37"/>
       <c r="AA15" s="38"/>
@@ -5661,35 +5809,35 @@
       <c r="B16" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="90"/>
-      <c r="D16" s="90"/>
-      <c r="E16" s="90"/>
-      <c r="F16" s="90"/>
-      <c r="G16" s="90"/>
-      <c r="H16" s="90"/>
-      <c r="I16" s="90"/>
-      <c r="J16" s="91">
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K16" s="92"/>
-      <c r="L16" s="93"/>
-      <c r="M16" s="96"/>
-      <c r="N16" s="97" t="s">
+      <c r="K16" s="12"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="O16" s="90"/>
-      <c r="P16" s="90"/>
-      <c r="Q16" s="90"/>
-      <c r="R16" s="90"/>
-      <c r="S16" s="90"/>
-      <c r="T16" s="90"/>
-      <c r="U16" s="90"/>
-      <c r="V16" s="91">
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="11"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="11"/>
+      <c r="V16" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W16" s="92"/>
+      <c r="W16" s="12"/>
       <c r="Y16" s="36"/>
       <c r="Z16" s="37"/>
       <c r="AA16" s="38"/>
@@ -5699,35 +5847,34 @@
       <c r="B17" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="90"/>
-      <c r="D17" s="90"/>
-      <c r="E17" s="90"/>
-      <c r="F17" s="90"/>
-      <c r="G17" s="90"/>
-      <c r="H17" s="90"/>
-      <c r="I17" s="90"/>
-      <c r="J17" s="91">
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K17" s="92"/>
-      <c r="L17" s="98"/>
-      <c r="M17" s="96"/>
-      <c r="N17" s="97" t="s">
+      <c r="K17" s="12"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O17" s="90"/>
-      <c r="P17" s="90"/>
-      <c r="Q17" s="90"/>
-      <c r="R17" s="90"/>
-      <c r="S17" s="90"/>
-      <c r="T17" s="90"/>
-      <c r="U17" s="90"/>
-      <c r="V17" s="91">
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11"/>
+      <c r="V17" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W17" s="92"/>
+      <c r="W17" s="12"/>
       <c r="Y17" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5785,31 +5932,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>298</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>465</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>1687</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -5818,11 +5965,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>42.175000000000004</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>50.15</v>
+        <v>7.9750000000000005</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5873,31 +6020,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.375</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7.45</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>11.625</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7.2750000000000004</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>42.174999999999997</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -5906,11 +6053,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>1.0543750000000001</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>1.2537499999999999</v>
+        <v>0.19937500000000002</v>
       </c>
     </row>
   </sheetData>
@@ -6198,42 +6345,25 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11">
-        <v>40</v>
-      </c>
-      <c r="D8" s="11">
-        <v>105</v>
-      </c>
-      <c r="E8" s="11">
-        <v>140</v>
-      </c>
-      <c r="F8" s="11">
-        <v>110</v>
-      </c>
-      <c r="G8" s="11">
-        <v>141</v>
-      </c>
-      <c r="H8" s="11">
-        <v>96</v>
-      </c>
-      <c r="I8" s="11">
-        <v>101</v>
-      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
       <c r="J8" s="15">
-        <f>SUM(C8:I8)/40</f>
-        <v>18.324999999999999</v>
+        <v>12</v>
       </c>
       <c r="K8" s="12">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11">
-        <v>40</v>
-      </c>
+      <c r="O8" s="11"/>
       <c r="P8" s="11"/>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
@@ -6242,22 +6372,20 @@
       <c r="U8" s="11"/>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>1</v>
-      </c>
-      <c r="W8" s="12">
-        <v>21</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>18.324999999999999</v>
+        <v>12</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>17.324999999999999</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -6266,17 +6394,31 @@
         <v>14</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="D9" s="11">
+        <v>40</v>
+      </c>
+      <c r="E9" s="11">
+        <v>29</v>
+      </c>
+      <c r="F9" s="11">
+        <v>50</v>
+      </c>
+      <c r="G9" s="11">
+        <v>155</v>
+      </c>
+      <c r="H9" s="11">
+        <v>98</v>
+      </c>
+      <c r="I9" s="11">
+        <v>170</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>13.55</v>
+      </c>
+      <c r="K9" s="12">
+        <v>20</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -6296,7 +6438,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>0</v>
+        <v>13.55</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
@@ -6304,7 +6446,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>13.55</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -6312,34 +6454,18 @@
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="11">
-        <v>300</v>
-      </c>
-      <c r="D10" s="11">
-        <v>132</v>
-      </c>
-      <c r="E10" s="11">
-        <v>132</v>
-      </c>
-      <c r="F10" s="11">
-        <v>172</v>
-      </c>
-      <c r="G10" s="11">
-        <v>148</v>
-      </c>
-      <c r="H10" s="11">
-        <v>146</v>
-      </c>
-      <c r="I10" s="11">
-        <v>226</v>
-      </c>
-      <c r="J10" s="15">
+      <c r="C10" s="72"/>
+      <c r="D10" s="72"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="72"/>
+      <c r="G10" s="72"/>
+      <c r="H10" s="72"/>
+      <c r="I10" s="72"/>
+      <c r="J10" s="73">
         <f t="shared" si="0"/>
-        <v>31.4</v>
-      </c>
-      <c r="K10" s="12">
-        <v>9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K10" s="12"/>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -6359,7 +6485,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>31.4</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -6367,7 +6493,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>31.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -6375,33 +6501,31 @@
       <c r="B11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="11">
-        <v>32</v>
-      </c>
+      <c r="C11" s="11"/>
       <c r="D11" s="11">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E11" s="11">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F11" s="11">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G11" s="11">
-        <v>163</v>
+        <v>45</v>
       </c>
       <c r="H11" s="11">
-        <v>133</v>
+        <v>30</v>
       </c>
       <c r="I11" s="11">
-        <v>134</v>
+        <v>45</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>14.6</v>
+        <v>6</v>
       </c>
       <c r="K11" s="12">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
@@ -6419,12 +6543,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W11" s="12">
-        <v>7</v>
-      </c>
+      <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>14.6</v>
+        <v>6</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -6432,7 +6554,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>14.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -6440,33 +6562,31 @@
       <c r="B12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="11">
-        <v>166</v>
-      </c>
+      <c r="C12" s="11"/>
       <c r="D12" s="11">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="E12" s="11">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="F12" s="11">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="G12" s="11">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="H12" s="11">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="I12" s="11">
         <v>56</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>11.1</v>
+        <v>7.7249999999999996</v>
       </c>
       <c r="K12" s="12">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
@@ -6484,12 +6604,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W12" s="12">
-        <v>10</v>
-      </c>
+      <c r="W12" s="12"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>11.1</v>
+        <v>7.7249999999999996</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
@@ -6497,7 +6615,7 @@
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>11.1</v>
+        <v>7.7249999999999996</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -6506,31 +6624,17 @@
         <v>43</v>
       </c>
       <c r="C13" s="11"/>
-      <c r="D13" s="11">
-        <v>500</v>
-      </c>
-      <c r="E13" s="11">
-        <v>760</v>
-      </c>
-      <c r="F13" s="11">
-        <v>840</v>
-      </c>
-      <c r="G13" s="11">
-        <v>480</v>
-      </c>
-      <c r="H13" s="11">
-        <v>500</v>
-      </c>
-      <c r="I13" s="11">
-        <v>660</v>
-      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
       <c r="J13" s="15">
         <f t="shared" si="0"/>
-        <v>93.5</v>
-      </c>
-      <c r="K13" s="12">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K13" s="12"/>
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
@@ -6565,10 +6669,11 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
       <c r="J14" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="12"/>
+        <v>166</v>
+      </c>
+      <c r="K14" s="12">
+        <v>5</v>
+      </c>
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
@@ -6603,10 +6708,11 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="12"/>
+        <v>16</v>
+      </c>
+      <c r="K15" s="12">
+        <v>26</v>
+      </c>
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
@@ -6641,10 +6747,11 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="12"/>
+        <v>10</v>
+      </c>
+      <c r="K16" s="12">
+        <v>14</v>
+      </c>
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
@@ -6679,10 +6786,11 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
       <c r="J17" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="18"/>
+        <v>8</v>
+      </c>
+      <c r="K17" s="18">
+        <v>10</v>
+      </c>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
         <v>38</v>
@@ -6698,7 +6806,7 @@
       <c r="W17" s="18"/>
       <c r="Y17" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z17" s="37">
         <f t="shared" si="3"/>
@@ -6706,7 +6814,7 @@
       </c>
       <c r="AA17" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
@@ -6714,42 +6822,42 @@
       <c r="B18" s="7"/>
       <c r="C18" s="25">
         <f t="shared" ref="C18:I18" si="5">SUM(C8:C17)</f>
-        <v>538</v>
+        <v>0</v>
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>811</v>
+        <v>177</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>1119</v>
+        <v>68</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>1193</v>
+        <v>110</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>988</v>
+        <v>317</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>931</v>
+        <v>148</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>1177</v>
+        <v>271</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>6757</v>
+        <v>1091</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
@@ -6777,20 +6885,20 @@
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>75.424999999999983</v>
+        <v>47.274999999999999</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>74.424999999999997</v>
+        <v>47.274999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6800,35 +6908,35 @@
       </c>
       <c r="C19" s="21">
         <f t="shared" ref="C19:J19" si="7">C18/40</f>
-        <v>13.45</v>
+        <v>0</v>
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>20.274999999999999</v>
+        <v>4.4249999999999998</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>27.975000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>29.824999999999999</v>
+        <v>2.75</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>24.7</v>
+        <v>7.9249999999999998</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>23.274999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>29.425000000000001</v>
+        <v>6.7750000000000004</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>168.92500000000001</v>
+        <v>27.274999999999999</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -6837,7 +6945,7 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
@@ -6865,20 +6973,20 @@
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>1.8856249999999997</v>
+        <v>1.181875</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>2.5000000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>1.860625</v>
+        <v>1.181875</v>
       </c>
     </row>
   </sheetData>

--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A643C5A2-AC90-4A78-9407-DBE588C60ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8671B80-C005-45B2-95A2-D5EF55B7DFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="12" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="14" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -6413,7 +6413,7 @@
         <v>170</v>
       </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
+        <f t="shared" ref="J9:J13" si="0">SUM(C9:I9)/40</f>
         <v>13.55</v>
       </c>
       <c r="K9" s="12">
@@ -7272,42 +7272,38 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11">
-        <v>107</v>
-      </c>
+      <c r="C8" s="11"/>
       <c r="D8" s="11">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="E8" s="11">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c r="F8" s="11">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G8" s="11">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="H8" s="11">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="I8" s="11">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>12.025</v>
+        <v>7.45</v>
       </c>
       <c r="K8" s="12">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11">
-        <v>83</v>
-      </c>
+      <c r="O8" s="11"/>
       <c r="P8" s="11"/>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
@@ -7316,22 +7312,20 @@
       <c r="U8" s="11"/>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>2.0750000000000002</v>
-      </c>
-      <c r="W8" s="12">
-        <v>21</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>12.025</v>
+        <v>7.45</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>2.0750000000000002</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>9.9499999999999993</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -7339,33 +7333,18 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11">
-        <v>52</v>
-      </c>
-      <c r="D9" s="11">
-        <v>43</v>
-      </c>
-      <c r="E9" s="11">
-        <v>84</v>
-      </c>
-      <c r="F9" s="11">
-        <v>45</v>
-      </c>
-      <c r="G9" s="11">
-        <v>46</v>
-      </c>
-      <c r="H9" s="11">
-        <v>70</v>
-      </c>
-      <c r="I9" s="11">
-        <v>61</v>
-      </c>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J13" si="0">SUM(C9:I9)/40</f>
-        <v>10.025</v>
+        <v>7</v>
       </c>
       <c r="K9" s="12">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
@@ -7380,23 +7359,21 @@
       <c r="T9" s="11"/>
       <c r="U9" s="11"/>
       <c r="V9" s="15">
-        <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12">
-        <v>14</v>
-      </c>
+        <f t="shared" ref="V9:V16" si="0">SUM(O9:U9)/40</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="12"/>
       <c r="Y9" s="36">
-        <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>10.025</v>
+        <f t="shared" ref="Y9:Y17" si="1">J9</f>
+        <v>7</v>
       </c>
       <c r="Z9" s="37">
-        <f t="shared" ref="Z9:Z17" si="3">V9</f>
+        <f t="shared" ref="Z9:Z17" si="2">V9</f>
         <v>0</v>
       </c>
       <c r="AA9" s="38">
-        <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>10.025</v>
+        <f t="shared" ref="AA9:AA17" si="3">Y9-Z9</f>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -7404,34 +7381,18 @@
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="11">
-        <v>276</v>
-      </c>
-      <c r="D10" s="11">
-        <v>6</v>
-      </c>
-      <c r="E10" s="11">
-        <v>6</v>
-      </c>
-      <c r="F10" s="11">
-        <v>0</v>
-      </c>
-      <c r="G10" s="11">
-        <v>34</v>
-      </c>
-      <c r="H10" s="11">
-        <v>68</v>
-      </c>
-      <c r="I10" s="11">
-        <v>38</v>
-      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
       <c r="J10" s="15">
-        <f t="shared" si="0"/>
-        <v>10.7</v>
-      </c>
-      <c r="K10" s="12">
-        <v>11</v>
-      </c>
+        <f t="shared" ref="J9:J13" si="4">SUM(C10:I10)/40</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="12"/>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -7445,24 +7406,21 @@
       <c r="T10" s="11"/>
       <c r="U10" s="11"/>
       <c r="V10" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="12"/>
+      <c r="Y10" s="36">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W10" s="12">
-        <f>7+9</f>
-        <v>16</v>
-      </c>
-      <c r="Y10" s="36">
+      <c r="Z10" s="37">
         <f t="shared" si="2"/>
-        <v>10.7</v>
-      </c>
-      <c r="Z10" s="37">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
-      </c>
-      <c r="AA10" s="38">
-        <f t="shared" si="4"/>
-        <v>10.7</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -7470,33 +7428,31 @@
       <c r="B11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="11">
-        <v>136</v>
-      </c>
+      <c r="C11" s="11"/>
       <c r="D11" s="11">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="E11" s="11">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F11" s="11">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="G11" s="11">
-        <v>106</v>
+        <v>60</v>
       </c>
       <c r="H11" s="11">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I11" s="11">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="J11" s="15">
-        <f t="shared" si="0"/>
-        <v>14.574999999999999</v>
+        <f t="shared" si="4"/>
+        <v>3.05</v>
       </c>
       <c r="K11" s="12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
@@ -7511,23 +7467,21 @@
       <c r="T11" s="11"/>
       <c r="U11" s="11"/>
       <c r="V11" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W11" s="12"/>
+      <c r="Y11" s="36">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12">
-        <v>9</v>
-      </c>
-      <c r="Y11" s="36">
+        <v>3.05</v>
+      </c>
+      <c r="Z11" s="37">
         <f t="shared" si="2"/>
-        <v>14.574999999999999</v>
-      </c>
-      <c r="Z11" s="37">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="38">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA11" s="38">
-        <f t="shared" si="4"/>
-        <v>14.574999999999999</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -7535,33 +7489,31 @@
       <c r="B12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="11">
-        <v>142</v>
-      </c>
+      <c r="C12" s="11"/>
       <c r="D12" s="11">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="E12" s="11">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="F12" s="11">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="G12" s="11">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H12" s="11">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="I12" s="11">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="J12" s="15">
-        <f t="shared" si="0"/>
-        <v>12.925000000000001</v>
+        <f t="shared" si="4"/>
+        <v>4.1500000000000004</v>
       </c>
       <c r="K12" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
@@ -7576,23 +7528,21 @@
       <c r="T12" s="11"/>
       <c r="U12" s="11"/>
       <c r="V12" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W12" s="12"/>
+      <c r="Y12" s="36">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="36">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="Z12" s="37">
         <f t="shared" si="2"/>
-        <v>12.925000000000001</v>
-      </c>
-      <c r="Z12" s="37">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="38">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA12" s="38">
-        <f t="shared" si="4"/>
-        <v>12.925000000000001</v>
+        <v>4.1500000000000004</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -7608,7 +7558,7 @@
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
       <c r="J13" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K13" s="12"/>
@@ -7625,12 +7575,10 @@
       <c r="T13" s="11"/>
       <c r="U13" s="11"/>
       <c r="V13" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12">
-        <v>4</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W13" s="12"/>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -7650,9 +7598,7 @@
       <c r="J14" s="15">
         <v>0</v>
       </c>
-      <c r="K14" s="12">
-        <v>0</v>
-      </c>
+      <c r="K14" s="12"/>
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
@@ -7666,7 +7612,7 @@
       <c r="T14" s="11"/>
       <c r="U14" s="11"/>
       <c r="V14" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W14" s="12"/>
@@ -7687,10 +7633,10 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="15">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="K15" s="12">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
@@ -7705,7 +7651,7 @@
       <c r="T15" s="11"/>
       <c r="U15" s="11"/>
       <c r="V15" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W15" s="12"/>
@@ -7726,10 +7672,10 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K16" s="12">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
@@ -7744,7 +7690,7 @@
       <c r="T16" s="11"/>
       <c r="U16" s="11"/>
       <c r="V16" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W16" s="12"/>
@@ -7765,9 +7711,11 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
       <c r="J17" s="15">
-        <v>8</v>
-      </c>
-      <c r="K17" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="K17" s="18">
+        <v>6</v>
+      </c>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
         <v>38</v>
@@ -7782,16 +7730,16 @@
       <c r="V17" s="15"/>
       <c r="W17" s="18"/>
       <c r="Y17" s="36">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="Z17" s="37">
         <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="Z17" s="37">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="38">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA17" s="38">
-        <f t="shared" si="4"/>
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
@@ -7799,42 +7747,42 @@
       <c r="B18" s="7"/>
       <c r="C18" s="25">
         <f t="shared" ref="C18:I18" si="5">SUM(C8:C17)</f>
-        <v>713</v>
+        <v>0</v>
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>335</v>
+        <v>33</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>314</v>
+        <v>28</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>170</v>
+        <v>61</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>301</v>
+        <v>220</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>267</v>
+        <v>109</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>310</v>
+        <v>135</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>2410</v>
+        <v>586</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
@@ -7862,20 +7810,20 @@
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>68.25</v>
+        <v>25.65</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>2.0750000000000002</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>66.174999999999997</v>
+        <v>25.65</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7885,35 +7833,35 @@
       </c>
       <c r="C19" s="21">
         <f t="shared" ref="C19:J19" si="7">C18/40</f>
-        <v>17.824999999999999</v>
+        <v>0</v>
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>8.375</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>7.85</v>
+        <v>0.7</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>4.25</v>
+        <v>1.5249999999999999</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>7.5250000000000004</v>
+        <v>5.5</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>6.6749999999999998</v>
+        <v>2.7250000000000001</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>7.75</v>
+        <v>3.375</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>60.25</v>
+        <v>14.65</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -7922,7 +7870,7 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>2.0750000000000002</v>
+        <v>0</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
@@ -7950,20 +7898,20 @@
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>2.0750000000000002</v>
+        <v>0</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>1.70625</v>
+        <v>0.64124999999999999</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>5.1875000000000004E-2</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>1.6543749999999999</v>
+        <v>0.64124999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8671B80-C005-45B2-95A2-D5EF55B7DFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E816C013-D550-49D3-8AE2-F84FABAD0BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="14" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1707" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1887" uniqueCount="53">
   <si>
     <t>Booking</t>
   </si>
@@ -211,6 +211,9 @@
   </si>
   <si>
     <t>Nabeel Traders</t>
+  </si>
+  <si>
+    <t>Off</t>
   </si>
 </sst>
 </file>
@@ -597,7 +600,7 @@
     <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -806,6 +809,27 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma 2 10" xfId="1" xr:uid="{AE1F4535-4203-4FAC-A25F-A3FC5C82F4CA}"/>
@@ -6364,28 +6388,42 @@
         <v>13</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>50</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>50</v>
+      </c>
+      <c r="R8" s="11">
+        <v>60</v>
+      </c>
+      <c r="S8" s="11">
+        <v>80</v>
+      </c>
+      <c r="T8" s="11">
+        <v>40</v>
+      </c>
+      <c r="U8" s="11">
+        <v>80</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>9</v>
+      </c>
+      <c r="W8" s="12">
+        <v>9</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>12</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -6425,28 +6463,42 @@
         <v>14</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>25</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>19</v>
+      </c>
+      <c r="R9" s="11">
+        <v>35</v>
+      </c>
+      <c r="S9" s="11">
+        <v>140</v>
+      </c>
+      <c r="T9" s="11">
+        <v>88</v>
+      </c>
+      <c r="U9" s="11">
+        <v>155</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>11.55</v>
+      </c>
+      <c r="W9" s="12">
+        <v>19</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
         <v>13.55</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>11.55</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>13.55</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -6471,14 +6523,14 @@
       <c r="N10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O10" s="72"/>
-      <c r="P10" s="72"/>
-      <c r="Q10" s="72"/>
-      <c r="R10" s="72"/>
-      <c r="S10" s="72"/>
-      <c r="T10" s="72"/>
-      <c r="U10" s="72"/>
-      <c r="V10" s="73">
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9"/>
+      <c r="S10" s="9"/>
+      <c r="T10" s="9"/>
+      <c r="U10" s="9"/>
+      <c r="V10" s="90">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6532,14 +6584,14 @@
       <c r="N11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
-      <c r="V11" s="15">
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="9"/>
+      <c r="T11" s="9"/>
+      <c r="U11" s="9"/>
+      <c r="V11" s="90">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6594,28 +6646,42 @@
         <v>28</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>52</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>0</v>
+      </c>
+      <c r="R12" s="11">
+        <v>0</v>
+      </c>
+      <c r="S12" s="11">
+        <v>68</v>
+      </c>
+      <c r="T12" s="11">
+        <v>20</v>
+      </c>
+      <c r="U12" s="11">
+        <v>56</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="W12" s="12">
+        <v>5</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
         <v>7.7249999999999996</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>7.7249999999999996</v>
+        <v>2.8249999999999993</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -6861,31 +6927,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>1018</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -6894,11 +6960,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>25.450000000000003</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>47.274999999999999</v>
+        <v>21.824999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6949,31 +7015,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.1749999999999998</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1.7250000000000001</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.375</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7.2750000000000004</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>25.45</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -6982,11 +7048,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>0.63625000000000009</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>1.181875</v>
+        <v>0.54562500000000003</v>
       </c>
     </row>
   </sheetData>
@@ -7304,28 +7370,42 @@
         <v>13</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>6</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>6</v>
+      </c>
+      <c r="R8" s="11">
+        <v>16</v>
+      </c>
+      <c r="S8" s="11">
+        <v>55</v>
+      </c>
+      <c r="T8" s="11">
+        <v>40</v>
+      </c>
+      <c r="U8" s="11">
+        <v>55</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>4.45</v>
+      </c>
+      <c r="W8" s="12">
+        <v>5</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>7.45</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>7.45</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -7389,7 +7469,7 @@
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
       <c r="J10" s="15">
-        <f t="shared" ref="J9:J13" si="4">SUM(C10:I10)/40</f>
+        <f t="shared" ref="J10:J13" si="4">SUM(C10:I10)/40</f>
         <v>0</v>
       </c>
       <c r="K10" s="12"/>
@@ -7460,28 +7540,42 @@
         <v>29</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>0</v>
+      </c>
+      <c r="R11" s="11">
+        <v>0</v>
+      </c>
+      <c r="S11" s="11">
+        <v>40</v>
+      </c>
+      <c r="T11" s="11">
+        <v>0</v>
+      </c>
+      <c r="U11" s="11">
+        <v>6</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="W11" s="12">
+        <v>1</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="1"/>
         <v>3.05</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="3"/>
-        <v>3.05</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -7521,28 +7615,42 @@
         <v>28</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>0</v>
+      </c>
+      <c r="R12" s="11">
+        <v>0</v>
+      </c>
+      <c r="S12" s="11">
+        <v>6</v>
+      </c>
+      <c r="T12" s="11">
+        <v>17</v>
+      </c>
+      <c r="U12" s="11">
+        <v>17</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>1.3</v>
+      </c>
+      <c r="W12" s="12">
+        <v>2</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="1"/>
         <v>4.1500000000000004</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="3"/>
-        <v>4.1500000000000004</v>
+        <v>2.8500000000000005</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -7786,31 +7894,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -7819,11 +7927,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>6.8999999999999995</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>25.65</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7874,31 +7982,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.5249999999999999</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1.425</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -7907,11 +8015,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>0.17249999999999999</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.64124999999999999</v>
+        <v>0.46875</v>
       </c>
     </row>
   </sheetData>
@@ -7930,7 +8038,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B31058E7-4F6C-46ED-9090-75BF8B81EBB6}">
-  <dimension ref="A1:AA19"/>
+  <dimension ref="A1:AA21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -8197,66 +8305,76 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11">
-        <v>255</v>
-      </c>
-      <c r="D8" s="11">
-        <v>56</v>
-      </c>
-      <c r="E8" s="11">
-        <v>56</v>
-      </c>
-      <c r="F8" s="11">
-        <v>0</v>
-      </c>
-      <c r="G8" s="11">
-        <v>70</v>
-      </c>
-      <c r="H8" s="11">
-        <v>75</v>
-      </c>
-      <c r="I8" s="11">
-        <v>80</v>
-      </c>
-      <c r="J8" s="15">
-        <f>SUM(C8:I8)/40</f>
-        <v>14.8</v>
-      </c>
-      <c r="K8" s="12">
-        <v>23</v>
-      </c>
-      <c r="L8" s="13"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="7" t="s">
+      <c r="C8" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="I8" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="K8" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="L8" s="96"/>
+      <c r="M8" s="97"/>
+      <c r="N8" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11">
-        <v>135</v>
-      </c>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
-      <c r="V8" s="15">
-        <f>SUM(O8:U8)/40</f>
-        <v>3.375</v>
-      </c>
-      <c r="W8" s="12">
-        <v>21</v>
-      </c>
-      <c r="Y8" s="36">
+      <c r="O8" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="P8" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q8" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="R8" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="S8" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="T8" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="U8" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="V8" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="W8" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y8" s="36" t="str">
         <f>J8</f>
-        <v>14.8</v>
-      </c>
-      <c r="Z8" s="37">
+        <v>Off</v>
+      </c>
+      <c r="Z8" s="37" t="str">
         <f>V8</f>
-        <v>3.375</v>
-      </c>
-      <c r="AA8" s="38">
+        <v>Off</v>
+      </c>
+      <c r="AA8" s="38" t="e">
         <f>Y8-Z8</f>
-        <v>11.425000000000001</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -8264,64 +8382,76 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11">
-        <v>80</v>
-      </c>
-      <c r="D9" s="11">
+      <c r="C9" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="11">
-        <v>18</v>
-      </c>
-      <c r="F9" s="11">
-        <v>35</v>
-      </c>
-      <c r="G9" s="11">
-        <v>157</v>
-      </c>
-      <c r="H9" s="11">
-        <v>153</v>
-      </c>
-      <c r="I9" s="11">
-        <v>185</v>
-      </c>
-      <c r="J9" s="15">
-        <f>SUM(C9:I9)/40</f>
-        <v>17</v>
-      </c>
-      <c r="K9" s="12">
-        <v>22</v>
-      </c>
-      <c r="L9" s="13"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="7" t="s">
+      <c r="D9" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="J9" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="K9" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="L9" s="96"/>
+      <c r="M9" s="97"/>
+      <c r="N9" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
-      <c r="V9" s="15">
-        <f t="shared" ref="V9:V16" si="0">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12">
-        <v>21</v>
-      </c>
-      <c r="Y9" s="36">
-        <f t="shared" ref="Y9:Y17" si="1">J9</f>
-        <v>17</v>
-      </c>
-      <c r="Z9" s="37">
-        <f t="shared" ref="Z9:Z17" si="2">V9</f>
-        <v>0</v>
-      </c>
-      <c r="AA9" s="38">
-        <f t="shared" ref="AA9:AA17" si="3">Y9-Z9</f>
-        <v>17</v>
+      <c r="O9" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="P9" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q9" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="R9" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="S9" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="T9" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="U9" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="V9" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="W9" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y9" s="36" t="str">
+        <f t="shared" ref="Y9:Y17" si="0">J9</f>
+        <v>Off</v>
+      </c>
+      <c r="Z9" s="37" t="str">
+        <f t="shared" ref="Z9:Z17" si="1">V9</f>
+        <v>Off</v>
+      </c>
+      <c r="AA9" s="38" t="e">
+        <f t="shared" ref="AA9:AA17" si="2">Y9-Z9</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -8329,64 +8459,76 @@
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="11">
-        <v>252</v>
-      </c>
-      <c r="D10" s="11">
-        <v>6</v>
-      </c>
-      <c r="E10" s="11">
-        <v>6</v>
-      </c>
-      <c r="F10" s="11">
-        <v>6</v>
-      </c>
-      <c r="G10" s="11">
+      <c r="C10" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="I10" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="J10" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="K10" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="L10" s="96"/>
+      <c r="M10" s="97"/>
+      <c r="N10" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="11">
-        <v>13</v>
-      </c>
-      <c r="I10" s="11">
-        <v>13</v>
-      </c>
-      <c r="J10" s="15">
-        <f t="shared" ref="J10:J17" si="4">SUM(C10:I10)/40</f>
-        <v>7.7750000000000004</v>
-      </c>
-      <c r="K10" s="12">
-        <v>7</v>
-      </c>
-      <c r="L10" s="13"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
-      <c r="V10" s="15">
+      <c r="O10" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="P10" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q10" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="R10" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="S10" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="T10" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="U10" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="V10" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="W10" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y10" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12">
-        <v>6</v>
-      </c>
-      <c r="Y10" s="36">
+        <v>Off</v>
+      </c>
+      <c r="Z10" s="37" t="str">
         <f t="shared" si="1"/>
-        <v>7.7750000000000004</v>
-      </c>
-      <c r="Z10" s="37">
+        <v>Off</v>
+      </c>
+      <c r="AA10" s="38" t="e">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AA10" s="38">
-        <f t="shared" si="3"/>
-        <v>7.7750000000000004</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -8394,64 +8536,76 @@
       <c r="B11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="11">
-        <v>44</v>
-      </c>
-      <c r="D11" s="11">
-        <v>0</v>
-      </c>
-      <c r="E11" s="11">
-        <v>0</v>
-      </c>
-      <c r="F11" s="11">
-        <v>40</v>
-      </c>
-      <c r="G11" s="11">
-        <v>50</v>
-      </c>
-      <c r="H11" s="11">
-        <v>50</v>
-      </c>
-      <c r="I11" s="11">
-        <v>100</v>
-      </c>
-      <c r="J11" s="15">
-        <f t="shared" si="4"/>
-        <v>7.1</v>
-      </c>
-      <c r="K11" s="12">
-        <v>4</v>
-      </c>
-      <c r="L11" s="13"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17" t="s">
+      <c r="C11" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="I11" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="J11" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="K11" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="L11" s="96"/>
+      <c r="M11" s="98"/>
+      <c r="N11" s="92" t="s">
         <v>29</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
-      <c r="V11" s="15">
+      <c r="O11" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="P11" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q11" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="R11" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="S11" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="T11" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="U11" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="V11" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="W11" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y11" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12">
-        <v>4</v>
-      </c>
-      <c r="Y11" s="36">
+        <v>Off</v>
+      </c>
+      <c r="Z11" s="37" t="str">
         <f t="shared" si="1"/>
-        <v>7.1</v>
-      </c>
-      <c r="Z11" s="37">
+        <v>Off</v>
+      </c>
+      <c r="AA11" s="38" t="e">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AA11" s="38">
-        <f t="shared" si="3"/>
-        <v>7.1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -8459,64 +8613,76 @@
       <c r="B12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="11">
-        <v>150</v>
-      </c>
-      <c r="D12" s="11">
-        <v>40</v>
-      </c>
-      <c r="E12" s="11">
-        <v>41</v>
-      </c>
-      <c r="F12" s="11">
-        <v>26</v>
-      </c>
-      <c r="G12" s="11">
-        <v>21</v>
-      </c>
-      <c r="H12" s="11">
-        <v>5</v>
-      </c>
-      <c r="I12" s="11">
-        <v>10</v>
-      </c>
-      <c r="J12" s="15">
-        <f t="shared" si="4"/>
-        <v>7.3250000000000002</v>
-      </c>
-      <c r="K12" s="12">
-        <v>12</v>
-      </c>
-      <c r="L12" s="13"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17" t="s">
+      <c r="C12" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="I12" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="J12" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="K12" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="L12" s="96"/>
+      <c r="M12" s="98"/>
+      <c r="N12" s="92" t="s">
         <v>28</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="15">
+      <c r="O12" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="P12" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q12" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="R12" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="S12" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="T12" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="U12" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="V12" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="W12" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y12" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12">
-        <v>5</v>
-      </c>
-      <c r="Y12" s="36">
+        <v>Off</v>
+      </c>
+      <c r="Z12" s="37" t="str">
         <f t="shared" si="1"/>
-        <v>7.3250000000000002</v>
-      </c>
-      <c r="Z12" s="37">
+        <v>Off</v>
+      </c>
+      <c r="AA12" s="38" t="e">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AA12" s="38">
-        <f t="shared" si="3"/>
-        <v>7.3250000000000002</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -8524,37 +8690,64 @@
       <c r="B13" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="15">
-        <v>93</v>
-      </c>
-      <c r="K13" s="12">
-        <v>1</v>
-      </c>
-      <c r="L13" s="13"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17" t="s">
+      <c r="C13" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="H13" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="I13" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="J13" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="K13" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="L13" s="96"/>
+      <c r="M13" s="98"/>
+      <c r="N13" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12">
-        <v>1</v>
+      <c r="O13" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="P13" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q13" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="R13" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="S13" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="T13" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="U13" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="V13" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="W13" s="43" t="s">
+        <v>52</v>
       </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
@@ -8565,36 +8758,65 @@
       <c r="B14" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="15">
-        <v>20</v>
-      </c>
-      <c r="K14" s="12">
+      <c r="C14" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="I14" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="J14" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="K14" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="L14" s="96"/>
+      <c r="M14" s="98"/>
+      <c r="N14" s="92" t="s">
         <v>17</v>
       </c>
-      <c r="L14" s="13"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="12"/>
+      <c r="O14" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="P14" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q14" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="R14" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="S14" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="T14" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="U14" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="V14" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="W14" s="43" t="s">
+        <v>52</v>
+      </c>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
       <c r="AA14" s="38"/>
@@ -8604,35 +8826,65 @@
       <c r="B15" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="15">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="12"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17" t="s">
+      <c r="C15" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="I15" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="J15" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="K15" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="L15" s="96"/>
+      <c r="M15" s="98"/>
+      <c r="N15" s="92" t="s">
         <v>35</v>
       </c>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="11"/>
-      <c r="S15" s="11"/>
-      <c r="T15" s="11"/>
-      <c r="U15" s="11"/>
-      <c r="V15" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W15" s="12"/>
+      <c r="O15" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="P15" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q15" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="R15" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="S15" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="T15" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="U15" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="V15" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="W15" s="43" t="s">
+        <v>52</v>
+      </c>
       <c r="Y15" s="36"/>
       <c r="Z15" s="37"/>
       <c r="AA15" s="38"/>
@@ -8642,35 +8894,65 @@
       <c r="B16" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="15">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="12"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17" t="s">
+      <c r="C16" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="J16" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="K16" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="L16" s="96"/>
+      <c r="M16" s="98"/>
+      <c r="N16" s="92" t="s">
         <v>36</v>
       </c>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W16" s="12"/>
+      <c r="O16" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="P16" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q16" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="R16" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="S16" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="T16" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="U16" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="V16" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="W16" s="43" t="s">
+        <v>52</v>
+      </c>
       <c r="Y16" s="36"/>
       <c r="Z16" s="37"/>
       <c r="AA16" s="38"/>
@@ -8680,126 +8962,161 @@
       <c r="B17" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="15">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="18"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17" t="s">
+      <c r="C17" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="F17" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="I17" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="J17" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="K17" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="L17" s="99"/>
+      <c r="M17" s="98"/>
+      <c r="N17" s="92" t="s">
         <v>38</v>
       </c>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
-      <c r="S17" s="11"/>
-      <c r="T17" s="11"/>
-      <c r="U17" s="11"/>
-      <c r="V17" s="15"/>
-      <c r="W17" s="18"/>
-      <c r="Y17" s="36">
+      <c r="O17" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="P17" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q17" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="R17" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="S17" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="T17" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="U17" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="V17" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="W17" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y17" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v>Off</v>
+      </c>
+      <c r="Z17" s="37" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z17" s="37">
+        <v>Off</v>
+      </c>
+      <c r="AA17" s="38" t="e">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AA17" s="38">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="7"/>
-      <c r="C18" s="25">
-        <f t="shared" ref="C18:I18" si="5">SUM(C8:C17)</f>
-        <v>781</v>
-      </c>
-      <c r="D18" s="25">
-        <f t="shared" si="5"/>
-        <v>154</v>
-      </c>
-      <c r="E18" s="25">
-        <f t="shared" si="5"/>
-        <v>121</v>
-      </c>
-      <c r="F18" s="25">
-        <f t="shared" si="5"/>
-        <v>107</v>
-      </c>
-      <c r="G18" s="25">
-        <f t="shared" si="5"/>
-        <v>313</v>
-      </c>
-      <c r="H18" s="25">
-        <f t="shared" si="5"/>
-        <v>296</v>
-      </c>
-      <c r="I18" s="25">
-        <f t="shared" si="5"/>
-        <v>388</v>
-      </c>
-      <c r="J18" s="26">
+      <c r="C18" s="93">
+        <f t="shared" ref="C18:I18" si="3">SUM(C8:C17)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E18" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="94">
         <f>SUM(C18:I18)</f>
-        <v>2160</v>
-      </c>
-      <c r="K18" s="28"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="25">
-        <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>135</v>
-      </c>
-      <c r="P18" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R18" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S18" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T18" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U18" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="V18" s="26">
+        <v>0</v>
+      </c>
+      <c r="K18" s="95"/>
+      <c r="L18" s="99"/>
+      <c r="M18" s="100"/>
+      <c r="N18" s="91"/>
+      <c r="O18" s="93">
+        <f t="shared" ref="O18:U18" si="4">SUM(O8:O17)</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="R18" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="94">
         <f>SUM(O18:U18)</f>
-        <v>135</v>
-      </c>
-      <c r="W18" s="28"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="95"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>54.000000000000007</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>3.375</v>
-      </c>
-      <c r="AA18" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="35" t="e">
         <f>SUM(AA8:AA17)</f>
-        <v>50.625000000000007</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -8808,87 +9125,96 @@
         <v>18</v>
       </c>
       <c r="C19" s="21">
-        <f t="shared" ref="C19:J19" si="7">C18/40</f>
-        <v>19.524999999999999</v>
+        <f t="shared" ref="C19:J19" si="5">C18/40</f>
+        <v>0</v>
       </c>
       <c r="D19" s="21">
-        <f t="shared" si="7"/>
-        <v>3.85</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="E19" s="21">
-        <f t="shared" si="7"/>
-        <v>3.0249999999999999</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="F19" s="21">
-        <f t="shared" si="7"/>
-        <v>2.6749999999999998</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="G19" s="21">
-        <f t="shared" si="7"/>
-        <v>7.8250000000000002</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="H19" s="21">
-        <f t="shared" si="7"/>
-        <v>7.4</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="I19" s="21">
-        <f t="shared" si="7"/>
-        <v>9.6999999999999993</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="J19" s="22">
-        <f t="shared" si="7"/>
-        <v>54</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="K19" s="23"/>
-      <c r="M19" s="1"/>
+      <c r="L19" s="99"/>
+      <c r="M19" s="100"/>
       <c r="N19" s="20" t="s">
         <v>18</v>
       </c>
       <c r="O19" s="21">
-        <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>3.375</v>
+        <f t="shared" ref="O19:V19" si="6">O18/40</f>
+        <v>0</v>
       </c>
       <c r="P19" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q19" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R19" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S19" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T19" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U19" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="V19" s="22">
-        <f t="shared" si="8"/>
-        <v>3.375</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>8.4375000000000006E-2</v>
-      </c>
-      <c r="AA19" s="41">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="41" t="e">
         <f>AA18/40</f>
-        <v>1.2656250000000002</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="L20" s="99"/>
+      <c r="M20" s="99"/>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="L21" s="99"/>
+      <c r="M21" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -9173,31 +9499,17 @@
         <v>13</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="11">
-        <v>20</v>
-      </c>
-      <c r="E8" s="11">
-        <v>20</v>
-      </c>
-      <c r="F8" s="11">
-        <v>0</v>
-      </c>
-      <c r="G8" s="11">
-        <v>30</v>
-      </c>
-      <c r="H8" s="11">
-        <v>60</v>
-      </c>
-      <c r="I8" s="11">
-        <v>30</v>
-      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>4</v>
-      </c>
-      <c r="K8" s="12">
-        <v>4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K8" s="12"/>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -9214,12 +9526,10 @@
         <f>SUM(O8:U8)/40</f>
         <v>0</v>
       </c>
-      <c r="W8" s="12">
-        <v>4</v>
-      </c>
+      <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -9227,7 +9537,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -9235,34 +9545,18 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11">
-        <v>80</v>
-      </c>
-      <c r="D9" s="11">
-        <v>0</v>
-      </c>
-      <c r="E9" s="11">
-        <v>80</v>
-      </c>
-      <c r="F9" s="11">
-        <v>80</v>
-      </c>
-      <c r="G9" s="11">
-        <v>0</v>
-      </c>
-      <c r="H9" s="11">
-        <v>0</v>
-      </c>
-      <c r="I9" s="11">
-        <v>20</v>
-      </c>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
-        <v>6.5</v>
-      </c>
-      <c r="K9" s="12">
-        <v>12</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K9" s="12"/>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -9279,12 +9573,10 @@
         <f t="shared" ref="V9:V17" si="1">SUM(O9:U9)/40</f>
         <v>0</v>
       </c>
-      <c r="W9" s="12">
-        <v>12</v>
-      </c>
+      <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
@@ -9292,7 +9584,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>6.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -9301,31 +9593,17 @@
         <v>15</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11">
-        <v>0</v>
-      </c>
-      <c r="E10" s="11">
-        <v>0</v>
-      </c>
-      <c r="F10" s="11">
-        <v>0</v>
-      </c>
-      <c r="G10" s="11">
-        <v>99</v>
-      </c>
-      <c r="H10" s="11">
-        <v>76</v>
-      </c>
-      <c r="I10" s="11">
-        <v>131</v>
-      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>7.65</v>
-      </c>
-      <c r="K10" s="12">
-        <v>7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K10" s="12"/>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -9342,12 +9620,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W10" s="12">
-        <v>7</v>
-      </c>
+      <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>7.65</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -9355,7 +9631,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>7.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -9363,33 +9639,31 @@
       <c r="B11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="11">
-        <v>284</v>
-      </c>
+      <c r="C11" s="11"/>
       <c r="D11" s="11">
-        <v>12</v>
+        <v>99</v>
       </c>
       <c r="E11" s="11">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F11" s="11">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="G11" s="11">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H11" s="11">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="I11" s="11">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>13.3</v>
+        <v>8.6750000000000007</v>
       </c>
       <c r="K11" s="12">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
@@ -9407,12 +9681,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W11" s="12">
-        <v>10</v>
-      </c>
+      <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>13.3</v>
+        <v>8.6750000000000007</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -9420,7 +9692,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>13.3</v>
+        <v>8.6750000000000007</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -9428,33 +9700,31 @@
       <c r="B12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="11">
-        <v>205</v>
-      </c>
+      <c r="C12" s="11"/>
       <c r="D12" s="11">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="E12" s="11">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="F12" s="11">
-        <v>36</v>
+        <v>106</v>
       </c>
       <c r="G12" s="11">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="H12" s="11">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="I12" s="11">
-        <v>38</v>
+        <v>200</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>8.5500000000000007</v>
+        <v>22.45</v>
       </c>
       <c r="K12" s="12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
@@ -9472,12 +9742,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W12" s="12">
-        <v>6</v>
-      </c>
+      <c r="W12" s="12"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>8.5500000000000007</v>
+        <v>22.45</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
@@ -9485,7 +9753,7 @@
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>8.5500000000000007</v>
+        <v>22.45</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -9521,9 +9789,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W13" s="12">
-        <v>4</v>
-      </c>
+      <c r="W13" s="12"/>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -9674,9 +9940,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W17" s="12">
-        <v>3</v>
-      </c>
+      <c r="W17" s="12"/>
       <c r="Y17" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -9695,35 +9959,35 @@
       <c r="B18" s="7"/>
       <c r="C18" s="25">
         <f t="shared" ref="C18:I18" si="5">SUM(C8:C17)</f>
-        <v>569</v>
+        <v>0</v>
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>116</v>
+        <v>170</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>192</v>
+        <v>253</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>340</v>
+        <v>294</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>1600</v>
+        <v>1245</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
@@ -9763,7 +10027,7 @@
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>40</v>
+        <v>31.125</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
@@ -9771,7 +10035,7 @@
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>40</v>
+        <v>31.125</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -9781,35 +10045,35 @@
       </c>
       <c r="C19" s="21">
         <f t="shared" ref="C19:J19" si="7">C18/40</f>
-        <v>14.225</v>
+        <v>0</v>
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>0.9</v>
+        <v>4.875</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>2.9</v>
+        <v>4.25</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>4.8</v>
+        <v>6.3250000000000002</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>5.2750000000000004</v>
+        <v>5.3250000000000002</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>8.5</v>
+        <v>7.35</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>31.125</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -9851,7 +10115,7 @@
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>1</v>
+        <v>0.77812499999999996</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
@@ -9859,7 +10123,7 @@
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>1</v>
+        <v>0.77812499999999996</v>
       </c>
     </row>
   </sheetData>

--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F54FB88D-A85B-4CBE-BF58-124F9BEF19E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932D5180-3E31-48AD-B0EC-6A18C37F894D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="14" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="18" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -9541,28 +9541,42 @@
         <v>13</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>50</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>40</v>
+      </c>
+      <c r="R8" s="11">
+        <v>30</v>
+      </c>
+      <c r="S8" s="11">
+        <v>85</v>
+      </c>
+      <c r="T8" s="11">
+        <v>30</v>
+      </c>
+      <c r="U8" s="11">
+        <v>85</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>8</v>
+      </c>
+      <c r="W8" s="12">
+        <v>8</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>11.5</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>11.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -9602,28 +9616,42 @@
         <v>14</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>120</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>80</v>
+      </c>
+      <c r="R9" s="11">
+        <v>1</v>
+      </c>
+      <c r="S9" s="11">
+        <v>100</v>
+      </c>
+      <c r="T9" s="11">
+        <v>100</v>
+      </c>
+      <c r="U9" s="11">
+        <v>80</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V17" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>12.025</v>
+      </c>
+      <c r="W9" s="12">
+        <v>20</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
         <v>12.025</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>12.025</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>12.025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -9710,28 +9738,42 @@
         <v>29</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>99</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>24</v>
+      </c>
+      <c r="R11" s="11">
+        <v>64</v>
+      </c>
+      <c r="S11" s="11">
+        <v>40</v>
+      </c>
+      <c r="T11" s="11">
+        <v>0</v>
+      </c>
+      <c r="U11" s="11">
+        <v>80</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>7.6749999999999998</v>
+      </c>
+      <c r="W11" s="12">
+        <v>6</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>8.6750000000000007</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.6749999999999998</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>8.6750000000000007</v>
+        <v>1.0000000000000009</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -9771,28 +9813,42 @@
         <v>28</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>50</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>50</v>
+      </c>
+      <c r="R12" s="11">
+        <v>60</v>
+      </c>
+      <c r="S12" s="11">
+        <v>120</v>
+      </c>
+      <c r="T12" s="11">
+        <v>160</v>
+      </c>
+      <c r="U12" s="11">
+        <v>160</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>15</v>
+      </c>
+      <c r="W12" s="12">
+        <v>4</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
         <v>22.45</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>22.45</v>
+        <v>7.4499999999999993</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -9870,17 +9926,31 @@
         <v>17</v>
       </c>
       <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
+      <c r="P14" s="11">
+        <v>360</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>600</v>
+      </c>
+      <c r="R14" s="11">
+        <v>800</v>
+      </c>
+      <c r="S14" s="11">
+        <v>1560</v>
+      </c>
+      <c r="T14" s="11">
+        <v>1638</v>
+      </c>
+      <c r="U14" s="11">
+        <v>2000</v>
+      </c>
       <c r="V14" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="12"/>
+        <v>173.95</v>
+      </c>
+      <c r="W14" s="12">
+        <v>9</v>
+      </c>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
       <c r="AA14" s="38"/>
@@ -10051,31 +10121,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>679</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>794</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>955</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1905</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1928</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2405</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>8666</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -10084,11 +10154,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>42.7</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>54.650000000000006</v>
+        <v>11.95</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -10139,31 +10209,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>16.975000000000001</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>19.850000000000001</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>23.875</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>47.625</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48.2</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>60.125</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>216.65</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -10172,11 +10242,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>1.0675000000000001</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>1.3662500000000002</v>
+        <v>0.29874999999999996</v>
       </c>
     </row>
   </sheetData>
@@ -11344,29 +11414,29 @@
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="E8" s="11">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="F8" s="11">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="G8" s="11">
-        <v>90</v>
+        <v>220</v>
       </c>
       <c r="H8" s="11">
-        <v>90</v>
+        <v>220</v>
       </c>
       <c r="I8" s="11">
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
+        <v>25</v>
+      </c>
+      <c r="K8" s="12">
         <v>11</v>
-      </c>
-      <c r="K8" s="12">
-        <v>12</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
@@ -11374,30 +11444,42 @@
         <v>13</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>80</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>80</v>
+      </c>
+      <c r="R8" s="11">
+        <v>120</v>
+      </c>
+      <c r="S8" s="11">
+        <v>210</v>
+      </c>
+      <c r="T8" s="11">
+        <v>210</v>
+      </c>
+      <c r="U8" s="11">
+        <v>260</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="W8" s="12">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -11407,29 +11489,29 @@
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="E9" s="11">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F9" s="11">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G9" s="11">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H9" s="11">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I9" s="11">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="K9" s="12">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
@@ -11437,30 +11519,42 @@
         <v>14</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>93</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>12</v>
+      </c>
+      <c r="R9" s="11">
+        <v>55</v>
+      </c>
+      <c r="S9" s="11">
+        <v>65</v>
+      </c>
+      <c r="T9" s="11">
+        <v>60</v>
+      </c>
+      <c r="U9" s="11">
+        <v>75</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W9" s="12">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>6.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -11469,31 +11563,17 @@
         <v>15</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11">
-        <v>0</v>
-      </c>
-      <c r="E10" s="11">
-        <v>0</v>
-      </c>
-      <c r="F10" s="11">
-        <v>20</v>
-      </c>
-      <c r="G10" s="11">
-        <v>65</v>
-      </c>
-      <c r="H10" s="11">
-        <v>12</v>
-      </c>
-      <c r="I10" s="11">
-        <v>83</v>
-      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>4.5</v>
-      </c>
-      <c r="K10" s="12">
-        <v>4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K10" s="12"/>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -11510,12 +11590,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W10" s="12">
-        <v>3</v>
-      </c>
+      <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -11523,7 +11601,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>4.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -11533,29 +11611,29 @@
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="E11" s="11">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="F11" s="11">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="G11" s="11">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="H11" s="11">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="I11" s="11">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>12.1</v>
+        <v>16.324999999999999</v>
       </c>
       <c r="K11" s="12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
@@ -11563,30 +11641,42 @@
         <v>29</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>58</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>58</v>
+      </c>
+      <c r="R11" s="11">
+        <v>69</v>
+      </c>
+      <c r="S11" s="11">
+        <v>57</v>
+      </c>
+      <c r="T11" s="11">
+        <v>37</v>
+      </c>
+      <c r="U11" s="11">
+        <v>10</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7.2249999999999996</v>
       </c>
       <c r="W11" s="12">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>12.1</v>
+        <v>16.324999999999999</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.2249999999999996</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>12.1</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -11612,28 +11702,42 @@
         <v>28</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>42</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>43</v>
+      </c>
+      <c r="R12" s="11">
+        <v>65</v>
+      </c>
+      <c r="S12" s="11">
+        <v>5</v>
+      </c>
+      <c r="T12" s="11">
+        <v>0</v>
+      </c>
+      <c r="U12" s="11">
+        <v>3</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>3.95</v>
+      </c>
+      <c r="W12" s="12">
+        <v>6</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-3.95</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -11669,9 +11773,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W13" s="12">
-        <v>8</v>
-      </c>
+      <c r="W13" s="12"/>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -11842,31 +11944,31 @@
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>55</v>
+        <v>303</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>182</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>99</v>
+        <v>276</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>353</v>
+        <v>474</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>1368</v>
+        <v>2093</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
@@ -11877,44 +11979,44 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>309</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>307</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>1767</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>34.200000000000003</v>
+        <v>52.325000000000003</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>44.175000000000004</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>34.200000000000003</v>
+        <v>8.1499999999999986</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -11928,31 +12030,31 @@
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>1.375</v>
+        <v>7.5750000000000002</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>1.25</v>
+        <v>4.55</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>2.4750000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>8.8249999999999993</v>
+        <v>11.85</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>7.2249999999999996</v>
+        <v>9.2249999999999996</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>13.05</v>
+        <v>12.225</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>34.200000000000003</v>
+        <v>52.325000000000003</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -11965,44 +12067,44 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6.8250000000000002</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.8250000000000002</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7.7249999999999996</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>8.4250000000000007</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7.6749999999999998</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>44.174999999999997</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0.85500000000000009</v>
+        <v>1.308125</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>1.1043750000000001</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.85500000000000009</v>
+        <v>0.20374999999999996</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.35">

--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932D5180-3E31-48AD-B0EC-6A18C37F894D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7DA53D5-A6F0-4229-BD62-0DE26EC73E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="18" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
@@ -603,7 +603,7 @@
     <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -824,6 +824,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma 2 10" xfId="1" xr:uid="{AE1F4535-4203-4FAC-A25F-A3FC5C82F4CA}"/>
@@ -11801,17 +11805,31 @@
         <v>17</v>
       </c>
       <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
+      <c r="P14" s="11">
+        <v>280</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>200</v>
+      </c>
+      <c r="R14" s="11">
+        <v>920</v>
+      </c>
+      <c r="S14" s="11">
+        <v>1400</v>
+      </c>
+      <c r="T14" s="11">
+        <v>1400</v>
+      </c>
+      <c r="U14" s="11">
+        <v>2000</v>
+      </c>
       <c r="V14" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="12"/>
+        <v>155</v>
+      </c>
+      <c r="W14" s="12">
+        <v>9</v>
+      </c>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
       <c r="AA14" s="38"/>
@@ -11979,31 +11997,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>273</v>
+        <v>553</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>193</v>
+        <v>393</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>309</v>
+        <v>1229</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>337</v>
+        <v>1737</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>307</v>
+        <v>1707</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>348</v>
+        <v>2348</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>1767</v>
+        <v>7967</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -12067,31 +12085,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>6.8250000000000002</v>
+        <v>13.824999999999999</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>4.8250000000000002</v>
+        <v>9.8249999999999993</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>7.7249999999999996</v>
+        <v>30.725000000000001</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>8.4250000000000007</v>
+        <v>43.424999999999997</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>7.6749999999999998</v>
+        <v>42.674999999999997</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>8.6999999999999993</v>
+        <v>58.7</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>44.174999999999997</v>
+        <v>199.17500000000001</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -13444,38 +13462,52 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
+      <c r="C8" s="96"/>
+      <c r="D8" s="96">
+        <v>23</v>
+      </c>
+      <c r="E8" s="96">
+        <v>39</v>
+      </c>
+      <c r="F8" s="96">
+        <v>54</v>
+      </c>
+      <c r="G8" s="96">
+        <v>213</v>
+      </c>
+      <c r="H8" s="96">
+        <v>143</v>
+      </c>
+      <c r="I8" s="96">
+        <v>154</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>15.65</v>
+      </c>
+      <c r="K8" s="12">
+        <v>16</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="43"/>
-      <c r="P8" s="43"/>
-      <c r="Q8" s="43"/>
-      <c r="R8" s="43"/>
-      <c r="S8" s="43"/>
-      <c r="T8" s="43"/>
-      <c r="U8" s="43"/>
-      <c r="V8" s="74">
+      <c r="O8" s="96"/>
+      <c r="P8" s="96"/>
+      <c r="Q8" s="96"/>
+      <c r="R8" s="96"/>
+      <c r="S8" s="96"/>
+      <c r="T8" s="96"/>
+      <c r="U8" s="96"/>
+      <c r="V8" s="97">
         <f>SUM(O8:U8)/40</f>
         <v>0</v>
       </c>
       <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>15.65</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -13483,7 +13515,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>15.65</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -13491,38 +13523,52 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
+      <c r="C9" s="96"/>
+      <c r="D9" s="96">
+        <v>21</v>
+      </c>
+      <c r="E9" s="96">
+        <v>16</v>
+      </c>
+      <c r="F9" s="96">
+        <v>23</v>
+      </c>
+      <c r="G9" s="96">
+        <v>101</v>
+      </c>
+      <c r="H9" s="96">
+        <v>96</v>
+      </c>
+      <c r="I9" s="96">
+        <v>143</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J18" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>10</v>
+      </c>
+      <c r="K9" s="12">
+        <v>20</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="O9" s="43"/>
-      <c r="P9" s="43"/>
-      <c r="Q9" s="43"/>
-      <c r="R9" s="43"/>
-      <c r="S9" s="43"/>
-      <c r="T9" s="43"/>
-      <c r="U9" s="43"/>
-      <c r="V9" s="74">
+      <c r="O9" s="96"/>
+      <c r="P9" s="96"/>
+      <c r="Q9" s="96"/>
+      <c r="R9" s="96"/>
+      <c r="S9" s="96"/>
+      <c r="T9" s="96"/>
+      <c r="U9" s="96"/>
+      <c r="V9" s="97">
         <f t="shared" ref="V9:V17" si="1">SUM(O9:U9)/40</f>
         <v>0</v>
       </c>
       <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
@@ -13530,7 +13576,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -13538,13 +13584,13 @@
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="43"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="96"/>
+      <c r="F10" s="96"/>
+      <c r="G10" s="96"/>
+      <c r="H10" s="96"/>
+      <c r="I10" s="96"/>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13555,14 +13601,14 @@
       <c r="N10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O10" s="43"/>
-      <c r="P10" s="43"/>
-      <c r="Q10" s="43"/>
-      <c r="R10" s="43"/>
-      <c r="S10" s="43"/>
-      <c r="T10" s="43"/>
-      <c r="U10" s="43"/>
-      <c r="V10" s="74">
+      <c r="O10" s="96"/>
+      <c r="P10" s="96"/>
+      <c r="Q10" s="96"/>
+      <c r="R10" s="96"/>
+      <c r="S10" s="96"/>
+      <c r="T10" s="96"/>
+      <c r="U10" s="96"/>
+      <c r="V10" s="97">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -13585,13 +13631,13 @@
       <c r="B11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="43"/>
+      <c r="C11" s="96"/>
+      <c r="D11" s="96"/>
+      <c r="E11" s="96"/>
+      <c r="F11" s="96"/>
+      <c r="G11" s="96"/>
+      <c r="H11" s="96"/>
+      <c r="I11" s="96"/>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13602,14 +13648,14 @@
       <c r="N11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="O11" s="43"/>
-      <c r="P11" s="43"/>
-      <c r="Q11" s="43"/>
-      <c r="R11" s="43"/>
-      <c r="S11" s="43"/>
-      <c r="T11" s="43"/>
-      <c r="U11" s="43"/>
-      <c r="V11" s="74">
+      <c r="O11" s="96"/>
+      <c r="P11" s="96"/>
+      <c r="Q11" s="96"/>
+      <c r="R11" s="96"/>
+      <c r="S11" s="96"/>
+      <c r="T11" s="96"/>
+      <c r="U11" s="96"/>
+      <c r="V11" s="97">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -13632,13 +13678,13 @@
       <c r="B12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
+      <c r="C12" s="96"/>
+      <c r="D12" s="96"/>
+      <c r="E12" s="96"/>
+      <c r="F12" s="96"/>
+      <c r="G12" s="96"/>
+      <c r="H12" s="96"/>
+      <c r="I12" s="96"/>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13649,14 +13695,14 @@
       <c r="N12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="O12" s="43"/>
-      <c r="P12" s="43"/>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="43"/>
-      <c r="S12" s="43"/>
-      <c r="T12" s="43"/>
-      <c r="U12" s="43"/>
-      <c r="V12" s="74">
+      <c r="O12" s="96"/>
+      <c r="P12" s="96"/>
+      <c r="Q12" s="96"/>
+      <c r="R12" s="96"/>
+      <c r="S12" s="96"/>
+      <c r="T12" s="96"/>
+      <c r="U12" s="96"/>
+      <c r="V12" s="97">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -13679,13 +13725,13 @@
       <c r="B13" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
+      <c r="C13" s="96"/>
+      <c r="D13" s="96"/>
+      <c r="E13" s="96"/>
+      <c r="F13" s="96"/>
+      <c r="G13" s="96"/>
+      <c r="H13" s="96"/>
+      <c r="I13" s="96"/>
       <c r="J13" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13696,14 +13742,14 @@
       <c r="N13" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="43"/>
-      <c r="T13" s="43"/>
-      <c r="U13" s="43"/>
-      <c r="V13" s="74">
+      <c r="O13" s="96"/>
+      <c r="P13" s="96"/>
+      <c r="Q13" s="96"/>
+      <c r="R13" s="96"/>
+      <c r="S13" s="96"/>
+      <c r="T13" s="96"/>
+      <c r="U13" s="96"/>
+      <c r="V13" s="97">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -13717,13 +13763,13 @@
       <c r="B14" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
+      <c r="C14" s="96"/>
+      <c r="D14" s="96"/>
+      <c r="E14" s="96"/>
+      <c r="F14" s="96"/>
+      <c r="G14" s="96"/>
+      <c r="H14" s="96"/>
+      <c r="I14" s="96"/>
       <c r="J14" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13734,14 +13780,14 @@
       <c r="N14" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="O14" s="43"/>
-      <c r="P14" s="43"/>
-      <c r="Q14" s="43"/>
-      <c r="R14" s="43"/>
-      <c r="S14" s="43"/>
-      <c r="T14" s="43"/>
-      <c r="U14" s="43"/>
-      <c r="V14" s="74">
+      <c r="O14" s="96"/>
+      <c r="P14" s="96"/>
+      <c r="Q14" s="96"/>
+      <c r="R14" s="96"/>
+      <c r="S14" s="96"/>
+      <c r="T14" s="96"/>
+      <c r="U14" s="96"/>
+      <c r="V14" s="97">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -13755,13 +13801,13 @@
       <c r="B15" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
+      <c r="C15" s="96"/>
+      <c r="D15" s="96"/>
+      <c r="E15" s="96"/>
+      <c r="F15" s="96"/>
+      <c r="G15" s="96"/>
+      <c r="H15" s="96"/>
+      <c r="I15" s="96"/>
       <c r="J15" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13772,14 +13818,14 @@
       <c r="N15" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="O15" s="43"/>
-      <c r="P15" s="43"/>
-      <c r="Q15" s="43"/>
-      <c r="R15" s="43"/>
-      <c r="S15" s="43"/>
-      <c r="T15" s="43"/>
-      <c r="U15" s="43"/>
-      <c r="V15" s="74">
+      <c r="O15" s="96"/>
+      <c r="P15" s="96"/>
+      <c r="Q15" s="96"/>
+      <c r="R15" s="96"/>
+      <c r="S15" s="96"/>
+      <c r="T15" s="96"/>
+      <c r="U15" s="96"/>
+      <c r="V15" s="97">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -13793,13 +13839,13 @@
       <c r="B16" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
+      <c r="C16" s="96"/>
+      <c r="D16" s="96"/>
+      <c r="E16" s="96"/>
+      <c r="F16" s="96"/>
+      <c r="G16" s="96"/>
+      <c r="H16" s="96"/>
+      <c r="I16" s="96"/>
       <c r="J16" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13810,14 +13856,14 @@
       <c r="N16" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="O16" s="43"/>
-      <c r="P16" s="43"/>
-      <c r="Q16" s="43"/>
-      <c r="R16" s="43"/>
-      <c r="S16" s="43"/>
-      <c r="T16" s="43"/>
-      <c r="U16" s="43"/>
-      <c r="V16" s="74">
+      <c r="O16" s="96"/>
+      <c r="P16" s="96"/>
+      <c r="Q16" s="96"/>
+      <c r="R16" s="96"/>
+      <c r="S16" s="96"/>
+      <c r="T16" s="96"/>
+      <c r="U16" s="96"/>
+      <c r="V16" s="97">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -13831,13 +13877,13 @@
       <c r="B17" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
+      <c r="C17" s="96"/>
+      <c r="D17" s="96"/>
+      <c r="E17" s="96"/>
+      <c r="F17" s="96"/>
+      <c r="G17" s="96"/>
+      <c r="H17" s="96"/>
+      <c r="I17" s="96"/>
       <c r="J17" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13847,14 +13893,14 @@
       <c r="N17" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O17" s="43"/>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="43"/>
-      <c r="R17" s="43"/>
-      <c r="S17" s="43"/>
-      <c r="T17" s="43"/>
-      <c r="U17" s="43"/>
-      <c r="V17" s="74">
+      <c r="O17" s="96"/>
+      <c r="P17" s="96"/>
+      <c r="Q17" s="96"/>
+      <c r="R17" s="96"/>
+      <c r="S17" s="96"/>
+      <c r="T17" s="96"/>
+      <c r="U17" s="96"/>
+      <c r="V17" s="97">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -13929,31 +13975,31 @@
       </c>
       <c r="D19" s="25">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="E19" s="25">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="F19" s="25">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="G19" s="25">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="H19" s="25">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="I19" s="25">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>297</v>
       </c>
       <c r="J19" s="26">
         <f>SUM(C19:I19)</f>
-        <v>0</v>
+        <v>1026</v>
       </c>
       <c r="K19" s="28"/>
       <c r="M19" s="1"/>
@@ -13993,7 +14039,7 @@
       <c r="W19" s="28"/>
       <c r="Y19" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>0</v>
+        <v>25.65</v>
       </c>
       <c r="Z19" s="34">
         <f>SUM(Z8:Z17)</f>
@@ -14001,7 +14047,7 @@
       </c>
       <c r="AA19" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>0</v>
+        <v>25.65</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -14015,31 +14061,31 @@
       </c>
       <c r="D20" s="21">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E20" s="21">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1.375</v>
       </c>
       <c r="F20" s="21">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1.925</v>
       </c>
       <c r="G20" s="21">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="H20" s="21">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>5.9749999999999996</v>
       </c>
       <c r="I20" s="21">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>7.4249999999999998</v>
       </c>
       <c r="J20" s="22">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>25.65</v>
       </c>
       <c r="K20" s="23"/>
       <c r="M20" s="1"/>
@@ -14081,7 +14127,7 @@
       <c r="W20" s="23"/>
       <c r="Y20" s="39">
         <f>Y19/40</f>
-        <v>0</v>
+        <v>0.64124999999999999</v>
       </c>
       <c r="Z20" s="40">
         <f>Z19/40</f>
@@ -14089,7 +14135,7 @@
       </c>
       <c r="AA20" s="41">
         <f>AA19/40</f>
-        <v>0</v>
+        <v>0.64124999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.35">

--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7DA53D5-A6F0-4229-BD62-0DE26EC73E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE734475-7D10-4FFC-841C-48C1BDABF480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="18" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="19" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1887" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1886" uniqueCount="54">
   <si>
     <t>Booking</t>
   </si>
@@ -603,7 +603,7 @@
     <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -824,10 +824,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma 2 10" xfId="1" xr:uid="{AE1F4535-4203-4FAC-A25F-A3FC5C82F4CA}"/>
@@ -13462,23 +13458,23 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="96"/>
-      <c r="D8" s="96">
+      <c r="C8" s="11"/>
+      <c r="D8" s="11">
         <v>23</v>
       </c>
-      <c r="E8" s="96">
+      <c r="E8" s="11">
         <v>39</v>
       </c>
-      <c r="F8" s="96">
+      <c r="F8" s="11">
         <v>54</v>
       </c>
-      <c r="G8" s="96">
+      <c r="G8" s="11">
         <v>213</v>
       </c>
-      <c r="H8" s="96">
+      <c r="H8" s="11">
         <v>143</v>
       </c>
-      <c r="I8" s="96">
+      <c r="I8" s="11">
         <v>154</v>
       </c>
       <c r="J8" s="15">
@@ -13493,29 +13489,43 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="96"/>
-      <c r="P8" s="96"/>
-      <c r="Q8" s="96"/>
-      <c r="R8" s="96"/>
-      <c r="S8" s="96"/>
-      <c r="T8" s="96"/>
-      <c r="U8" s="96"/>
-      <c r="V8" s="97">
+      <c r="O8" s="11"/>
+      <c r="P8" s="11">
+        <v>23</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>39</v>
+      </c>
+      <c r="R8" s="11">
+        <v>14</v>
+      </c>
+      <c r="S8" s="11">
+        <v>213</v>
+      </c>
+      <c r="T8" s="11">
+        <v>143</v>
+      </c>
+      <c r="U8" s="11">
+        <v>154</v>
+      </c>
+      <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>14.65</v>
+      </c>
+      <c r="W8" s="12">
+        <v>12</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>15.65</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>14.65</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>15.65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -13523,23 +13533,23 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="96"/>
-      <c r="D9" s="96">
+      <c r="C9" s="11"/>
+      <c r="D9" s="11">
         <v>21</v>
       </c>
-      <c r="E9" s="96">
+      <c r="E9" s="11">
         <v>16</v>
       </c>
-      <c r="F9" s="96">
+      <c r="F9" s="11">
         <v>23</v>
       </c>
-      <c r="G9" s="96">
+      <c r="G9" s="11">
         <v>101</v>
       </c>
-      <c r="H9" s="96">
+      <c r="H9" s="11">
         <v>96</v>
       </c>
-      <c r="I9" s="96">
+      <c r="I9" s="11">
         <v>143</v>
       </c>
       <c r="J9" s="15">
@@ -13554,29 +13564,43 @@
       <c r="N9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="O9" s="96"/>
-      <c r="P9" s="96"/>
-      <c r="Q9" s="96"/>
-      <c r="R9" s="96"/>
-      <c r="S9" s="96"/>
-      <c r="T9" s="96"/>
-      <c r="U9" s="96"/>
-      <c r="V9" s="97">
+      <c r="O9" s="11"/>
+      <c r="P9" s="11">
+        <v>21</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>16</v>
+      </c>
+      <c r="R9" s="11">
+        <v>21</v>
+      </c>
+      <c r="S9" s="11">
+        <v>91</v>
+      </c>
+      <c r="T9" s="11">
+        <v>86</v>
+      </c>
+      <c r="U9" s="11">
+        <v>133</v>
+      </c>
+      <c r="V9" s="15">
         <f t="shared" ref="V9:V17" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="W9" s="12">
+        <v>20</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
         <v>10</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>10</v>
+        <v>0.80000000000000071</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -13584,13 +13608,13 @@
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="96"/>
-      <c r="D10" s="96"/>
-      <c r="E10" s="96"/>
-      <c r="F10" s="96"/>
-      <c r="G10" s="96"/>
-      <c r="H10" s="96"/>
-      <c r="I10" s="96"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13601,14 +13625,14 @@
       <c r="N10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O10" s="96"/>
-      <c r="P10" s="96"/>
-      <c r="Q10" s="96"/>
-      <c r="R10" s="96"/>
-      <c r="S10" s="96"/>
-      <c r="T10" s="96"/>
-      <c r="U10" s="96"/>
-      <c r="V10" s="97">
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="11"/>
+      <c r="T10" s="11"/>
+      <c r="U10" s="11"/>
+      <c r="V10" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -13631,13 +13655,13 @@
       <c r="B11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="96"/>
-      <c r="D11" s="96"/>
-      <c r="E11" s="96"/>
-      <c r="F11" s="96"/>
-      <c r="G11" s="96"/>
-      <c r="H11" s="96"/>
-      <c r="I11" s="96"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13648,29 +13672,43 @@
       <c r="N11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="O11" s="96"/>
-      <c r="P11" s="96"/>
-      <c r="Q11" s="96"/>
-      <c r="R11" s="96"/>
-      <c r="S11" s="96"/>
-      <c r="T11" s="96"/>
-      <c r="U11" s="96"/>
-      <c r="V11" s="97">
+      <c r="O11" s="11"/>
+      <c r="P11" s="11">
+        <v>26</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>26</v>
+      </c>
+      <c r="R11" s="11">
+        <v>28</v>
+      </c>
+      <c r="S11" s="11">
+        <v>70</v>
+      </c>
+      <c r="T11" s="11">
+        <v>38</v>
+      </c>
+      <c r="U11" s="11">
+        <v>106</v>
+      </c>
+      <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>7.35</v>
+      </c>
+      <c r="W11" s="12">
+        <v>8</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.35</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-7.35</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -13678,13 +13716,13 @@
       <c r="B12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="96"/>
-      <c r="D12" s="96"/>
-      <c r="E12" s="96"/>
-      <c r="F12" s="96"/>
-      <c r="G12" s="96"/>
-      <c r="H12" s="96"/>
-      <c r="I12" s="96"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13695,14 +13733,14 @@
       <c r="N12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="O12" s="96"/>
-      <c r="P12" s="96"/>
-      <c r="Q12" s="96"/>
-      <c r="R12" s="96"/>
-      <c r="S12" s="96"/>
-      <c r="T12" s="96"/>
-      <c r="U12" s="96"/>
-      <c r="V12" s="97">
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
+      <c r="V12" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -13725,13 +13763,13 @@
       <c r="B13" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="96"/>
-      <c r="D13" s="96"/>
-      <c r="E13" s="96"/>
-      <c r="F13" s="96"/>
-      <c r="G13" s="96"/>
-      <c r="H13" s="96"/>
-      <c r="I13" s="96"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
       <c r="J13" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13742,14 +13780,14 @@
       <c r="N13" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="O13" s="96"/>
-      <c r="P13" s="96"/>
-      <c r="Q13" s="96"/>
-      <c r="R13" s="96"/>
-      <c r="S13" s="96"/>
-      <c r="T13" s="96"/>
-      <c r="U13" s="96"/>
-      <c r="V13" s="97">
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
+      <c r="T13" s="11"/>
+      <c r="U13" s="11"/>
+      <c r="V13" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -13763,13 +13801,13 @@
       <c r="B14" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="96"/>
-      <c r="D14" s="96"/>
-      <c r="E14" s="96"/>
-      <c r="F14" s="96"/>
-      <c r="G14" s="96"/>
-      <c r="H14" s="96"/>
-      <c r="I14" s="96"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
       <c r="J14" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13780,14 +13818,14 @@
       <c r="N14" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="O14" s="96"/>
-      <c r="P14" s="96"/>
-      <c r="Q14" s="96"/>
-      <c r="R14" s="96"/>
-      <c r="S14" s="96"/>
-      <c r="T14" s="96"/>
-      <c r="U14" s="96"/>
-      <c r="V14" s="97">
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="11"/>
+      <c r="V14" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -13801,13 +13839,13 @@
       <c r="B15" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="96"/>
-      <c r="D15" s="96"/>
-      <c r="E15" s="96"/>
-      <c r="F15" s="96"/>
-      <c r="G15" s="96"/>
-      <c r="H15" s="96"/>
-      <c r="I15" s="96"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
       <c r="J15" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13818,14 +13856,14 @@
       <c r="N15" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="O15" s="96"/>
-      <c r="P15" s="96"/>
-      <c r="Q15" s="96"/>
-      <c r="R15" s="96"/>
-      <c r="S15" s="96"/>
-      <c r="T15" s="96"/>
-      <c r="U15" s="96"/>
-      <c r="V15" s="97">
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="11"/>
+      <c r="V15" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -13839,13 +13877,13 @@
       <c r="B16" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="96"/>
-      <c r="D16" s="96"/>
-      <c r="E16" s="96"/>
-      <c r="F16" s="96"/>
-      <c r="G16" s="96"/>
-      <c r="H16" s="96"/>
-      <c r="I16" s="96"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
       <c r="J16" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13856,14 +13894,14 @@
       <c r="N16" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="O16" s="96"/>
-      <c r="P16" s="96"/>
-      <c r="Q16" s="96"/>
-      <c r="R16" s="96"/>
-      <c r="S16" s="96"/>
-      <c r="T16" s="96"/>
-      <c r="U16" s="96"/>
-      <c r="V16" s="97">
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="11"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="11"/>
+      <c r="V16" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -13877,13 +13915,13 @@
       <c r="B17" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="96"/>
-      <c r="D17" s="96"/>
-      <c r="E17" s="96"/>
-      <c r="F17" s="96"/>
-      <c r="G17" s="96"/>
-      <c r="H17" s="96"/>
-      <c r="I17" s="96"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
       <c r="J17" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13893,14 +13931,14 @@
       <c r="N17" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O17" s="96"/>
-      <c r="P17" s="96"/>
-      <c r="Q17" s="96"/>
-      <c r="R17" s="96"/>
-      <c r="S17" s="96"/>
-      <c r="T17" s="96"/>
-      <c r="U17" s="96"/>
-      <c r="V17" s="97">
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11"/>
+      <c r="V17" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -14010,31 +14048,31 @@
       </c>
       <c r="P19" s="70">
         <f t="shared" ref="P19:U19" si="9">SUM(P8:P18)</f>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Q19" s="70">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="R19" s="70">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="S19" s="70">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="T19" s="70">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="U19" s="70">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>393</v>
       </c>
       <c r="V19" s="26">
         <f>SUM(O19:U19)</f>
-        <v>0</v>
+        <v>1248</v>
       </c>
       <c r="W19" s="28"/>
       <c r="Y19" s="33">
@@ -14043,11 +14081,11 @@
       </c>
       <c r="Z19" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>31.200000000000003</v>
       </c>
       <c r="AA19" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>25.65</v>
+        <v>-5.5499999999999989</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -14098,31 +14136,31 @@
       </c>
       <c r="P20" s="21">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q20" s="21">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.0249999999999999</v>
       </c>
       <c r="R20" s="21">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1.575</v>
       </c>
       <c r="S20" s="21">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9.35</v>
       </c>
       <c r="T20" s="21">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>6.6749999999999998</v>
       </c>
       <c r="U20" s="21">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9.8249999999999993</v>
       </c>
       <c r="V20" s="22">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>31.2</v>
       </c>
       <c r="W20" s="23"/>
       <c r="Y20" s="39">
@@ -14131,11 +14169,11 @@
       </c>
       <c r="Z20" s="40">
         <f>Z19/40</f>
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AA20" s="41">
         <f>AA19/40</f>
-        <v>0.64124999999999999</v>
+        <v>-0.13874999999999998</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.35">
@@ -14477,29 +14515,17 @@
         <v>13</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="11">
-        <v>20</v>
-      </c>
-      <c r="E8" s="11">
-        <v>20</v>
-      </c>
-      <c r="F8" s="11">
-        <v>120</v>
-      </c>
-      <c r="G8" s="11">
-        <v>20</v>
-      </c>
-      <c r="H8" s="11">
-        <v>20</v>
-      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
       <c r="I8" s="11"/>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>5</v>
-      </c>
-      <c r="K8" s="12">
-        <v>12</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K8" s="12"/>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -14516,12 +14542,10 @@
         <f>SUM(O8:U8)/40</f>
         <v>0</v>
       </c>
-      <c r="W8" s="12">
-        <v>11</v>
-      </c>
+      <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -14529,7 +14553,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -14538,31 +14562,17 @@
         <v>14</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="11">
-        <v>12</v>
-      </c>
-      <c r="E9" s="11">
-        <v>15</v>
-      </c>
-      <c r="F9" s="11">
-        <v>13</v>
-      </c>
-      <c r="G9" s="11">
-        <v>70</v>
-      </c>
-      <c r="H9" s="11">
-        <v>70</v>
-      </c>
-      <c r="I9" s="11">
-        <v>60</v>
-      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
-        <v>6</v>
-      </c>
-      <c r="K9" s="12">
-        <v>10</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K9" s="12"/>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -14579,12 +14589,10 @@
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
         <v>0</v>
       </c>
-      <c r="W9" s="12">
-        <v>10</v>
-      </c>
+      <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
@@ -14592,7 +14600,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -14601,31 +14609,17 @@
         <v>15</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11">
-        <v>0</v>
-      </c>
-      <c r="E10" s="11">
-        <v>0</v>
-      </c>
-      <c r="F10" s="11">
-        <v>0</v>
-      </c>
-      <c r="G10" s="11">
-        <v>104</v>
-      </c>
-      <c r="H10" s="11">
-        <v>60</v>
-      </c>
-      <c r="I10" s="11">
-        <v>74</v>
-      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>5.95</v>
-      </c>
-      <c r="K10" s="12">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K10" s="12"/>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -14642,12 +14636,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W10" s="12">
-        <v>6</v>
-      </c>
+      <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -14655,7 +14647,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>5.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -14664,31 +14656,17 @@
         <v>29</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="11">
-        <v>40</v>
-      </c>
-      <c r="E11" s="11">
-        <v>40</v>
-      </c>
-      <c r="F11" s="11">
-        <v>80</v>
-      </c>
-      <c r="G11" s="11">
-        <v>95</v>
-      </c>
-      <c r="H11" s="11">
-        <v>95</v>
-      </c>
-      <c r="I11" s="11">
-        <v>170</v>
-      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="K11" s="12">
-        <v>5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K11" s="12"/>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -14705,12 +14683,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W11" s="12">
-        <v>5</v>
-      </c>
+      <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -14718,7 +14694,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -14727,16 +14703,31 @@
         <v>28</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="93" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="95"/>
-      <c r="K12" s="12"/>
+      <c r="D12" s="11">
+        <v>105</v>
+      </c>
+      <c r="E12" s="11">
+        <v>64</v>
+      </c>
+      <c r="F12" s="11">
+        <v>95</v>
+      </c>
+      <c r="G12" s="11">
+        <v>102</v>
+      </c>
+      <c r="H12" s="11">
+        <v>98</v>
+      </c>
+      <c r="I12" s="11">
+        <v>108</v>
+      </c>
+      <c r="J12" s="15">
+        <f t="shared" si="0"/>
+        <v>14.3</v>
+      </c>
+      <c r="K12" s="12">
+        <v>12</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
@@ -14754,17 +14745,17 @@
         <v>0</v>
       </c>
       <c r="W12" s="12"/>
-      <c r="Y12" s="36" t="str">
+      <c r="Y12" s="36">
         <f>D12</f>
-        <v>Leave</v>
+        <v>105</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA12" s="38" t="e">
+      <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -14971,31 +14962,31 @@
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>213</v>
+        <v>95</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>289</v>
+        <v>102</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>245</v>
+        <v>98</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>304</v>
+        <v>108</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>1198</v>
+        <v>572</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
@@ -15035,15 +15026,15 @@
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>29.95</v>
+        <v>105</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
         <v>0</v>
       </c>
-      <c r="AA18" s="35" t="e">
+      <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>#VALUE!</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -15057,31 +15048,31 @@
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>1.8</v>
+        <v>2.625</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>1.875</v>
+        <v>1.6</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>5.3250000000000002</v>
+        <v>2.375</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>7.2249999999999996</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>6.125</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>7.6</v>
+        <v>2.7</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>29.95</v>
+        <v>14.3</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -15123,20 +15114,19 @@
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0.74875000000000003</v>
+        <v>2.625</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
         <v>0</v>
       </c>
-      <c r="AA19" s="41" t="e">
+      <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>#VALUE!</v>
+        <v>2.625</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="D12:J12"/>
+  <mergeCells count="7">
     <mergeCell ref="Y3:AA4"/>
     <mergeCell ref="B2:J5"/>
     <mergeCell ref="N2:V5"/>

--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE734475-7D10-4FFC-841C-48C1BDABF480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0FB4EA-7708-4961-8AA1-014A35A182F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="19" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="21" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1886" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1885" uniqueCount="54">
   <si>
     <t>Booking</t>
   </si>
@@ -13819,17 +13819,31 @@
         <v>17</v>
       </c>
       <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
+      <c r="P14" s="11">
+        <v>172</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>80</v>
+      </c>
+      <c r="R14" s="11">
+        <v>197</v>
+      </c>
+      <c r="S14" s="11">
+        <v>277</v>
+      </c>
+      <c r="T14" s="11">
+        <v>320</v>
+      </c>
+      <c r="U14" s="11">
+        <v>827</v>
+      </c>
       <c r="V14" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="12"/>
+        <v>46.825000000000003</v>
+      </c>
+      <c r="W14" s="12">
+        <v>5</v>
+      </c>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
       <c r="AA14" s="38"/>
@@ -13942,9 +13956,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W17" s="18">
-        <v>5</v>
-      </c>
+      <c r="W17" s="18"/>
       <c r="Y17" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -14048,31 +14060,31 @@
       </c>
       <c r="P19" s="70">
         <f t="shared" ref="P19:U19" si="9">SUM(P8:P18)</f>
-        <v>70</v>
+        <v>242</v>
       </c>
       <c r="Q19" s="70">
         <f t="shared" si="9"/>
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="R19" s="70">
         <f t="shared" si="9"/>
-        <v>63</v>
+        <v>260</v>
       </c>
       <c r="S19" s="70">
         <f t="shared" si="9"/>
-        <v>374</v>
+        <v>651</v>
       </c>
       <c r="T19" s="70">
         <f t="shared" si="9"/>
-        <v>267</v>
+        <v>587</v>
       </c>
       <c r="U19" s="70">
         <f t="shared" si="9"/>
-        <v>393</v>
+        <v>1220</v>
       </c>
       <c r="V19" s="26">
         <f>SUM(O19:U19)</f>
-        <v>1248</v>
+        <v>3121</v>
       </c>
       <c r="W19" s="28"/>
       <c r="Y19" s="33">
@@ -14136,31 +14148,31 @@
       </c>
       <c r="P20" s="21">
         <f t="shared" si="11"/>
-        <v>1.75</v>
+        <v>6.05</v>
       </c>
       <c r="Q20" s="21">
         <f t="shared" si="11"/>
-        <v>2.0249999999999999</v>
+        <v>4.0250000000000004</v>
       </c>
       <c r="R20" s="21">
         <f t="shared" si="11"/>
-        <v>1.575</v>
+        <v>6.5</v>
       </c>
       <c r="S20" s="21">
         <f t="shared" si="11"/>
-        <v>9.35</v>
+        <v>16.274999999999999</v>
       </c>
       <c r="T20" s="21">
         <f t="shared" si="11"/>
-        <v>6.6749999999999998</v>
+        <v>14.675000000000001</v>
       </c>
       <c r="U20" s="21">
         <f t="shared" si="11"/>
-        <v>9.8249999999999993</v>
+        <v>30.5</v>
       </c>
       <c r="V20" s="22">
         <f t="shared" si="11"/>
-        <v>31.2</v>
+        <v>78.025000000000006</v>
       </c>
       <c r="W20" s="23"/>
       <c r="Y20" s="39">
@@ -14515,17 +14527,31 @@
         <v>13</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="D8" s="11">
+        <v>40</v>
+      </c>
+      <c r="E8" s="11">
+        <v>0</v>
+      </c>
+      <c r="F8" s="11">
+        <v>160</v>
+      </c>
+      <c r="G8" s="11">
+        <v>250</v>
+      </c>
+      <c r="H8" s="11">
+        <v>210</v>
+      </c>
+      <c r="I8" s="11">
+        <v>300</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="K8" s="12">
+        <v>7</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -14545,7 +14571,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -14553,7 +14579,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -14562,45 +14588,73 @@
         <v>14</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="D9" s="11">
+        <v>60</v>
+      </c>
+      <c r="E9" s="11">
+        <v>50</v>
+      </c>
+      <c r="F9" s="11">
+        <v>50</v>
+      </c>
+      <c r="G9" s="11">
+        <v>120</v>
+      </c>
+      <c r="H9" s="11">
+        <v>65</v>
+      </c>
+      <c r="I9" s="11">
+        <v>135</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="K9" s="12">
+        <v>16</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
         <v>14</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>60</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>45</v>
+      </c>
+      <c r="R9" s="11">
+        <v>45</v>
+      </c>
+      <c r="S9" s="11">
+        <v>60</v>
+      </c>
+      <c r="T9" s="11">
+        <v>45</v>
+      </c>
+      <c r="U9" s="11">
+        <v>80</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>8.375</v>
+      </c>
+      <c r="W9" s="12">
+        <v>14</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>8.375</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>3.625</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -14656,17 +14710,31 @@
         <v>29</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="D11" s="11">
+        <v>78</v>
+      </c>
+      <c r="E11" s="11">
+        <v>50</v>
+      </c>
+      <c r="F11" s="11">
+        <v>56</v>
+      </c>
+      <c r="G11" s="11">
+        <v>65</v>
+      </c>
+      <c r="H11" s="11">
+        <v>105</v>
+      </c>
+      <c r="I11" s="11">
+        <v>30</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>9.6</v>
+      </c>
+      <c r="K11" s="12">
+        <v>5</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -14686,7 +14754,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -14694,7 +14762,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -14962,31 +15030,31 @@
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>105</v>
+        <v>283</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>64</v>
+        <v>164</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>95</v>
+        <v>361</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>102</v>
+        <v>537</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>98</v>
+        <v>478</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>108</v>
+        <v>573</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>572</v>
+        <v>2396</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
@@ -14997,44 +15065,44 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>335</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>105</v>
+        <v>150.6</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>8.375</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>105</v>
+        <v>142.22499999999999</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -15048,31 +15116,31 @@
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>2.625</v>
+        <v>7.0750000000000002</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>1.6</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>2.375</v>
+        <v>9.0250000000000004</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>2.5499999999999998</v>
+        <v>13.425000000000001</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>2.4500000000000002</v>
+        <v>11.95</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>2.7</v>
+        <v>14.324999999999999</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>14.3</v>
+        <v>59.9</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -15085,44 +15153,44 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1.125</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1.125</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1.125</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>8.375</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>2.625</v>
+        <v>3.7649999999999997</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>0.20937500000000001</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>2.625</v>
+        <v>3.555625</v>
       </c>
     </row>
   </sheetData>
@@ -15408,29 +15476,29 @@
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="E8" s="11">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="F8" s="11">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="G8" s="11">
-        <v>102</v>
+        <v>210</v>
       </c>
       <c r="H8" s="11">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="I8" s="11">
-        <v>142</v>
+        <v>210</v>
       </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>19.875</v>
+        <v>14</v>
       </c>
       <c r="K8" s="12">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
@@ -15453,7 +15521,7 @@
       </c>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>19.875</v>
+        <v>14</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -15461,7 +15529,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>19.875</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -15471,29 +15539,29 @@
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11">
-        <v>8</v>
+        <v>162</v>
       </c>
       <c r="E9" s="11">
-        <v>10</v>
+        <v>147</v>
       </c>
       <c r="F9" s="11">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="G9" s="11">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="H9" s="11">
-        <v>26</v>
+        <v>132</v>
       </c>
       <c r="I9" s="11">
         <v>120</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J11" si="0">SUM(C9:I9)/40</f>
-        <v>9.1</v>
+        <v>19.375</v>
       </c>
       <c r="K9" s="12">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
@@ -15516,7 +15584,7 @@
       </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>9.1</v>
+        <v>19.375</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
@@ -15524,7 +15592,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>9.1</v>
+        <v>19.375</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -15533,31 +15601,17 @@
         <v>15</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11">
-        <v>4</v>
-      </c>
-      <c r="E10" s="11">
-        <v>4</v>
-      </c>
-      <c r="F10" s="11">
-        <v>16</v>
-      </c>
-      <c r="G10" s="11">
-        <v>115</v>
-      </c>
-      <c r="H10" s="11">
-        <v>65</v>
-      </c>
-      <c r="I10" s="11">
-        <v>61</v>
-      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>6.625</v>
-      </c>
-      <c r="K10" s="12">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K10" s="12"/>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -15579,7 +15633,7 @@
       </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>6.625</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -15587,7 +15641,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>6.625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -15597,29 +15651,29 @@
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E11" s="11">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F11" s="11">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G11" s="11">
-        <v>179</v>
+        <v>63</v>
       </c>
       <c r="H11" s="11">
-        <v>134</v>
+        <v>23</v>
       </c>
       <c r="I11" s="11">
-        <v>139</v>
+        <v>88</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>13.9</v>
+        <v>4.95</v>
       </c>
       <c r="K11" s="12">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
@@ -15642,7 +15696,7 @@
       </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>13.9</v>
+        <v>4.95</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -15650,7 +15704,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>13.9</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -15658,16 +15712,17 @@
       <c r="B12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="93" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="94"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="95"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="15">
+        <f t="shared" ref="J12:J17" si="5">SUM(C12:I12)/40</f>
+        <v>0</v>
+      </c>
       <c r="K12" s="12"/>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
@@ -15686,17 +15741,17 @@
         <v>0</v>
       </c>
       <c r="W12" s="12"/>
-      <c r="Y12" s="36" t="str">
+      <c r="Y12" s="36">
         <f>C12</f>
-        <v>Leave</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA12" s="38" t="e">
+      <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -15712,11 +15767,10 @@
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
       <c r="J13" s="15">
-        <v>56</v>
-      </c>
-      <c r="K13" s="12">
-        <v>5</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="12"/>
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
@@ -15753,11 +15807,10 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
       <c r="J14" s="15">
-        <v>21</v>
-      </c>
-      <c r="K14" s="12">
-        <v>14</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="12"/>
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
@@ -15793,11 +15846,10 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="15">
-        <v>8</v>
-      </c>
-      <c r="K15" s="12">
-        <v>10</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="12"/>
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
@@ -15833,11 +15885,10 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="15">
-        <v>7</v>
-      </c>
-      <c r="K16" s="12">
-        <v>8</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="12"/>
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
@@ -15873,7 +15924,8 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
       <c r="J17" s="15">
-        <v>7</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
@@ -15891,7 +15943,7 @@
       <c r="W17" s="18"/>
       <c r="Y17" s="36">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="37">
         <f t="shared" si="3"/>
@@ -15899,73 +15951,73 @@
       </c>
       <c r="AA17" s="38">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="7"/>
       <c r="C18" s="25">
-        <f t="shared" ref="C18:I18" si="5">SUM(C8:C17)</f>
+        <f t="shared" ref="C18:I18" si="6">SUM(C8:C17)</f>
         <v>0</v>
       </c>
       <c r="D18" s="25">
-        <f t="shared" si="5"/>
-        <v>176</v>
+        <f t="shared" si="6"/>
+        <v>174</v>
       </c>
       <c r="E18" s="25">
-        <f t="shared" si="5"/>
-        <v>158</v>
+        <f t="shared" si="6"/>
+        <v>147</v>
       </c>
       <c r="F18" s="25">
-        <f t="shared" si="5"/>
-        <v>351</v>
+        <f t="shared" si="6"/>
+        <v>174</v>
       </c>
       <c r="G18" s="25">
-        <f t="shared" si="5"/>
-        <v>482</v>
+        <f t="shared" si="6"/>
+        <v>325</v>
       </c>
       <c r="H18" s="25">
-        <f t="shared" si="5"/>
-        <v>351</v>
+        <f t="shared" si="6"/>
+        <v>295</v>
       </c>
       <c r="I18" s="25">
-        <f t="shared" si="5"/>
-        <v>462</v>
+        <f t="shared" si="6"/>
+        <v>418</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>1980</v>
+        <v>1533</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
       <c r="N18" s="7"/>
       <c r="O18" s="25">
-        <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
+        <f t="shared" ref="O18:U18" si="7">SUM(O8:O17)</f>
         <v>0</v>
       </c>
       <c r="P18" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q18" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R18" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S18" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T18" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="U18" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V18" s="26">
@@ -15975,15 +16027,15 @@
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>56.5</v>
+        <v>38.325000000000003</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
         <v>0</v>
       </c>
-      <c r="AA18" s="35" t="e">
+      <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>#VALUE!</v>
+        <v>38.325000000000003</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -15992,36 +16044,36 @@
         <v>18</v>
       </c>
       <c r="C19" s="21">
-        <f t="shared" ref="C19:I19" si="7">C18/40</f>
+        <f t="shared" ref="C19:I19" si="8">C18/40</f>
         <v>0</v>
       </c>
       <c r="D19" s="21">
-        <f t="shared" si="7"/>
-        <v>4.4000000000000004</v>
+        <f t="shared" si="8"/>
+        <v>4.3499999999999996</v>
       </c>
       <c r="E19" s="21">
-        <f t="shared" si="7"/>
-        <v>3.95</v>
+        <f t="shared" si="8"/>
+        <v>3.6749999999999998</v>
       </c>
       <c r="F19" s="21">
-        <f t="shared" si="7"/>
-        <v>8.7750000000000004</v>
+        <f t="shared" si="8"/>
+        <v>4.3499999999999996</v>
       </c>
       <c r="G19" s="21">
-        <f t="shared" si="7"/>
-        <v>12.05</v>
+        <f t="shared" si="8"/>
+        <v>8.125</v>
       </c>
       <c r="H19" s="21">
-        <f t="shared" si="7"/>
-        <v>8.7750000000000004</v>
+        <f t="shared" si="8"/>
+        <v>7.375</v>
       </c>
       <c r="I19" s="21">
-        <f t="shared" si="7"/>
-        <v>11.55</v>
+        <f t="shared" si="8"/>
+        <v>10.45</v>
       </c>
       <c r="J19" s="22">
         <f>SUM(J8:J16)</f>
-        <v>141.5</v>
+        <v>38.325000000000003</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -16029,31 +16081,31 @@
         <v>18</v>
       </c>
       <c r="O19" s="21">
-        <f t="shared" ref="O19:U19" si="8">O18/40</f>
+        <f t="shared" ref="O19:U19" si="9">O18/40</f>
         <v>0</v>
       </c>
       <c r="P19" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Q19" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R19" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S19" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T19" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U19" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V19" s="22">
@@ -16063,20 +16115,19 @@
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>1.4125000000000001</v>
+        <v>0.95812500000000012</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
         <v>0</v>
       </c>
-      <c r="AA19" s="41" t="e">
+      <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>#VALUE!</v>
+        <v>0.95812500000000012</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="C12:J12"/>
+  <mergeCells count="7">
     <mergeCell ref="Y3:AA4"/>
     <mergeCell ref="B2:J5"/>
     <mergeCell ref="N2:V5"/>

--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0FB4EA-7708-4961-8AA1-014A35A182F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F901BA56-13D1-4754-8402-72AC62184A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="21" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1885" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1885" uniqueCount="55">
   <si>
     <t>Booking</t>
   </si>
@@ -217,6 +217,9 @@
   </si>
   <si>
     <t xml:space="preserve">Nabel Traders </t>
+  </si>
+  <si>
+    <t>Zeshan1</t>
   </si>
 </sst>
 </file>
@@ -14275,10 +14278,10 @@
     <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="3.81640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="3.6328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="5.453125" customWidth="1"/>
     <col min="25" max="25" width="7.453125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9.36328125" bestFit="1" customWidth="1"/>
@@ -14558,28 +14561,42 @@
         <v>13</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>40</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>0</v>
+      </c>
+      <c r="R8" s="11">
+        <v>160</v>
+      </c>
+      <c r="S8" s="11">
+        <v>250</v>
+      </c>
+      <c r="T8" s="11">
+        <v>210</v>
+      </c>
+      <c r="U8" s="11">
+        <v>300</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="W8" s="12">
+        <v>7</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>24</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -14741,28 +14758,42 @@
         <v>29</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>65</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>37</v>
+      </c>
+      <c r="R11" s="11">
+        <v>42</v>
+      </c>
+      <c r="S11" s="11">
+        <v>65</v>
+      </c>
+      <c r="T11" s="11">
+        <v>105</v>
+      </c>
+      <c r="U11" s="11">
+        <v>30</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>8.6</v>
+      </c>
+      <c r="W11" s="12">
+        <v>4</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>9.6</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>9.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -14802,28 +14833,42 @@
         <v>28</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>84</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>48</v>
+      </c>
+      <c r="R12" s="11">
+        <v>74</v>
+      </c>
+      <c r="S12" s="11">
+        <v>87</v>
+      </c>
+      <c r="T12" s="11">
+        <v>88</v>
+      </c>
+      <c r="U12" s="11">
+        <v>93</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>11.85</v>
+      </c>
+      <c r="W12" s="12">
+        <v>10</v>
+      </c>
       <c r="Y12" s="36">
         <f>D12</f>
         <v>105</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>11.85</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>105</v>
+        <v>93.15</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -14887,17 +14932,31 @@
         <v>17</v>
       </c>
       <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
+      <c r="P14" s="11">
+        <v>640</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>600</v>
+      </c>
+      <c r="R14" s="11">
+        <v>1040</v>
+      </c>
+      <c r="S14" s="11">
+        <v>880</v>
+      </c>
+      <c r="T14" s="11">
+        <v>1360</v>
+      </c>
+      <c r="U14" s="11">
+        <v>2400</v>
+      </c>
       <c r="V14" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="12"/>
+        <v>173</v>
+      </c>
+      <c r="W14" s="12">
+        <v>6</v>
+      </c>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
       <c r="AA14" s="38"/>
@@ -15065,31 +15124,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>60</v>
+        <v>889</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>45</v>
+        <v>730</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>45</v>
+        <v>1361</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>60</v>
+        <v>1342</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>45</v>
+        <v>1808</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>80</v>
+        <v>2903</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>335</v>
+        <v>9033</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -15098,11 +15157,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>8.375</v>
+        <v>52.825000000000003</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>142.22499999999999</v>
+        <v>97.775000000000006</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -15153,31 +15212,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>1.5</v>
+        <v>22.225000000000001</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>1.125</v>
+        <v>18.25</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>1.125</v>
+        <v>34.024999999999999</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>1.5</v>
+        <v>33.549999999999997</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>1.125</v>
+        <v>45.2</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>72.575000000000003</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>8.375</v>
+        <v>225.82499999999999</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -15186,11 +15245,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0.20937500000000001</v>
+        <v>1.3206250000000002</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>3.555625</v>
+        <v>2.444375</v>
       </c>
     </row>
   </sheetData>
@@ -15472,7 +15531,7 @@
     <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="14"/>
       <c r="B8" s="7" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11">
@@ -15516,9 +15575,7 @@
         <f>SUM(O8:U8)/40</f>
         <v>0</v>
       </c>
-      <c r="W8" s="12">
-        <v>19</v>
-      </c>
+      <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>14</v>
@@ -15579,9 +15636,7 @@
         <f t="shared" ref="V9:V13" si="1">SUM(O9:U9)/40</f>
         <v>0</v>
       </c>
-      <c r="W9" s="12">
-        <v>18</v>
-      </c>
+      <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
         <v>19.375</v>
@@ -15598,20 +15653,34 @@
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="7" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="D10" s="11">
+        <v>10</v>
+      </c>
+      <c r="E10" s="11">
+        <v>20</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
+        <v>260</v>
+      </c>
+      <c r="H10" s="11">
+        <v>220</v>
+      </c>
+      <c r="I10" s="11">
+        <v>240</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>18.75</v>
+      </c>
+      <c r="K10" s="12">
+        <v>9</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -15628,12 +15697,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W10" s="12">
-        <v>7</v>
-      </c>
+      <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>18.75</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -15641,7 +15708,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -15691,9 +15758,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W11" s="12">
-        <v>7</v>
-      </c>
+      <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>4.95</v>
@@ -15713,17 +15778,31 @@
         <v>28</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="D12" s="11">
+        <v>68</v>
+      </c>
+      <c r="E12" s="11">
+        <v>82</v>
+      </c>
+      <c r="F12" s="11">
+        <v>85</v>
+      </c>
+      <c r="G12" s="11">
+        <v>128</v>
+      </c>
+      <c r="H12" s="11">
+        <v>69</v>
+      </c>
+      <c r="I12" s="11">
+        <v>192</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" ref="J12:J17" si="5">SUM(C12:I12)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>15.6</v>
+      </c>
+      <c r="K12" s="12">
+        <v>13</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
@@ -15787,9 +15866,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W13" s="12">
-        <v>13</v>
-      </c>
+      <c r="W13" s="12"/>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -15826,9 +15903,7 @@
       <c r="V14" s="15">
         <v>21</v>
       </c>
-      <c r="W14" s="12">
-        <v>14</v>
-      </c>
+      <c r="W14" s="12"/>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
       <c r="AA14" s="38"/>
@@ -15865,9 +15940,7 @@
       <c r="V15" s="15">
         <v>8</v>
       </c>
-      <c r="W15" s="12">
-        <v>10</v>
-      </c>
+      <c r="W15" s="12"/>
       <c r="Y15" s="36"/>
       <c r="Z15" s="37"/>
       <c r="AA15" s="38"/>
@@ -15904,9 +15977,7 @@
       <c r="V16" s="15">
         <v>7</v>
       </c>
-      <c r="W16" s="12">
-        <v>8</v>
-      </c>
+      <c r="W16" s="12"/>
       <c r="Y16" s="36"/>
       <c r="Z16" s="37"/>
       <c r="AA16" s="38"/>
@@ -15963,31 +16034,31 @@
       </c>
       <c r="D18" s="25">
         <f t="shared" si="6"/>
-        <v>174</v>
+        <v>252</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="6"/>
-        <v>147</v>
+        <v>249</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="6"/>
-        <v>174</v>
+        <v>259</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="6"/>
-        <v>325</v>
+        <v>713</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="6"/>
-        <v>295</v>
+        <v>584</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="6"/>
-        <v>418</v>
+        <v>850</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>1533</v>
+        <v>2907</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
@@ -16027,7 +16098,7 @@
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>38.325000000000003</v>
+        <v>57.075000000000003</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
@@ -16035,7 +16106,7 @@
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>38.325000000000003</v>
+        <v>57.075000000000003</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -16049,31 +16120,31 @@
       </c>
       <c r="D19" s="21">
         <f t="shared" si="8"/>
-        <v>4.3499999999999996</v>
+        <v>6.3</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="8"/>
-        <v>3.6749999999999998</v>
+        <v>6.2249999999999996</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="8"/>
-        <v>4.3499999999999996</v>
+        <v>6.4749999999999996</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="8"/>
-        <v>8.125</v>
+        <v>17.824999999999999</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="8"/>
-        <v>7.375</v>
+        <v>14.6</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="8"/>
-        <v>10.45</v>
+        <v>21.25</v>
       </c>
       <c r="J19" s="22">
         <f>SUM(J8:J16)</f>
-        <v>38.325000000000003</v>
+        <v>72.674999999999997</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -16115,7 +16186,7 @@
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0.95812500000000012</v>
+        <v>1.4268750000000001</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
@@ -16123,7 +16194,7 @@
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.95812500000000012</v>
+        <v>1.4268750000000001</v>
       </c>
     </row>
   </sheetData>

--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F901BA56-13D1-4754-8402-72AC62184A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFA40EDE-CD92-4C64-AE1B-A31ADBD3887F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="21" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1885" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1884" uniqueCount="54">
   <si>
     <t>Booking</t>
   </si>
@@ -175,9 +175,6 @@
   </si>
   <si>
     <t>.</t>
-  </si>
-  <si>
-    <t>Leave</t>
   </si>
   <si>
     <t xml:space="preserve">Monday </t>
@@ -606,7 +603,7 @@
     <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -817,15 +814,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2801,7 +2789,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -2818,7 +2806,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -3709,7 +3697,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -3725,7 +3713,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -4133,10 +4121,10 @@
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="W1" t="s">
+        <v>48</v>
+      </c>
+      <c r="X1" t="s">
         <v>49</v>
-      </c>
-      <c r="X1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
@@ -4705,7 +4693,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -4722,7 +4710,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11">
@@ -5714,7 +5702,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -5731,7 +5719,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -6134,7 +6122,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="M1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -6684,7 +6672,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -6701,7 +6689,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -7653,7 +7641,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -7670,7 +7658,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11">
@@ -8331,31 +8319,31 @@
         <v>13</v>
       </c>
       <c r="C8" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D8" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E8" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F8" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G8" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H8" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I8" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J8" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K8" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
@@ -8363,31 +8351,31 @@
         <v>13</v>
       </c>
       <c r="O8" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P8" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q8" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="R8" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S8" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T8" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U8" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V8" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="W8" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y8" s="36" t="str">
         <f>J8</f>
@@ -8408,31 +8396,31 @@
         <v>14</v>
       </c>
       <c r="C9" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D9" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E9" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F9" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G9" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H9" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I9" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J9" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K9" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
@@ -8440,31 +8428,31 @@
         <v>14</v>
       </c>
       <c r="O9" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P9" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q9" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="R9" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S9" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T9" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U9" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V9" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="W9" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y9" s="36" t="str">
         <f t="shared" ref="Y9:Y17" si="0">J9</f>
@@ -8485,31 +8473,31 @@
         <v>15</v>
       </c>
       <c r="C10" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D10" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E10" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F10" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H10" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I10" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J10" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K10" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
@@ -8517,31 +8505,31 @@
         <v>15</v>
       </c>
       <c r="O10" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P10" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q10" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="R10" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S10" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T10" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U10" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V10" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="W10" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y10" s="36" t="str">
         <f t="shared" si="0"/>
@@ -8562,31 +8550,31 @@
         <v>29</v>
       </c>
       <c r="C11" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E11" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F11" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G11" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H11" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I11" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J11" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K11" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
@@ -8594,31 +8582,31 @@
         <v>29</v>
       </c>
       <c r="O11" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P11" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q11" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="R11" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S11" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T11" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U11" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V11" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="W11" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y11" s="36" t="str">
         <f t="shared" si="0"/>
@@ -8639,31 +8627,31 @@
         <v>28</v>
       </c>
       <c r="C12" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E12" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F12" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G12" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H12" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I12" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J12" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K12" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
@@ -8671,31 +8659,31 @@
         <v>28</v>
       </c>
       <c r="O12" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P12" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q12" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="R12" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S12" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T12" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U12" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V12" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="W12" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y12" s="36" t="str">
         <f t="shared" si="0"/>
@@ -8713,66 +8701,66 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E13" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F13" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G13" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H13" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I13" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J13" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K13" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="78" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O13" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P13" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q13" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="R13" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S13" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T13" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U13" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V13" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="W13" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
@@ -8784,31 +8772,31 @@
         <v>17</v>
       </c>
       <c r="C14" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D14" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E14" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F14" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G14" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H14" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I14" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J14" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K14" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
@@ -8816,31 +8804,31 @@
         <v>17</v>
       </c>
       <c r="O14" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P14" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q14" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="R14" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S14" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T14" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U14" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V14" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="W14" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
@@ -8852,31 +8840,31 @@
         <v>35</v>
       </c>
       <c r="C15" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E15" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F15" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G15" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H15" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I15" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J15" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K15" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
@@ -8884,31 +8872,31 @@
         <v>35</v>
       </c>
       <c r="O15" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P15" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q15" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="R15" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S15" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T15" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U15" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V15" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="W15" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y15" s="36"/>
       <c r="Z15" s="37"/>
@@ -8920,31 +8908,31 @@
         <v>36</v>
       </c>
       <c r="C16" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E16" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F16" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G16" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H16" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I16" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J16" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K16" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
@@ -8952,31 +8940,31 @@
         <v>36</v>
       </c>
       <c r="O16" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P16" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q16" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="R16" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S16" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T16" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U16" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V16" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="W16" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y16" s="36"/>
       <c r="Z16" s="37"/>
@@ -8988,62 +8976,62 @@
         <v>38</v>
       </c>
       <c r="C17" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D17" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E17" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F17" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G17" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H17" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I17" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J17" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K17" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M17" s="16"/>
       <c r="N17" s="78" t="s">
         <v>38</v>
       </c>
       <c r="O17" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P17" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q17" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="R17" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S17" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T17" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U17" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V17" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="W17" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y17" s="36" t="str">
         <f t="shared" si="0"/>
@@ -9857,7 +9845,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -9874,7 +9862,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -10768,7 +10756,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -10785,7 +10773,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -11746,7 +11734,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -11763,7 +11751,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -13764,7 +13752,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -13781,7 +13769,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -14874,7 +14862,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -14891,7 +14879,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -15531,7 +15519,7 @@
     <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="14"/>
       <c r="B8" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11">
@@ -15565,28 +15553,45 @@
         <v>13</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>10</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>20</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <f>260+170</f>
+        <v>430</v>
+      </c>
+      <c r="T8" s="11">
+        <f>220+120</f>
+        <v>340</v>
+      </c>
+      <c r="U8" s="11">
+        <f>240+190</f>
+        <v>430</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>30.75</v>
+      </c>
+      <c r="W8" s="12">
+        <v>29</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>14</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>30.75</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>14</v>
+        <v>-16.75</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -15626,28 +15631,42 @@
         <v>14</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>95</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>125</v>
+      </c>
+      <c r="R9" s="11">
+        <v>130</v>
+      </c>
+      <c r="S9" s="11">
+        <v>40</v>
+      </c>
+      <c r="T9" s="11">
+        <v>80</v>
+      </c>
+      <c r="U9" s="11">
+        <v>120</v>
+      </c>
       <c r="V9" s="15">
-        <f t="shared" ref="V9:V13" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
+        <v>14.75</v>
+      </c>
+      <c r="W9" s="12">
+        <v>13</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
         <v>19.375</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>14.75</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>19.375</v>
+        <v>4.625</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -15748,28 +15767,42 @@
         <v>29</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>12</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>0</v>
+      </c>
+      <c r="R11" s="11">
+        <v>12</v>
+      </c>
+      <c r="S11" s="11">
+        <v>63</v>
+      </c>
+      <c r="T11" s="11">
+        <v>23</v>
+      </c>
+      <c r="U11" s="11">
+        <v>64</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="W11" s="12">
+        <v>4</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>4.95</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>4.95</v>
+        <v>0.60000000000000053</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -15809,34 +15842,48 @@
         <v>28</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>41</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>58</v>
+      </c>
+      <c r="R12" s="11">
+        <v>54</v>
+      </c>
+      <c r="S12" s="11">
+        <v>113</v>
+      </c>
+      <c r="T12" s="11">
+        <v>59</v>
+      </c>
+      <c r="U12" s="11">
+        <v>165</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>12.25</v>
+      </c>
+      <c r="W12" s="12">
+        <v>10</v>
+      </c>
       <c r="Y12" s="36">
         <f>C12</f>
         <v>0</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>12.25</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-12.25</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -15853,7 +15900,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -15901,7 +15948,8 @@
       <c r="T14" s="11"/>
       <c r="U14" s="11"/>
       <c r="V14" s="15">
-        <v>21</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="W14" s="12"/>
       <c r="Y14" s="36"/>
@@ -15938,7 +15986,8 @@
       <c r="T15" s="11"/>
       <c r="U15" s="11"/>
       <c r="V15" s="15">
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="W15" s="12"/>
       <c r="Y15" s="36"/>
@@ -15975,7 +16024,8 @@
       <c r="T16" s="11"/>
       <c r="U16" s="11"/>
       <c r="V16" s="15">
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="W16" s="12"/>
       <c r="Y16" s="36"/>
@@ -16069,31 +16119,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>203</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>646</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>2484</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -16102,11 +16152,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>62.1</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>57.075000000000003</v>
+        <v>-5.0249999999999995</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -16157,31 +16207,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>5.0750000000000002</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>12.55</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>19.475000000000001</v>
       </c>
       <c r="V19" s="22">
         <f>SUM(V8:V16)</f>
-        <v>36</v>
+        <v>62.1</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -16190,11 +16240,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>1.5525</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>1.4268750000000001</v>
+        <v>-0.12562499999999999</v>
       </c>
     </row>
   </sheetData>
@@ -16481,31 +16531,17 @@
         <v>13</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="11">
-        <v>0</v>
-      </c>
-      <c r="E8" s="11">
-        <v>0</v>
-      </c>
-      <c r="F8" s="11">
-        <v>40</v>
-      </c>
-      <c r="G8" s="11">
-        <v>60</v>
-      </c>
-      <c r="H8" s="11">
-        <v>60</v>
-      </c>
-      <c r="I8" s="11">
-        <v>0</v>
-      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>4</v>
-      </c>
-      <c r="K8" s="12">
-        <v>17</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K8" s="12"/>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -16522,12 +16558,10 @@
         <f>SUM(O8:U8)/40</f>
         <v>0</v>
       </c>
-      <c r="W8" s="12">
-        <v>16</v>
-      </c>
+      <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -16535,7 +16569,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -16543,45 +16577,46 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="93" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="94"/>
-      <c r="E9" s="94"/>
-      <c r="F9" s="94"/>
-      <c r="G9" s="94"/>
-      <c r="H9" s="94"/>
-      <c r="I9" s="94"/>
-      <c r="J9" s="95"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="15">
+        <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
+        <v>0</v>
+      </c>
       <c r="K9" s="12"/>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="O9" s="43"/>
-      <c r="P9" s="43"/>
-      <c r="Q9" s="43"/>
-      <c r="R9" s="43"/>
-      <c r="S9" s="43"/>
-      <c r="T9" s="43"/>
-      <c r="U9" s="43"/>
-      <c r="V9" s="74">
-        <f t="shared" ref="V9:V16" si="0">SUM(O9:U9)/40</f>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="11"/>
+      <c r="T9" s="11"/>
+      <c r="U9" s="11"/>
+      <c r="V9" s="15">
+        <f>SUM(O9:U9)/40</f>
         <v>0</v>
       </c>
       <c r="W9" s="12"/>
-      <c r="Y9" s="36" t="str">
+      <c r="Y9" s="36">
         <f>C9</f>
-        <v>Leave</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="1">V9</f>
         <v>0</v>
       </c>
-      <c r="AA9" s="38" t="e">
+      <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="2">Y9-Z9</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -16590,31 +16625,17 @@
         <v>15</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11">
-        <v>40</v>
-      </c>
-      <c r="E10" s="11">
-        <v>18</v>
-      </c>
-      <c r="F10" s="11">
-        <v>40</v>
-      </c>
-      <c r="G10" s="11">
-        <v>0</v>
-      </c>
-      <c r="H10" s="11">
-        <v>0</v>
-      </c>
-      <c r="I10" s="11">
-        <v>0</v>
-      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
       <c r="J10" s="15">
-        <f t="shared" ref="J10:J17" si="3">SUM(C10:I10)/40</f>
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="K10" s="12">
-        <v>4</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="12"/>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -16628,15 +16649,13 @@
       <c r="T10" s="11"/>
       <c r="U10" s="11"/>
       <c r="V10" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12">
-        <v>4</v>
-      </c>
+        <f t="shared" ref="V9:V16" si="3">SUM(O10:U10)/40</f>
+        <v>0</v>
+      </c>
+      <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" ref="Y10:Y17" si="4">J10</f>
-        <v>2.4500000000000002</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="1"/>
@@ -16644,7 +16663,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="2"/>
-        <v>2.4500000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -16654,29 +16673,29 @@
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E11" s="11">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="F11" s="11">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G11" s="11">
-        <v>32</v>
+        <v>164</v>
       </c>
       <c r="H11" s="11">
-        <v>31</v>
+        <v>184</v>
       </c>
       <c r="I11" s="11">
-        <v>30</v>
+        <v>212</v>
       </c>
       <c r="J11" s="15">
-        <f t="shared" si="3"/>
-        <v>3.375</v>
+        <f t="shared" si="0"/>
+        <v>16.850000000000001</v>
       </c>
       <c r="K11" s="12">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
@@ -16691,15 +16710,13 @@
       <c r="T11" s="11"/>
       <c r="U11" s="11"/>
       <c r="V11" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12">
-        <v>4</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="4"/>
-        <v>3.375</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="1"/>
@@ -16707,7 +16724,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="2"/>
-        <v>3.375</v>
+        <v>16.850000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -16716,31 +16733,17 @@
         <v>28</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11">
-        <v>16</v>
-      </c>
-      <c r="E12" s="11">
-        <v>73</v>
-      </c>
-      <c r="F12" s="11">
-        <v>55</v>
-      </c>
-      <c r="G12" s="11">
-        <v>72</v>
-      </c>
-      <c r="H12" s="11">
-        <v>62</v>
-      </c>
-      <c r="I12" s="11">
-        <v>66</v>
-      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
       <c r="J12" s="15">
-        <f t="shared" si="3"/>
-        <v>8.6</v>
-      </c>
-      <c r="K12" s="12">
-        <v>6</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="12"/>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
@@ -16754,15 +16757,13 @@
       <c r="T12" s="11"/>
       <c r="U12" s="11"/>
       <c r="V12" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12">
-        <v>6</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W12" s="12"/>
       <c r="Y12" s="36">
         <f t="shared" si="4"/>
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="1"/>
@@ -16770,44 +16771,30 @@
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="2"/>
-        <v>8.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11"/>
-      <c r="D13" s="11">
-        <v>200</v>
-      </c>
-      <c r="E13" s="11">
-        <v>280</v>
-      </c>
-      <c r="F13" s="11">
-        <v>320</v>
-      </c>
-      <c r="G13" s="11">
-        <v>440</v>
-      </c>
-      <c r="H13" s="11">
-        <v>360</v>
-      </c>
-      <c r="I13" s="11">
-        <v>520</v>
-      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
       <c r="J13" s="15">
-        <f t="shared" si="3"/>
-        <v>53</v>
-      </c>
-      <c r="K13" s="12">
-        <v>3</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="12"/>
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -16817,12 +16804,10 @@
       <c r="T13" s="11"/>
       <c r="U13" s="11"/>
       <c r="V13" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12">
-        <v>4</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W13" s="12"/>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -16840,7 +16825,7 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
       <c r="J14" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K14" s="12"/>
@@ -16857,7 +16842,7 @@
       <c r="T14" s="11"/>
       <c r="U14" s="11"/>
       <c r="V14" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W14" s="12"/>
@@ -16878,7 +16863,7 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K15" s="12"/>
@@ -16895,7 +16880,7 @@
       <c r="T15" s="11"/>
       <c r="U15" s="11"/>
       <c r="V15" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W15" s="12"/>
@@ -16916,7 +16901,7 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K16" s="12"/>
@@ -16933,7 +16918,7 @@
       <c r="T16" s="11"/>
       <c r="U16" s="11"/>
       <c r="V16" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W16" s="12"/>
@@ -16954,7 +16939,7 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
       <c r="J17" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J10:J17" si="5">SUM(C17:I17)/40</f>
         <v>0</v>
       </c>
       <c r="K17" s="18"/>
@@ -16988,66 +16973,66 @@
       <c r="A18" s="1"/>
       <c r="B18" s="7"/>
       <c r="C18" s="25">
-        <f t="shared" ref="C18:I18" si="5">SUM(C8:C17)</f>
+        <f t="shared" ref="C18:I18" si="6">SUM(C8:C17)</f>
         <v>0</v>
       </c>
       <c r="D18" s="25">
-        <f t="shared" si="5"/>
-        <v>274</v>
+        <f t="shared" si="6"/>
+        <v>24</v>
       </c>
       <c r="E18" s="25">
-        <f t="shared" si="5"/>
-        <v>377</v>
+        <f t="shared" si="6"/>
+        <v>64</v>
       </c>
       <c r="F18" s="25">
-        <f t="shared" si="5"/>
-        <v>473</v>
+        <f t="shared" si="6"/>
+        <v>26</v>
       </c>
       <c r="G18" s="25">
-        <f t="shared" si="5"/>
-        <v>604</v>
+        <f t="shared" si="6"/>
+        <v>164</v>
       </c>
       <c r="H18" s="25">
-        <f t="shared" si="5"/>
-        <v>513</v>
+        <f t="shared" si="6"/>
+        <v>184</v>
       </c>
       <c r="I18" s="25">
-        <f t="shared" si="5"/>
-        <v>616</v>
+        <f t="shared" si="6"/>
+        <v>212</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>2857</v>
+        <v>674</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
       <c r="N18" s="7"/>
       <c r="O18" s="25">
-        <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
+        <f t="shared" ref="O18:U18" si="7">SUM(O8:O17)</f>
         <v>0</v>
       </c>
       <c r="P18" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q18" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R18" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S18" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T18" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="U18" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V18" s="26">
@@ -17057,15 +17042,15 @@
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>18.424999999999997</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
         <v>0</v>
       </c>
-      <c r="AA18" s="35" t="e">
+      <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>#VALUE!</v>
+        <v>16.850000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -17074,36 +17059,36 @@
         <v>18</v>
       </c>
       <c r="C19" s="21">
-        <f t="shared" ref="C19:J19" si="7">C18/40</f>
+        <f t="shared" ref="C19:J19" si="8">C18/40</f>
         <v>0</v>
       </c>
       <c r="D19" s="21">
-        <f t="shared" si="7"/>
-        <v>6.85</v>
+        <f t="shared" si="8"/>
+        <v>0.6</v>
       </c>
       <c r="E19" s="21">
-        <f t="shared" si="7"/>
-        <v>9.4250000000000007</v>
+        <f t="shared" si="8"/>
+        <v>1.6</v>
       </c>
       <c r="F19" s="21">
-        <f t="shared" si="7"/>
-        <v>11.824999999999999</v>
+        <f t="shared" si="8"/>
+        <v>0.65</v>
       </c>
       <c r="G19" s="21">
-        <f t="shared" si="7"/>
-        <v>15.1</v>
+        <f t="shared" si="8"/>
+        <v>4.0999999999999996</v>
       </c>
       <c r="H19" s="21">
-        <f t="shared" si="7"/>
-        <v>12.824999999999999</v>
+        <f t="shared" si="8"/>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I19" s="21">
-        <f t="shared" si="7"/>
-        <v>15.4</v>
+        <f t="shared" si="8"/>
+        <v>5.3</v>
       </c>
       <c r="J19" s="22">
-        <f t="shared" si="7"/>
-        <v>71.424999999999997</v>
+        <f t="shared" si="8"/>
+        <v>16.850000000000001</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -17111,54 +17096,53 @@
         <v>18</v>
       </c>
       <c r="O19" s="21">
-        <f t="shared" ref="O19:V19" si="8">O18/40</f>
+        <f t="shared" ref="O19:V19" si="9">O18/40</f>
         <v>0</v>
       </c>
       <c r="P19" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Q19" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R19" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S19" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T19" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U19" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V19" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0.46062499999999995</v>
+        <v>0.42125000000000001</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
         <v>0</v>
       </c>
-      <c r="AA19" s="41" t="e">
+      <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>#VALUE!</v>
+        <v>0.42125000000000001</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="C9:J9"/>
+  <mergeCells count="7">
     <mergeCell ref="Y3:AA4"/>
     <mergeCell ref="B2:J5"/>
     <mergeCell ref="N2:V5"/>
@@ -17756,7 +17740,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -17781,7 +17765,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -18713,7 +18697,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -18730,7 +18714,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -19662,7 +19646,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -19679,7 +19663,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -20542,7 +20526,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -20559,7 +20543,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -21573,7 +21557,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11">
@@ -21602,7 +21586,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -22627,7 +22611,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11">
@@ -22658,7 +22642,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -23775,7 +23759,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -23792,7 +23776,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -23973,7 +23957,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11">
@@ -24915,7 +24899,7 @@
       <c r="L18" s="13"/>
       <c r="M18" s="16"/>
       <c r="N18" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O18" s="11"/>
       <c r="P18" s="11">
@@ -26854,7 +26838,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="43"/>
       <c r="D13" s="43"/>
@@ -26871,7 +26855,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O13" s="43"/>
       <c r="P13" s="43"/>
@@ -27889,7 +27873,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="59"/>
       <c r="B13" s="60" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="54"/>
       <c r="D13" s="54"/>
@@ -27906,7 +27890,7 @@
       <c r="L13" s="56"/>
       <c r="M13" s="16"/>
       <c r="N13" s="60" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -28930,7 +28914,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -28947,7 +28931,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -29122,7 +29106,7 @@
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11">
@@ -29397,7 +29381,7 @@
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="X1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
@@ -29426,7 +29410,7 @@
       <c r="U2" s="83"/>
       <c r="V2" s="83"/>
       <c r="X2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -29969,7 +29953,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -29986,7 +29970,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -30997,7 +30981,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -31014,7 +30998,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -31992,7 +31976,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -32009,7 +31993,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>

--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFA40EDE-CD92-4C64-AE1B-A31ADBD3887F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124AF600-17D2-4DC2-8343-9EFC7FD6D4B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="21" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="23" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1884" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="58">
   <si>
     <t>Booking</t>
   </si>
@@ -217,6 +217,18 @@
   </si>
   <si>
     <t>Zeshan1</t>
+  </si>
+  <si>
+    <t>KK</t>
+  </si>
+  <si>
+    <t>Risen</t>
+  </si>
+  <si>
+    <t>Clinix</t>
+  </si>
+  <si>
+    <t>4Season</t>
   </si>
 </sst>
 </file>
@@ -15638,7 +15650,7 @@
         <v>125</v>
       </c>
       <c r="R9" s="11">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="S9" s="11">
         <v>40</v>
@@ -15651,7 +15663,7 @@
       </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
-        <v>14.75</v>
+        <v>14.875</v>
       </c>
       <c r="W9" s="12">
         <v>13</v>
@@ -15662,11 +15674,11 @@
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>14.75</v>
+        <v>14.875</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>4.625</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -15941,17 +15953,31 @@
         <v>17</v>
       </c>
       <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
+      <c r="P14" s="11">
+        <v>1279</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>1160</v>
+      </c>
+      <c r="R14" s="11">
+        <v>1159</v>
+      </c>
+      <c r="S14" s="11">
+        <v>1279</v>
+      </c>
+      <c r="T14" s="11">
+        <v>1158</v>
+      </c>
+      <c r="U14" s="11">
+        <v>1239</v>
+      </c>
       <c r="V14" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="12"/>
+        <v>181.85</v>
+      </c>
+      <c r="W14" s="12">
+        <v>4</v>
+      </c>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
       <c r="AA14" s="38"/>
@@ -16119,31 +16145,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="7"/>
-        <v>158</v>
+        <v>1437</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="7"/>
-        <v>203</v>
+        <v>1363</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="7"/>
-        <v>196</v>
+        <v>1360</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="7"/>
-        <v>646</v>
+        <v>1925</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="7"/>
-        <v>502</v>
+        <v>1660</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="7"/>
-        <v>779</v>
+        <v>2018</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>2484</v>
+        <v>9763</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -16152,11 +16178,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>62.1</v>
+        <v>62.225000000000001</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>-5.0249999999999995</v>
+        <v>-5.1499999999999995</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -16207,31 +16233,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="9"/>
-        <v>3.95</v>
+        <v>35.924999999999997</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="9"/>
-        <v>5.0750000000000002</v>
+        <v>34.075000000000003</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="9"/>
-        <v>4.9000000000000004</v>
+        <v>34</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="9"/>
-        <v>16.149999999999999</v>
+        <v>48.125</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="9"/>
-        <v>12.55</v>
+        <v>41.5</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="9"/>
-        <v>19.475000000000001</v>
+        <v>50.45</v>
       </c>
       <c r="V19" s="22">
         <f>SUM(V8:V16)</f>
-        <v>62.1</v>
+        <v>244.07499999999999</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -16240,11 +16266,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>1.5525</v>
+        <v>1.555625</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>-0.12562499999999999</v>
+        <v>-0.12874999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -16263,7 +16289,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8654740-B301-4AC2-BE07-AD027904CFB3}">
-  <dimension ref="A1:AA19"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -16289,7 +16315,7 @@
     <col min="27" max="27" width="6.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -16309,7 +16335,7 @@
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="83" t="s">
         <v>0</v>
@@ -16335,7 +16361,7 @@
       <c r="U2" s="83"/>
       <c r="V2" s="83"/>
     </row>
-    <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:29" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="83"/>
       <c r="C3" s="83"/>
@@ -16362,7 +16388,7 @@
       <c r="Z3" s="88"/>
       <c r="AA3" s="88"/>
     </row>
-    <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:29" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="B4" s="83"/>
       <c r="C4" s="83"/>
@@ -16387,7 +16413,7 @@
       <c r="Z4" s="88"/>
       <c r="AA4" s="88"/>
     </row>
-    <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="84"/>
       <c r="C5" s="84"/>
@@ -16418,7 +16444,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -16457,7 +16483,7 @@
       <c r="Z6" s="15"/>
       <c r="AA6" s="18"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A7" s="6"/>
       <c r="B7" s="7" t="s">
         <v>5</v>
@@ -16525,7 +16551,7 @@
       <c r="Z7" s="15"/>
       <c r="AA7" s="18"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A8" s="14"/>
       <c r="B8" s="7" t="s">
         <v>13</v>
@@ -16572,7 +16598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="7" t="s">
         <v>14</v>
@@ -16595,31 +16621,45 @@
         <v>14</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>78</v>
+      </c>
+      <c r="R9" s="11">
+        <v>120</v>
+      </c>
+      <c r="S9" s="11">
+        <v>1</v>
+      </c>
+      <c r="T9" s="11">
+        <v>1</v>
+      </c>
+      <c r="U9" s="11">
+        <v>1</v>
+      </c>
       <c r="V9" s="15">
         <f>SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>5.0250000000000004</v>
+      </c>
+      <c r="W9" s="12">
+        <v>14</v>
+      </c>
       <c r="Y9" s="36">
         <f>C9</f>
         <v>0</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="1">V9</f>
-        <v>0</v>
+        <v>5.0250000000000004</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="2">Y9-Z9</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
+        <v>-5.0250000000000004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="7" t="s">
         <v>15</v>
@@ -16649,7 +16689,7 @@
       <c r="T10" s="11"/>
       <c r="U10" s="11"/>
       <c r="V10" s="15">
-        <f t="shared" ref="V9:V16" si="3">SUM(O10:U10)/40</f>
+        <f t="shared" ref="V10:V16" si="3">SUM(O10:U10)/40</f>
         <v>0</v>
       </c>
       <c r="W10" s="12"/>
@@ -16666,7 +16706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
         <v>29</v>
@@ -16703,31 +16743,48 @@
         <v>29</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>24</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>64</v>
+      </c>
+      <c r="R11" s="11">
+        <v>26</v>
+      </c>
+      <c r="S11" s="11">
+        <v>164</v>
+      </c>
+      <c r="T11" s="11">
+        <v>184</v>
+      </c>
+      <c r="U11" s="11">
+        <v>212</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>16.850000000000001</v>
+      </c>
+      <c r="W11" s="12">
+        <v>5</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="4"/>
         <v>16.850000000000001</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="2"/>
-        <v>16.850000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
         <v>28</v>
@@ -16773,8 +16830,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="AC12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
         <v>42</v>
@@ -16811,8 +16871,11 @@
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="AC13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
         <v>17</v>
@@ -16849,8 +16912,11 @@
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
       <c r="AA14" s="38"/>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="AC14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
         <v>35</v>
@@ -16888,7 +16954,7 @@
       <c r="Z15" s="37"/>
       <c r="AA15" s="38"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
         <v>36</v>
@@ -16939,7 +17005,7 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
       <c r="J17" s="15">
-        <f t="shared" ref="J10:J17" si="5">SUM(C17:I17)/40</f>
+        <f t="shared" ref="J17" si="5">SUM(C17:I17)/40</f>
         <v>0</v>
       </c>
       <c r="K17" s="18"/>
@@ -17013,31 +17079,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>875</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -17046,11 +17112,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>21.875</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>16.850000000000001</v>
+        <v>-5.0250000000000004</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -17101,31 +17167,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>4.125</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>4.625</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>5.3250000000000002</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>21.875</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -17134,11 +17200,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>0.546875</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.42125000000000001</v>
+        <v>-0.12562500000000001</v>
       </c>
     </row>
   </sheetData>
@@ -17423,42 +17489,25 @@
       <c r="B8" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="11">
-        <v>17</v>
-      </c>
-      <c r="D8" s="11">
-        <v>60</v>
-      </c>
-      <c r="E8" s="11">
-        <v>60</v>
-      </c>
-      <c r="F8" s="11">
-        <v>80</v>
-      </c>
-      <c r="G8" s="11">
-        <v>90</v>
-      </c>
-      <c r="H8" s="11">
-        <v>100</v>
-      </c>
-      <c r="I8" s="11">
-        <v>170</v>
-      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
       <c r="J8" s="15">
-        <f>SUM(C8:I8)/40</f>
-        <v>14.425000000000001</v>
+        <v>15</v>
       </c>
       <c r="K8" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="O8" s="11">
-        <v>17</v>
-      </c>
+      <c r="O8" s="11"/>
       <c r="P8" s="11"/>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
@@ -17467,22 +17516,20 @@
       <c r="U8" s="11"/>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0.42499999999999999</v>
-      </c>
-      <c r="W8" s="12">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>14.425000000000001</v>
+        <v>15</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0.42499999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -17491,31 +17538,17 @@
         <v>31</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="11">
-        <v>0</v>
-      </c>
-      <c r="E9" s="11">
-        <v>10</v>
-      </c>
-      <c r="F9" s="11">
-        <v>20</v>
-      </c>
-      <c r="G9" s="11">
-        <v>70</v>
-      </c>
-      <c r="H9" s="11">
-        <v>80</v>
-      </c>
-      <c r="I9" s="11">
-        <v>200</v>
-      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J15" si="0">SUM(C9:I9)/40</f>
-        <v>9.5</v>
-      </c>
-      <c r="K9" s="12">
-        <v>21</v>
-      </c>
+        <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="12"/>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -17532,12 +17565,10 @@
         <f t="shared" ref="V9:V17" si="1">SUM(O9:U9)/40</f>
         <v>0</v>
       </c>
-      <c r="W9" s="12">
-        <v>21</v>
-      </c>
+      <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
@@ -17545,7 +17576,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>9.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -17554,31 +17585,17 @@
         <v>32</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11">
-        <v>29</v>
-      </c>
-      <c r="E10" s="11">
-        <v>24</v>
-      </c>
-      <c r="F10" s="11">
-        <v>67</v>
-      </c>
-      <c r="G10" s="11">
-        <v>39</v>
-      </c>
-      <c r="H10" s="11">
-        <v>34</v>
-      </c>
-      <c r="I10" s="11">
-        <v>87</v>
-      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="K10" s="12">
-        <v>5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K10" s="12"/>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -17595,12 +17612,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W10" s="12">
-        <v>5</v>
-      </c>
+      <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -17608,7 +17623,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -17618,29 +17633,29 @@
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="E11" s="11">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F11" s="11">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G11" s="11">
-        <v>52</v>
+        <v>108</v>
       </c>
       <c r="H11" s="11">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="I11" s="11">
-        <v>52</v>
+        <v>125</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>3.6</v>
+        <v>10.7</v>
       </c>
       <c r="K11" s="12">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
@@ -17658,12 +17673,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W11" s="12">
-        <v>5</v>
-      </c>
+      <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>3.6</v>
+        <v>10.7</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -17671,7 +17684,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>3.6</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -17681,29 +17694,29 @@
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11">
-        <v>12</v>
+        <v>106</v>
       </c>
       <c r="E12" s="11">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="F12" s="11">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="G12" s="11">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="H12" s="11">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="I12" s="11">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>4.3</v>
+        <v>9.35</v>
       </c>
       <c r="K12" s="12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
@@ -17721,12 +17734,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W12" s="12">
-        <v>5</v>
-      </c>
+      <c r="W12" s="12"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>4.3</v>
+        <v>9.35</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
@@ -17734,7 +17745,7 @@
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>4.3</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -17745,23 +17756,15 @@
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
-      <c r="F13" s="11">
-        <v>400</v>
-      </c>
+      <c r="F13" s="11"/>
       <c r="G13" s="11"/>
-      <c r="H13" s="11">
-        <v>800</v>
-      </c>
-      <c r="I13" s="11">
-        <v>400</v>
-      </c>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
       <c r="J13" s="15">
         <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="K13" s="12">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K13" s="12"/>
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
@@ -17778,9 +17781,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W13" s="12">
-        <v>3</v>
-      </c>
+      <c r="W13" s="12"/>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -17874,11 +17875,10 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="15">
-        <v>8</v>
-      </c>
-      <c r="K16" s="12">
-        <v>9</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="12"/>
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
@@ -17913,7 +17913,8 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
       <c r="J17" s="15">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
@@ -17931,12 +17932,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W17" s="12">
-        <v>5</v>
-      </c>
+      <c r="W17" s="12"/>
       <c r="Y17" s="36">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="37">
         <f t="shared" si="3"/>
@@ -17944,7 +17943,7 @@
       </c>
       <c r="AA17" s="38">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
@@ -17952,42 +17951,42 @@
       <c r="B18" s="7"/>
       <c r="C18" s="25">
         <f t="shared" ref="C18:I18" si="5">SUM(C8:C17)</f>
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>603</v>
+        <v>151</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>291</v>
+        <v>130</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>1091</v>
+        <v>114</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>919</v>
+        <v>155</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>3153</v>
+        <v>802</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
@@ -18015,20 +18014,20 @@
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>46.824999999999996</v>
+        <v>35.049999999999997</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0.42499999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>46.4</v>
+        <v>35.049999999999997</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -18038,35 +18037,35 @@
       </c>
       <c r="C19" s="21">
         <f t="shared" ref="C19:J19" si="7">C18/40</f>
-        <v>0.42499999999999999</v>
+        <v>0</v>
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>2.5249999999999999</v>
+        <v>3.375</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>3.2749999999999999</v>
+        <v>2.9249999999999998</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>15.074999999999999</v>
+        <v>3.7749999999999999</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>7.2750000000000004</v>
+        <v>3.25</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>27.274999999999999</v>
+        <v>2.85</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>22.975000000000001</v>
+        <v>3.875</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>78.825000000000003</v>
+        <v>20.05</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -18075,7 +18074,7 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>0.42499999999999999</v>
+        <v>0</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
@@ -18103,20 +18102,20 @@
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0.42499999999999999</v>
+        <v>0</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>1.1706249999999998</v>
+        <v>0.87624999999999997</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>1.0624999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>1.1599999999999999</v>
+        <v>0.87624999999999997</v>
       </c>
     </row>
   </sheetData>

--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124AF600-17D2-4DC2-8343-9EFC7FD6D4B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12DF53E6-AA22-4659-B956-8CBE7EB8FA69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="23" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="22" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1884" uniqueCount="54">
   <si>
     <t>Booking</t>
   </si>
@@ -217,18 +217,6 @@
   </si>
   <si>
     <t>Zeshan1</t>
-  </si>
-  <si>
-    <t>KK</t>
-  </si>
-  <si>
-    <t>Risen</t>
-  </si>
-  <si>
-    <t>Clinix</t>
-  </si>
-  <si>
-    <t>4Season</t>
   </si>
 </sst>
 </file>
@@ -16289,7 +16277,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8654740-B301-4AC2-BE07-AD027904CFB3}">
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -16315,7 +16303,7 @@
     <col min="27" max="27" width="6.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -16335,7 +16323,7 @@
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="83" t="s">
         <v>0</v>
@@ -16361,7 +16349,7 @@
       <c r="U2" s="83"/>
       <c r="V2" s="83"/>
     </row>
-    <row r="3" spans="1:29" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="83"/>
       <c r="C3" s="83"/>
@@ -16388,7 +16376,7 @@
       <c r="Z3" s="88"/>
       <c r="AA3" s="88"/>
     </row>
-    <row r="4" spans="1:29" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="B4" s="83"/>
       <c r="C4" s="83"/>
@@ -16413,7 +16401,7 @@
       <c r="Z4" s="88"/>
       <c r="AA4" s="88"/>
     </row>
-    <row r="5" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="84"/>
       <c r="C5" s="84"/>
@@ -16444,7 +16432,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -16483,7 +16471,7 @@
       <c r="Z6" s="15"/>
       <c r="AA6" s="18"/>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A7" s="6"/>
       <c r="B7" s="7" t="s">
         <v>5</v>
@@ -16551,7 +16539,7 @@
       <c r="Z7" s="15"/>
       <c r="AA7" s="18"/>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="14"/>
       <c r="B8" s="7" t="s">
         <v>13</v>
@@ -16574,31 +16562,45 @@
         <v>13</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>75</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>60</v>
+      </c>
+      <c r="R8" s="11">
+        <v>65</v>
+      </c>
+      <c r="S8" s="11">
+        <v>205</v>
+      </c>
+      <c r="T8" s="11">
+        <v>150</v>
+      </c>
+      <c r="U8" s="11">
+        <v>195</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>18.75</v>
+      </c>
+      <c r="W8" s="12">
+        <v>20</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>0</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>18.75</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.35">
+        <v>-18.75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="7" t="s">
         <v>14</v>
@@ -16659,7 +16661,7 @@
         <v>-5.0250000000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="7" t="s">
         <v>15</v>
@@ -16706,7 +16708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
         <v>29</v>
@@ -16780,11 +16782,8 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
         <v>28</v>
@@ -16807,34 +16806,45 @@
         <v>28</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>47</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>26</v>
+      </c>
+      <c r="R12" s="11">
+        <v>63</v>
+      </c>
+      <c r="S12" s="11">
+        <v>82</v>
+      </c>
+      <c r="T12" s="11">
+        <v>41</v>
+      </c>
+      <c r="U12" s="11">
+        <v>45</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>7.6</v>
+      </c>
+      <c r="W12" s="12">
+        <v>9</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.35">
+        <v>-7.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
         <v>42</v>
@@ -16871,11 +16881,8 @@
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
-      <c r="AC13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
         <v>17</v>
@@ -16898,25 +16905,36 @@
         <v>17</v>
       </c>
       <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
+      <c r="P14" s="11">
+        <v>320</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>280</v>
+      </c>
+      <c r="R14" s="11">
+        <v>320</v>
+      </c>
+      <c r="S14" s="11">
+        <v>360</v>
+      </c>
+      <c r="T14" s="11">
+        <v>320</v>
+      </c>
+      <c r="U14" s="11">
+        <v>460</v>
+      </c>
       <c r="V14" s="15">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="12"/>
+        <v>51.5</v>
+      </c>
+      <c r="W14" s="12">
+        <v>3</v>
+      </c>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
       <c r="AA14" s="38"/>
-      <c r="AC14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
         <v>35</v>
@@ -16954,7 +16972,7 @@
       <c r="Z15" s="37"/>
       <c r="AA15" s="38"/>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
         <v>36</v>
@@ -17079,31 +17097,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="7"/>
-        <v>24</v>
+        <v>466</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="7"/>
-        <v>142</v>
+        <v>508</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="7"/>
-        <v>146</v>
+        <v>594</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="7"/>
-        <v>165</v>
+        <v>812</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="7"/>
-        <v>185</v>
+        <v>696</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="7"/>
-        <v>213</v>
+        <v>913</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>875</v>
+        <v>3989</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -17112,11 +17130,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>21.875</v>
+        <v>48.225000000000001</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>-5.0250000000000004</v>
+        <v>-31.375</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -17167,31 +17185,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="9"/>
-        <v>0.6</v>
+        <v>11.65</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="9"/>
-        <v>3.55</v>
+        <v>12.7</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="9"/>
-        <v>3.65</v>
+        <v>14.85</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="9"/>
-        <v>4.125</v>
+        <v>20.3</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="9"/>
-        <v>4.625</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="9"/>
-        <v>5.3250000000000002</v>
+        <v>22.824999999999999</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="9"/>
-        <v>21.875</v>
+        <v>99.724999999999994</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -17200,11 +17218,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0.546875</v>
+        <v>1.2056249999999999</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>-0.12562500000000001</v>
+        <v>-0.78437500000000004</v>
       </c>
     </row>
   </sheetData>

--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12DF53E6-AA22-4659-B956-8CBE7EB8FA69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9429064-F537-4AEB-99C4-7E49279B7D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="22" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="25" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -603,7 +603,7 @@
     <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -782,6 +782,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1132,6 +1143,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4FB7967-E2EB-4CA7-BAB0-3E7FDF23CB2C}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1170,10 +1182,10 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="L1" s="86">
+      <c r="L1" s="91">
         <v>46032</v>
       </c>
-      <c r="M1" s="87"/>
+      <c r="M1" s="92"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -1185,104 +1197,104 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
-      <c r="L2" s="87"/>
-      <c r="M2" s="87"/>
-      <c r="N2" s="83" t="s">
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="82" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="82"/>
-      <c r="AA3" s="82"/>
+      <c r="Z3" s="87"/>
+      <c r="AA3" s="87"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="82"/>
-      <c r="Z4" s="82"/>
-      <c r="AA4" s="82"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="87"/>
+      <c r="Z4" s="87"/>
+      <c r="AA4" s="87"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -1299,16 +1311,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -1316,16 +1328,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -2178,6 +2190,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A6F57C8-6669-47B4-92C0-B801164619FC}">
+  <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2225,103 +2238,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -2338,16 +2351,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -2355,16 +2368,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -3197,6 +3210,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A69DB511-BA97-45BD-9562-F3C78F09ECB1}">
+  <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -3245,103 +3259,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -3358,16 +3372,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -3375,16 +3389,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -3558,13 +3572,13 @@
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="90"/>
-      <c r="D10" s="91"/>
-      <c r="E10" s="91"/>
-      <c r="F10" s="91"/>
-      <c r="G10" s="91"/>
-      <c r="H10" s="91"/>
-      <c r="I10" s="92"/>
+      <c r="C10" s="95"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="96"/>
+      <c r="F10" s="96"/>
+      <c r="G10" s="96"/>
+      <c r="H10" s="96"/>
+      <c r="I10" s="97"/>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4076,6 +4090,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCF0B926-7A0E-4186-8371-73B2B7C1B1B1}">
+  <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -4129,103 +4144,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -4242,16 +4257,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -4259,16 +4274,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -5090,6 +5105,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EBF7685-68CE-4230-832D-5008B05982CE}">
+  <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -5138,103 +5154,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -5251,16 +5267,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -5268,16 +5284,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -6085,6 +6101,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74048549-5414-4AF3-BA9C-2F8578E10521}">
+  <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -6135,103 +6152,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -6248,16 +6265,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -6265,16 +6282,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -7056,6 +7073,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3F409FB-57DF-48A4-8BA9-78EADEE000FC}">
+  <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -7104,103 +7122,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -7217,16 +7235,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -7234,16 +7252,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -8051,6 +8069,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B31058E7-4F6C-46ED-9090-75BF8B81EBB6}">
+  <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -8099,103 +8118,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -8212,16 +8231,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -8229,16 +8248,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -9234,6 +9253,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31BF237B-B436-499A-99A1-CE21BCFCEC29}">
+  <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -9281,103 +9301,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -9394,16 +9414,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -9411,16 +9431,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -10256,6 +10276,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5A5E597-1A73-411F-A36C-51BC98AA4226}">
+  <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -10304,103 +10325,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -10417,16 +10438,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -10434,16 +10455,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -11136,6 +11157,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FED4E2C-B3C5-473E-8709-91E86C4798CE}">
+  <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:AA27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -11184,103 +11206,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -11297,16 +11319,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -11314,16 +11336,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -12134,6 +12156,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{818C4D50-A789-4515-ABA1-71936FBC5F42}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -12172,10 +12195,10 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="L1" s="86">
+      <c r="L1" s="91">
         <v>46063</v>
       </c>
-      <c r="M1" s="87"/>
+      <c r="M1" s="92"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -12187,104 +12210,104 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
-      <c r="L2" s="87"/>
-      <c r="M2" s="87"/>
-      <c r="N2" s="83" t="s">
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -12301,16 +12324,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -12318,16 +12341,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -13182,6 +13205,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DE02268-B5C0-4F7D-B124-8932172B8A1F}">
+  <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:AA31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -13230,103 +13254,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -13343,16 +13367,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -13360,16 +13384,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -14250,6 +14274,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44600EF4-F35E-451F-BF84-5B668D1495CC}">
+  <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -14298,103 +14323,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -14411,16 +14436,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -14428,16 +14453,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -15256,6 +15281,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5B39ECB-3983-42D8-9225-B9053A82A404}">
+  <sheetPr codeName="Sheet22"/>
   <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -15302,103 +15328,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -15415,16 +15441,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -15432,16 +15458,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -16277,6 +16303,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8654740-B301-4AC2-BE07-AD027904CFB3}">
+  <sheetPr codeName="Sheet23"/>
   <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -16325,103 +16352,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -16438,16 +16465,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -16455,16 +16482,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -17241,6 +17268,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E0D980-13F5-4660-9608-17A818D5AFD2}">
+  <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -17288,103 +17316,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -17401,16 +17429,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -17418,16 +17446,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -17526,28 +17554,42 @@
         <v>30</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>95</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>45</v>
+      </c>
+      <c r="R8" s="11">
+        <v>150</v>
+      </c>
+      <c r="S8" s="11">
+        <v>80</v>
+      </c>
+      <c r="T8" s="11">
+        <v>60</v>
+      </c>
+      <c r="U8" s="11">
+        <v>80</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>12.75</v>
+      </c>
+      <c r="W8" s="12">
+        <v>17</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>15</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>12.75</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>15</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -17681,28 +17723,42 @@
         <v>29</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>17</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>15</v>
+      </c>
+      <c r="R11" s="11">
+        <v>17</v>
+      </c>
+      <c r="S11" s="11">
+        <v>92</v>
+      </c>
+      <c r="T11" s="11">
+        <v>82</v>
+      </c>
+      <c r="U11" s="11">
+        <v>97</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>8</v>
+      </c>
+      <c r="W11" s="12">
+        <v>8</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>10.7</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>10.7</v>
+        <v>2.6999999999999993</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -17742,28 +17798,42 @@
         <v>28</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>80</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>80</v>
+      </c>
+      <c r="R12" s="11">
+        <v>80</v>
+      </c>
+      <c r="S12" s="11">
+        <v>12</v>
+      </c>
+      <c r="T12" s="11">
+        <v>16</v>
+      </c>
+      <c r="U12" s="11">
+        <v>30</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>7.45</v>
+      </c>
+      <c r="W12" s="12">
+        <v>5</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
         <v>9.35</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.45</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>9.35</v>
+        <v>1.8999999999999995</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -17827,17 +17897,31 @@
         <v>17</v>
       </c>
       <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
+      <c r="P14" s="11">
+        <v>184</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>682</v>
+      </c>
+      <c r="R14" s="11">
+        <v>448</v>
+      </c>
+      <c r="S14" s="11">
+        <v>911</v>
+      </c>
+      <c r="T14" s="11">
+        <v>768</v>
+      </c>
+      <c r="U14" s="11">
+        <v>950</v>
+      </c>
       <c r="V14" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="12"/>
+        <v>98.575000000000003</v>
+      </c>
+      <c r="W14" s="12">
+        <v>5</v>
+      </c>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
       <c r="AA14" s="38"/>
@@ -18008,31 +18092,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>376</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>822</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>695</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1095</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>926</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1157</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>5071</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -18041,11 +18125,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>28.2</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>35.049999999999997</v>
+        <v>6.8499999999999988</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -18096,31 +18180,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>20.55</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>17.375</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>27.375</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>23.15</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>28.925000000000001</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>126.77500000000001</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -18129,11 +18213,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>0.70499999999999996</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.87624999999999997</v>
+        <v>0.17124999999999996</v>
       </c>
     </row>
   </sheetData>
@@ -18152,6 +18236,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34852770-3894-49D3-936F-C905C6D666C9}">
+  <sheetPr codeName="Sheet25"/>
   <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -18200,103 +18285,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -18313,16 +18398,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -18330,16 +18415,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -18419,54 +18504,32 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11">
-        <v>20</v>
-      </c>
-      <c r="E8" s="11">
-        <v>20</v>
-      </c>
-      <c r="F8" s="11">
-        <v>40</v>
-      </c>
-      <c r="G8" s="11">
-        <v>15</v>
-      </c>
-      <c r="H8" s="11">
-        <v>10</v>
-      </c>
-      <c r="I8" s="11">
-        <v>215</v>
-      </c>
-      <c r="J8" s="15">
-        <f>SUM(C8:I8)/40</f>
-        <v>8</v>
-      </c>
-      <c r="K8" s="12">
-        <v>7</v>
-      </c>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="74"/>
+      <c r="K8" s="82"/>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
-      <c r="V8" s="15">
-        <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12">
-        <v>7</v>
-      </c>
+      <c r="O8" s="43"/>
+      <c r="P8" s="43"/>
+      <c r="Q8" s="43"/>
+      <c r="R8" s="43"/>
+      <c r="S8" s="43"/>
+      <c r="T8" s="43"/>
+      <c r="U8" s="43"/>
+      <c r="V8" s="74"/>
+      <c r="W8" s="82"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -18474,7 +18537,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -18482,45 +18545,39 @@
       <c r="B9" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="11"/>
+      <c r="C9" s="43"/>
       <c r="D9" s="43"/>
       <c r="E9" s="43"/>
       <c r="F9" s="43"/>
       <c r="G9" s="43"/>
       <c r="H9" s="43"/>
       <c r="I9" s="43"/>
-      <c r="J9" s="15">
-        <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+      <c r="J9" s="74"/>
+      <c r="K9" s="82"/>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="O9" s="11"/>
+      <c r="O9" s="43"/>
       <c r="P9" s="43"/>
       <c r="Q9" s="43"/>
       <c r="R9" s="43"/>
       <c r="S9" s="43"/>
       <c r="T9" s="43"/>
       <c r="U9" s="43"/>
-      <c r="V9" s="15">
-        <f t="shared" ref="V9:V17" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+      <c r="V9" s="74"/>
+      <c r="W9" s="82"/>
       <c r="Y9" s="36">
-        <f t="shared" ref="Y9:Y17" si="2">J9</f>
+        <f t="shared" ref="Y9:Y17" si="0">J9</f>
         <v>0</v>
       </c>
       <c r="Z9" s="37">
-        <f t="shared" ref="Z9:Z17" si="3">V9</f>
+        <f t="shared" ref="Z9:Z17" si="1">V9</f>
         <v>0</v>
       </c>
       <c r="AA9" s="38">
-        <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
+        <f t="shared" ref="AA9:AA17" si="2">Y9-Z9</f>
         <v>0</v>
       </c>
     </row>
@@ -18529,60 +18586,40 @@
       <c r="B10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11">
-        <v>88</v>
-      </c>
-      <c r="F10" s="11">
-        <v>6</v>
-      </c>
-      <c r="G10" s="11">
-        <v>6</v>
-      </c>
-      <c r="H10" s="11">
-        <v>268</v>
-      </c>
-      <c r="I10" s="11">
-        <v>264</v>
-      </c>
-      <c r="J10" s="15">
-        <f t="shared" si="0"/>
-        <v>15.8</v>
-      </c>
-      <c r="K10" s="12">
-        <v>5</v>
-      </c>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="74"/>
+      <c r="K10" s="82"/>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
-      <c r="V10" s="15">
+      <c r="O10" s="43"/>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="43"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="43"/>
+      <c r="T10" s="43"/>
+      <c r="U10" s="43"/>
+      <c r="V10" s="74"/>
+      <c r="W10" s="82"/>
+      <c r="Y10" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W10" s="12">
-        <v>5</v>
-      </c>
-      <c r="Y10" s="36">
+      <c r="AA10" s="38">
         <f t="shared" si="2"/>
-        <v>15.8</v>
-      </c>
-      <c r="Z10" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA10" s="38">
-        <f t="shared" si="4"/>
-        <v>15.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -18590,62 +18627,40 @@
       <c r="B11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11">
-        <v>65</v>
-      </c>
-      <c r="E11" s="11">
-        <v>59</v>
-      </c>
-      <c r="F11" s="11">
-        <v>84</v>
-      </c>
-      <c r="G11" s="11">
-        <v>72</v>
-      </c>
-      <c r="H11" s="11">
-        <v>66</v>
-      </c>
-      <c r="I11" s="11">
-        <v>104</v>
-      </c>
-      <c r="J11" s="15">
-        <f t="shared" si="0"/>
-        <v>11.25</v>
-      </c>
-      <c r="K11" s="12">
-        <v>8</v>
-      </c>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="74"/>
+      <c r="K11" s="82"/>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
-      <c r="V11" s="15">
+      <c r="O11" s="43"/>
+      <c r="P11" s="43"/>
+      <c r="Q11" s="43"/>
+      <c r="R11" s="43"/>
+      <c r="S11" s="43"/>
+      <c r="T11" s="43"/>
+      <c r="U11" s="43"/>
+      <c r="V11" s="74"/>
+      <c r="W11" s="82"/>
+      <c r="Y11" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W11" s="12">
-        <v>6</v>
-      </c>
-      <c r="Y11" s="36">
+      <c r="AA11" s="38">
         <f t="shared" si="2"/>
-        <v>11.25</v>
-      </c>
-      <c r="Z11" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA11" s="38">
-        <f t="shared" si="4"/>
-        <v>11.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -18653,62 +18668,40 @@
       <c r="B12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11">
-        <v>44</v>
-      </c>
-      <c r="E12" s="11">
-        <v>4</v>
-      </c>
-      <c r="F12" s="11">
-        <v>74</v>
-      </c>
-      <c r="G12" s="11">
-        <v>36</v>
-      </c>
-      <c r="H12" s="11">
-        <v>33</v>
-      </c>
-      <c r="I12" s="11">
-        <v>33</v>
-      </c>
-      <c r="J12" s="15">
-        <f t="shared" si="0"/>
-        <v>5.6</v>
-      </c>
-      <c r="K12" s="12">
-        <v>7</v>
-      </c>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="74"/>
+      <c r="K12" s="82"/>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="15">
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="43"/>
+      <c r="V12" s="74"/>
+      <c r="W12" s="82"/>
+      <c r="Y12" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W12" s="12">
-        <v>5</v>
-      </c>
-      <c r="Y12" s="36">
+      <c r="AA12" s="38">
         <f t="shared" si="2"/>
-        <v>5.6</v>
-      </c>
-      <c r="Z12" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA12" s="38">
-        <f t="shared" si="4"/>
-        <v>5.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -18716,37 +18709,29 @@
       <c r="B13" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="12"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="74"/>
+      <c r="K13" s="82"/>
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12">
-        <v>5</v>
-      </c>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="43"/>
+      <c r="T13" s="43"/>
+      <c r="U13" s="43"/>
+      <c r="V13" s="74"/>
+      <c r="W13" s="82"/>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -18756,35 +18741,29 @@
       <c r="B14" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="12"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="74"/>
+      <c r="K14" s="82"/>
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="12"/>
+      <c r="O14" s="43"/>
+      <c r="P14" s="43"/>
+      <c r="Q14" s="43"/>
+      <c r="R14" s="43"/>
+      <c r="S14" s="43"/>
+      <c r="T14" s="43"/>
+      <c r="U14" s="43"/>
+      <c r="V14" s="74"/>
+      <c r="W14" s="82"/>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
       <c r="AA14" s="38"/>
@@ -18794,35 +18773,29 @@
       <c r="B15" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="12"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="74"/>
+      <c r="K15" s="82"/>
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="11"/>
-      <c r="S15" s="11"/>
-      <c r="T15" s="11"/>
-      <c r="U15" s="11"/>
-      <c r="V15" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W15" s="12"/>
+      <c r="O15" s="43"/>
+      <c r="P15" s="43"/>
+      <c r="Q15" s="43"/>
+      <c r="R15" s="43"/>
+      <c r="S15" s="43"/>
+      <c r="T15" s="43"/>
+      <c r="U15" s="43"/>
+      <c r="V15" s="74"/>
+      <c r="W15" s="82"/>
       <c r="Y15" s="36"/>
       <c r="Z15" s="37"/>
       <c r="AA15" s="38"/>
@@ -18832,35 +18805,29 @@
       <c r="B16" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="12"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="74"/>
+      <c r="K16" s="82"/>
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W16" s="12"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="43"/>
+      <c r="R16" s="43"/>
+      <c r="S16" s="43"/>
+      <c r="T16" s="43"/>
+      <c r="U16" s="43"/>
+      <c r="V16" s="74"/>
+      <c r="W16" s="82"/>
       <c r="Y16" s="36"/>
       <c r="Z16" s="37"/>
       <c r="AA16" s="38"/>
@@ -18870,121 +18837,94 @@
       <c r="B17" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="18"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="74">
+        <f t="shared" ref="J17" si="3">SUM(C17:I17)/40</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="83"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
-      <c r="S17" s="11"/>
-      <c r="T17" s="11"/>
-      <c r="U17" s="11"/>
-      <c r="V17" s="15">
+      <c r="O17" s="43"/>
+      <c r="P17" s="43"/>
+      <c r="Q17" s="43"/>
+      <c r="R17" s="43"/>
+      <c r="S17" s="43"/>
+      <c r="T17" s="43"/>
+      <c r="U17" s="43"/>
+      <c r="V17" s="74"/>
+      <c r="W17" s="83"/>
+      <c r="Y17" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z17" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W17" s="18"/>
-      <c r="Y17" s="36">
+      <c r="AA17" s="38">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Z17" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA17" s="38">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="7"/>
-      <c r="C18" s="25">
-        <f t="shared" ref="C18:I18" si="5">SUM(C8:C17)</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="25">
-        <f t="shared" si="5"/>
-        <v>129</v>
-      </c>
-      <c r="E18" s="25">
-        <f t="shared" si="5"/>
-        <v>171</v>
-      </c>
-      <c r="F18" s="25">
-        <f t="shared" si="5"/>
-        <v>204</v>
-      </c>
-      <c r="G18" s="25">
-        <f t="shared" si="5"/>
-        <v>129</v>
-      </c>
-      <c r="H18" s="25">
-        <f t="shared" si="5"/>
-        <v>377</v>
-      </c>
-      <c r="I18" s="25">
-        <f t="shared" si="5"/>
-        <v>616</v>
-      </c>
-      <c r="J18" s="26">
+      <c r="C18" s="79">
+        <f t="shared" ref="C18:I18" si="4">SUM(C8:C17)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="79">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E18" s="79">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="79">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="79">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="79">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="79">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="80">
         <f>SUM(C18:I18)</f>
-        <v>1626</v>
-      </c>
-      <c r="K18" s="28"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="81"/>
       <c r="M18" s="1"/>
       <c r="N18" s="7"/>
-      <c r="O18" s="25">
-        <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>0</v>
-      </c>
-      <c r="P18" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R18" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S18" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T18" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U18" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="V18" s="26">
-        <f>SUM(O18:U18)</f>
-        <v>0</v>
-      </c>
-      <c r="W18" s="28"/>
+      <c r="O18" s="79"/>
+      <c r="P18" s="79"/>
+      <c r="Q18" s="79"/>
+      <c r="R18" s="79"/>
+      <c r="S18" s="79"/>
+      <c r="T18" s="79"/>
+      <c r="U18" s="79"/>
+      <c r="V18" s="80"/>
+      <c r="W18" s="81"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>40.65</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
@@ -18992,7 +18932,7 @@
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>40.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -19000,79 +18940,55 @@
       <c r="B19" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="21">
-        <f t="shared" ref="C19:J19" si="7">C18/40</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="21">
-        <f t="shared" si="7"/>
-        <v>3.2250000000000001</v>
-      </c>
-      <c r="E19" s="21">
-        <f t="shared" si="7"/>
-        <v>4.2750000000000004</v>
-      </c>
-      <c r="F19" s="21">
-        <f t="shared" si="7"/>
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="G19" s="21">
-        <f t="shared" si="7"/>
-        <v>3.2250000000000001</v>
-      </c>
-      <c r="H19" s="21">
-        <f t="shared" si="7"/>
-        <v>9.4250000000000007</v>
-      </c>
-      <c r="I19" s="21">
-        <f t="shared" si="7"/>
-        <v>15.4</v>
-      </c>
-      <c r="J19" s="22">
-        <f t="shared" si="7"/>
-        <v>40.65</v>
-      </c>
-      <c r="K19" s="23"/>
+      <c r="C19" s="84">
+        <f t="shared" ref="C19:J19" si="5">C18/40</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="84">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E19" s="84">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="84">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="84">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H19" s="84">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I19" s="84">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="85">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="86"/>
       <c r="M19" s="1"/>
       <c r="N19" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="O19" s="21">
-        <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>0</v>
-      </c>
-      <c r="P19" s="21">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="21">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="R19" s="21">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="S19" s="21">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="T19" s="21">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="U19" s="21">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V19" s="22">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="W19" s="23"/>
+      <c r="O19" s="84"/>
+      <c r="P19" s="84"/>
+      <c r="Q19" s="84"/>
+      <c r="R19" s="84"/>
+      <c r="S19" s="84"/>
+      <c r="T19" s="84"/>
+      <c r="U19" s="84"/>
+      <c r="V19" s="85"/>
+      <c r="W19" s="86"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>1.0162499999999999</v>
+        <v>0</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
@@ -19080,7 +18996,7 @@
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>1.0162499999999999</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -19099,6 +19015,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1A00C44-2950-4D8E-9E22-FF4AAE187093}">
+  <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -19147,103 +19064,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -19260,16 +19177,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -19277,16 +19194,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -19368,29 +19285,29 @@
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="E8" s="11">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="F8" s="11">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="G8" s="11">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="H8" s="11">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="I8" s="11">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>11.9</v>
+        <v>20.25</v>
       </c>
       <c r="K8" s="12">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
@@ -19398,30 +19315,42 @@
         <v>13</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>80</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>80</v>
+      </c>
+      <c r="R8" s="11">
+        <v>80</v>
+      </c>
+      <c r="S8" s="11">
+        <v>120</v>
+      </c>
+      <c r="T8" s="11">
+        <v>80</v>
+      </c>
+      <c r="U8" s="11">
+        <v>120</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="W8" s="12">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>11.9</v>
+        <v>20.25</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>11.9</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -19477,31 +19406,17 @@
         <v>15</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11">
-        <v>15</v>
-      </c>
-      <c r="E10" s="11">
-        <v>12</v>
-      </c>
-      <c r="F10" s="11">
-        <v>13</v>
-      </c>
-      <c r="G10" s="11">
-        <v>93</v>
-      </c>
-      <c r="H10" s="11">
-        <v>93</v>
-      </c>
-      <c r="I10" s="11">
-        <v>92</v>
-      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>7.95</v>
-      </c>
-      <c r="K10" s="12">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K10" s="12"/>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -19518,12 +19433,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W10" s="12">
-        <v>8</v>
-      </c>
+      <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>7.95</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -19531,7 +19444,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>7.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -19541,29 +19454,29 @@
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="E11" s="11">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="F11" s="11">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="G11" s="11">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="H11" s="11">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="I11" s="11">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>4.5999999999999996</v>
+        <v>11.425000000000001</v>
       </c>
       <c r="K11" s="12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
@@ -19581,12 +19494,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W11" s="12">
-        <v>4</v>
-      </c>
+      <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>4.5999999999999996</v>
+        <v>11.425000000000001</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -19594,7 +19505,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>4.5999999999999996</v>
+        <v>11.425000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -19603,31 +19514,17 @@
         <v>28</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11">
-        <v>60</v>
-      </c>
-      <c r="E12" s="11">
-        <v>20</v>
-      </c>
-      <c r="F12" s="11">
-        <v>84</v>
-      </c>
-      <c r="G12" s="11">
-        <v>56</v>
-      </c>
-      <c r="H12" s="11">
-        <v>53</v>
-      </c>
-      <c r="I12" s="11">
-        <v>53</v>
-      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>8.15</v>
-      </c>
-      <c r="K12" s="12">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K12" s="12"/>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
@@ -19644,12 +19541,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W12" s="12">
-        <v>8</v>
-      </c>
+      <c r="W12" s="12"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>8.15</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
@@ -19657,7 +19552,7 @@
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>8.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -19693,9 +19588,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W13" s="12">
-        <v>1</v>
-      </c>
+      <c r="W13" s="12"/>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -19866,31 +19759,31 @@
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>124</v>
+        <v>199</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>100</v>
+        <v>189</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>226</v>
+        <v>201</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>404</v>
+        <v>245</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>1304</v>
+        <v>1267</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
@@ -19901,44 +19794,44 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>32.6</v>
+        <v>31.675000000000001</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>32.6</v>
+        <v>17.675000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -19952,31 +19845,31 @@
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>3.1</v>
+        <v>4.9749999999999996</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>2.5</v>
+        <v>4.7249999999999996</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>5.45</v>
+        <v>6.0250000000000004</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>5.65</v>
+        <v>5.0250000000000004</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>10.1</v>
+        <v>6.125</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>32.6</v>
+        <v>31.675000000000001</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -19989,44 +19882,44 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0.81500000000000006</v>
+        <v>0.791875</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.81500000000000006</v>
+        <v>0.44187500000000002</v>
       </c>
     </row>
   </sheetData>
@@ -20045,6 +19938,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C5F6109-5400-4343-A102-C2C414DDFBDF}">
+  <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:AA22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -20091,103 +19985,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -20204,16 +20098,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -20221,16 +20115,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -21012,6 +20906,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8009CC4-0AF4-4E7F-B044-5E07B86C5D3C}">
+  <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:AA22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -21060,103 +20955,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -21173,16 +21068,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -21190,16 +21085,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -22049,6 +21944,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{753F267E-9AB4-4A14-B158-934CAE66BC78}">
+  <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:AA22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -22096,103 +21992,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -22209,16 +22105,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -22226,16 +22122,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -23134,6 +23030,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAD5E74C-C447-4A90-B62E-14FECF9BB5AD}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -23184,103 +23081,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -23297,16 +23194,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -23314,16 +23211,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -24198,6 +24095,7 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E84A1E7-4231-4CD7-B906-1741794EB6A0}">
+  <sheetPr codeName="Sheet30"/>
   <dimension ref="A1:AA23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -24245,103 +24143,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -24358,16 +24256,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -24375,16 +24273,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -25242,6 +25140,7 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE9DEC90-B3AB-443E-9C2F-99376CA7B8EA}">
+  <sheetPr codeName="Sheet31"/>
   <dimension ref="A1:AA21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -25265,103 +25164,103 @@
       <c r="A1" s="75">
         <v>46296</v>
       </c>
-      <c r="B1" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
+      <c r="B1" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
       <c r="M1" s="1"/>
-      <c r="N1" s="83" t="s">
+      <c r="N1" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="83"/>
-      <c r="S1" s="83"/>
-      <c r="T1" s="83"/>
-      <c r="U1" s="83"/>
-      <c r="V1" s="83"/>
+      <c r="O1" s="88"/>
+      <c r="P1" s="88"/>
+      <c r="Q1" s="88"/>
+      <c r="R1" s="88"/>
+      <c r="S1" s="88"/>
+      <c r="T1" s="88"/>
+      <c r="U1" s="88"/>
+      <c r="V1" s="88"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83"/>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
-      <c r="Y2" s="88" t="s">
+      <c r="N2" s="88"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
+      <c r="Y2" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z2" s="88"/>
-      <c r="AA2" s="88"/>
+      <c r="Z2" s="93"/>
+      <c r="AA2" s="93"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88"/>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
-      <c r="J4" s="84"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="84"/>
-      <c r="O4" s="84"/>
-      <c r="P4" s="84"/>
-      <c r="Q4" s="84"/>
-      <c r="R4" s="84"/>
-      <c r="S4" s="84"/>
-      <c r="T4" s="84"/>
-      <c r="U4" s="84"/>
-      <c r="V4" s="84"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
       <c r="Y4" s="29" t="s">
         <v>0</v>
       </c>
@@ -25378,16 +25277,16 @@
       <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="85" t="s">
+      <c r="D5" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="85"/>
-      <c r="F5" s="85"/>
-      <c r="G5" s="85" t="s">
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="85"/>
-      <c r="I5" s="85"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
       <c r="J5" s="4"/>
       <c r="K5" s="5"/>
       <c r="M5" s="1"/>
@@ -25395,16 +25294,16 @@
       <c r="O5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P5" s="85" t="s">
+      <c r="P5" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q5" s="85"/>
-      <c r="R5" s="85"/>
-      <c r="S5" s="85" t="s">
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T5" s="85"/>
-      <c r="U5" s="85"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
       <c r="V5" s="4"/>
       <c r="W5" s="5"/>
       <c r="Y5" s="30"/>
@@ -26343,6 +26242,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{286FBE16-0424-4AA6-A26A-B37C87397264}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -26393,103 +26293,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -26506,16 +26406,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -26523,16 +26423,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -27237,6 +27137,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD3A0396-7890-4995-B70F-491025A8A037}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:AA20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -27289,111 +27190,111 @@
     </row>
     <row r="2" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="44"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="K2" s="44"/>
       <c r="L2" s="44"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="44"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="K3" s="44"/>
       <c r="L3" s="44"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="44"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="K4" s="44"/>
       <c r="L4" s="44"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="44"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="K5" s="44"/>
       <c r="L5" s="44"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -27410,16 +27311,16 @@
       <c r="C6" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="89" t="s">
+      <c r="D6" s="94" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="89" t="s">
+      <c r="E6" s="94"/>
+      <c r="F6" s="94"/>
+      <c r="G6" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="89"/>
-      <c r="I6" s="89"/>
+      <c r="H6" s="94"/>
+      <c r="I6" s="94"/>
       <c r="J6" s="47"/>
       <c r="K6" s="48"/>
       <c r="L6" s="44"/>
@@ -27428,16 +27329,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -28289,6 +28190,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{902B1D63-9221-4747-B7FB-C6037E7ADA17}">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -28339,103 +28241,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -28452,16 +28354,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -28469,16 +28371,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -29352,6 +29254,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93633F42-AC98-43DD-8F7A-85910B527402}">
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -29403,106 +29306,106 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
       <c r="X2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -29519,16 +29422,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -29536,16 +29439,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -30387,6 +30290,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B9C4E6D-17E5-4D33-833A-ACEA6390716F}">
+  <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -30434,103 +30338,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -30547,16 +30451,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -30564,16 +30468,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -31409,6 +31313,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00FF78AC-42E1-47D8-9009-F093134445D4}">
+  <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:AA22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -31457,103 +31362,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="Y3" s="88" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="Y3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -31570,16 +31475,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85" t="s">
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -31587,16 +31492,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85" t="s">
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>

--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9429064-F537-4AEB-99C4-7E49279B7D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E70ABB8-D8FA-46E5-87B9-B2E992D6340F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="25" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="27" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -19376,28 +19376,42 @@
         <v>14</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>72</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>32</v>
+      </c>
+      <c r="R9" s="11">
+        <v>52</v>
+      </c>
+      <c r="S9" s="11">
+        <v>70</v>
+      </c>
+      <c r="T9" s="11">
+        <v>70</v>
+      </c>
+      <c r="U9" s="11">
+        <v>145</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>11.025</v>
+      </c>
+      <c r="W9" s="12">
+        <v>7</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
         <v>0</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>11.025</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>-11.025</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -19484,28 +19498,42 @@
         <v>29</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>44</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>84</v>
+      </c>
+      <c r="R11" s="11">
+        <v>4</v>
+      </c>
+      <c r="S11" s="11">
+        <v>56</v>
+      </c>
+      <c r="T11" s="11">
+        <v>96</v>
+      </c>
+      <c r="U11" s="11">
+        <v>57</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>8.5250000000000004</v>
+      </c>
+      <c r="W11" s="12">
+        <v>5</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>11.425000000000001</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.5250000000000004</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>11.425000000000001</v>
+        <v>2.9000000000000004</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -19616,17 +19644,29 @@
         <v>17</v>
       </c>
       <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
+      <c r="P14" s="11">
+        <v>80</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>80</v>
+      </c>
       <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
+      <c r="S14" s="11">
+        <v>120</v>
+      </c>
+      <c r="T14" s="11">
+        <v>120</v>
+      </c>
+      <c r="U14" s="11">
+        <v>120</v>
+      </c>
       <c r="V14" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="12"/>
+        <v>13</v>
+      </c>
+      <c r="W14" s="12">
+        <v>2</v>
+      </c>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
       <c r="AA14" s="38"/>
@@ -19794,31 +19834,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>80</v>
+        <v>276</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>80</v>
+        <v>276</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>366</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>80</v>
+        <v>366</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>442</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>560</v>
+        <v>1862</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -19827,11 +19867,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>14</v>
+        <v>33.549999999999997</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>17.675000000000001</v>
+        <v>-1.875</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -19882,31 +19922,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>6.9</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>6.9</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>9.15</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>9.15</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>11.05</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>14</v>
+        <v>46.55</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -19915,11 +19955,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0.35</v>
+        <v>0.83874999999999988</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.44187500000000002</v>
+        <v>-4.6875E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20222,28 +20262,42 @@
         <v>30</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>20</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>0</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>40</v>
+      </c>
+      <c r="T8" s="11">
+        <v>20</v>
+      </c>
+      <c r="U8" s="11">
+        <v>60</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>3.5</v>
+      </c>
+      <c r="W8" s="12">
+        <v>11</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>0</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -20269,28 +20323,42 @@
         <v>31</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>20</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>20</v>
+      </c>
+      <c r="R9" s="11">
+        <v>0</v>
+      </c>
+      <c r="S9" s="11">
+        <v>116</v>
+      </c>
+      <c r="T9" s="11">
+        <v>70</v>
+      </c>
+      <c r="U9" s="11">
+        <v>292</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>12.95</v>
+      </c>
+      <c r="W9" s="12">
+        <v>16</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y20" si="2">J9</f>
         <v>0</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z20" si="3">V9</f>
-        <v>0</v>
+        <v>12.95</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA20" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>-12.95</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -20363,28 +20431,42 @@
         <v>29</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>20</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>20</v>
+      </c>
+      <c r="R11" s="11">
+        <v>0</v>
+      </c>
+      <c r="S11" s="11">
+        <v>68</v>
+      </c>
+      <c r="T11" s="11">
+        <v>128</v>
+      </c>
+      <c r="U11" s="11">
+        <v>59</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>7.375</v>
+      </c>
+      <c r="W11" s="12">
+        <v>6</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.375</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-7.375</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -20410,28 +20492,42 @@
         <v>28</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>6</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>6</v>
+      </c>
+      <c r="R12" s="11">
+        <v>0</v>
+      </c>
+      <c r="S12" s="11">
+        <v>18</v>
+      </c>
+      <c r="T12" s="11">
+        <v>24</v>
+      </c>
+      <c r="U12" s="11">
+        <v>32</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>2.15</v>
+      </c>
+      <c r="W12" s="12">
+        <v>4</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -20762,11 +20858,11 @@
       </c>
       <c r="P21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="Q21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="R21" s="25">
         <f t="shared" si="6"/>
@@ -20774,19 +20870,19 @@
       </c>
       <c r="S21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="T21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="U21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>443</v>
       </c>
       <c r="V21" s="26">
         <f>SUM(O21:U21)</f>
-        <v>0</v>
+        <v>1039</v>
       </c>
       <c r="W21" s="28"/>
       <c r="Y21" s="33">
@@ -20795,11 +20891,11 @@
       </c>
       <c r="Z21" s="34">
         <f>SUM(Z8:Z20)</f>
-        <v>0</v>
+        <v>25.974999999999998</v>
       </c>
       <c r="AA21" s="35">
         <f>SUM(AA8:AA20)</f>
-        <v>0</v>
+        <v>-25.974999999999998</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -20850,11 +20946,11 @@
       </c>
       <c r="P22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="R22" s="21">
         <f t="shared" si="8"/>
@@ -20862,19 +20958,19 @@
       </c>
       <c r="S22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="T22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="U22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>11.074999999999999</v>
       </c>
       <c r="V22" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>25.975000000000001</v>
       </c>
       <c r="W22" s="23"/>
       <c r="Y22" s="39">
@@ -20883,11 +20979,11 @@
       </c>
       <c r="Z22" s="40">
         <f>Z21/40</f>
-        <v>0</v>
+        <v>0.64937499999999992</v>
       </c>
       <c r="AA22" s="41">
         <f>AA21/40</f>
-        <v>0</v>
+        <v>-0.64937499999999992</v>
       </c>
     </row>
   </sheetData>
@@ -21175,23 +21271,31 @@
         <v>30</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
+      <c r="D8" s="11">
+        <v>80</v>
+      </c>
+      <c r="E8" s="11">
+        <v>40</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
       <c r="G8" s="11">
-        <v>800</v>
+        <v>255</v>
       </c>
       <c r="H8" s="11">
-        <v>720</v>
+        <v>110</v>
       </c>
       <c r="I8" s="11">
-        <v>880</v>
+        <v>155</v>
       </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>60</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>16</v>
+      </c>
+      <c r="K8" s="12">
+        <v>8</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -21213,7 +21317,7 @@
       </c>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -21221,7 +21325,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>60</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -21229,30 +21333,34 @@
       <c r="B9" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="11"/>
+      <c r="C9" s="11">
+        <v>20</v>
+      </c>
       <c r="D9" s="11">
-        <v>105</v>
+        <v>200</v>
       </c>
       <c r="E9" s="11">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="F9" s="11">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="G9" s="11">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H9" s="11">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I9" s="11">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J15" si="0">SUM(C9:I9)/40</f>
-        <v>9.5</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>16</v>
+      </c>
+      <c r="K9" s="12">
+        <v>25</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -21274,7 +21382,7 @@
       </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>9.5</v>
+        <v>16</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
@@ -21282,7 +21390,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>9.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -21291,27 +21399,15 @@
         <v>32</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11">
-        <v>26</v>
-      </c>
-      <c r="E10" s="11">
-        <v>25</v>
-      </c>
-      <c r="F10" s="11">
-        <v>105</v>
-      </c>
-      <c r="G10" s="11">
-        <v>227</v>
-      </c>
-      <c r="H10" s="11">
-        <v>164</v>
-      </c>
-      <c r="I10" s="11">
-        <v>125</v>
-      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>16.8</v>
+        <v>0</v>
       </c>
       <c r="K10" s="12"/>
       <c r="L10" s="13"/>
@@ -21335,7 +21431,7 @@
       </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>16.8</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -21343,7 +21439,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>16.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -21353,28 +21449,30 @@
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E11" s="11">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F11" s="11">
         <v>0</v>
       </c>
       <c r="G11" s="11">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="H11" s="11">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="I11" s="11">
-        <v>40</v>
+        <v>109</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>6.8</v>
+      </c>
+      <c r="K11" s="12">
+        <v>5</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -21394,7 +21492,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>6.8</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -21402,7 +21500,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -21411,27 +21509,15 @@
         <v>28</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11">
-        <v>40</v>
-      </c>
-      <c r="E12" s="11">
-        <v>28</v>
-      </c>
-      <c r="F12" s="11">
-        <v>34</v>
-      </c>
-      <c r="G12" s="11">
-        <v>80</v>
-      </c>
-      <c r="H12" s="11">
-        <v>0</v>
-      </c>
-      <c r="I12" s="11">
-        <v>80</v>
-      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12"/>
       <c r="L12" s="13"/>
@@ -21455,7 +21541,7 @@
       </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
@@ -21463,7 +21549,7 @@
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>6.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -21472,27 +21558,15 @@
         <v>42</v>
       </c>
       <c r="C13" s="11"/>
-      <c r="D13" s="11">
-        <v>840</v>
-      </c>
-      <c r="E13" s="11">
-        <v>680</v>
-      </c>
-      <c r="F13" s="11">
-        <v>1040</v>
-      </c>
-      <c r="G13" s="11">
-        <v>760</v>
-      </c>
-      <c r="H13" s="11">
-        <v>640</v>
-      </c>
-      <c r="I13" s="11">
-        <v>1000</v>
-      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
       <c r="J13" s="15">
         <f t="shared" si="0"/>
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12"/>
       <c r="L13" s="13"/>
@@ -21761,35 +21835,35 @@
       <c r="B21" s="7"/>
       <c r="C21" s="25">
         <f t="shared" ref="C21:I21" si="5">SUM(C8:C17)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D21" s="25">
         <f t="shared" si="5"/>
-        <v>1011</v>
+        <v>292</v>
       </c>
       <c r="E21" s="25">
         <f t="shared" si="5"/>
-        <v>813</v>
+        <v>202</v>
       </c>
       <c r="F21" s="25">
         <f t="shared" si="5"/>
-        <v>1244</v>
+        <v>0</v>
       </c>
       <c r="G21" s="25">
         <f t="shared" si="5"/>
-        <v>1967</v>
+        <v>417</v>
       </c>
       <c r="H21" s="25">
         <f t="shared" si="5"/>
-        <v>1544</v>
+        <v>217</v>
       </c>
       <c r="I21" s="25">
         <f t="shared" si="5"/>
-        <v>2175</v>
+        <v>404</v>
       </c>
       <c r="J21" s="26">
         <f>SUM(C21:I21)</f>
-        <v>8754</v>
+        <v>1552</v>
       </c>
       <c r="K21" s="28"/>
       <c r="M21" s="1"/>
@@ -21829,7 +21903,7 @@
       <c r="W21" s="28"/>
       <c r="Y21" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>94.85</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="Z21" s="34">
         <f>SUM(Z8:Z17)</f>
@@ -21837,7 +21911,7 @@
       </c>
       <c r="AA21" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>94.85</v>
+        <v>38.799999999999997</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -21847,35 +21921,35 @@
       </c>
       <c r="C22" s="21">
         <f t="shared" ref="C22:I22" si="7">C21/40</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D22" s="21">
         <f t="shared" si="7"/>
-        <v>25.274999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="E22" s="21">
         <f t="shared" si="7"/>
-        <v>20.324999999999999</v>
+        <v>5.05</v>
       </c>
       <c r="F22" s="21">
         <f t="shared" si="7"/>
-        <v>31.1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="21">
         <f t="shared" si="7"/>
-        <v>49.174999999999997</v>
+        <v>10.425000000000001</v>
       </c>
       <c r="H22" s="21">
         <f t="shared" si="7"/>
-        <v>38.6</v>
+        <v>5.4249999999999998</v>
       </c>
       <c r="I22" s="21">
         <f t="shared" si="7"/>
-        <v>54.375</v>
+        <v>10.1</v>
       </c>
       <c r="J22" s="22">
         <f>SUM(J8:J20)</f>
-        <v>218.85</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="K22" s="23"/>
       <c r="M22" s="1"/>
@@ -21917,7 +21991,7 @@
       <c r="W22" s="23"/>
       <c r="Y22" s="39">
         <f>Y21/40</f>
-        <v>2.3712499999999999</v>
+        <v>0.97</v>
       </c>
       <c r="Z22" s="40">
         <f>Z21/40</f>
@@ -21925,7 +21999,7 @@
       </c>
       <c r="AA22" s="41">
         <f>AA21/40</f>
-        <v>2.3712499999999999</v>
+        <v>0.97</v>
       </c>
     </row>
   </sheetData>

--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E70ABB8-D8FA-46E5-87B9-B2E992D6340F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B906B5-0942-46C0-9E81-95B156DEFD2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="27" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
@@ -407,7 +407,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -596,6 +596,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -603,7 +612,7 @@
     <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -824,6 +833,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -20591,17 +20603,31 @@
         <v>17</v>
       </c>
       <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
+      <c r="P14" s="11">
+        <v>320</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>359</v>
+      </c>
+      <c r="R14" s="11">
+        <v>120</v>
+      </c>
+      <c r="S14" s="11">
+        <v>440</v>
+      </c>
+      <c r="T14" s="11">
+        <v>600</v>
+      </c>
+      <c r="U14" s="11">
+        <v>1520</v>
+      </c>
       <c r="V14" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="12"/>
+        <v>83.974999999999994</v>
+      </c>
+      <c r="W14" s="12">
+        <v>5</v>
+      </c>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
       <c r="AA14" s="38"/>
@@ -20858,31 +20884,31 @@
       </c>
       <c r="P21" s="25">
         <f t="shared" si="6"/>
-        <v>66</v>
+        <v>386</v>
       </c>
       <c r="Q21" s="25">
         <f t="shared" si="6"/>
-        <v>46</v>
+        <v>405</v>
       </c>
       <c r="R21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S21" s="25">
         <f t="shared" si="6"/>
-        <v>242</v>
+        <v>682</v>
       </c>
       <c r="T21" s="25">
         <f t="shared" si="6"/>
-        <v>242</v>
+        <v>842</v>
       </c>
       <c r="U21" s="25">
         <f t="shared" si="6"/>
-        <v>443</v>
+        <v>1963</v>
       </c>
       <c r="V21" s="26">
         <f>SUM(O21:U21)</f>
-        <v>1039</v>
+        <v>4398</v>
       </c>
       <c r="W21" s="28"/>
       <c r="Y21" s="33">
@@ -20946,31 +20972,31 @@
       </c>
       <c r="P22" s="21">
         <f t="shared" si="8"/>
-        <v>1.65</v>
+        <v>9.65</v>
       </c>
       <c r="Q22" s="21">
         <f t="shared" si="8"/>
-        <v>1.1499999999999999</v>
+        <v>10.125</v>
       </c>
       <c r="R22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S22" s="21">
         <f t="shared" si="8"/>
-        <v>6.05</v>
+        <v>17.05</v>
       </c>
       <c r="T22" s="21">
         <f t="shared" si="8"/>
-        <v>6.05</v>
+        <v>21.05</v>
       </c>
       <c r="U22" s="21">
         <f t="shared" si="8"/>
-        <v>11.074999999999999</v>
+        <v>49.075000000000003</v>
       </c>
       <c r="V22" s="22">
         <f t="shared" si="8"/>
-        <v>25.975000000000001</v>
+        <v>109.95</v>
       </c>
       <c r="W22" s="23"/>
       <c r="Y22" s="39">
@@ -21302,18 +21328,30 @@
         <v>30</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>80</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>40</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>245</v>
+      </c>
+      <c r="T8" s="11">
+        <v>110</v>
+      </c>
+      <c r="U8" s="11">
+        <v>125</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W8" s="12">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y8" s="36">
         <f>J8</f>
@@ -21321,11 +21359,11 @@
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -21367,18 +21405,30 @@
         <v>31</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>140</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>90</v>
+      </c>
+      <c r="R9" s="11">
+        <v>0</v>
+      </c>
+      <c r="S9" s="11">
+        <v>70</v>
+      </c>
+      <c r="T9" s="11">
+        <v>30</v>
+      </c>
+      <c r="U9" s="11">
+        <v>120</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
+        <v>11.25</v>
       </c>
       <c r="W9" s="12">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
@@ -21386,11 +21436,11 @@
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>11.25</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>16</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -21426,9 +21476,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W10" s="12">
-        <v>8</v>
-      </c>
+      <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -21479,28 +21527,42 @@
         <v>29</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>12</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>12</v>
+      </c>
+      <c r="R11" s="11">
+        <v>0</v>
+      </c>
+      <c r="S11" s="11">
+        <v>72</v>
+      </c>
+      <c r="T11" s="11">
+        <v>67</v>
+      </c>
+      <c r="U11" s="11">
+        <v>109</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>6.8</v>
+      </c>
+      <c r="W11" s="12">
+        <v>5</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>6.8</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>6.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -21509,43 +21571,70 @@
         <v>28</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="D12" s="11">
+        <v>34</v>
+      </c>
+      <c r="E12" s="11">
+        <v>34</v>
+      </c>
+      <c r="F12" s="11">
+        <v>0</v>
+      </c>
+      <c r="G12" s="11">
+        <v>51</v>
+      </c>
+      <c r="H12" s="11">
+        <v>42</v>
+      </c>
+      <c r="I12" s="11">
+        <v>31</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>4.8</v>
+      </c>
+      <c r="K12" s="12">
+        <v>7</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
         <v>28</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>34</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>34</v>
+      </c>
+      <c r="R12" s="11">
+        <v>0</v>
+      </c>
+      <c r="S12" s="11">
+        <v>51</v>
+      </c>
+      <c r="T12" s="11">
+        <v>42</v>
+      </c>
+      <c r="U12" s="11">
+        <v>31</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W12" s="12">
-        <v>3</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="X12" s="98"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
@@ -21585,9 +21674,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W13" s="12">
-        <v>6</v>
-      </c>
+      <c r="W13" s="12"/>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -21839,11 +21926,11 @@
       </c>
       <c r="D21" s="25">
         <f t="shared" si="5"/>
-        <v>292</v>
+        <v>326</v>
       </c>
       <c r="E21" s="25">
         <f t="shared" si="5"/>
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="F21" s="25">
         <f t="shared" si="5"/>
@@ -21851,19 +21938,19 @@
       </c>
       <c r="G21" s="25">
         <f t="shared" si="5"/>
-        <v>417</v>
+        <v>468</v>
       </c>
       <c r="H21" s="25">
         <f t="shared" si="5"/>
-        <v>217</v>
+        <v>259</v>
       </c>
       <c r="I21" s="25">
         <f t="shared" si="5"/>
-        <v>404</v>
+        <v>435</v>
       </c>
       <c r="J21" s="26">
         <f>SUM(C21:I21)</f>
-        <v>1552</v>
+        <v>1744</v>
       </c>
       <c r="K21" s="28"/>
       <c r="M21" s="1"/>
@@ -21874,11 +21961,11 @@
       </c>
       <c r="P21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="Q21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="R21" s="25">
         <f t="shared" si="6"/>
@@ -21886,32 +21973,32 @@
       </c>
       <c r="S21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>438</v>
       </c>
       <c r="T21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="U21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="V21" s="26">
         <f>SUM(O21:U21)</f>
-        <v>0</v>
+        <v>1514</v>
       </c>
       <c r="W21" s="28"/>
       <c r="Y21" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>38.799999999999997</v>
+        <v>43.599999999999994</v>
       </c>
       <c r="Z21" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>37.849999999999994</v>
       </c>
       <c r="AA21" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>38.799999999999997</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -21925,11 +22012,11 @@
       </c>
       <c r="D22" s="21">
         <f t="shared" si="7"/>
-        <v>7.3</v>
+        <v>8.15</v>
       </c>
       <c r="E22" s="21">
         <f t="shared" si="7"/>
-        <v>5.05</v>
+        <v>5.9</v>
       </c>
       <c r="F22" s="21">
         <f t="shared" si="7"/>
@@ -21937,19 +22024,19 @@
       </c>
       <c r="G22" s="21">
         <f t="shared" si="7"/>
-        <v>10.425000000000001</v>
+        <v>11.7</v>
       </c>
       <c r="H22" s="21">
         <f t="shared" si="7"/>
-        <v>5.4249999999999998</v>
+        <v>6.4749999999999996</v>
       </c>
       <c r="I22" s="21">
         <f t="shared" si="7"/>
-        <v>10.1</v>
+        <v>10.875</v>
       </c>
       <c r="J22" s="22">
         <f>SUM(J8:J20)</f>
-        <v>38.799999999999997</v>
+        <v>43.599999999999994</v>
       </c>
       <c r="K22" s="23"/>
       <c r="M22" s="1"/>
@@ -21962,11 +22049,11 @@
       </c>
       <c r="P22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="Q22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="R22" s="21">
         <f t="shared" si="8"/>
@@ -21974,32 +22061,32 @@
       </c>
       <c r="S22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>10.95</v>
       </c>
       <c r="T22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6.2249999999999996</v>
       </c>
       <c r="U22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>9.625</v>
       </c>
       <c r="V22" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>37.85</v>
       </c>
       <c r="W22" s="23"/>
       <c r="Y22" s="39">
         <f>Y21/40</f>
-        <v>0.97</v>
+        <v>1.0899999999999999</v>
       </c>
       <c r="Z22" s="40">
         <f>Z21/40</f>
-        <v>0</v>
+        <v>0.94624999999999981</v>
       </c>
       <c r="AA22" s="41">
         <f>AA21/40</f>
-        <v>0.97</v>
+        <v>0.14374999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B906B5-0942-46C0-9E81-95B156DEFD2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B75BA5FE-6E0A-41F8-A171-26D73D299F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="27" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="29" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1884" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1884" uniqueCount="56">
   <si>
     <t>Booking</t>
   </si>
@@ -217,6 +217,12 @@
   </si>
   <si>
     <t>Zeshan1</t>
+  </si>
+  <si>
+    <t>Nabbel SD</t>
+  </si>
+  <si>
+    <t>70G</t>
   </si>
 </sst>
 </file>
@@ -802,6 +808,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -833,9 +842,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1194,10 +1200,10 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="L1" s="91">
+      <c r="L1" s="92">
         <v>46032</v>
       </c>
-      <c r="M1" s="92"/>
+      <c r="M1" s="93"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -1209,104 +1215,104 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="88" t="s">
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="L2" s="93"/>
+      <c r="M2" s="93"/>
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="87" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="87"/>
-      <c r="AA3" s="87"/>
+      <c r="Z3" s="88"/>
+      <c r="AA3" s="88"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="87"/>
-      <c r="Z4" s="87"/>
-      <c r="AA4" s="87"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="88"/>
+      <c r="Z4" s="88"/>
+      <c r="AA4" s="88"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -1323,16 +1329,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -1340,16 +1346,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -2250,103 +2256,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -2363,16 +2369,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -2380,16 +2386,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -3271,103 +3277,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -3384,16 +3390,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -3401,16 +3407,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -3584,13 +3590,13 @@
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="95"/>
-      <c r="D10" s="96"/>
-      <c r="E10" s="96"/>
-      <c r="F10" s="96"/>
-      <c r="G10" s="96"/>
-      <c r="H10" s="96"/>
-      <c r="I10" s="97"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="97"/>
+      <c r="F10" s="97"/>
+      <c r="G10" s="97"/>
+      <c r="H10" s="97"/>
+      <c r="I10" s="98"/>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4156,103 +4162,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -4269,16 +4275,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -4286,16 +4292,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -5166,103 +5172,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -5279,16 +5285,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -5296,16 +5302,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -6164,103 +6170,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -6277,16 +6283,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -6294,16 +6300,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -7134,103 +7140,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -7247,16 +7253,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -7264,16 +7270,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -8130,103 +8136,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -8243,16 +8249,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -8260,16 +8266,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -9313,103 +9319,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -9426,16 +9432,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -9443,16 +9449,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -10337,103 +10343,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -10450,16 +10456,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -10467,16 +10473,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -11218,103 +11224,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -11331,16 +11337,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -11348,16 +11354,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -12207,10 +12213,10 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="L1" s="91">
+      <c r="L1" s="92">
         <v>46063</v>
       </c>
-      <c r="M1" s="92"/>
+      <c r="M1" s="93"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -12222,104 +12228,104 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="88" t="s">
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="L2" s="93"/>
+      <c r="M2" s="93"/>
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -12336,16 +12342,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -12353,16 +12359,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -13266,103 +13272,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -13379,16 +13385,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -13396,16 +13402,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -14335,103 +14341,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -14448,16 +14454,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -14465,16 +14471,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -15340,103 +15346,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -15453,16 +15459,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -15470,16 +15476,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -16364,103 +16370,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -16477,16 +16483,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -16494,16 +16500,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -17328,103 +17334,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -17441,16 +17447,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -17458,16 +17464,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -18297,103 +18303,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -18410,16 +18416,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -18427,16 +18433,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -19076,103 +19082,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -19189,16 +19195,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -19206,16 +19212,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -20037,103 +20043,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -20150,16 +20156,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -20167,16 +20173,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -21077,103 +21083,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -21190,16 +21196,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -21207,16 +21213,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -21627,7 +21633,7 @@
       <c r="W12" s="12">
         <v>7</v>
       </c>
-      <c r="X12" s="98"/>
+      <c r="X12" s="87"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
         <v>4.8</v>
@@ -21702,17 +21708,31 @@
         <v>17</v>
       </c>
       <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
+      <c r="P14" s="11">
+        <v>160</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>275</v>
+      </c>
+      <c r="R14" s="11">
+        <v>0</v>
+      </c>
+      <c r="S14" s="11">
+        <v>61</v>
+      </c>
+      <c r="T14" s="11">
+        <v>279</v>
+      </c>
+      <c r="U14" s="11">
+        <v>480</v>
+      </c>
       <c r="V14" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="12"/>
+        <v>31.375</v>
+      </c>
+      <c r="W14" s="12">
+        <v>3</v>
+      </c>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
       <c r="AA14" s="38"/>
@@ -21961,11 +21981,11 @@
       </c>
       <c r="P21" s="25">
         <f t="shared" si="6"/>
-        <v>266</v>
+        <v>426</v>
       </c>
       <c r="Q21" s="25">
         <f t="shared" si="6"/>
-        <v>176</v>
+        <v>451</v>
       </c>
       <c r="R21" s="25">
         <f t="shared" si="6"/>
@@ -21973,19 +21993,19 @@
       </c>
       <c r="S21" s="25">
         <f t="shared" si="6"/>
-        <v>438</v>
+        <v>499</v>
       </c>
       <c r="T21" s="25">
         <f t="shared" si="6"/>
-        <v>249</v>
+        <v>528</v>
       </c>
       <c r="U21" s="25">
         <f t="shared" si="6"/>
-        <v>385</v>
+        <v>865</v>
       </c>
       <c r="V21" s="26">
         <f>SUM(O21:U21)</f>
-        <v>1514</v>
+        <v>2769</v>
       </c>
       <c r="W21" s="28"/>
       <c r="Y21" s="33">
@@ -22049,11 +22069,11 @@
       </c>
       <c r="P22" s="21">
         <f t="shared" si="8"/>
-        <v>6.65</v>
+        <v>10.65</v>
       </c>
       <c r="Q22" s="21">
         <f t="shared" si="8"/>
-        <v>4.4000000000000004</v>
+        <v>11.275</v>
       </c>
       <c r="R22" s="21">
         <f t="shared" si="8"/>
@@ -22061,19 +22081,19 @@
       </c>
       <c r="S22" s="21">
         <f t="shared" si="8"/>
-        <v>10.95</v>
+        <v>12.475</v>
       </c>
       <c r="T22" s="21">
         <f t="shared" si="8"/>
-        <v>6.2249999999999996</v>
+        <v>13.2</v>
       </c>
       <c r="U22" s="21">
         <f t="shared" si="8"/>
-        <v>9.625</v>
+        <v>21.625</v>
       </c>
       <c r="V22" s="22">
         <f t="shared" si="8"/>
-        <v>37.85</v>
+        <v>69.224999999999994</v>
       </c>
       <c r="W22" s="23"/>
       <c r="Y22" s="39">
@@ -22153,103 +22173,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -22266,16 +22286,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -22283,16 +22303,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -22373,61 +22393,59 @@
         <v>30</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="11">
-        <v>35</v>
-      </c>
-      <c r="E8" s="11">
-        <v>30</v>
-      </c>
-      <c r="F8" s="11">
-        <v>55</v>
-      </c>
-      <c r="G8" s="11">
-        <v>90</v>
-      </c>
-      <c r="H8" s="11">
-        <v>75</v>
-      </c>
-      <c r="I8" s="11">
-        <v>135</v>
-      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>10.5</v>
-      </c>
-      <c r="K8" s="12">
-        <v>9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K8" s="12"/>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
         <v>30</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>60</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>70</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>0</v>
+      </c>
+      <c r="T8" s="11">
+        <v>90</v>
+      </c>
+      <c r="U8" s="11">
+        <v>330</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
+        <v>13.75</v>
       </c>
       <c r="W8" s="12">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>13.75</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>10.5</v>
+        <v>-13.75</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -22436,61 +22454,59 @@
         <v>31</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="11">
-        <v>55</v>
-      </c>
-      <c r="E9" s="11">
-        <v>50</v>
-      </c>
-      <c r="F9" s="11">
-        <v>95</v>
-      </c>
-      <c r="G9" s="11">
-        <v>95</v>
-      </c>
-      <c r="H9" s="11">
-        <v>50</v>
-      </c>
-      <c r="I9" s="11">
-        <v>55</v>
-      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
-        <v>10</v>
-      </c>
-      <c r="K9" s="12">
-        <v>27</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K9" s="12"/>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
         <v>31</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>82</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>86</v>
+      </c>
+      <c r="R9" s="11">
+        <v>6</v>
+      </c>
+      <c r="S9" s="11">
+        <v>30</v>
+      </c>
+      <c r="T9" s="11">
+        <v>87</v>
+      </c>
+      <c r="U9" s="11">
+        <v>92</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V20" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
+        <v>9.5749999999999993</v>
       </c>
       <c r="W9" s="12">
         <v>15</v>
       </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y20" si="2">J9</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z20" si="3">V9</f>
-        <v>0</v>
+        <v>9.5749999999999993</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA20" si="4">Y9-Z9</f>
-        <v>10</v>
+        <v>-9.5749999999999993</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -22499,31 +22515,17 @@
         <v>32</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11">
-        <v>92</v>
-      </c>
-      <c r="E10" s="11">
-        <v>92</v>
-      </c>
-      <c r="F10" s="11">
-        <v>86</v>
-      </c>
-      <c r="G10" s="11">
-        <v>114</v>
-      </c>
-      <c r="H10" s="11">
-        <v>113</v>
-      </c>
-      <c r="I10" s="11">
-        <v>113</v>
-      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>15.25</v>
-      </c>
-      <c r="K10" s="12">
-        <v>7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K10" s="12"/>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -22540,12 +22542,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W10" s="12">
-        <v>5</v>
-      </c>
+      <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>15.25</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -22553,7 +22553,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>15.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -22562,61 +22562,59 @@
         <v>29</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="11">
-        <v>4</v>
-      </c>
-      <c r="E11" s="11">
-        <v>54</v>
-      </c>
-      <c r="F11" s="11">
-        <v>54</v>
-      </c>
-      <c r="G11" s="11">
-        <v>111</v>
-      </c>
-      <c r="H11" s="11">
-        <v>60</v>
-      </c>
-      <c r="I11" s="11">
-        <v>121</v>
-      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>10.1</v>
-      </c>
-      <c r="K11" s="12">
-        <v>9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K11" s="12"/>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
         <v>29</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>0</v>
+      </c>
+      <c r="R11" s="11">
+        <v>0</v>
+      </c>
+      <c r="S11" s="11">
+        <v>0</v>
+      </c>
+      <c r="T11" s="11">
+        <v>0</v>
+      </c>
+      <c r="U11" s="11">
+        <v>80</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W11" s="12">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>10.1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -22625,61 +22623,59 @@
         <v>28</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11">
-        <v>10</v>
-      </c>
-      <c r="E12" s="11">
-        <v>45</v>
-      </c>
-      <c r="F12" s="11">
-        <v>140</v>
-      </c>
-      <c r="G12" s="11">
-        <v>43</v>
-      </c>
-      <c r="H12" s="11">
-        <v>40</v>
-      </c>
-      <c r="I12" s="11">
-        <v>12</v>
-      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>7.25</v>
-      </c>
-      <c r="K12" s="12">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K12" s="12"/>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
         <v>28</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>47</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>30</v>
+      </c>
+      <c r="R12" s="11">
+        <v>0</v>
+      </c>
+      <c r="S12" s="11">
+        <v>0</v>
+      </c>
+      <c r="T12" s="11">
+        <v>38</v>
+      </c>
+      <c r="U12" s="11">
+        <v>63</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="W12" s="12">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>7.25</v>
+        <v>-4.45</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -22688,31 +22684,17 @@
         <v>42</v>
       </c>
       <c r="C13" s="11"/>
-      <c r="D13" s="11">
-        <v>400</v>
-      </c>
-      <c r="E13" s="11">
-        <v>320</v>
-      </c>
-      <c r="F13" s="11">
-        <v>440</v>
-      </c>
-      <c r="G13" s="11">
-        <v>1080</v>
-      </c>
-      <c r="H13" s="11">
-        <v>1000</v>
-      </c>
-      <c r="I13" s="11">
-        <v>1120</v>
-      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
       <c r="J13" s="15">
         <f t="shared" si="0"/>
-        <v>109</v>
-      </c>
-      <c r="K13" s="12">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K13" s="12"/>
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
@@ -22729,9 +22711,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W13" s="12">
-        <v>5</v>
-      </c>
+      <c r="W13" s="12"/>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -22763,13 +22743,19 @@
       <c r="Q14" s="11"/>
       <c r="R14" s="11"/>
       <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
+      <c r="T14" s="11">
+        <v>320</v>
+      </c>
+      <c r="U14" s="11">
+        <v>1120</v>
+      </c>
       <c r="V14" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="12"/>
+        <v>36</v>
+      </c>
+      <c r="W14" s="12">
+        <v>2</v>
+      </c>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
       <c r="AA14" s="38"/>
@@ -22794,20 +22780,32 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
+        <v>54</v>
+      </c>
+      <c r="O15" s="11">
+        <v>4000</v>
+      </c>
+      <c r="P15" s="11">
+        <v>1000</v>
+      </c>
+      <c r="Q15" s="11">
+        <v>1000</v>
+      </c>
       <c r="R15" s="11"/>
       <c r="S15" s="11"/>
-      <c r="T15" s="11"/>
-      <c r="U15" s="11"/>
+      <c r="T15" s="11">
+        <v>3200</v>
+      </c>
+      <c r="U15" s="11">
+        <v>4800</v>
+      </c>
       <c r="V15" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W15" s="12"/>
+        <v>350</v>
+      </c>
+      <c r="W15" s="12">
+        <v>1</v>
+      </c>
       <c r="Y15" s="36"/>
       <c r="Z15" s="37"/>
       <c r="AA15" s="38"/>
@@ -23010,79 +23008,79 @@
       </c>
       <c r="D21" s="25">
         <f t="shared" si="5"/>
-        <v>596</v>
+        <v>0</v>
       </c>
       <c r="E21" s="25">
         <f t="shared" si="5"/>
-        <v>591</v>
+        <v>0</v>
       </c>
       <c r="F21" s="25">
         <f t="shared" si="5"/>
-        <v>870</v>
+        <v>0</v>
       </c>
       <c r="G21" s="25">
         <f t="shared" si="5"/>
-        <v>1533</v>
+        <v>0</v>
       </c>
       <c r="H21" s="25">
         <f t="shared" si="5"/>
-        <v>1338</v>
+        <v>0</v>
       </c>
       <c r="I21" s="25">
         <f t="shared" si="5"/>
-        <v>1556</v>
+        <v>0</v>
       </c>
       <c r="J21" s="26">
         <f>SUM(C21:I21)</f>
-        <v>6484</v>
+        <v>0</v>
       </c>
       <c r="K21" s="28"/>
       <c r="M21" s="1"/>
       <c r="N21" s="7"/>
       <c r="O21" s="25">
         <f t="shared" ref="O21:U21" si="6">SUM(O8:O20)</f>
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="P21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1189</v>
       </c>
       <c r="Q21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1186</v>
       </c>
       <c r="R21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="T21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3735</v>
       </c>
       <c r="U21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>6485</v>
       </c>
       <c r="V21" s="26">
         <f>SUM(O21:U21)</f>
-        <v>0</v>
+        <v>16631</v>
       </c>
       <c r="W21" s="28"/>
       <c r="Y21" s="33">
         <f>SUM(Y8:Y20)</f>
-        <v>53.1</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="34">
         <f>SUM(Z8:Z20)</f>
-        <v>0</v>
+        <v>29.774999999999999</v>
       </c>
       <c r="AA21" s="35">
         <f>SUM(AA8:AA20)</f>
-        <v>53.1</v>
+        <v>-29.774999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -23096,31 +23094,31 @@
       </c>
       <c r="D22" s="21">
         <f t="shared" si="7"/>
-        <v>14.9</v>
+        <v>0</v>
       </c>
       <c r="E22" s="21">
         <f t="shared" si="7"/>
-        <v>14.775</v>
+        <v>0</v>
       </c>
       <c r="F22" s="21">
         <f t="shared" si="7"/>
-        <v>21.75</v>
+        <v>0</v>
       </c>
       <c r="G22" s="21">
         <f t="shared" si="7"/>
-        <v>38.325000000000003</v>
+        <v>0</v>
       </c>
       <c r="H22" s="21">
         <f t="shared" si="7"/>
-        <v>33.450000000000003</v>
+        <v>0</v>
       </c>
       <c r="I22" s="21">
         <f t="shared" si="7"/>
-        <v>38.9</v>
+        <v>0</v>
       </c>
       <c r="J22" s="22">
         <f>SUM(J8:J20)</f>
-        <v>162.1</v>
+        <v>0</v>
       </c>
       <c r="K22" s="23"/>
       <c r="M22" s="1" t="s">
@@ -23131,48 +23129,48 @@
       </c>
       <c r="O22" s="21">
         <f t="shared" ref="O22:V22" si="8">O21/40</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>29.725000000000001</v>
       </c>
       <c r="Q22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>29.65</v>
       </c>
       <c r="R22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="S22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="T22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>93.375</v>
       </c>
       <c r="U22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>162.125</v>
       </c>
       <c r="V22" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>415.77499999999998</v>
       </c>
       <c r="W22" s="23"/>
       <c r="Y22" s="39">
         <f>Y21/40</f>
-        <v>1.3275000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="40">
         <f>Z21/40</f>
-        <v>0</v>
+        <v>0.74437500000000001</v>
       </c>
       <c r="AA22" s="41">
         <f>AA21/40</f>
-        <v>1.3275000000000001</v>
+        <v>-0.74437500000000001</v>
       </c>
     </row>
   </sheetData>
@@ -23242,103 +23240,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -23355,16 +23353,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -23372,16 +23370,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -24304,103 +24302,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -24417,33 +24415,33 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="P6" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -24524,47 +24522,75 @@
         <v>30</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="D8" s="11">
+        <v>82</v>
+      </c>
+      <c r="E8" s="11">
+        <v>70</v>
+      </c>
+      <c r="F8" s="11">
+        <v>40</v>
+      </c>
+      <c r="G8" s="11">
+        <v>0</v>
+      </c>
+      <c r="H8" s="11">
+        <v>142</v>
+      </c>
+      <c r="I8" s="11">
+        <v>122</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>11.4</v>
+      </c>
+      <c r="K8" s="12">
+        <v>29</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>84</v>
+      </c>
+      <c r="P8" s="11">
+        <v>82</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>70</v>
+      </c>
+      <c r="R8" s="11">
+        <v>40</v>
+      </c>
+      <c r="S8" s="11">
+        <v>0</v>
+      </c>
+      <c r="T8" s="11">
+        <v>142</v>
+      </c>
+      <c r="U8" s="11">
+        <v>122</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="W8" s="12">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>-2.0999999999999996</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -24600,9 +24626,7 @@
         <f t="shared" ref="V9:V18" si="1">SUM(O9:U9)/40</f>
         <v>0</v>
       </c>
-      <c r="W9" s="12">
-        <v>30</v>
-      </c>
+      <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y21" si="2">J9</f>
         <v>0</v>
@@ -24649,9 +24673,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W10" s="12">
-        <v>2</v>
-      </c>
+      <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -24698,9 +24720,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W11" s="12">
-        <v>2</v>
-      </c>
+      <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -24737,18 +24757,30 @@
         <v>28</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>54</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>42</v>
+      </c>
+      <c r="R12" s="11">
+        <v>0</v>
+      </c>
+      <c r="S12" s="11">
+        <v>0</v>
+      </c>
+      <c r="T12" s="11">
+        <v>42</v>
+      </c>
+      <c r="U12" s="11">
+        <v>52</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W12" s="12">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
@@ -24756,11 +24788,11 @@
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-4.75</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -24796,9 +24828,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W13" s="12">
-        <v>4</v>
-      </c>
+      <c r="W13" s="12"/>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -25119,15 +25149,15 @@
       </c>
       <c r="D22" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="E22" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F22" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G22" s="25">
         <f t="shared" si="5"/>
@@ -25135,34 +25165,34 @@
       </c>
       <c r="H22" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="I22" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="J22" s="26">
         <f>SUM(C22:I22)</f>
-        <v>0</v>
+        <v>456</v>
       </c>
       <c r="K22" s="28"/>
       <c r="M22" s="1"/>
       <c r="N22" s="7"/>
       <c r="O22" s="25">
         <f t="shared" ref="O22:U22" si="6">SUM(O8:O21)</f>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="P22" s="25">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>164</v>
       </c>
       <c r="Q22" s="25">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>136</v>
       </c>
       <c r="R22" s="25">
         <f t="shared" si="6"/>
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="S22" s="25">
         <f t="shared" si="6"/>
@@ -25170,28 +25200,28 @@
       </c>
       <c r="T22" s="25">
         <f t="shared" si="6"/>
-        <v>12</v>
+        <v>196</v>
       </c>
       <c r="U22" s="25">
         <f t="shared" si="6"/>
-        <v>17</v>
+        <v>191</v>
       </c>
       <c r="V22" s="26">
         <f>SUM(O22:U22)</f>
-        <v>138</v>
+        <v>868</v>
       </c>
       <c r="W22" s="28"/>
       <c r="Y22" s="33">
         <f>SUM(Y8:Y21)</f>
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="Z22" s="34">
         <f>SUM(Z8:Z21)</f>
-        <v>0</v>
+        <v>18.25</v>
       </c>
       <c r="AA22" s="35">
         <f>SUM(AA8:AA21)</f>
-        <v>0</v>
+        <v>-6.85</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25205,15 +25235,15 @@
       </c>
       <c r="D23" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="E23" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="F23" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="21">
         <f t="shared" si="7"/>
@@ -25221,19 +25251,19 @@
       </c>
       <c r="H23" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="I23" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="J23" s="22">
         <f>SUM(J8:J20)</f>
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="K23" s="22">
         <f>SUM(K8:K20)</f>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M23" s="1"/>
       <c r="N23" s="20" t="s">
@@ -25241,19 +25271,19 @@
       </c>
       <c r="O23" s="21">
         <f t="shared" ref="O23:V23" si="8">O22/40</f>
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P23" s="21">
         <f t="shared" si="8"/>
-        <v>0.7</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="Q23" s="21">
         <f t="shared" si="8"/>
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="R23" s="21">
         <f t="shared" si="8"/>
-        <v>0.85</v>
+        <v>1.85</v>
       </c>
       <c r="S23" s="21">
         <f t="shared" si="8"/>
@@ -25261,28 +25291,28 @@
       </c>
       <c r="T23" s="21">
         <f t="shared" si="8"/>
-        <v>0.3</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="U23" s="21">
         <f t="shared" si="8"/>
-        <v>0.42499999999999999</v>
+        <v>4.7750000000000004</v>
       </c>
       <c r="V23" s="22">
         <f t="shared" si="8"/>
-        <v>3.45</v>
+        <v>21.7</v>
       </c>
       <c r="W23" s="23"/>
       <c r="Y23" s="39">
         <f>Y22/40</f>
-        <v>0</v>
+        <v>0.28500000000000003</v>
       </c>
       <c r="Z23" s="40">
         <f>Z22/40</f>
-        <v>0</v>
+        <v>0.45624999999999999</v>
       </c>
       <c r="AA23" s="41">
         <f>AA22/40</f>
-        <v>0</v>
+        <v>-0.17124999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -25325,103 +25355,103 @@
       <c r="A1" s="75">
         <v>46296</v>
       </c>
-      <c r="B1" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
+      <c r="B1" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
       <c r="M1" s="1"/>
-      <c r="N1" s="88" t="s">
+      <c r="N1" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O1" s="88"/>
-      <c r="P1" s="88"/>
-      <c r="Q1" s="88"/>
-      <c r="R1" s="88"/>
-      <c r="S1" s="88"/>
-      <c r="T1" s="88"/>
-      <c r="U1" s="88"/>
-      <c r="V1" s="88"/>
+      <c r="O1" s="89"/>
+      <c r="P1" s="89"/>
+      <c r="Q1" s="89"/>
+      <c r="R1" s="89"/>
+      <c r="S1" s="89"/>
+      <c r="T1" s="89"/>
+      <c r="U1" s="89"/>
+      <c r="V1" s="89"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88"/>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
-      <c r="Y2" s="93" t="s">
+      <c r="N2" s="89"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
+      <c r="Y2" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z2" s="93"/>
-      <c r="AA2" s="93"/>
+      <c r="Z2" s="94"/>
+      <c r="AA2" s="94"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93"/>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="89"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="89"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="90"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="89"/>
-      <c r="O4" s="89"/>
-      <c r="P4" s="89"/>
-      <c r="Q4" s="89"/>
-      <c r="R4" s="89"/>
-      <c r="S4" s="89"/>
-      <c r="T4" s="89"/>
-      <c r="U4" s="89"/>
-      <c r="V4" s="89"/>
+      <c r="N4" s="90"/>
+      <c r="O4" s="90"/>
+      <c r="P4" s="90"/>
+      <c r="Q4" s="90"/>
+      <c r="R4" s="90"/>
+      <c r="S4" s="90"/>
+      <c r="T4" s="90"/>
+      <c r="U4" s="90"/>
+      <c r="V4" s="90"/>
       <c r="Y4" s="29" t="s">
         <v>0</v>
       </c>
@@ -25438,16 +25468,16 @@
       <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="90" t="s">
+      <c r="D5" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="90"/>
-      <c r="F5" s="90"/>
-      <c r="G5" s="90" t="s">
+      <c r="E5" s="91"/>
+      <c r="F5" s="91"/>
+      <c r="G5" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="90"/>
-      <c r="I5" s="90"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="91"/>
       <c r="J5" s="4"/>
       <c r="K5" s="5"/>
       <c r="M5" s="1"/>
@@ -25455,16 +25485,16 @@
       <c r="O5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P5" s="90" t="s">
+      <c r="P5" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q5" s="90"/>
-      <c r="R5" s="90"/>
-      <c r="S5" s="90" t="s">
+      <c r="Q5" s="91"/>
+      <c r="R5" s="91"/>
+      <c r="S5" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T5" s="90"/>
-      <c r="U5" s="90"/>
+      <c r="T5" s="91"/>
+      <c r="U5" s="91"/>
       <c r="V5" s="4"/>
       <c r="W5" s="5"/>
       <c r="Y5" s="30"/>
@@ -26454,103 +26484,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -26567,16 +26597,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -26584,16 +26614,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -27351,111 +27381,111 @@
     </row>
     <row r="2" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="44"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="K2" s="44"/>
       <c r="L2" s="44"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="44"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="K3" s="44"/>
       <c r="L3" s="44"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="44"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="K4" s="44"/>
       <c r="L4" s="44"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="44"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="K5" s="44"/>
       <c r="L5" s="44"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -27472,16 +27502,16 @@
       <c r="C6" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="94" t="s">
+      <c r="D6" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="94"/>
-      <c r="F6" s="94"/>
-      <c r="G6" s="94" t="s">
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="94"/>
-      <c r="I6" s="94"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
       <c r="J6" s="47"/>
       <c r="K6" s="48"/>
       <c r="L6" s="44"/>
@@ -27490,16 +27520,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -28402,103 +28432,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -28515,16 +28545,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -28532,16 +28562,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -29467,106 +29497,106 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
       <c r="X2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -29583,16 +29613,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -29600,16 +29630,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -30499,103 +30529,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -30612,16 +30642,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -30629,16 +30659,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -31523,103 +31553,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="88" t="s">
+      <c r="N2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="Y3" s="93" t="s">
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="Y3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="93"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="89"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="89"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -31636,16 +31666,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90" t="s">
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -31653,16 +31683,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90" t="s">
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>

--- a/OCT_2026/Reports/Daily Booking VS Execution.xlsx
+++ b/OCT_2026/Reports/Daily Booking VS Execution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B75BA5FE-6E0A-41F8-A171-26D73D299F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A586E97D-FD89-4FF0-B1BA-17CC15D5AE25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" activeTab="29" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
@@ -24273,7 +24273,7 @@
     <col min="18" max="18" width="3.08984375" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="3.6328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="5.453125" customWidth="1"/>
     <col min="25" max="25" width="7.453125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9.36328125" bestFit="1" customWidth="1"/>
@@ -24553,7 +24553,7 @@
         <v>30</v>
       </c>
       <c r="O8" s="11">
-        <v>84</v>
+        <v>336</v>
       </c>
       <c r="P8" s="11">
         <v>82</v>
@@ -24575,7 +24575,7 @@
       </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>13.5</v>
+        <v>19.8</v>
       </c>
       <c r="W8" s="12">
         <v>27</v>
@@ -24586,11 +24586,11 @@
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>13.5</v>
+        <v>19.8</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>-2.0999999999999996</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -24615,29 +24615,42 @@
       <c r="N9" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="O9" s="11"/>
+      <c r="O9" s="11">
+        <v>48</v>
+      </c>
       <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="Q9" s="11">
+        <v>80</v>
+      </c>
+      <c r="R9" s="11">
+        <v>40</v>
+      </c>
+      <c r="S9" s="11">
+        <v>0</v>
+      </c>
+      <c r="T9" s="11">
+        <v>0</v>
+      </c>
+      <c r="U9" s="11">
+        <v>40</v>
+      </c>
       <c r="V9" s="15">
-        <f t="shared" ref="V9:V18" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>80</v>
+      </c>
+      <c r="W9" s="12">
+        <v>6</v>
+      </c>
       <c r="Y9" s="36">
-        <f t="shared" ref="Y9:Y21" si="2">J9</f>
+        <f t="shared" ref="Y9:Y21" si="1">J9</f>
         <v>0</v>
       </c>
       <c r="Z9" s="37">
-        <f t="shared" ref="Z9:Z21" si="3">V9</f>
-        <v>0</v>
+        <f t="shared" ref="Z9:Z21" si="2">V9</f>
+        <v>80</v>
       </c>
       <c r="AA9" s="38">
-        <f t="shared" ref="AA9:AA21" si="4">Y9-Z9</f>
-        <v>0</v>
+        <f t="shared" ref="AA9:AA21" si="3">Y9-Z9</f>
+        <v>-80</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -24670,20 +24683,20 @@
       <c r="T10" s="11"/>
       <c r="U10" s="11"/>
       <c r="V10" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="V10:V18" si="4">SUM(O10:U10)/40</f>
         <v>0</v>
       </c>
       <c r="W10" s="12"/>
       <c r="Y10" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="37">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z10" s="37">
+      <c r="AA10" s="38">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA10" s="38">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -24710,28 +24723,42 @@
         <v>29</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>120</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>80</v>
+      </c>
+      <c r="R11" s="11">
+        <v>0</v>
+      </c>
+      <c r="S11" s="11">
+        <v>0</v>
+      </c>
+      <c r="T11" s="11">
+        <v>40</v>
+      </c>
+      <c r="U11" s="11">
+        <v>120</v>
+      </c>
       <c r="V11" s="15">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="W11" s="12">
+        <v>4</v>
+      </c>
+      <c r="Y11" s="36">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W11" s="12"/>
-      <c r="Y11" s="36">
+      <c r="Z11" s="37">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Z11" s="37">
+        <v>9</v>
+      </c>
+      <c r="AA11" s="38">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA11" s="38">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -24776,22 +24803,22 @@
         <v>52</v>
       </c>
       <c r="V12" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>4.75</v>
       </c>
       <c r="W12" s="12">
         <v>10</v>
       </c>
       <c r="Y12" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="37">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Z12" s="37">
+        <v>4.75</v>
+      </c>
+      <c r="AA12" s="38">
         <f t="shared" si="3"/>
-        <v>4.75</v>
-      </c>
-      <c r="AA12" s="38">
-        <f t="shared" si="4"/>
         <v>-4.75</v>
       </c>
     </row>
@@ -24817,18 +24844,30 @@
       <c r="N13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
+      <c r="O13" s="11">
+        <v>252</v>
+      </c>
+      <c r="P13" s="11">
+        <v>494</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>294</v>
+      </c>
       <c r="R13" s="11"/>
       <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="T13" s="11">
+        <v>591</v>
+      </c>
+      <c r="U13" s="11">
+        <v>1440</v>
+      </c>
       <c r="V13" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12"/>
+        <f t="shared" si="4"/>
+        <v>76.775000000000006</v>
+      </c>
+      <c r="W13" s="12">
+        <v>12</v>
+      </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -24863,7 +24902,7 @@
       <c r="T14" s="11"/>
       <c r="U14" s="11"/>
       <c r="V14" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W14" s="12"/>
@@ -24901,7 +24940,7 @@
       <c r="T15" s="11"/>
       <c r="U15" s="11"/>
       <c r="V15" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W15" s="12"/>
@@ -24939,7 +24978,7 @@
       <c r="T16" s="11"/>
       <c r="U16" s="11"/>
       <c r="V16" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W16" s="12"/>
@@ -24977,13 +25016,13 @@
       <c r="T17" s="11"/>
       <c r="U17" s="11"/>
       <c r="V17" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W17" s="12"/>
       <c r="Y17" s="36"/>
       <c r="Z17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA17" s="38"/>
@@ -25008,31 +25047,17 @@
         <v>41</v>
       </c>
       <c r="O18" s="11"/>
-      <c r="P18" s="11">
-        <v>28</v>
-      </c>
-      <c r="Q18" s="11">
-        <v>24</v>
-      </c>
-      <c r="R18" s="11">
-        <v>34</v>
-      </c>
-      <c r="S18" s="11">
-        <v>23</v>
-      </c>
-      <c r="T18" s="11">
-        <v>12</v>
-      </c>
-      <c r="U18" s="11">
-        <v>17</v>
-      </c>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="11"/>
+      <c r="T18" s="11"/>
+      <c r="U18" s="11"/>
       <c r="V18" s="15">
-        <f t="shared" si="1"/>
-        <v>3.45</v>
-      </c>
-      <c r="W18" s="12">
-        <v>6</v>
-      </c>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="12"/>
       <c r="Y18" s="36"/>
       <c r="Z18" s="37"/>
       <c r="AA18" s="38"/>
@@ -25128,15 +25153,15 @@
       <c r="V21" s="15"/>
       <c r="W21" s="18"/>
       <c r="Y21" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z21" s="37">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z21" s="37">
+      <c r="AA21" s="38">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA21" s="38">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -25180,35 +25205,35 @@
       <c r="N22" s="7"/>
       <c r="O22" s="25">
         <f t="shared" ref="O22:U22" si="6">SUM(O8:O21)</f>
-        <v>84</v>
+        <v>636</v>
       </c>
       <c r="P22" s="25">
         <f t="shared" si="6"/>
-        <v>164</v>
+        <v>750</v>
       </c>
       <c r="Q22" s="25">
         <f t="shared" si="6"/>
-        <v>136</v>
+        <v>566</v>
       </c>
       <c r="R22" s="25">
         <f t="shared" si="6"/>
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="S22" s="25">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="T22" s="25">
         <f t="shared" si="6"/>
-        <v>196</v>
+        <v>815</v>
       </c>
       <c r="U22" s="25">
         <f t="shared" si="6"/>
-        <v>191</v>
+        <v>1774</v>
       </c>
       <c r="V22" s="26">
         <f>SUM(O22:U22)</f>
-        <v>868</v>
+        <v>4621</v>
       </c>
       <c r="W22" s="28"/>
       <c r="Y22" s="33">
@@ -25217,11 +25242,11 @@
       </c>
       <c r="Z22" s="34">
         <f>SUM(Z8:Z21)</f>
-        <v>18.25</v>
+        <v>113.55</v>
       </c>
       <c r="AA22" s="35">
         <f>SUM(AA8:AA21)</f>
-        <v>-6.85</v>
+        <v>-102.15</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25271,35 +25296,35 @@
       </c>
       <c r="O23" s="21">
         <f t="shared" ref="O23:V23" si="8">O22/40</f>
-        <v>2.1</v>
+        <v>15.9</v>
       </c>
       <c r="P23" s="21">
         <f t="shared" si="8"/>
-        <v>4.0999999999999996</v>
+        <v>18.75</v>
       </c>
       <c r="Q23" s="21">
         <f t="shared" si="8"/>
-        <v>3.4</v>
+        <v>14.15</v>
       </c>
       <c r="R23" s="21">
         <f t="shared" si="8"/>
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="S23" s="21">
         <f t="shared" si="8"/>
-        <v>0.57499999999999996</v>
+        <v>0</v>
       </c>
       <c r="T23" s="21">
         <f t="shared" si="8"/>
-        <v>4.9000000000000004</v>
+        <v>20.375</v>
       </c>
       <c r="U23" s="21">
         <f t="shared" si="8"/>
-        <v>4.7750000000000004</v>
+        <v>44.35</v>
       </c>
       <c r="V23" s="22">
         <f t="shared" si="8"/>
-        <v>21.7</v>
+        <v>115.52500000000001</v>
       </c>
       <c r="W23" s="23"/>
       <c r="Y23" s="39">
@@ -25308,11 +25333,11 @@
       </c>
       <c r="Z23" s="40">
         <f>Z22/40</f>
-        <v>0.45624999999999999</v>
+        <v>2.8387500000000001</v>
       </c>
       <c r="AA23" s="41">
         <f>AA22/40</f>
-        <v>-0.17124999999999999</v>
+        <v>-2.55375</v>
       </c>
     </row>
   </sheetData>
